--- a/output/china_dg_all.xlsx
+++ b/output/china_dg_all.xlsx
@@ -24,23 +24,24 @@
     <sheet name="各地区房地产开发投资情况" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="各地区房地产开发规模与开、竣工面积增长情况" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="各地居民消费价格分类指数(上年同月=100)(2016-" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="各月日本居民消费价格涨跌率、失业率和进出口贸易" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="各月欧元区居民消费价格涨跌率、失业率和进出口贸易" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="各月美国居民消费价格涨跌率、失业率和进出口贸易" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="各行业固定资产投资(不含农户)" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="固定资产投资资金来源情况" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="固定资产投资（不含农户）" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="工业主要产品产量及增长速度" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="工业分大类行业增加值增长速度" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="工业增加值增速" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="工业生产者购进价格指数" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="房地产开发投资" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="按登记注册类型分的固定资产投资（不含农户）情况" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="社会消费品零售总额" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="累计全国及36个大中城市居民消费价格分类指数(上年同期=" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="能源产品产量" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="邮电业务量完成情况" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="限额以上企业（单位）商品零售类值" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="各地居民消费和商品零售价格指数" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="各月日本居民消费价格涨跌率、失业率和进出口贸易" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="各月欧元区居民消费价格涨跌率、失业率和进出口贸易" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="各月美国居民消费价格涨跌率、失业率和进出口贸易" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="各行业固定资产投资(不含农户)" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="固定资产投资资金来源情况" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="固定资产投资（不含农户）" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="工业主要产品产量及增长速度" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="工业分大类行业增加值增长速度" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="工业增加值增速" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="工业生产者购进价格指数" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="房地产开发投资" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="按登记注册类型分的固定资产投资（不含农户）情况" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="社会消费品零售总额" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="累计全国及36个大中城市居民消费价格分类指数(上年同期=" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="能源产品产量" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="邮电业务量完成情况" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="限额以上企业（单位）商品零售类值" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4065,7 +4066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4074,7 +4075,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>各月日本居民消费价格涨跌率、失业率和进出口贸易 / 消费者价格涨跌率</t>
+          <t>各地居民消费和商品零售价格指数 / 商品零售价格指数_上年同月=100</t>
         </is>
       </c>
     </row>
@@ -4086,20 +4087,5378 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2010-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2010-02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2010-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2010-04</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2010-05</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2010-06</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2010-07</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2010-08</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2010-09</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2010-10</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2010-11</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2010-12</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2011-01</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2011-02</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2011-03</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2011-04</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2011-05</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2011-06</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2011-07</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2011-08</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2011-09</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2011-11</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2012-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2012-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2012-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2012-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2012-05</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2012-06</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2012-07</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2012-08</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2012-09</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2012-10</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2012-11</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2012-12</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2013-01</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2013-02</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2014-02</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>2014-03</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>2014-04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>日本</t>
-        </is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>101.7831244</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>102.48656553</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>102.32719575</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>102.79552428</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>103.07605354</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>102.71876391</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>102.83265969</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>103.04627687</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>103.03514156</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>103.9014352</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>104.71459852</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>104.13044312</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>103.71631554</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>104.29995294</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>104.5863</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>104.7398</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>104.9239</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>105.8488</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>106.09178719</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>105.96372969</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>106.03516853</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>105.32205132</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>103.98981075</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>103.84285346</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>104.08469875</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>102.88370108</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>103.48254775</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>103.09670389</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>102.50245485</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>101.39525969</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>100.75616204</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>101.02124634</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>100.92998366</v>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>100.89743734</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>101.14481202</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>101.5369868</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>101.25930211</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>102.07329294</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>100.8288927</v>
+      </c>
+      <c r="AO4" s="1" t="n">
+        <v>100.93777393</v>
+      </c>
+      <c r="AP4" s="1" t="n">
+        <v>100.70072652</v>
+      </c>
+      <c r="AQ4" s="1" t="n">
+        <v>101.41919392</v>
+      </c>
+      <c r="AR4" s="1" t="n">
+        <v>101.6885703</v>
+      </c>
+      <c r="AS4" s="1" t="n">
+        <v>101.58559437</v>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>101.9116028</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>101.67159748</v>
+      </c>
+      <c r="AV4" s="1" t="n">
+        <v>101.24567344</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>101.1126319</v>
+      </c>
+      <c r="AX4" s="1" t="n">
+        <v>100.75186065</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>101.24346089</v>
+      </c>
+      <c r="AZ4" s="1" t="n">
+        <v>100.80731036</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>99.02370000000001</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>99.4465</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>99.5947</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>99.8379</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>100.8472</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>100.1113</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>100.069</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>100.3855</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>100.2484</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>101.2603</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>101.9736</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>102.2537</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>101.7832</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>102.3235</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>102.7514</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>103.0183</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>102.9634</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>103.5818</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>103.9832</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>104.469</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>104.6463</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>104.0166</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>102.8364</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>102.64817581</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>102.39282569</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>101.97981774</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>102.05440413</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>101.72737849</v>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>101.08426754</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>100.15185526</v>
+      </c>
+      <c r="AF5" s="1" t="n">
+        <v>99.6042855</v>
+      </c>
+      <c r="AG5" s="1" t="n">
+        <v>99.53645093</v>
+      </c>
+      <c r="AH5" s="1" t="n">
+        <v>99.64003071</v>
+      </c>
+      <c r="AI5" s="1" t="n">
+        <v>99.53679725000001</v>
+      </c>
+      <c r="AJ5" s="1" t="n">
+        <v>99.53523837</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>99.57861646000001</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>99.87660608</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>100.40863309</v>
+      </c>
+      <c r="AN5" s="1" t="n">
+        <v>99.70156568</v>
+      </c>
+      <c r="AO5" s="1" t="n">
+        <v>99.46817378</v>
+      </c>
+      <c r="AP5" s="1" t="n">
+        <v>99.06736051999999</v>
+      </c>
+      <c r="AQ5" s="1" t="n">
+        <v>99.88881438</v>
+      </c>
+      <c r="AR5" s="1" t="n">
+        <v>100.00082687</v>
+      </c>
+      <c r="AS5" s="1" t="n">
+        <v>99.64253927</v>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>99.84847189000001</v>
+      </c>
+      <c r="AU5" s="1" t="n">
+        <v>99.82528671999999</v>
+      </c>
+      <c r="AV5" s="1" t="n">
+        <v>99.55248224</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>99.36229513000001</v>
+      </c>
+      <c r="AX5" s="1" t="n">
+        <v>98.79496233</v>
+      </c>
+      <c r="AY5" s="1" t="n">
+        <v>99.23403426</v>
+      </c>
+      <c r="AZ5" s="1" t="n">
+        <v>98.80690961000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>102.7072</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>102.8354</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>102.8145</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>102.7785</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>103.3721</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>103.4548</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>103.1847</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>103.8054</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>103.3094</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>104.0815</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>104.7435</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>103.8392</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>102.9874</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>103.5395</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>102.9809</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>103.7959</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>104.0928</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>105.1388</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>106.2611</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>106.1179</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>106.6425</v>
+      </c>
+      <c r="W6" s="1" t="n">
+        <v>105.7024</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>104.4399</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>104.52585014</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>105.37616191</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>104.38861837</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>105.27849497</v>
+      </c>
+      <c r="AC6" s="1" t="n">
+        <v>104.23654604</v>
+      </c>
+      <c r="AD6" s="1" t="n">
+        <v>103.96421339</v>
+      </c>
+      <c r="AE6" s="1" t="n">
+        <v>103.25751262</v>
+      </c>
+      <c r="AF6" s="1" t="n">
+        <v>102.11176779</v>
+      </c>
+      <c r="AG6" s="1" t="n">
+        <v>102.33496471</v>
+      </c>
+      <c r="AH6" s="1" t="n">
+        <v>101.76976513</v>
+      </c>
+      <c r="AI6" s="1" t="n">
+        <v>101.36099149</v>
+      </c>
+      <c r="AJ6" s="1" t="n">
+        <v>100.86490838</v>
+      </c>
+      <c r="AK6" s="1" t="n">
+        <v>100.75791954</v>
+      </c>
+      <c r="AL6" s="1" t="n">
+        <v>100.77403517</v>
+      </c>
+      <c r="AM6" s="1" t="n">
+        <v>101.85999777</v>
+      </c>
+      <c r="AN6" s="1" t="n">
+        <v>100.60014888</v>
+      </c>
+      <c r="AO6" s="1" t="n">
+        <v>101.23859963</v>
+      </c>
+      <c r="AP6" s="1" t="n">
+        <v>100.74769632</v>
+      </c>
+      <c r="AQ6" s="1" t="n">
+        <v>101.66741729</v>
+      </c>
+      <c r="AR6" s="1" t="n">
+        <v>102.20365974</v>
+      </c>
+      <c r="AS6" s="1" t="n">
+        <v>101.61859935</v>
+      </c>
+      <c r="AT6" s="1" t="n">
+        <v>102.32393901</v>
+      </c>
+      <c r="AU6" s="1" t="n">
+        <v>102.49714008</v>
+      </c>
+      <c r="AV6" s="1" t="n">
+        <v>102.28478193</v>
+      </c>
+      <c r="AW6" s="1" t="n">
+        <v>101.72893463</v>
+      </c>
+      <c r="AX6" s="1" t="n">
+        <v>101.70526946</v>
+      </c>
+      <c r="AY6" s="1" t="n">
+        <v>102.29218536</v>
+      </c>
+      <c r="AZ6" s="1" t="n">
+        <v>101.25693923</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>河北省</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>102.4747</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>102.8075</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>102.7268</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>103.145</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>103.122</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>102.7585</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>102.6855</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>103.2445</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>102.4863</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>103.5664</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>104.3073</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>103.9104</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>102.8811</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>104.105</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>104.2966</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>104.3373</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>104.8687</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>106.0342</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>106.7165</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>106.0538</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>106.5337</v>
+      </c>
+      <c r="W7" s="1" t="n">
+        <v>105.703</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>104.3379</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>104.38339756</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>105.04653549</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>103.04600108</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>103.85920228</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>103.13828717</v>
+      </c>
+      <c r="AD7" s="1" t="n">
+        <v>102.21274403</v>
+      </c>
+      <c r="AE7" s="1" t="n">
+        <v>101.25139957</v>
+      </c>
+      <c r="AF7" s="1" t="n">
+        <v>100.42118636</v>
+      </c>
+      <c r="AG7" s="1" t="n">
+        <v>101.4867463</v>
+      </c>
+      <c r="AH7" s="1" t="n">
+        <v>101.06924609</v>
+      </c>
+      <c r="AI7" s="1" t="n">
+        <v>100.96316966</v>
+      </c>
+      <c r="AJ7" s="1" t="n">
+        <v>101.45646708</v>
+      </c>
+      <c r="AK7" s="1" t="n">
+        <v>102.0283745</v>
+      </c>
+      <c r="AL7" s="1" t="n">
+        <v>102.15621809</v>
+      </c>
+      <c r="AM7" s="1" t="n">
+        <v>103.54061715</v>
+      </c>
+      <c r="AN7" s="1" t="n">
+        <v>101.67401336</v>
+      </c>
+      <c r="AO7" s="1" t="n">
+        <v>101.98707601</v>
+      </c>
+      <c r="AP7" s="1" t="n">
+        <v>101.64729418</v>
+      </c>
+      <c r="AQ7" s="1" t="n">
+        <v>102.53700266</v>
+      </c>
+      <c r="AR7" s="1" t="n">
+        <v>102.74465692</v>
+      </c>
+      <c r="AS7" s="1" t="n">
+        <v>101.65579232</v>
+      </c>
+      <c r="AT7" s="1" t="n">
+        <v>102.44509294</v>
+      </c>
+      <c r="AU7" s="1" t="n">
+        <v>102.16172819</v>
+      </c>
+      <c r="AV7" s="1" t="n">
+        <v>100.87088005</v>
+      </c>
+      <c r="AW7" s="1" t="n">
+        <v>100.39797194</v>
+      </c>
+      <c r="AX7" s="1" t="n">
+        <v>100.41129969</v>
+      </c>
+      <c r="AY7" s="1" t="n">
+        <v>101.5292528</v>
+      </c>
+      <c r="AZ7" s="1" t="n">
+        <v>100.9492926</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>101.5637</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>102.1211</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>101.4639</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>101.5958</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>101.5995</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>101.6405</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>101.7688</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>102.2695</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>102.1943</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>103.4703</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>104.4512</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>103.6883</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>103.5753</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>103.9492</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>104.3499</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>103.982</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>104.5931</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>105.7313</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>106.2537</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>106.0307</v>
+      </c>
+      <c r="V8" s="1" t="n">
+        <v>106.5455</v>
+      </c>
+      <c r="W8" s="1" t="n">
+        <v>106.0491</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>104.1737</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>104.0797482</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <v>104.38970078</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>102.89207292</v>
+      </c>
+      <c r="AB8" s="1" t="n">
+        <v>103.5768254</v>
+      </c>
+      <c r="AC8" s="1" t="n">
+        <v>103.35413356</v>
+      </c>
+      <c r="AD8" s="1" t="n">
+        <v>102.59231583</v>
+      </c>
+      <c r="AE8" s="1" t="n">
+        <v>101.28830888</v>
+      </c>
+      <c r="AF8" s="1" t="n">
+        <v>100.37883394</v>
+      </c>
+      <c r="AG8" s="1" t="n">
+        <v>100.73683682</v>
+      </c>
+      <c r="AH8" s="1" t="n">
+        <v>100.56343011</v>
+      </c>
+      <c r="AI8" s="1" t="n">
+        <v>100.46473931</v>
+      </c>
+      <c r="AJ8" s="1" t="n">
+        <v>100.66100899</v>
+      </c>
+      <c r="AK8" s="1" t="n">
+        <v>101.39259092</v>
+      </c>
+      <c r="AL8" s="1" t="n">
+        <v>101.34716435</v>
+      </c>
+      <c r="AM8" s="1" t="n">
+        <v>102.75047225</v>
+      </c>
+      <c r="AN8" s="1" t="n">
+        <v>101.10485392</v>
+      </c>
+      <c r="AO8" s="1" t="n">
+        <v>101.30333128</v>
+      </c>
+      <c r="AP8" s="1" t="n">
+        <v>101.12210661</v>
+      </c>
+      <c r="AQ8" s="1" t="n">
+        <v>101.89415051</v>
+      </c>
+      <c r="AR8" s="1" t="n">
+        <v>102.44950297</v>
+      </c>
+      <c r="AS8" s="1" t="n">
+        <v>101.90796922</v>
+      </c>
+      <c r="AT8" s="1" t="n">
+        <v>102.25871339</v>
+      </c>
+      <c r="AU8" s="1" t="n">
+        <v>102.24608979</v>
+      </c>
+      <c r="AV8" s="1" t="n">
+        <v>101.01440139</v>
+      </c>
+      <c r="AW8" s="1" t="n">
+        <v>100.92199886</v>
+      </c>
+      <c r="AX8" s="1" t="n">
+        <v>100.39623632</v>
+      </c>
+      <c r="AY8" s="1" t="n">
+        <v>101.21710126</v>
+      </c>
+      <c r="AZ8" s="1" t="n">
+        <v>100.64766512</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>内蒙古自治区</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>102.0561</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>102.8874</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>102.4414</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>102.6576</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>102.7277</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>102.3076</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>102.284</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>103.0273</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>102.814</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>103.8376</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>104.9811</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>104.3512</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>104.1412</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>104.322</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>104.346</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>104.348</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>104.6898</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>105.5477</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>105.9126</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>105.7983</v>
+      </c>
+      <c r="V9" s="1" t="n">
+        <v>106.1131</v>
+      </c>
+      <c r="W9" s="1" t="n">
+        <v>105.4279</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>103.8378</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>104.20550149</v>
+      </c>
+      <c r="Z9" s="1" t="n">
+        <v>104.5620772</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>103.32486315</v>
+      </c>
+      <c r="AB9" s="1" t="n">
+        <v>103.49394811</v>
+      </c>
+      <c r="AC9" s="1" t="n">
+        <v>103.26031563</v>
+      </c>
+      <c r="AD9" s="1" t="n">
+        <v>103.01209093</v>
+      </c>
+      <c r="AE9" s="1" t="n">
+        <v>102.2543506</v>
+      </c>
+      <c r="AF9" s="1" t="n">
+        <v>101.57591366</v>
+      </c>
+      <c r="AG9" s="1" t="n">
+        <v>101.4978696</v>
+      </c>
+      <c r="AH9" s="1" t="n">
+        <v>101.43995509</v>
+      </c>
+      <c r="AI9" s="1" t="n">
+        <v>101.47117164</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
+        <v>101.9751145</v>
+      </c>
+      <c r="AK9" s="1" t="n">
+        <v>101.84720554</v>
+      </c>
+      <c r="AL9" s="1" t="n">
+        <v>101.95652468</v>
+      </c>
+      <c r="AM9" s="1" t="n">
+        <v>103.42942447</v>
+      </c>
+      <c r="AN9" s="1" t="n">
+        <v>102.70196584</v>
+      </c>
+      <c r="AO9" s="1" t="n">
+        <v>102.90074014</v>
+      </c>
+      <c r="AP9" s="1" t="n">
+        <v>102.55037129</v>
+      </c>
+      <c r="AQ9" s="1" t="n">
+        <v>102.79766064</v>
+      </c>
+      <c r="AR9" s="1" t="n">
+        <v>102.93859605</v>
+      </c>
+      <c r="AS9" s="1" t="n">
+        <v>102.79332733</v>
+      </c>
+      <c r="AT9" s="1" t="n">
+        <v>102.65852665</v>
+      </c>
+      <c r="AU9" s="1" t="n">
+        <v>102.23293236</v>
+      </c>
+      <c r="AV9" s="1" t="n">
+        <v>101.70074407</v>
+      </c>
+      <c r="AW9" s="1" t="n">
+        <v>101.23105468</v>
+      </c>
+      <c r="AX9" s="1" t="n">
+        <v>100.89161513</v>
+      </c>
+      <c r="AY9" s="1" t="n">
+        <v>101.16803834</v>
+      </c>
+      <c r="AZ9" s="1" t="n">
+        <v>100.6269996</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>辽宁省</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>103.4754</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>102.7779</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>102.6857</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>102.5593</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>101.606</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>101.3465</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>101.8061</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>103.4726</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>102.8084</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>104.3841</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>106.4943</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>105.2364</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>103.986</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>104.6493</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>104.8804</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>105.1065</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>105.508</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>106.5329</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>106.4335</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>105.7408</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>106.0898</v>
+      </c>
+      <c r="W10" s="1" t="n">
+        <v>105.0557</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>103.3452</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>103.40627723</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <v>104.15162411</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>102.62479913</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <v>102.98018648</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <v>102.63398699</v>
+      </c>
+      <c r="AD10" s="1" t="n">
+        <v>102.05575964</v>
+      </c>
+      <c r="AE10" s="1" t="n">
+        <v>101.33560993</v>
+      </c>
+      <c r="AF10" s="1" t="n">
+        <v>101.27314637</v>
+      </c>
+      <c r="AG10" s="1" t="n">
+        <v>101.6821688</v>
+      </c>
+      <c r="AH10" s="1" t="n">
+        <v>101.58578159</v>
+      </c>
+      <c r="AI10" s="1" t="n">
+        <v>101.94663727</v>
+      </c>
+      <c r="AJ10" s="1" t="n">
+        <v>101.91382851</v>
+      </c>
+      <c r="AK10" s="1" t="n">
+        <v>102.29830394</v>
+      </c>
+      <c r="AL10" s="1" t="n">
+        <v>101.84767078</v>
+      </c>
+      <c r="AM10" s="1" t="n">
+        <v>103.41825448</v>
+      </c>
+      <c r="AN10" s="1" t="n">
+        <v>101.9786591</v>
+      </c>
+      <c r="AO10" s="1" t="n">
+        <v>101.74004917</v>
+      </c>
+      <c r="AP10" s="1" t="n">
+        <v>101.39735703</v>
+      </c>
+      <c r="AQ10" s="1" t="n">
+        <v>101.52273433</v>
+      </c>
+      <c r="AR10" s="1" t="n">
+        <v>101.47610291</v>
+      </c>
+      <c r="AS10" s="1" t="n">
+        <v>100.69734221</v>
+      </c>
+      <c r="AT10" s="1" t="n">
+        <v>101.52475039</v>
+      </c>
+      <c r="AU10" s="1" t="n">
+        <v>101.42186414</v>
+      </c>
+      <c r="AV10" s="1" t="n">
+        <v>100.6034669</v>
+      </c>
+      <c r="AW10" s="1" t="n">
+        <v>100.47966839</v>
+      </c>
+      <c r="AX10" s="1" t="n">
+        <v>99.86603096</v>
+      </c>
+      <c r="AY10" s="1" t="n">
+        <v>100.89244216</v>
+      </c>
+      <c r="AZ10" s="1" t="n">
+        <v>101.00924471</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>吉林省</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>103.692</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>104.0968</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>103.5492</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>104.2838</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>104.0799</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>103.6603</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>103.5361</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>104.5249</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>103.8124</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>104.3953</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>105.7275</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>104.1825</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>103.5105</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>103.7544</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>104.2568</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>104.5662</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>105.0836</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>105.9217</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>106.116</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>105.855</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>106.0869</v>
+      </c>
+      <c r="W11" s="1" t="n">
+        <v>105.4682</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>103.597</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>104.19100185</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <v>104.1590619</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>103.17892886</v>
+      </c>
+      <c r="AB11" s="1" t="n">
+        <v>103.00617612</v>
+      </c>
+      <c r="AC11" s="1" t="n">
+        <v>102.46173532</v>
+      </c>
+      <c r="AD11" s="1" t="n">
+        <v>101.77206857</v>
+      </c>
+      <c r="AE11" s="1" t="n">
+        <v>100.94375238</v>
+      </c>
+      <c r="AF11" s="1" t="n">
+        <v>100.2467298</v>
+      </c>
+      <c r="AG11" s="1" t="n">
+        <v>100.46249774</v>
+      </c>
+      <c r="AH11" s="1" t="n">
+        <v>100.8431906</v>
+      </c>
+      <c r="AI11" s="1" t="n">
+        <v>100.9402449</v>
+      </c>
+      <c r="AJ11" s="1" t="n">
+        <v>100.9281351</v>
+      </c>
+      <c r="AK11" s="1" t="n">
+        <v>101.00269855</v>
+      </c>
+      <c r="AL11" s="1" t="n">
+        <v>101.14084084</v>
+      </c>
+      <c r="AM11" s="1" t="n">
+        <v>102.61277979</v>
+      </c>
+      <c r="AN11" s="1" t="n">
+        <v>101.72928801</v>
+      </c>
+      <c r="AO11" s="1" t="n">
+        <v>101.14007759</v>
+      </c>
+      <c r="AP11" s="1" t="n">
+        <v>100.97124425</v>
+      </c>
+      <c r="AQ11" s="1" t="n">
+        <v>101.30972865</v>
+      </c>
+      <c r="AR11" s="1" t="n">
+        <v>102.07290271</v>
+      </c>
+      <c r="AS11" s="1" t="n">
+        <v>101.87008913</v>
+      </c>
+      <c r="AT11" s="1" t="n">
+        <v>102.31365323</v>
+      </c>
+      <c r="AU11" s="1" t="n">
+        <v>101.63667485</v>
+      </c>
+      <c r="AV11" s="1" t="n">
+        <v>101.10168898</v>
+      </c>
+      <c r="AW11" s="1" t="n">
+        <v>101.44337003</v>
+      </c>
+      <c r="AX11" s="1" t="n">
+        <v>100.53811774</v>
+      </c>
+      <c r="AY11" s="1" t="n">
+        <v>101.14547038</v>
+      </c>
+      <c r="AZ11" s="1" t="n">
+        <v>101.33115776</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>黑龙江省</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>102.5193</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>102.7601</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>103.6509</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>103.6767</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>102.5802</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>102.1561</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>102.3375</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>102.8848</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>102.4556</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>103.816</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>105.0652</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>103.798</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>103.1808</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>103.6156</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>103.568</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>103.844</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>104.3863</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>105.5909</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>105.8377</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>106.1177</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>106.2237</v>
+      </c>
+      <c r="W12" s="1" t="n">
+        <v>105.2338</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>103.3425</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>103.23290695</v>
+      </c>
+      <c r="Z12" s="1" t="n">
+        <v>103.83445644</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>102.56718312</v>
+      </c>
+      <c r="AB12" s="1" t="n">
+        <v>103.43003892</v>
+      </c>
+      <c r="AC12" s="1" t="n">
+        <v>103.3536798</v>
+      </c>
+      <c r="AD12" s="1" t="n">
+        <v>102.86102373</v>
+      </c>
+      <c r="AE12" s="1" t="n">
+        <v>101.43109456</v>
+      </c>
+      <c r="AF12" s="1" t="n">
+        <v>100.69499726</v>
+      </c>
+      <c r="AG12" s="1" t="n">
+        <v>101.51067089</v>
+      </c>
+      <c r="AH12" s="1" t="n">
+        <v>101.61806746</v>
+      </c>
+      <c r="AI12" s="1" t="n">
+        <v>101.65163844</v>
+      </c>
+      <c r="AJ12" s="1" t="n">
+        <v>101.62131918</v>
+      </c>
+      <c r="AK12" s="1" t="n">
+        <v>101.93785294</v>
+      </c>
+      <c r="AL12" s="1" t="n">
+        <v>101.34518364</v>
+      </c>
+      <c r="AM12" s="1" t="n">
+        <v>103.49975258</v>
+      </c>
+      <c r="AN12" s="1" t="n">
+        <v>100.73509173</v>
+      </c>
+      <c r="AO12" s="1" t="n">
+        <v>100.09425727</v>
+      </c>
+      <c r="AP12" s="1" t="n">
+        <v>100.04562672</v>
+      </c>
+      <c r="AQ12" s="1" t="n">
+        <v>100.30693107</v>
+      </c>
+      <c r="AR12" s="1" t="n">
+        <v>101.00645565</v>
+      </c>
+      <c r="AS12" s="1" t="n">
+        <v>100.32200863</v>
+      </c>
+      <c r="AT12" s="1" t="n">
+        <v>101.21603277</v>
+      </c>
+      <c r="AU12" s="1" t="n">
+        <v>101.87837777</v>
+      </c>
+      <c r="AV12" s="1" t="n">
+        <v>100.96819706</v>
+      </c>
+      <c r="AW12" s="1" t="n">
+        <v>101.08184481</v>
+      </c>
+      <c r="AX12" s="1" t="n">
+        <v>99.33001303</v>
+      </c>
+      <c r="AY12" s="1" t="n">
+        <v>100.64102622</v>
+      </c>
+      <c r="AZ12" s="1" t="n">
+        <v>100.89878154</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>100.407</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>99.32599999999999</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>100.411</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>101.3827</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>101.7597</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>101.6773</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>102.5976</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>101.6991</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>102.2167</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>102.8518</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>103.0934</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>103.1334</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>102.8181</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>103.1845</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>103.6613</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>104.0052</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>104.5141</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>104.7757</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>104.4356</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>105.2082</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>105.0612</v>
+      </c>
+      <c r="W13" s="1" t="n">
+        <v>104.4051</v>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>103.6155</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>103.0245258</v>
+      </c>
+      <c r="Z13" s="1" t="n">
+        <v>102.98754257</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>102.81823757</v>
+      </c>
+      <c r="AB13" s="1" t="n">
+        <v>102.69966612</v>
+      </c>
+      <c r="AC13" s="1" t="n">
+        <v>102.26546983</v>
+      </c>
+      <c r="AD13" s="1" t="n">
+        <v>101.43127593</v>
+      </c>
+      <c r="AE13" s="1" t="n">
+        <v>100.82923777</v>
+      </c>
+      <c r="AF13" s="1" t="n">
+        <v>100.36621008</v>
+      </c>
+      <c r="AG13" s="1" t="n">
+        <v>100.44007931</v>
+      </c>
+      <c r="AH13" s="1" t="n">
+        <v>100.20301486</v>
+      </c>
+      <c r="AI13" s="1" t="n">
+        <v>100.48840081</v>
+      </c>
+      <c r="AJ13" s="1" t="n">
+        <v>100.0391722</v>
+      </c>
+      <c r="AK13" s="1" t="n">
+        <v>100.17944945</v>
+      </c>
+      <c r="AL13" s="1" t="n">
+        <v>100.30895128</v>
+      </c>
+      <c r="AM13" s="1" t="n">
+        <v>100.29907558</v>
+      </c>
+      <c r="AN13" s="1" t="n">
+        <v>99.8265327</v>
+      </c>
+      <c r="AO13" s="1" t="n">
+        <v>99.95777077</v>
+      </c>
+      <c r="AP13" s="1" t="n">
+        <v>99.90731159000001</v>
+      </c>
+      <c r="AQ13" s="1" t="n">
+        <v>100.18832483</v>
+      </c>
+      <c r="AR13" s="1" t="n">
+        <v>100.30255713</v>
+      </c>
+      <c r="AS13" s="1" t="n">
+        <v>100.35237764</v>
+      </c>
+      <c r="AT13" s="1" t="n">
+        <v>100.22831185</v>
+      </c>
+      <c r="AU13" s="1" t="n">
+        <v>100.12995236</v>
+      </c>
+      <c r="AV13" s="1" t="n">
+        <v>100.06528684</v>
+      </c>
+      <c r="AW13" s="1" t="n">
+        <v>100.12948266</v>
+      </c>
+      <c r="AX13" s="1" t="n">
+        <v>100.08874351</v>
+      </c>
+      <c r="AY13" s="1" t="n">
+        <v>100.24574605</v>
+      </c>
+      <c r="AZ13" s="1" t="n">
+        <v>100.09697929</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>江苏省</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>101.6921</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>102.1611</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>102.2195</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>102.8166</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>103.5564</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>103.3191</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>103.3959</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>103.2217</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>103.3485</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>103.8019</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>104.8067</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>103.9876</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>103.3507</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>103.9626</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>104.1839</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>104.253</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>104.6591</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>105.7442</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>105.8116</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>105.6832</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>105.5882</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>105.1319</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>103.6996</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>103.47285414</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <v>103.46133696</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>102.9535925</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>103.46093668</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>103.2873044</v>
+      </c>
+      <c r="AD14" s="1" t="n">
+        <v>102.43835758</v>
+      </c>
+      <c r="AE14" s="1" t="n">
+        <v>101.18741759</v>
+      </c>
+      <c r="AF14" s="1" t="n">
+        <v>101.13421633</v>
+      </c>
+      <c r="AG14" s="1" t="n">
+        <v>101.44137303</v>
+      </c>
+      <c r="AH14" s="1" t="n">
+        <v>101.0497463</v>
+      </c>
+      <c r="AI14" s="1" t="n">
+        <v>101.13741626</v>
+      </c>
+      <c r="AJ14" s="1" t="n">
+        <v>101.47890325</v>
+      </c>
+      <c r="AK14" s="1" t="n">
+        <v>101.7587573</v>
+      </c>
+      <c r="AL14" s="1" t="n">
+        <v>101.60535337</v>
+      </c>
+      <c r="AM14" s="1" t="n">
+        <v>101.53686315</v>
+      </c>
+      <c r="AN14" s="1" t="n">
+        <v>100.73256677</v>
+      </c>
+      <c r="AO14" s="1" t="n">
+        <v>101.10144503</v>
+      </c>
+      <c r="AP14" s="1" t="n">
+        <v>100.62738161</v>
+      </c>
+      <c r="AQ14" s="1" t="n">
+        <v>101.64611646</v>
+      </c>
+      <c r="AR14" s="1" t="n">
+        <v>101.47225976</v>
+      </c>
+      <c r="AS14" s="1" t="n">
+        <v>101.63782804</v>
+      </c>
+      <c r="AT14" s="1" t="n">
+        <v>101.849513</v>
+      </c>
+      <c r="AU14" s="1" t="n">
+        <v>101.56528827</v>
+      </c>
+      <c r="AV14" s="1" t="n">
+        <v>101.42896315</v>
+      </c>
+      <c r="AW14" s="1" t="n">
+        <v>101.18701639</v>
+      </c>
+      <c r="AX14" s="1" t="n">
+        <v>101.20200882</v>
+      </c>
+      <c r="AY14" s="1" t="n">
+        <v>101.55219861</v>
+      </c>
+      <c r="AZ14" s="1" t="n">
+        <v>101.18881918</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>浙江省</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>103.2829</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>103.8786</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>103.7228</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>104.2123</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>104.6865</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>103.8696</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>103.7035</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>102.911</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>103.1915</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>103.7827</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>105.11</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>104.4938</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>104.1527</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>104.7162</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>104.8338</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>105.179</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>105.4232</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>106.6445</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>106.7853</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>106.7739</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>106.9575</v>
+      </c>
+      <c r="W15" s="1" t="n">
+        <v>106.0917</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>104.4016</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>104.21441471</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <v>104.42641775</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>103.28234288</v>
+      </c>
+      <c r="AB15" s="1" t="n">
+        <v>104.05930456</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <v>103.25379359</v>
+      </c>
+      <c r="AD15" s="1" t="n">
+        <v>102.42863725</v>
+      </c>
+      <c r="AE15" s="1" t="n">
+        <v>100.82629226</v>
+      </c>
+      <c r="AF15" s="1" t="n">
+        <v>100.37244547</v>
+      </c>
+      <c r="AG15" s="1" t="n">
+        <v>100.81987809</v>
+      </c>
+      <c r="AH15" s="1" t="n">
+        <v>100.57576486</v>
+      </c>
+      <c r="AI15" s="1" t="n">
+        <v>100.63628703</v>
+      </c>
+      <c r="AJ15" s="1" t="n">
+        <v>100.92310857</v>
+      </c>
+      <c r="AK15" s="1" t="n">
+        <v>100.9528866</v>
+      </c>
+      <c r="AL15" s="1" t="n">
+        <v>100.69766076</v>
+      </c>
+      <c r="AM15" s="1" t="n">
+        <v>101.28833848</v>
+      </c>
+      <c r="AN15" s="1" t="n">
+        <v>99.83072792999999</v>
+      </c>
+      <c r="AO15" s="1" t="n">
+        <v>99.98091955</v>
+      </c>
+      <c r="AP15" s="1" t="n">
+        <v>100.07833741</v>
+      </c>
+      <c r="AQ15" s="1" t="n">
+        <v>101.15277444</v>
+      </c>
+      <c r="AR15" s="1" t="n">
+        <v>101.30424609</v>
+      </c>
+      <c r="AS15" s="1" t="n">
+        <v>101.06903936</v>
+      </c>
+      <c r="AT15" s="1" t="n">
+        <v>101.40041632</v>
+      </c>
+      <c r="AU15" s="1" t="n">
+        <v>101.56416084</v>
+      </c>
+      <c r="AV15" s="1" t="n">
+        <v>101.56922989</v>
+      </c>
+      <c r="AW15" s="1" t="n">
+        <v>101.3480354</v>
+      </c>
+      <c r="AX15" s="1" t="n">
+        <v>101.22817721</v>
+      </c>
+      <c r="AY15" s="1" t="n">
+        <v>101.76091264</v>
+      </c>
+      <c r="AZ15" s="1" t="n">
+        <v>101.11623376</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>安徽省</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>102.4004</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>102.52</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>102.4496</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>102.93</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>102.9096</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>102.7015</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>102.7245</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>102.7218</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>103.3877</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>104.5675</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>105.4325</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>104.2162</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>103.2255</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>104.434</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>104.9481</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>105.2195</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>105.6047</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>107.0443</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>106.9086</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>106.1972</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>106.2626</v>
+      </c>
+      <c r="W16" s="1" t="n">
+        <v>105.6883</v>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>103.9999</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>104.07317589</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <v>104.79140728</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>103.05834077</v>
+      </c>
+      <c r="AB16" s="1" t="n">
+        <v>103.67103205</v>
+      </c>
+      <c r="AC16" s="1" t="n">
+        <v>103.19644716</v>
+      </c>
+      <c r="AD16" s="1" t="n">
+        <v>102.53039283</v>
+      </c>
+      <c r="AE16" s="1" t="n">
+        <v>101.06059384</v>
+      </c>
+      <c r="AF16" s="1" t="n">
+        <v>100.52821313</v>
+      </c>
+      <c r="AG16" s="1" t="n">
+        <v>101.0812527</v>
+      </c>
+      <c r="AH16" s="1" t="n">
+        <v>100.92301373</v>
+      </c>
+      <c r="AI16" s="1" t="n">
+        <v>100.85669112</v>
+      </c>
+      <c r="AJ16" s="1" t="n">
+        <v>101.40015587</v>
+      </c>
+      <c r="AK16" s="1" t="n">
+        <v>101.72038291</v>
+      </c>
+      <c r="AL16" s="1" t="n">
+        <v>101.22189741</v>
+      </c>
+      <c r="AM16" s="1" t="n">
+        <v>101.99512441</v>
+      </c>
+      <c r="AN16" s="1" t="n">
+        <v>100.6572788</v>
+      </c>
+      <c r="AO16" s="1" t="n">
+        <v>100.92950199</v>
+      </c>
+      <c r="AP16" s="1" t="n">
+        <v>100.53515998</v>
+      </c>
+      <c r="AQ16" s="1" t="n">
+        <v>101.71180357</v>
+      </c>
+      <c r="AR16" s="1" t="n">
+        <v>101.72745028</v>
+      </c>
+      <c r="AS16" s="1" t="n">
+        <v>101.52396607</v>
+      </c>
+      <c r="AT16" s="1" t="n">
+        <v>101.71120396</v>
+      </c>
+      <c r="AU16" s="1" t="n">
+        <v>101.19513615</v>
+      </c>
+      <c r="AV16" s="1" t="n">
+        <v>100.63335901</v>
+      </c>
+      <c r="AW16" s="1" t="n">
+        <v>100.4115245</v>
+      </c>
+      <c r="AX16" s="1" t="n">
+        <v>100.03686352</v>
+      </c>
+      <c r="AY16" s="1" t="n">
+        <v>100.52008194</v>
+      </c>
+      <c r="AZ16" s="1" t="n">
+        <v>100.01358421</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>102.7189</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>103.5835</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>103.1244</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>103.1985</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>103.3018</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>103.4022</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>103.4929</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>102.6726</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>102.9003</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>103.6562</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>104.673</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>103.5368</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>102.9877</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>103.8784</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>104.217</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>104.7101</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>105.0649</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>105.4418</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>105.6741</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>106.2541</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>106.4394</v>
+      </c>
+      <c r="W17" s="1" t="n">
+        <v>105.0614</v>
+      </c>
+      <c r="X17" s="1" t="n">
+        <v>104.1591</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>104.30547022</v>
+      </c>
+      <c r="Z17" s="1" t="n">
+        <v>104.03524232</v>
+      </c>
+      <c r="AA17" s="1" t="n">
+        <v>103.13574527</v>
+      </c>
+      <c r="AB17" s="1" t="n">
+        <v>103.70288535</v>
+      </c>
+      <c r="AC17" s="1" t="n">
+        <v>103.35251228</v>
+      </c>
+      <c r="AD17" s="1" t="n">
+        <v>102.66019139</v>
+      </c>
+      <c r="AE17" s="1" t="n">
+        <v>101.38018446</v>
+      </c>
+      <c r="AF17" s="1" t="n">
+        <v>100.64859497</v>
+      </c>
+      <c r="AG17" s="1" t="n">
+        <v>100.87449385</v>
+      </c>
+      <c r="AH17" s="1" t="n">
+        <v>100.51363058</v>
+      </c>
+      <c r="AI17" s="1" t="n">
+        <v>100.49389675</v>
+      </c>
+      <c r="AJ17" s="1" t="n">
+        <v>100.43111166</v>
+      </c>
+      <c r="AK17" s="1" t="n">
+        <v>101.09617766</v>
+      </c>
+      <c r="AL17" s="1" t="n">
+        <v>100.88777162</v>
+      </c>
+      <c r="AM17" s="1" t="n">
+        <v>101.24680709</v>
+      </c>
+      <c r="AN17" s="1" t="n">
+        <v>99.86577579999999</v>
+      </c>
+      <c r="AO17" s="1" t="n">
+        <v>100.11726507</v>
+      </c>
+      <c r="AP17" s="1" t="n">
+        <v>99.93064952</v>
+      </c>
+      <c r="AQ17" s="1" t="n">
+        <v>101.09457544</v>
+      </c>
+      <c r="AR17" s="1" t="n">
+        <v>101.53105681</v>
+      </c>
+      <c r="AS17" s="1" t="n">
+        <v>101.50720221</v>
+      </c>
+      <c r="AT17" s="1" t="n">
+        <v>101.77049303</v>
+      </c>
+      <c r="AU17" s="1" t="n">
+        <v>102.08184402</v>
+      </c>
+      <c r="AV17" s="1" t="n">
+        <v>101.26563082</v>
+      </c>
+      <c r="AW17" s="1" t="n">
+        <v>101.24754287</v>
+      </c>
+      <c r="AX17" s="1" t="n">
+        <v>100.83709794</v>
+      </c>
+      <c r="AY17" s="1" t="n">
+        <v>101.75101919</v>
+      </c>
+      <c r="AZ17" s="1" t="n">
+        <v>100.70729072</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>江西省</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>101.0673</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>101.7542</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>101.9399</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>102.5799</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>102.9473</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>102.6912</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>102.907</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>102.6386</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>102.8309</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>103.6802</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>104.017</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>103.5628</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>103.4945</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>104.1855</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>104.3845</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>104.6548</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>104.9641</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>105.9606</v>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>106.2292</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>105.7663</v>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>105.5981</v>
+      </c>
+      <c r="W18" s="1" t="n">
+        <v>105.0253</v>
+      </c>
+      <c r="X18" s="1" t="n">
+        <v>104.0184</v>
+      </c>
+      <c r="Y18" s="1" t="n">
+        <v>103.68681759</v>
+      </c>
+      <c r="Z18" s="1" t="n">
+        <v>104.43017783</v>
+      </c>
+      <c r="AA18" s="1" t="n">
+        <v>103.29802791</v>
+      </c>
+      <c r="AB18" s="1" t="n">
+        <v>103.47591249</v>
+      </c>
+      <c r="AC18" s="1" t="n">
+        <v>102.8806955</v>
+      </c>
+      <c r="AD18" s="1" t="n">
+        <v>102.60860255</v>
+      </c>
+      <c r="AE18" s="1" t="n">
+        <v>101.49416563</v>
+      </c>
+      <c r="AF18" s="1" t="n">
+        <v>100.54520034</v>
+      </c>
+      <c r="AG18" s="1" t="n">
+        <v>100.74139187</v>
+      </c>
+      <c r="AH18" s="1" t="n">
+        <v>101.18979876</v>
+      </c>
+      <c r="AI18" s="1" t="n">
+        <v>101.205287</v>
+      </c>
+      <c r="AJ18" s="1" t="n">
+        <v>101.47338247</v>
+      </c>
+      <c r="AK18" s="1" t="n">
+        <v>101.73829672</v>
+      </c>
+      <c r="AL18" s="1" t="n">
+        <v>101.15954927</v>
+      </c>
+      <c r="AM18" s="1" t="n">
+        <v>101.94442473</v>
+      </c>
+      <c r="AN18" s="1" t="n">
+        <v>101.02808194</v>
+      </c>
+      <c r="AO18" s="1" t="n">
+        <v>101.22154698</v>
+      </c>
+      <c r="AP18" s="1" t="n">
+        <v>100.74424144</v>
+      </c>
+      <c r="AQ18" s="1" t="n">
+        <v>101.11179659</v>
+      </c>
+      <c r="AR18" s="1" t="n">
+        <v>101.49452483</v>
+      </c>
+      <c r="AS18" s="1" t="n">
+        <v>101.75681631</v>
+      </c>
+      <c r="AT18" s="1" t="n">
+        <v>101.84891315</v>
+      </c>
+      <c r="AU18" s="1" t="n">
+        <v>101.77953852</v>
+      </c>
+      <c r="AV18" s="1" t="n">
+        <v>101.58953901</v>
+      </c>
+      <c r="AW18" s="1" t="n">
+        <v>101.37725305</v>
+      </c>
+      <c r="AX18" s="1" t="n">
+        <v>101.13212283</v>
+      </c>
+      <c r="AY18" s="1" t="n">
+        <v>101.43333644</v>
+      </c>
+      <c r="AZ18" s="1" t="n">
+        <v>101.01326573</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>101.9684</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>102.743</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>102.2632</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>102.4885</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>102.406</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>101.9003</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>102.1673</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>102.7374</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>102.7154</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>103.4819</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>104.2828</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>103.3129</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>102.8288</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>103.3205</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>103.8832</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>104.099</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>104.6355</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>105.8523</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>106.1102</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>105.7352</v>
+      </c>
+      <c r="V19" s="1" t="n">
+        <v>105.8367</v>
+      </c>
+      <c r="W19" s="1" t="n">
+        <v>105.2395</v>
+      </c>
+      <c r="X19" s="1" t="n">
+        <v>104.1645</v>
+      </c>
+      <c r="Y19" s="1" t="n">
+        <v>104.18924477</v>
+      </c>
+      <c r="Z19" s="1" t="n">
+        <v>104.58819793</v>
+      </c>
+      <c r="AA19" s="1" t="n">
+        <v>103.11811905</v>
+      </c>
+      <c r="AB19" s="1" t="n">
+        <v>103.44140434</v>
+      </c>
+      <c r="AC19" s="1" t="n">
+        <v>102.71439753</v>
+      </c>
+      <c r="AD19" s="1" t="n">
+        <v>101.86907817</v>
+      </c>
+      <c r="AE19" s="1" t="n">
+        <v>100.87277695</v>
+      </c>
+      <c r="AF19" s="1" t="n">
+        <v>100.33370991</v>
+      </c>
+      <c r="AG19" s="1" t="n">
+        <v>100.73292272</v>
+      </c>
+      <c r="AH19" s="1" t="n">
+        <v>100.35620968</v>
+      </c>
+      <c r="AI19" s="1" t="n">
+        <v>100.24463936</v>
+      </c>
+      <c r="AJ19" s="1" t="n">
+        <v>100.4147009</v>
+      </c>
+      <c r="AK19" s="1" t="n">
+        <v>101.01163262</v>
+      </c>
+      <c r="AL19" s="1" t="n">
+        <v>101.00603608</v>
+      </c>
+      <c r="AM19" s="1" t="n">
+        <v>102.28226895</v>
+      </c>
+      <c r="AN19" s="1" t="n">
+        <v>100.87787219</v>
+      </c>
+      <c r="AO19" s="1" t="n">
+        <v>101.03710178</v>
+      </c>
+      <c r="AP19" s="1" t="n">
+        <v>100.81545332</v>
+      </c>
+      <c r="AQ19" s="1" t="n">
+        <v>101.54564638</v>
+      </c>
+      <c r="AR19" s="1" t="n">
+        <v>101.76476959</v>
+      </c>
+      <c r="AS19" s="1" t="n">
+        <v>101.43556475</v>
+      </c>
+      <c r="AT19" s="1" t="n">
+        <v>101.72187595</v>
+      </c>
+      <c r="AU19" s="1" t="n">
+        <v>101.77243667</v>
+      </c>
+      <c r="AV19" s="1" t="n">
+        <v>101.00176426</v>
+      </c>
+      <c r="AW19" s="1" t="n">
+        <v>100.83666062</v>
+      </c>
+      <c r="AX19" s="1" t="n">
+        <v>100.2305146</v>
+      </c>
+      <c r="AY19" s="1" t="n">
+        <v>101.02314007</v>
+      </c>
+      <c r="AZ19" s="1" t="n">
+        <v>100.89268141</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>河南省</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>101.6743</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>102.5199</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>102.2996</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>102.9391</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>103.1718</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>102.8064</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>102.9777</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>103.9504</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>104.1656</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>105.6526</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>106.8976</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>105.735</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>104.9587</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>105.3666</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>105.8859</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>105.7704</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>105.9726</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>107.2836</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>107.2506</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>106.5201</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>106.5329</v>
+      </c>
+      <c r="W20" s="1" t="n">
+        <v>105.3766</v>
+      </c>
+      <c r="X20" s="1" t="n">
+        <v>103.8258</v>
+      </c>
+      <c r="Y20" s="1" t="n">
+        <v>104.20819344</v>
+      </c>
+      <c r="Z20" s="1" t="n">
+        <v>104.8963323</v>
+      </c>
+      <c r="AA20" s="1" t="n">
+        <v>103.30090917</v>
+      </c>
+      <c r="AB20" s="1" t="n">
+        <v>103.89893966</v>
+      </c>
+      <c r="AC20" s="1" t="n">
+        <v>103.49007572</v>
+      </c>
+      <c r="AD20" s="1" t="n">
+        <v>102.77444088</v>
+      </c>
+      <c r="AE20" s="1" t="n">
+        <v>101.53918265</v>
+      </c>
+      <c r="AF20" s="1" t="n">
+        <v>101.07322827</v>
+      </c>
+      <c r="AG20" s="1" t="n">
+        <v>101.37856326</v>
+      </c>
+      <c r="AH20" s="1" t="n">
+        <v>101.15593416</v>
+      </c>
+      <c r="AI20" s="1" t="n">
+        <v>101.06888127</v>
+      </c>
+      <c r="AJ20" s="1" t="n">
+        <v>101.29203276</v>
+      </c>
+      <c r="AK20" s="1" t="n">
+        <v>101.66415829</v>
+      </c>
+      <c r="AL20" s="1" t="n">
+        <v>101.38949493</v>
+      </c>
+      <c r="AM20" s="1" t="n">
+        <v>102.79393119</v>
+      </c>
+      <c r="AN20" s="1" t="n">
+        <v>101.29705544</v>
+      </c>
+      <c r="AO20" s="1" t="n">
+        <v>101.39647221</v>
+      </c>
+      <c r="AP20" s="1" t="n">
+        <v>101.28379544</v>
+      </c>
+      <c r="AQ20" s="1" t="n">
+        <v>102.14474854</v>
+      </c>
+      <c r="AR20" s="1" t="n">
+        <v>102.41602499</v>
+      </c>
+      <c r="AS20" s="1" t="n">
+        <v>102.29554898</v>
+      </c>
+      <c r="AT20" s="1" t="n">
+        <v>102.55145501</v>
+      </c>
+      <c r="AU20" s="1" t="n">
+        <v>102.00691107</v>
+      </c>
+      <c r="AV20" s="1" t="n">
+        <v>101.38163103</v>
+      </c>
+      <c r="AW20" s="1" t="n">
+        <v>100.92189127</v>
+      </c>
+      <c r="AX20" s="1" t="n">
+        <v>100.25784598</v>
+      </c>
+      <c r="AY20" s="1" t="n">
+        <v>100.98636381</v>
+      </c>
+      <c r="AZ20" s="1" t="n">
+        <v>100.65359382</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>湖北省</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>101.2144</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>101.7748</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>101.725</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>102.3646</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>102.8823</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>102.9112</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>103.1508</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>103.6068</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>103.6014</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>104.4487</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>105.44</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>104.6542</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>103.995</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>105.3172</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>105.3994</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>105.4454</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>105.5658</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>106.6356</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>106.6034</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>106.1807</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>106.6069</v>
+      </c>
+      <c r="W21" s="1" t="n">
+        <v>106.0581</v>
+      </c>
+      <c r="X21" s="1" t="n">
+        <v>104.4269</v>
+      </c>
+      <c r="Y21" s="1" t="n">
+        <v>104.3576343</v>
+      </c>
+      <c r="Z21" s="1" t="n">
+        <v>104.66375937</v>
+      </c>
+      <c r="AA21" s="1" t="n">
+        <v>102.98087007</v>
+      </c>
+      <c r="AB21" s="1" t="n">
+        <v>103.80667758</v>
+      </c>
+      <c r="AC21" s="1" t="n">
+        <v>103.72684037</v>
+      </c>
+      <c r="AD21" s="1" t="n">
+        <v>103.23183928</v>
+      </c>
+      <c r="AE21" s="1" t="n">
+        <v>101.97351596</v>
+      </c>
+      <c r="AF21" s="1" t="n">
+        <v>101.57079943</v>
+      </c>
+      <c r="AG21" s="1" t="n">
+        <v>101.71331608</v>
+      </c>
+      <c r="AH21" s="1" t="n">
+        <v>101.64824091</v>
+      </c>
+      <c r="AI21" s="1" t="n">
+        <v>101.43067321</v>
+      </c>
+      <c r="AJ21" s="1" t="n">
+        <v>101.85105333</v>
+      </c>
+      <c r="AK21" s="1" t="n">
+        <v>102.10989235</v>
+      </c>
+      <c r="AL21" s="1" t="n">
+        <v>101.76886083</v>
+      </c>
+      <c r="AM21" s="1" t="n">
+        <v>102.77631202</v>
+      </c>
+      <c r="AN21" s="1" t="n">
+        <v>101.66683009</v>
+      </c>
+      <c r="AO21" s="1" t="n">
+        <v>101.52770255</v>
+      </c>
+      <c r="AP21" s="1" t="n">
+        <v>101.4178245</v>
+      </c>
+      <c r="AQ21" s="1" t="n">
+        <v>101.86059984</v>
+      </c>
+      <c r="AR21" s="1" t="n">
+        <v>101.96899075</v>
+      </c>
+      <c r="AS21" s="1" t="n">
+        <v>101.98374531</v>
+      </c>
+      <c r="AT21" s="1" t="n">
+        <v>102.02179988</v>
+      </c>
+      <c r="AU21" s="1" t="n">
+        <v>101.71259889</v>
+      </c>
+      <c r="AV21" s="1" t="n">
+        <v>101.291408</v>
+      </c>
+      <c r="AW21" s="1" t="n">
+        <v>100.9775965</v>
+      </c>
+      <c r="AX21" s="1" t="n">
+        <v>100.71789845</v>
+      </c>
+      <c r="AY21" s="1" t="n">
+        <v>100.87618721</v>
+      </c>
+      <c r="AZ21" s="1" t="n">
+        <v>100.52700194</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>100.9703</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>102.2624</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>102.2947</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>102.8108</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>103.266</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>103.2372</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>103.1805</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>103.1488</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>103.031</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>103.7771</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>104.4988</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>104.4471</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>104.992</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>105.7062</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>105.5906</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>105.6636</v>
+      </c>
+      <c r="R22" s="1" t="n">
+        <v>105.4254</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>105.9717</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>106.2011</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>106.4421</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>106.462</v>
+      </c>
+      <c r="W22" s="1" t="n">
+        <v>105.7113</v>
+      </c>
+      <c r="X22" s="1" t="n">
+        <v>104.297</v>
+      </c>
+      <c r="Y22" s="1" t="n">
+        <v>103.6738369</v>
+      </c>
+      <c r="Z22" s="1" t="n">
+        <v>103.5995123</v>
+      </c>
+      <c r="AA22" s="1" t="n">
+        <v>102.01618421</v>
+      </c>
+      <c r="AB22" s="1" t="n">
+        <v>103.22995714</v>
+      </c>
+      <c r="AC22" s="1" t="n">
+        <v>102.96479337</v>
+      </c>
+      <c r="AD22" s="1" t="n">
+        <v>102.69734408</v>
+      </c>
+      <c r="AE22" s="1" t="n">
+        <v>101.4913632</v>
+      </c>
+      <c r="AF22" s="1" t="n">
+        <v>100.52068667</v>
+      </c>
+      <c r="AG22" s="1" t="n">
+        <v>100.72291598</v>
+      </c>
+      <c r="AH22" s="1" t="n">
+        <v>100.80051088</v>
+      </c>
+      <c r="AI22" s="1" t="n">
+        <v>100.76716639</v>
+      </c>
+      <c r="AJ22" s="1" t="n">
+        <v>100.77288392</v>
+      </c>
+      <c r="AK22" s="1" t="n">
+        <v>101.44308457</v>
+      </c>
+      <c r="AL22" s="1" t="n">
+        <v>100.91069143</v>
+      </c>
+      <c r="AM22" s="1" t="n">
+        <v>101.67045822</v>
+      </c>
+      <c r="AN22" s="1" t="n">
+        <v>100.70490099</v>
+      </c>
+      <c r="AO22" s="1" t="n">
+        <v>100.72945217</v>
+      </c>
+      <c r="AP22" s="1" t="n">
+        <v>100.58876281</v>
+      </c>
+      <c r="AQ22" s="1" t="n">
+        <v>101.49223124</v>
+      </c>
+      <c r="AR22" s="1" t="n">
+        <v>102.16104486</v>
+      </c>
+      <c r="AS22" s="1" t="n">
+        <v>102.43976637</v>
+      </c>
+      <c r="AT22" s="1" t="n">
+        <v>102.85050726</v>
+      </c>
+      <c r="AU22" s="1" t="n">
+        <v>102.41641593</v>
+      </c>
+      <c r="AV22" s="1" t="n">
+        <v>102.26819839</v>
+      </c>
+      <c r="AW22" s="1" t="n">
+        <v>102.21740646</v>
+      </c>
+      <c r="AX22" s="1" t="n">
+        <v>101.84925145</v>
+      </c>
+      <c r="AY22" s="1" t="n">
+        <v>101.58202284</v>
+      </c>
+      <c r="AZ22" s="1" t="n">
+        <v>101.0266922</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>101.3165</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>103.5879</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>102.7217</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>103.5042</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>104.2975</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>103.4883</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>103.1532</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>102.8946</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>102.9705</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>103.9784</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>103.9581</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>103.8641</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>104.0131</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>104.0604</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>104.6839</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>105.1717</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>104.9687</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>105.597</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>106.3066</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>106.3625</v>
+      </c>
+      <c r="V23" s="1" t="n">
+        <v>106.0471</v>
+      </c>
+      <c r="W23" s="1" t="n">
+        <v>105.2851</v>
+      </c>
+      <c r="X23" s="1" t="n">
+        <v>104.3489</v>
+      </c>
+      <c r="Y23" s="1" t="n">
+        <v>104.14353152</v>
+      </c>
+      <c r="Z23" s="1" t="n">
+        <v>103.83965234</v>
+      </c>
+      <c r="AA23" s="1" t="n">
+        <v>102.59963529</v>
+      </c>
+      <c r="AB23" s="1" t="n">
+        <v>103.91265689</v>
+      </c>
+      <c r="AC23" s="1" t="n">
+        <v>103.53203664</v>
+      </c>
+      <c r="AD23" s="1" t="n">
+        <v>102.99665955</v>
+      </c>
+      <c r="AE23" s="1" t="n">
+        <v>101.7610696</v>
+      </c>
+      <c r="AF23" s="1" t="n">
+        <v>100.78771324</v>
+      </c>
+      <c r="AG23" s="1" t="n">
+        <v>101.08280564</v>
+      </c>
+      <c r="AH23" s="1" t="n">
+        <v>101.18811768</v>
+      </c>
+      <c r="AI23" s="1" t="n">
+        <v>101.04248301</v>
+      </c>
+      <c r="AJ23" s="1" t="n">
+        <v>101.58204345</v>
+      </c>
+      <c r="AK23" s="1" t="n">
+        <v>102.0425371</v>
+      </c>
+      <c r="AL23" s="1" t="n">
+        <v>101.05206915</v>
+      </c>
+      <c r="AM23" s="1" t="n">
+        <v>101.58165977</v>
+      </c>
+      <c r="AN23" s="1" t="n">
+        <v>99.98070740999999</v>
+      </c>
+      <c r="AO23" s="1" t="n">
+        <v>100.20664473</v>
+      </c>
+      <c r="AP23" s="1" t="n">
+        <v>99.87452657999999</v>
+      </c>
+      <c r="AQ23" s="1" t="n">
+        <v>100.67722832</v>
+      </c>
+      <c r="AR23" s="1" t="n">
+        <v>100.85839721</v>
+      </c>
+      <c r="AS23" s="1" t="n">
+        <v>101.38324035</v>
+      </c>
+      <c r="AT23" s="1" t="n">
+        <v>102.13824708</v>
+      </c>
+      <c r="AU23" s="1" t="n">
+        <v>101.24459233</v>
+      </c>
+      <c r="AV23" s="1" t="n">
+        <v>101.26468657</v>
+      </c>
+      <c r="AW23" s="1" t="n">
+        <v>101.67511994</v>
+      </c>
+      <c r="AX23" s="1" t="n">
+        <v>101.6566651</v>
+      </c>
+      <c r="AY23" s="1" t="n">
+        <v>101.96758644</v>
+      </c>
+      <c r="AZ23" s="1" t="n">
+        <v>101.32675238</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>广西壮族自治区</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>101.5252</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>102.9785</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>102.1407</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>102.8454</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>103.31</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>102.7886</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>102.8895</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>102.8001</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>102.5485</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>103.7516</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>104.1635</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>104.3125</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>105.1311</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>105.8187</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <v>106.3119</v>
+      </c>
+      <c r="Q24" s="1" t="n">
+        <v>107.065</v>
+      </c>
+      <c r="R24" s="1" t="n">
+        <v>107.1638</v>
+      </c>
+      <c r="S24" s="1" t="n">
+        <v>107.393</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>107.5032</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>106.8167</v>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>106.4315</v>
+      </c>
+      <c r="W24" s="1" t="n">
+        <v>105.5212</v>
+      </c>
+      <c r="X24" s="1" t="n">
+        <v>103.8855</v>
+      </c>
+      <c r="Y24" s="1" t="n">
+        <v>102.87258117</v>
+      </c>
+      <c r="Z24" s="1" t="n">
+        <v>103.68319029</v>
+      </c>
+      <c r="AA24" s="1" t="n">
+        <v>102.63142823</v>
+      </c>
+      <c r="AB24" s="1" t="n">
+        <v>103.50176316</v>
+      </c>
+      <c r="AC24" s="1" t="n">
+        <v>102.6088486</v>
+      </c>
+      <c r="AD24" s="1" t="n">
+        <v>102.18178671</v>
+      </c>
+      <c r="AE24" s="1" t="n">
+        <v>101.78724278</v>
+      </c>
+      <c r="AF24" s="1" t="n">
+        <v>100.96677278</v>
+      </c>
+      <c r="AG24" s="1" t="n">
+        <v>101.74742515</v>
+      </c>
+      <c r="AH24" s="1" t="n">
+        <v>102.23797508</v>
+      </c>
+      <c r="AI24" s="1" t="n">
+        <v>101.69150477</v>
+      </c>
+      <c r="AJ24" s="1" t="n">
+        <v>102.15156573</v>
+      </c>
+      <c r="AK24" s="1" t="n">
+        <v>102.49310098</v>
+      </c>
+      <c r="AL24" s="1" t="n">
+        <v>101.2742721</v>
+      </c>
+      <c r="AM24" s="1" t="n">
+        <v>101.57647956</v>
+      </c>
+      <c r="AN24" s="1" t="n">
+        <v>100.3240382</v>
+      </c>
+      <c r="AO24" s="1" t="n">
+        <v>100.14190343</v>
+      </c>
+      <c r="AP24" s="1" t="n">
+        <v>100.00516255</v>
+      </c>
+      <c r="AQ24" s="1" t="n">
+        <v>100.79006192</v>
+      </c>
+      <c r="AR24" s="1" t="n">
+        <v>101.06572459</v>
+      </c>
+      <c r="AS24" s="1" t="n">
+        <v>101.48031421</v>
+      </c>
+      <c r="AT24" s="1" t="n">
+        <v>102.03803054</v>
+      </c>
+      <c r="AU24" s="1" t="n">
+        <v>101.8308143</v>
+      </c>
+      <c r="AV24" s="1" t="n">
+        <v>101.96861182</v>
+      </c>
+      <c r="AW24" s="1" t="n">
+        <v>101.58445457</v>
+      </c>
+      <c r="AX24" s="1" t="n">
+        <v>101.3737773</v>
+      </c>
+      <c r="AY24" s="1" t="n">
+        <v>101.87292773</v>
+      </c>
+      <c r="AZ24" s="1" t="n">
+        <v>101.74178142</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>海南省</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>101.7858</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>104.1717</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>103.1787</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>104.0602</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>104.7426</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>104.2853</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>104.1246</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>104.1864</v>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>105.257</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>107.0941</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>106.829</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>105.837</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>106.1064</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>105.9821</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <v>106.0639</v>
+      </c>
+      <c r="Q25" s="1" t="n">
+        <v>105.6794</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <v>105.2018</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>106.0433</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>106.5394</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>105.7141</v>
+      </c>
+      <c r="V25" s="1" t="n">
+        <v>105.3204</v>
+      </c>
+      <c r="W25" s="1" t="n">
+        <v>104.3227</v>
+      </c>
+      <c r="X25" s="1" t="n">
+        <v>103.5682</v>
+      </c>
+      <c r="Y25" s="1" t="n">
+        <v>104.28672331</v>
+      </c>
+      <c r="Z25" s="1" t="n">
+        <v>104.19248436</v>
+      </c>
+      <c r="AA25" s="1" t="n">
+        <v>102.76537777</v>
+      </c>
+      <c r="AB25" s="1" t="n">
+        <v>103.78491459</v>
+      </c>
+      <c r="AC25" s="1" t="n">
+        <v>103.60173544</v>
+      </c>
+      <c r="AD25" s="1" t="n">
+        <v>103.75435955</v>
+      </c>
+      <c r="AE25" s="1" t="n">
+        <v>102.87058173</v>
+      </c>
+      <c r="AF25" s="1" t="n">
+        <v>102.21681667</v>
+      </c>
+      <c r="AG25" s="1" t="n">
+        <v>102.67390835</v>
+      </c>
+      <c r="AH25" s="1" t="n">
+        <v>102.27677026</v>
+      </c>
+      <c r="AI25" s="1" t="n">
+        <v>101.42248885</v>
+      </c>
+      <c r="AJ25" s="1" t="n">
+        <v>101.5693365</v>
+      </c>
+      <c r="AK25" s="1" t="n">
+        <v>101.00808727</v>
+      </c>
+      <c r="AL25" s="1" t="n">
+        <v>100.76562177</v>
+      </c>
+      <c r="AM25" s="1" t="n">
+        <v>101.19992413</v>
+      </c>
+      <c r="AN25" s="1" t="n">
+        <v>100.82543807</v>
+      </c>
+      <c r="AO25" s="1" t="n">
+        <v>101.05360246</v>
+      </c>
+      <c r="AP25" s="1" t="n">
+        <v>100.88333985</v>
+      </c>
+      <c r="AQ25" s="1" t="n">
+        <v>101.02111098</v>
+      </c>
+      <c r="AR25" s="1" t="n">
+        <v>101.24979425</v>
+      </c>
+      <c r="AS25" s="1" t="n">
+        <v>102.0394125</v>
+      </c>
+      <c r="AT25" s="1" t="n">
+        <v>102.11221351</v>
+      </c>
+      <c r="AU25" s="1" t="n">
+        <v>102.5148986</v>
+      </c>
+      <c r="AV25" s="1" t="n">
+        <v>102.48719538</v>
+      </c>
+      <c r="AW25" s="1" t="n">
+        <v>102.53737909</v>
+      </c>
+      <c r="AX25" s="1" t="n">
+        <v>102.15032387</v>
+      </c>
+      <c r="AY25" s="1" t="n">
+        <v>101.88978288</v>
+      </c>
+      <c r="AZ25" s="1" t="n">
+        <v>100.93017023</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>99.595</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>100.1855</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>100.0307</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>100.6268</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>102.0594</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>101.9266</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>101.5465</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>102.4068</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>102.1015</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>102.9854</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>104.1254</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>103.3356</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>102.9575</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>104.2228</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <v>104.4399</v>
+      </c>
+      <c r="Q26" s="1" t="n">
+        <v>104.0587</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <v>104.1175</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>105.3753</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>105.7733</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>105.7527</v>
+      </c>
+      <c r="V26" s="1" t="n">
+        <v>105.8011</v>
+      </c>
+      <c r="W26" s="1" t="n">
+        <v>104.7338</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <v>104.4957</v>
+      </c>
+      <c r="Y26" s="1" t="n">
+        <v>104.19686599</v>
+      </c>
+      <c r="Z26" s="1" t="n">
+        <v>103.8576059</v>
+      </c>
+      <c r="AA26" s="1" t="n">
+        <v>102.79179066</v>
+      </c>
+      <c r="AB26" s="1" t="n">
+        <v>103.02973992</v>
+      </c>
+      <c r="AC26" s="1" t="n">
+        <v>103.23012715</v>
+      </c>
+      <c r="AD26" s="1" t="n">
+        <v>102.62460501</v>
+      </c>
+      <c r="AE26" s="1" t="n">
+        <v>101.41643822</v>
+      </c>
+      <c r="AF26" s="1" t="n">
+        <v>100.52057764</v>
+      </c>
+      <c r="AG26" s="1" t="n">
+        <v>99.78852274</v>
+      </c>
+      <c r="AH26" s="1" t="n">
+        <v>100.33701195</v>
+      </c>
+      <c r="AI26" s="1" t="n">
+        <v>100.40327057</v>
+      </c>
+      <c r="AJ26" s="1" t="n">
+        <v>100.42913778</v>
+      </c>
+      <c r="AK26" s="1" t="n">
+        <v>100.82900702</v>
+      </c>
+      <c r="AL26" s="1" t="n">
+        <v>101.27481259</v>
+      </c>
+      <c r="AM26" s="1" t="n">
+        <v>102.06389749</v>
+      </c>
+      <c r="AN26" s="1" t="n">
+        <v>101.30891488</v>
+      </c>
+      <c r="AO26" s="1" t="n">
+        <v>101.51850926</v>
+      </c>
+      <c r="AP26" s="1" t="n">
+        <v>101.2907312</v>
+      </c>
+      <c r="AQ26" s="1" t="n">
+        <v>101.65625261</v>
+      </c>
+      <c r="AR26" s="1" t="n">
+        <v>102.66867489</v>
+      </c>
+      <c r="AS26" s="1" t="n">
+        <v>102.5313562</v>
+      </c>
+      <c r="AT26" s="1" t="n">
+        <v>102.25202107</v>
+      </c>
+      <c r="AU26" s="1" t="n">
+        <v>101.99712888</v>
+      </c>
+      <c r="AV26" s="1" t="n">
+        <v>101.45717956</v>
+      </c>
+      <c r="AW26" s="1" t="n">
+        <v>101.05797161</v>
+      </c>
+      <c r="AX26" s="1" t="n">
+        <v>100.60448748</v>
+      </c>
+      <c r="AY26" s="1" t="n">
+        <v>100.99336365</v>
+      </c>
+      <c r="AZ26" s="1" t="n">
+        <v>100.31220882</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>100.7366</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>101.3852</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>101.6477</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>102.1597</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>102.7087</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>102.6436</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>103.1773</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>103.8191</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>104.2897</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>104.7209</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>104.8518</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>104.2893</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>104.5849</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>105.9423</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>105.8518</v>
+      </c>
+      <c r="Q27" s="1" t="n">
+        <v>105.1414</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <v>104.5729</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>105.1789</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>105.0279</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>104.8778</v>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>104.5424</v>
+      </c>
+      <c r="W27" s="1" t="n">
+        <v>104.3596</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <v>103.1658</v>
+      </c>
+      <c r="Y27" s="1" t="n">
+        <v>102.67934328</v>
+      </c>
+      <c r="Z27" s="1" t="n">
+        <v>103.16632295</v>
+      </c>
+      <c r="AA27" s="1" t="n">
+        <v>101.73638897</v>
+      </c>
+      <c r="AB27" s="1" t="n">
+        <v>102.32698087</v>
+      </c>
+      <c r="AC27" s="1" t="n">
+        <v>102.68102923</v>
+      </c>
+      <c r="AD27" s="1" t="n">
+        <v>102.41102659</v>
+      </c>
+      <c r="AE27" s="1" t="n">
+        <v>101.67439758</v>
+      </c>
+      <c r="AF27" s="1" t="n">
+        <v>101.04298116</v>
+      </c>
+      <c r="AG27" s="1" t="n">
+        <v>100.56537684</v>
+      </c>
+      <c r="AH27" s="1" t="n">
+        <v>100.57071567</v>
+      </c>
+      <c r="AI27" s="1" t="n">
+        <v>100.35924671</v>
+      </c>
+      <c r="AJ27" s="1" t="n">
+        <v>101.22024855</v>
+      </c>
+      <c r="AK27" s="1" t="n">
+        <v>101.81222661</v>
+      </c>
+      <c r="AL27" s="1" t="n">
+        <v>101.4635252</v>
+      </c>
+      <c r="AM27" s="1" t="n">
+        <v>102.05197596</v>
+      </c>
+      <c r="AN27" s="1" t="n">
+        <v>100.93782596</v>
+      </c>
+      <c r="AO27" s="1" t="n">
+        <v>101.01529081</v>
+      </c>
+      <c r="AP27" s="1" t="n">
+        <v>100.90807352</v>
+      </c>
+      <c r="AQ27" s="1" t="n">
+        <v>101.20602374</v>
+      </c>
+      <c r="AR27" s="1" t="n">
+        <v>101.93916693</v>
+      </c>
+      <c r="AS27" s="1" t="n">
+        <v>102.02204759</v>
+      </c>
+      <c r="AT27" s="1" t="n">
+        <v>102.35386466</v>
+      </c>
+      <c r="AU27" s="1" t="n">
+        <v>102.09348371</v>
+      </c>
+      <c r="AV27" s="1" t="n">
+        <v>101.50597116</v>
+      </c>
+      <c r="AW27" s="1" t="n">
+        <v>101.11471847</v>
+      </c>
+      <c r="AX27" s="1" t="n">
+        <v>100.61803416</v>
+      </c>
+      <c r="AY27" s="1" t="n">
+        <v>100.8315862</v>
+      </c>
+      <c r="AZ27" s="1" t="n">
+        <v>100.19517812</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>贵州省</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>100.6401</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>101.5934</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>102.2881</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>102.6713</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>103.0453</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>103.227</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>103.0437</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>103.3097</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>103.2155</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>103.313</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>104.6828</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>104.6482</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>105.3714</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>105.4667</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <v>104.7038</v>
+      </c>
+      <c r="Q28" s="1" t="n">
+        <v>105.046</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <v>105.1129</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>105.5311</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>105.9418</v>
+      </c>
+      <c r="U28" s="1" t="n">
+        <v>106.0963</v>
+      </c>
+      <c r="V28" s="1" t="n">
+        <v>106.9413</v>
+      </c>
+      <c r="W28" s="1" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="X28" s="1" t="n">
+        <v>104.6141</v>
+      </c>
+      <c r="Y28" s="1" t="n">
+        <v>104.25521367</v>
+      </c>
+      <c r="Z28" s="1" t="n">
+        <v>103.86133003</v>
+      </c>
+      <c r="AA28" s="1" t="n">
+        <v>103.03875819</v>
+      </c>
+      <c r="AB28" s="1" t="n">
+        <v>103.34284469</v>
+      </c>
+      <c r="AC28" s="1" t="n">
+        <v>102.70613455</v>
+      </c>
+      <c r="AD28" s="1" t="n">
+        <v>102.58588137</v>
+      </c>
+      <c r="AE28" s="1" t="n">
+        <v>102.12975239</v>
+      </c>
+      <c r="AF28" s="1" t="n">
+        <v>101.41846564</v>
+      </c>
+      <c r="AG28" s="1" t="n">
+        <v>100.93078136</v>
+      </c>
+      <c r="AH28" s="1" t="n">
+        <v>100.44848962</v>
+      </c>
+      <c r="AI28" s="1" t="n">
+        <v>100.51922896</v>
+      </c>
+      <c r="AJ28" s="1" t="n">
+        <v>101.26832211</v>
+      </c>
+      <c r="AK28" s="1" t="n">
+        <v>101.73594162</v>
+      </c>
+      <c r="AL28" s="1" t="n">
+        <v>101.81781981</v>
+      </c>
+      <c r="AM28" s="1" t="n">
+        <v>102.36192834</v>
+      </c>
+      <c r="AN28" s="1" t="n">
+        <v>101.80405976</v>
+      </c>
+      <c r="AO28" s="1" t="n">
+        <v>101.74916489</v>
+      </c>
+      <c r="AP28" s="1" t="n">
+        <v>101.33409611</v>
+      </c>
+      <c r="AQ28" s="1" t="n">
+        <v>101.16159219</v>
+      </c>
+      <c r="AR28" s="1" t="n">
+        <v>101.44227527</v>
+      </c>
+      <c r="AS28" s="1" t="n">
+        <v>101.86608335</v>
+      </c>
+      <c r="AT28" s="1" t="n">
+        <v>101.64651499</v>
+      </c>
+      <c r="AU28" s="1" t="n">
+        <v>101.10765871</v>
+      </c>
+      <c r="AV28" s="1" t="n">
+        <v>100.83955854</v>
+      </c>
+      <c r="AW28" s="1" t="n">
+        <v>100.60493356</v>
+      </c>
+      <c r="AX28" s="1" t="n">
+        <v>100.25786976</v>
+      </c>
+      <c r="AY28" s="1" t="n">
+        <v>100.92650305</v>
+      </c>
+      <c r="AZ28" s="1" t="n">
+        <v>100.92723649</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>云南省</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>102.1893</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>103.1185</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>103.9181</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>103.9009</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>104.2103</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>103.812</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>104.2164</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>104.3575</v>
+      </c>
+      <c r="J29" s="1" t="n">
+        <v>103.6823</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>103.7314</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>103.8639</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="N29" s="1" t="n">
+        <v>102.8985</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>103.4145</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <v>103.6924</v>
+      </c>
+      <c r="Q29" s="1" t="n">
+        <v>104.09</v>
+      </c>
+      <c r="R29" s="1" t="n">
+        <v>103.7702</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>105.0809</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>106.0456</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>106.4791</v>
+      </c>
+      <c r="V29" s="1" t="n">
+        <v>107.0534</v>
+      </c>
+      <c r="W29" s="1" t="n">
+        <v>106.8855</v>
+      </c>
+      <c r="X29" s="1" t="n">
+        <v>105.7032</v>
+      </c>
+      <c r="Y29" s="1" t="n">
+        <v>105.78128725</v>
+      </c>
+      <c r="Z29" s="1" t="n">
+        <v>105.4530363</v>
+      </c>
+      <c r="AA29" s="1" t="n">
+        <v>104.43033162</v>
+      </c>
+      <c r="AB29" s="1" t="n">
+        <v>104.48281331</v>
+      </c>
+      <c r="AC29" s="1" t="n">
+        <v>103.94925301</v>
+      </c>
+      <c r="AD29" s="1" t="n">
+        <v>104.07735255</v>
+      </c>
+      <c r="AE29" s="1" t="n">
+        <v>101.96080225</v>
+      </c>
+      <c r="AF29" s="1" t="n">
+        <v>100.21636425</v>
+      </c>
+      <c r="AG29" s="1" t="n">
+        <v>99.97370372</v>
+      </c>
+      <c r="AH29" s="1" t="n">
+        <v>100.30665931</v>
+      </c>
+      <c r="AI29" s="1" t="n">
+        <v>100.66069572</v>
+      </c>
+      <c r="AJ29" s="1" t="n">
+        <v>101.2053198</v>
+      </c>
+      <c r="AK29" s="1" t="n">
+        <v>101.8917323</v>
+      </c>
+      <c r="AL29" s="1" t="n">
+        <v>102.09792222</v>
+      </c>
+      <c r="AM29" s="1" t="n">
+        <v>102.9448595</v>
+      </c>
+      <c r="AN29" s="1" t="n">
+        <v>102.32151003</v>
+      </c>
+      <c r="AO29" s="1" t="n">
+        <v>102.21776354</v>
+      </c>
+      <c r="AP29" s="1" t="n">
+        <v>101.67795533</v>
+      </c>
+      <c r="AQ29" s="1" t="n">
+        <v>102.77548822</v>
+      </c>
+      <c r="AR29" s="1" t="n">
+        <v>103.64929508</v>
+      </c>
+      <c r="AS29" s="1" t="n">
+        <v>103.37005737</v>
+      </c>
+      <c r="AT29" s="1" t="n">
+        <v>102.78315008</v>
+      </c>
+      <c r="AU29" s="1" t="n">
+        <v>102.42464546</v>
+      </c>
+      <c r="AV29" s="1" t="n">
+        <v>102.08181169</v>
+      </c>
+      <c r="AW29" s="1" t="n">
+        <v>102.08402083</v>
+      </c>
+      <c r="AX29" s="1" t="n">
+        <v>101.23834608</v>
+      </c>
+      <c r="AY29" s="1" t="n">
+        <v>101.33436411</v>
+      </c>
+      <c r="AZ29" s="1" t="n">
+        <v>100.86726298</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>西藏自治区</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>101.2951</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>100.4145</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>100.2144</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>100.4241</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>100.6297</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>100.2345</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>100.2443</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>100.6299</v>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>100.8866</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>101.453</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>102.8209</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>102.9844</v>
+      </c>
+      <c r="N30" s="1" t="n">
+        <v>102.8162</v>
+      </c>
+      <c r="O30" s="1" t="n">
+        <v>103.1577</v>
+      </c>
+      <c r="P30" s="1" t="n">
+        <v>103.7983</v>
+      </c>
+      <c r="Q30" s="1" t="n">
+        <v>103.8663</v>
+      </c>
+      <c r="R30" s="1" t="n">
+        <v>103.564</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <v>103.5471</v>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>103.6479</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>103.8198</v>
+      </c>
+      <c r="V30" s="1" t="n">
+        <v>104.1497</v>
+      </c>
+      <c r="W30" s="1" t="n">
+        <v>104.0234</v>
+      </c>
+      <c r="X30" s="1" t="n">
+        <v>103.8044</v>
+      </c>
+      <c r="Y30" s="1" t="n">
+        <v>104.0625465</v>
+      </c>
+      <c r="Z30" s="1" t="n">
+        <v>104.04020697</v>
+      </c>
+      <c r="AA30" s="1" t="n">
+        <v>103.79465379</v>
+      </c>
+      <c r="AB30" s="1" t="n">
+        <v>103.54737586</v>
+      </c>
+      <c r="AC30" s="1" t="n">
+        <v>103.76918722</v>
+      </c>
+      <c r="AD30" s="1" t="n">
+        <v>103.86169255</v>
+      </c>
+      <c r="AE30" s="1" t="n">
+        <v>103.25612938</v>
+      </c>
+      <c r="AF30" s="1" t="n">
+        <v>102.95648832</v>
+      </c>
+      <c r="AG30" s="1" t="n">
+        <v>102.34457367</v>
+      </c>
+      <c r="AH30" s="1" t="n">
+        <v>102.03759373</v>
+      </c>
+      <c r="AI30" s="1" t="n">
+        <v>101.88556755</v>
+      </c>
+      <c r="AJ30" s="1" t="n">
+        <v>101.70386446</v>
+      </c>
+      <c r="AK30" s="1" t="n">
+        <v>101.51124183</v>
+      </c>
+      <c r="AL30" s="1" t="n">
+        <v>101.91801379</v>
+      </c>
+      <c r="AM30" s="1" t="n">
+        <v>102.61610773</v>
+      </c>
+      <c r="AN30" s="1" t="n">
+        <v>102.07127809</v>
+      </c>
+      <c r="AO30" s="1" t="n">
+        <v>102.05716309</v>
+      </c>
+      <c r="AP30" s="1" t="n">
+        <v>102.72947433</v>
+      </c>
+      <c r="AQ30" s="1" t="n">
+        <v>103.4263804</v>
+      </c>
+      <c r="AR30" s="1" t="n">
+        <v>103.52762567</v>
+      </c>
+      <c r="AS30" s="1" t="n">
+        <v>103.90605783</v>
+      </c>
+      <c r="AT30" s="1" t="n">
+        <v>103.71923102</v>
+      </c>
+      <c r="AU30" s="1" t="n">
+        <v>103.50485346</v>
+      </c>
+      <c r="AV30" s="1" t="n">
+        <v>103.30071579</v>
+      </c>
+      <c r="AW30" s="1" t="n">
+        <v>103.01608244</v>
+      </c>
+      <c r="AX30" s="1" t="n">
+        <v>102.36836021</v>
+      </c>
+      <c r="AY30" s="1" t="n">
+        <v>102.73360779</v>
+      </c>
+      <c r="AZ30" s="1" t="n">
+        <v>102.37209816</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>陕西省</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>102.2027</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>102.9103</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>102.6022</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>103.1631</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>102.8188</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>103.3194</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>104.1518</v>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>104.0994</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>104.5591</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>105.4041</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>104.6907</v>
+      </c>
+      <c r="N31" s="1" t="n">
+        <v>103.8189</v>
+      </c>
+      <c r="O31" s="1" t="n">
+        <v>103.8534</v>
+      </c>
+      <c r="P31" s="1" t="n">
+        <v>104.48</v>
+      </c>
+      <c r="Q31" s="1" t="n">
+        <v>103.8314</v>
+      </c>
+      <c r="R31" s="1" t="n">
+        <v>104.317</v>
+      </c>
+      <c r="S31" s="1" t="n">
+        <v>105.6875</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>105.6939</v>
+      </c>
+      <c r="U31" s="1" t="n">
+        <v>105.7232</v>
+      </c>
+      <c r="V31" s="1" t="n">
+        <v>106.1289</v>
+      </c>
+      <c r="W31" s="1" t="n">
+        <v>105.532</v>
+      </c>
+      <c r="X31" s="1" t="n">
+        <v>104.2017</v>
+      </c>
+      <c r="Y31" s="1" t="n">
+        <v>104.44680556</v>
+      </c>
+      <c r="Z31" s="1" t="n">
+        <v>104.82880942</v>
+      </c>
+      <c r="AA31" s="1" t="n">
+        <v>103.61500414</v>
+      </c>
+      <c r="AB31" s="1" t="n">
+        <v>103.85938828</v>
+      </c>
+      <c r="AC31" s="1" t="n">
+        <v>103.66447957</v>
+      </c>
+      <c r="AD31" s="1" t="n">
+        <v>103.00646289</v>
+      </c>
+      <c r="AE31" s="1" t="n">
+        <v>101.63346053</v>
+      </c>
+      <c r="AF31" s="1" t="n">
+        <v>100.95903313</v>
+      </c>
+      <c r="AG31" s="1" t="n">
+        <v>100.92658764</v>
+      </c>
+      <c r="AH31" s="1" t="n">
+        <v>101.02841181</v>
+      </c>
+      <c r="AI31" s="1" t="n">
+        <v>100.95324209</v>
+      </c>
+      <c r="AJ31" s="1" t="n">
+        <v>101.30542925</v>
+      </c>
+      <c r="AK31" s="1" t="n">
+        <v>101.61092139</v>
+      </c>
+      <c r="AL31" s="1" t="n">
+        <v>101.54566206</v>
+      </c>
+      <c r="AM31" s="1" t="n">
+        <v>102.72224614</v>
+      </c>
+      <c r="AN31" s="1" t="n">
+        <v>101.10230515</v>
+      </c>
+      <c r="AO31" s="1" t="n">
+        <v>101.57255398</v>
+      </c>
+      <c r="AP31" s="1" t="n">
+        <v>101.25366894</v>
+      </c>
+      <c r="AQ31" s="1" t="n">
+        <v>102.083056</v>
+      </c>
+      <c r="AR31" s="1" t="n">
+        <v>102.20095567</v>
+      </c>
+      <c r="AS31" s="1" t="n">
+        <v>102.07948888</v>
+      </c>
+      <c r="AT31" s="1" t="n">
+        <v>101.9512411</v>
+      </c>
+      <c r="AU31" s="1" t="n">
+        <v>101.82311774</v>
+      </c>
+      <c r="AV31" s="1" t="n">
+        <v>101.16164326</v>
+      </c>
+      <c r="AW31" s="1" t="n">
+        <v>101.27428443</v>
+      </c>
+      <c r="AX31" s="1" t="n">
+        <v>100.69459883</v>
+      </c>
+      <c r="AY31" s="1" t="n">
+        <v>101.23261893</v>
+      </c>
+      <c r="AZ31" s="1" t="n">
+        <v>100.19029527</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>甘肃省</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>102.6132</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>102.7111</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>103.0479</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>104.0119</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>103.7173</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>103.1834</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>104.0736</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>104.279</v>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>104.5752</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>105.3245</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>107.4496</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>106.434</v>
+      </c>
+      <c r="N32" s="1" t="n">
+        <v>105.8213</v>
+      </c>
+      <c r="O32" s="1" t="n">
+        <v>106.1162</v>
+      </c>
+      <c r="P32" s="1" t="n">
+        <v>105.8545</v>
+      </c>
+      <c r="Q32" s="1" t="n">
+        <v>105.4352</v>
+      </c>
+      <c r="R32" s="1" t="n">
+        <v>104.9253</v>
+      </c>
+      <c r="S32" s="1" t="n">
+        <v>106.0484</v>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>106.7024</v>
+      </c>
+      <c r="U32" s="1" t="n">
+        <v>106.2832</v>
+      </c>
+      <c r="V32" s="1" t="n">
+        <v>105.9252</v>
+      </c>
+      <c r="W32" s="1" t="n">
+        <v>105.3686</v>
+      </c>
+      <c r="X32" s="1" t="n">
+        <v>103.5058</v>
+      </c>
+      <c r="Y32" s="1" t="n">
+        <v>103.09028093</v>
+      </c>
+      <c r="Z32" s="1" t="n">
+        <v>103.28294193</v>
+      </c>
+      <c r="AA32" s="1" t="n">
+        <v>103.02738643</v>
+      </c>
+      <c r="AB32" s="1" t="n">
+        <v>103.32179551</v>
+      </c>
+      <c r="AC32" s="1" t="n">
+        <v>103.30077557</v>
+      </c>
+      <c r="AD32" s="1" t="n">
+        <v>103.45144836</v>
+      </c>
+      <c r="AE32" s="1" t="n">
+        <v>102.52223797</v>
+      </c>
+      <c r="AF32" s="1" t="n">
+        <v>101.23648328</v>
+      </c>
+      <c r="AG32" s="1" t="n">
+        <v>101.64595575</v>
+      </c>
+      <c r="AH32" s="1" t="n">
+        <v>102.2738928</v>
+      </c>
+      <c r="AI32" s="1" t="n">
+        <v>102.30498901</v>
+      </c>
+      <c r="AJ32" s="1" t="n">
+        <v>102.1193913</v>
+      </c>
+      <c r="AK32" s="1" t="n">
+        <v>102.72493536</v>
+      </c>
+      <c r="AL32" s="1" t="n">
+        <v>102.77246063</v>
+      </c>
+      <c r="AM32" s="1" t="n">
+        <v>102.37830276</v>
+      </c>
+      <c r="AN32" s="1" t="n">
+        <v>101.58179011</v>
+      </c>
+      <c r="AO32" s="1" t="n">
+        <v>102.34042278</v>
+      </c>
+      <c r="AP32" s="1" t="n">
+        <v>102.31514372</v>
+      </c>
+      <c r="AQ32" s="1" t="n">
+        <v>102.78648457</v>
+      </c>
+      <c r="AR32" s="1" t="n">
+        <v>103.31969198</v>
+      </c>
+      <c r="AS32" s="1" t="n">
+        <v>102.83623034</v>
+      </c>
+      <c r="AT32" s="1" t="n">
+        <v>102.60115013</v>
+      </c>
+      <c r="AU32" s="1" t="n">
+        <v>102.76969994</v>
+      </c>
+      <c r="AV32" s="1" t="n">
+        <v>102.28993109</v>
+      </c>
+      <c r="AW32" s="1" t="n">
+        <v>102.14339735</v>
+      </c>
+      <c r="AX32" s="1" t="n">
+        <v>102.09458098</v>
+      </c>
+      <c r="AY32" s="1" t="n">
+        <v>102.21311227</v>
+      </c>
+      <c r="AZ32" s="1" t="n">
+        <v>101.38415709</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>青海省</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>102.041</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>102.773</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>102.875</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>103.5968</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>104.0541</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>103.5946</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>104.1631</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>105.0075</v>
+      </c>
+      <c r="J33" s="1" t="n">
+        <v>104.9438</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>105.4631</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>106.6545</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>106.2833</v>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>106.8304</v>
+      </c>
+      <c r="O33" s="1" t="n">
+        <v>108.3847</v>
+      </c>
+      <c r="P33" s="1" t="n">
+        <v>108.2568</v>
+      </c>
+      <c r="Q33" s="1" t="n">
+        <v>107.7543</v>
+      </c>
+      <c r="R33" s="1" t="n">
+        <v>106.2395</v>
+      </c>
+      <c r="S33" s="1" t="n">
+        <v>105.3859</v>
+      </c>
+      <c r="T33" s="1" t="n">
+        <v>104.8333</v>
+      </c>
+      <c r="U33" s="1" t="n">
+        <v>104.7296</v>
+      </c>
+      <c r="V33" s="1" t="n">
+        <v>104.7264</v>
+      </c>
+      <c r="W33" s="1" t="n">
+        <v>104.2547</v>
+      </c>
+      <c r="X33" s="1" t="n">
+        <v>102.477</v>
+      </c>
+      <c r="Y33" s="1" t="n">
+        <v>101.13751946</v>
+      </c>
+      <c r="Z33" s="1" t="n">
+        <v>101.82340469</v>
+      </c>
+      <c r="AA33" s="1" t="n">
+        <v>100.13913528</v>
+      </c>
+      <c r="AB33" s="1" t="n">
+        <v>100.31321649</v>
+      </c>
+      <c r="AC33" s="1" t="n">
+        <v>100.84101776</v>
+      </c>
+      <c r="AD33" s="1" t="n">
+        <v>101.4637357</v>
+      </c>
+      <c r="AE33" s="1" t="n">
+        <v>102.24791436</v>
+      </c>
+      <c r="AF33" s="1" t="n">
+        <v>101.91949519</v>
+      </c>
+      <c r="AG33" s="1" t="n">
+        <v>102.71126655</v>
+      </c>
+      <c r="AH33" s="1" t="n">
+        <v>102.81640458</v>
+      </c>
+      <c r="AI33" s="1" t="n">
+        <v>103.20106574</v>
+      </c>
+      <c r="AJ33" s="1" t="n">
+        <v>103.44749938</v>
+      </c>
+      <c r="AK33" s="1" t="n">
+        <v>104.06502692</v>
+      </c>
+      <c r="AL33" s="1" t="n">
+        <v>103.48022089</v>
+      </c>
+      <c r="AM33" s="1" t="n">
+        <v>104.32747036</v>
+      </c>
+      <c r="AN33" s="1" t="n">
+        <v>103.57652388</v>
+      </c>
+      <c r="AO33" s="1" t="n">
+        <v>103.37780902</v>
+      </c>
+      <c r="AP33" s="1" t="n">
+        <v>103.07803939</v>
+      </c>
+      <c r="AQ33" s="1" t="n">
+        <v>103.52547045</v>
+      </c>
+      <c r="AR33" s="1" t="n">
+        <v>103.65656052</v>
+      </c>
+      <c r="AS33" s="1" t="n">
+        <v>102.17625497</v>
+      </c>
+      <c r="AT33" s="1" t="n">
+        <v>101.62108554</v>
+      </c>
+      <c r="AU33" s="1" t="n">
+        <v>101.15428769</v>
+      </c>
+      <c r="AV33" s="1" t="n">
+        <v>101.19263458</v>
+      </c>
+      <c r="AW33" s="1" t="n">
+        <v>101.7414415</v>
+      </c>
+      <c r="AX33" s="1" t="n">
+        <v>100.995281</v>
+      </c>
+      <c r="AY33" s="1" t="n">
+        <v>100.82269566</v>
+      </c>
+      <c r="AZ33" s="1" t="n">
+        <v>100.45477485</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>宁夏回族自治区</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>100.9438</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>102.1665</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>101.3026</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>102.4428</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>102.2588</v>
+      </c>
+      <c r="G34" s="1" t="n">
+        <v>102.0258</v>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>102.9571</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>103.4238</v>
+      </c>
+      <c r="J34" s="1" t="n">
+        <v>103.4983</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>104.7357</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>106.5224</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <v>106.1066</v>
+      </c>
+      <c r="N34" s="1" t="n">
+        <v>105.9063</v>
+      </c>
+      <c r="O34" s="1" t="n">
+        <v>105.6326</v>
+      </c>
+      <c r="P34" s="1" t="n">
+        <v>106.5849</v>
+      </c>
+      <c r="Q34" s="1" t="n">
+        <v>105.8775</v>
+      </c>
+      <c r="R34" s="1" t="n">
+        <v>105.7293</v>
+      </c>
+      <c r="S34" s="1" t="n">
+        <v>106.5385</v>
+      </c>
+      <c r="T34" s="1" t="n">
+        <v>106.5129</v>
+      </c>
+      <c r="U34" s="1" t="n">
+        <v>105.7545</v>
+      </c>
+      <c r="V34" s="1" t="n">
+        <v>105.979</v>
+      </c>
+      <c r="W34" s="1" t="n">
+        <v>104.9844</v>
+      </c>
+      <c r="X34" s="1" t="n">
+        <v>102.5121</v>
+      </c>
+      <c r="Y34" s="1" t="n">
+        <v>101.3007797</v>
+      </c>
+      <c r="Z34" s="1" t="n">
+        <v>101.3250003</v>
+      </c>
+      <c r="AA34" s="1" t="n">
+        <v>101.42472388</v>
+      </c>
+      <c r="AB34" s="1" t="n">
+        <v>101.58601913</v>
+      </c>
+      <c r="AC34" s="1" t="n">
+        <v>101.39120135</v>
+      </c>
+      <c r="AD34" s="1" t="n">
+        <v>101.12314599</v>
+      </c>
+      <c r="AE34" s="1" t="n">
+        <v>99.63887957</v>
+      </c>
+      <c r="AF34" s="1" t="n">
+        <v>99.07610056999999</v>
+      </c>
+      <c r="AG34" s="1" t="n">
+        <v>100.20776703</v>
+      </c>
+      <c r="AH34" s="1" t="n">
+        <v>100.22948254</v>
+      </c>
+      <c r="AI34" s="1" t="n">
+        <v>100.71222141</v>
+      </c>
+      <c r="AJ34" s="1" t="n">
+        <v>101.71584697</v>
+      </c>
+      <c r="AK34" s="1" t="n">
+        <v>103.21000794</v>
+      </c>
+      <c r="AL34" s="1" t="n">
+        <v>102.50110637</v>
+      </c>
+      <c r="AM34" s="1" t="n">
+        <v>102.42319315</v>
+      </c>
+      <c r="AN34" s="1" t="n">
+        <v>101.8088481</v>
+      </c>
+      <c r="AO34" s="1" t="n">
+        <v>102.58147878</v>
+      </c>
+      <c r="AP34" s="1" t="n">
+        <v>102.64329448</v>
+      </c>
+      <c r="AQ34" s="1" t="n">
+        <v>103.28456286</v>
+      </c>
+      <c r="AR34" s="1" t="n">
+        <v>103.49461142</v>
+      </c>
+      <c r="AS34" s="1" t="n">
+        <v>102.0362367</v>
+      </c>
+      <c r="AT34" s="1" t="n">
+        <v>102.30005427</v>
+      </c>
+      <c r="AU34" s="1" t="n">
+        <v>102.11904683</v>
+      </c>
+      <c r="AV34" s="1" t="n">
+        <v>101.58210317</v>
+      </c>
+      <c r="AW34" s="1" t="n">
+        <v>101.33847025</v>
+      </c>
+      <c r="AX34" s="1" t="n">
+        <v>101.60246077</v>
+      </c>
+      <c r="AY34" s="1" t="n">
+        <v>101.38096282</v>
+      </c>
+      <c r="AZ34" s="1" t="n">
+        <v>100.40923198</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>新疆维吾尔自治区</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>103.2584</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>104.417</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>103.5612</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>104.2986</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>104.2133</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>103.9328</v>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>104.7041</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>105.382</v>
+      </c>
+      <c r="J35" s="1" t="n">
+        <v>105.2578</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>105.8624</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>105.9246</v>
+      </c>
+      <c r="M35" s="1" t="n">
+        <v>104.7732</v>
+      </c>
+      <c r="N35" s="1" t="n">
+        <v>104.1212</v>
+      </c>
+      <c r="O35" s="1" t="n">
+        <v>104.3425</v>
+      </c>
+      <c r="P35" s="1" t="n">
+        <v>105.1754</v>
+      </c>
+      <c r="Q35" s="1" t="n">
+        <v>105.0875</v>
+      </c>
+      <c r="R35" s="1" t="n">
+        <v>104.6272</v>
+      </c>
+      <c r="S35" s="1" t="n">
+        <v>105.2867</v>
+      </c>
+      <c r="T35" s="1" t="n">
+        <v>106.0041</v>
+      </c>
+      <c r="U35" s="1" t="n">
+        <v>106.3638</v>
+      </c>
+      <c r="V35" s="1" t="n">
+        <v>106.0931</v>
+      </c>
+      <c r="W35" s="1" t="n">
+        <v>105.7809</v>
+      </c>
+      <c r="X35" s="1" t="n">
+        <v>105.4999</v>
+      </c>
+      <c r="Y35" s="1" t="n">
+        <v>103.40850479</v>
+      </c>
+      <c r="Z35" s="1" t="n">
+        <v>105.2040636</v>
+      </c>
+      <c r="AA35" s="1" t="n">
+        <v>104.65580453</v>
+      </c>
+      <c r="AB35" s="1" t="n">
+        <v>103.84217574</v>
+      </c>
+      <c r="AC35" s="1" t="n">
+        <v>103.4455361</v>
+      </c>
+      <c r="AD35" s="1" t="n">
+        <v>103.27829909</v>
+      </c>
+      <c r="AE35" s="1" t="n">
+        <v>103.12025037</v>
+      </c>
+      <c r="AF35" s="1" t="n">
+        <v>101.9161599</v>
+      </c>
+      <c r="AG35" s="1" t="n">
+        <v>101.87011731</v>
+      </c>
+      <c r="AH35" s="1" t="n">
+        <v>102.10295837</v>
+      </c>
+      <c r="AI35" s="1" t="n">
+        <v>102.58837258</v>
+      </c>
+      <c r="AJ35" s="1" t="n">
+        <v>102.39826324</v>
+      </c>
+      <c r="AK35" s="1" t="n">
+        <v>104.88448196</v>
+      </c>
+      <c r="AL35" s="1" t="n">
+        <v>103.90461623</v>
+      </c>
+      <c r="AM35" s="1" t="n">
+        <v>104.04220433</v>
+      </c>
+      <c r="AN35" s="1" t="n">
+        <v>103.24304296</v>
+      </c>
+      <c r="AO35" s="1" t="n">
+        <v>103.22193221</v>
+      </c>
+      <c r="AP35" s="1" t="n">
+        <v>103.18721681</v>
+      </c>
+      <c r="AQ35" s="1" t="n">
+        <v>103.20460046</v>
+      </c>
+      <c r="AR35" s="1" t="n">
+        <v>103.51862888</v>
+      </c>
+      <c r="AS35" s="1" t="n">
+        <v>103.3653754</v>
+      </c>
+      <c r="AT35" s="1" t="n">
+        <v>103.22167609</v>
+      </c>
+      <c r="AU35" s="1" t="n">
+        <v>102.90329856</v>
+      </c>
+      <c r="AV35" s="1" t="n">
+        <v>102.29305761</v>
+      </c>
+      <c r="AW35" s="1" t="n">
+        <v>102.07702301</v>
+      </c>
+      <c r="AX35" s="1" t="n">
+        <v>101.58809226</v>
+      </c>
+      <c r="AY35" s="1" t="n">
+        <v>102.30943261</v>
+      </c>
+      <c r="AZ35" s="1" t="n">
+        <v>101.77079808</v>
       </c>
     </row>
   </sheetData>
@@ -4113,7 +9472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4122,7 +9481,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>各月欧元区居民消费价格涨跌率、失业率和进出口贸易 / 消费者价格涨跌率</t>
+          <t>各月日本居民消费价格涨跌率、失业率和进出口贸易 / 消费者价格涨跌率</t>
         </is>
       </c>
     </row>
@@ -4137,11 +9496,16 @@
           <t>2026-04</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>欧洲货币联盟</t>
+          <t>日本</t>
         </is>
       </c>
     </row>
@@ -4778,7 +10142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4787,7 +10151,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>各月美国居民消费价格涨跌率、失业率和进出口贸易 / 消费者价格涨跌率</t>
+          <t>各月欧元区居民消费价格涨跌率、失业率和进出口贸易 / 消费者价格涨跌率</t>
         </is>
       </c>
     </row>
@@ -4802,16 +10166,11 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>欧洲货币联盟</t>
         </is>
       </c>
     </row>
@@ -4835,7 +10194,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>各行业固定资产投资(不含农户) / 固定资产投资完成额</t>
+          <t>各月美国居民消费价格涨跌率、失业率和进出口贸易 / 消费者价格涨跌率</t>
         </is>
       </c>
     </row>
@@ -4859,7 +10218,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>美国</t>
         </is>
       </c>
     </row>
@@ -4874,7 +10233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4883,7 +10242,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>固定资产投资资金来源情况 / 固定资产投资_其他资金</t>
+          <t>各行业固定资产投资(不含农户) / 固定资产投资完成额</t>
         </is>
       </c>
     </row>
@@ -4901,11 +10260,6 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>2026-05</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -4936,7 +10290,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>固定资产投资（不含农户） / 房地产开发投资完成额</t>
+          <t>固定资产投资资金来源情况 / 固定资产投资_其他资金</t>
         </is>
       </c>
     </row>
@@ -4967,15 +10321,6 @@
         <is>
           <t>全国</t>
         </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>23969.4</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>30355.68</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>38073.7</v>
       </c>
     </row>
   </sheetData>
@@ -4998,7 +10343,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>工业主要产品产量及增长速度 / 产品产量_中厚宽钢带_工业</t>
+          <t>固定资产投资（不含农户） / 房地产开发投资完成额</t>
         </is>
       </c>
     </row>
@@ -5031,13 +10376,13 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1759.8</v>
+        <v>23969.4</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>1815.4</v>
+        <v>30355.68</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1911.3</v>
+        <v>38073.7</v>
       </c>
     </row>
   </sheetData>
@@ -5060,7 +10405,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>工业分大类行业增加值增长速度 / 工业增加值</t>
+          <t>工业主要产品产量及增长速度 / 产品产量_中厚宽钢带_工业</t>
         </is>
       </c>
     </row>
@@ -5091,6 +10436,15 @@
         <is>
           <t>全国</t>
         </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1759.8</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1815.4</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>1911.3</v>
       </c>
     </row>
   </sheetData>
@@ -5113,7 +10467,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>工业增加值增速 / 工业增加值</t>
+          <t>工业分大类行业增加值增长速度 / 工业增加值</t>
         </is>
       </c>
     </row>
@@ -5166,7 +10520,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>工业生产者购进价格指数 / 工业生产者购进价格指数_其他工业原材料及半成品类_工业_上年同月=100</t>
+          <t>工业增加值增速 / 工业增加值</t>
         </is>
       </c>
     </row>
@@ -5197,15 +10551,6 @@
         <is>
           <t>全国</t>
         </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>101.5</v>
       </c>
     </row>
   </sheetData>
@@ -5219,7 +10564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:BB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5228,7 +10573,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>房地产开发投资 / 房地产开发投资完成额</t>
+          <t>工业生产者购进价格指数 / 工业生产者购进价格指数_其他工业原材料及半成品类_工业_上年同月=100</t>
         </is>
       </c>
     </row>
@@ -5240,15 +10585,265 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -5261,13 +10856,163 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>23969.4</v>
+        <v>104.9</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>30355.68</v>
+        <v>103.8</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>38073.7</v>
+        <v>103.4</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AO4" s="1" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="AP4" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="AQ4" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="AR4" s="1" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="AS4" s="1" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="AV4" s="1" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="AX4" s="1" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="AZ4" s="1" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="BA4" s="1" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="BB4" s="1" t="n">
+        <v>101.5</v>
       </c>
     </row>
   </sheetData>
@@ -5290,7 +11035,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>按登记注册类型分的固定资产投资（不含农户）情况 / 固定资产投资</t>
+          <t>房地产开发投资 / 房地产开发投资完成额</t>
         </is>
       </c>
     </row>
@@ -5321,6 +11066,15 @@
         <is>
           <t>全国</t>
         </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>23969.4</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>30355.68</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>38073.7</v>
       </c>
     </row>
   </sheetData>
@@ -5405,7 +11159,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>社会消费品零售总额 / 社会消费品零售总额</t>
+          <t>按登记注册类型分的固定资产投资（不含农户）情况 / 固定资产投资</t>
         </is>
       </c>
     </row>
@@ -5436,15 +11190,6 @@
         <is>
           <t>全国</t>
         </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>37246.5</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>41090</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>42690.7</v>
       </c>
     </row>
   </sheetData>
@@ -5467,7 +11212,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>累计全国及36个大中城市居民消费价格分类指数(上年同期=100)(2016-) / 居民消费价格指数_上年同期=100_鲜瓜果</t>
+          <t>社会消费品零售总额 / 社会消费品零售总额</t>
         </is>
       </c>
     </row>
@@ -5500,13 +11245,13 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>103</v>
+        <v>37246.5</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>101.9</v>
+        <v>41090</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>101.5</v>
+        <v>42690.7</v>
       </c>
     </row>
   </sheetData>
@@ -5529,7 +11274,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>能源产品产量 / 能源生产量_原油</t>
+          <t>累计全国及36个大中城市居民消费价格分类指数(上年同期=100)(2016-) / 居民消费价格指数_上年同期=100_鲜瓜果</t>
         </is>
       </c>
     </row>
@@ -5562,13 +11307,13 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1794.3</v>
+        <v>103</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>1856.8</v>
+        <v>101.9</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1811.7</v>
+        <v>101.5</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +11336,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>邮电业务量完成情况 / 互联网宽带接入用户数</t>
+          <t>能源产品产量 / 能源生产量_原油</t>
         </is>
       </c>
     </row>
@@ -5624,13 +11369,13 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>69809.00999999999</v>
+        <v>1794.3</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>69943.3</v>
+        <v>1856.8</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>70105.60000000001</v>
+        <v>1811.7</v>
       </c>
     </row>
   </sheetData>
@@ -5653,6 +11398,68 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>邮电业务量完成情况 / 互联网宽带接入用户数</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>地区\期間</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>69809.00999999999</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>69943.3</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>70105.60000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>限额以上企业（单位）商品零售类值 / 社会消费品零售总额_中西药品类_限额以上</t>
         </is>
       </c>

--- a/output/china_dg_all.xlsx
+++ b/output/china_dg_all.xlsx
@@ -7549,7 +7549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW35"/>
+  <dimension ref="A1:BH35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7735,75 +7735,130 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>2013-02</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
           <t>2015-02</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>2015-03</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>2015-04</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2015-05</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>2015-09</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>2015-10</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2015-11</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>2015-12</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2018-12</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -8044,7 +8099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU35"/>
+  <dimension ref="A1:CF35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8230,195 +8285,250 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>2013-02</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
           <t>2015-02</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>2015-03</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>2015-04</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2015-05</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>2015-09</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>2015-10</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2015-11</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>2015-12</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2016-12</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>2017-09</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2017-10</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>2017-11</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>2017-12</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>2018-02</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>2018-03</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>2018-04</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>2018-05</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>2018-06</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2018-07</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>2018-08</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2019-10</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>2019-11</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2019-12</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>2020-08</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>2020-09</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>2020-10</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>2020-11</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>2020-12</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>2021-08</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>2021-09</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>2021-10</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>2021-11</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>2021-12</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -9099,7 +9209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:AN35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9225,75 +9335,90 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2011-11</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>2012-08</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2012-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>2012-11</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2012-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>2015-09</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>2015-10</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>2015-11</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>2015-12</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -9369,45 +9494,54 @@
         <v>109.9605</v>
       </c>
       <c r="W4" s="1" t="n">
+        <v>108.0376</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>105.055</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>103.4507</v>
+      </c>
+      <c r="Z4" s="1" t="n">
         <v>95.895</v>
       </c>
-      <c r="X4" s="1" t="n">
+      <c r="AA4" s="1" t="n">
         <v>95.9006</v>
       </c>
-      <c r="Y4" s="1" t="n">
+      <c r="AB4" s="1" t="n">
         <v>96.7187</v>
       </c>
-      <c r="Z4" s="1" t="n">
+      <c r="AC4" s="1" t="n">
         <v>97.2311</v>
       </c>
-      <c r="AA4" s="1" t="n">
+      <c r="AD4" s="1" t="n">
         <v>97.5808</v>
       </c>
-      <c r="AB4" s="1" t="n">
+      <c r="AE4" s="1" t="n">
         <v>94.4213</v>
       </c>
-      <c r="AC4" s="1" t="n">
+      <c r="AF4" s="1" t="n">
         <v>93.9346</v>
       </c>
-      <c r="AD4" s="1" t="n">
+      <c r="AG4" s="1" t="n">
         <v>93.39749999999999</v>
       </c>
-      <c r="AE4" s="1" t="n">
+      <c r="AH4" s="1" t="n">
         <v>93.1617</v>
       </c>
-      <c r="AF4" s="1" t="n">
+      <c r="AI4" s="1" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="AG4" s="1" t="n">
+      <c r="AJ4" s="1" t="n">
         <v>93.0989</v>
       </c>
-      <c r="AH4" s="1" t="n">
+      <c r="AK4" s="1" t="n">
         <v>93.17870000000001</v>
       </c>
-      <c r="AI4" s="1" t="n">
+      <c r="AL4" s="1" t="n">
         <v>103.5</v>
       </c>
-      <c r="AJ4" s="1" t="n">
+      <c r="AM4" s="1" t="n">
         <v>105.8</v>
       </c>
     </row>
@@ -9481,48 +9615,57 @@
         <v>109.6237</v>
       </c>
       <c r="W5" s="1" t="n">
+        <v>108.4165</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>105.7402</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>105.5978</v>
+      </c>
+      <c r="Z5" s="1" t="n">
         <v>95.7478</v>
       </c>
-      <c r="X5" s="1" t="n">
+      <c r="AA5" s="1" t="n">
         <v>96.4487</v>
       </c>
-      <c r="Y5" s="1" t="n">
+      <c r="AB5" s="1" t="n">
         <v>97.09869999999999</v>
       </c>
-      <c r="Z5" s="1" t="n">
+      <c r="AC5" s="1" t="n">
         <v>97.33750000000001</v>
       </c>
-      <c r="AA5" s="1" t="n">
+      <c r="AD5" s="1" t="n">
         <v>97.0891</v>
       </c>
-      <c r="AB5" s="1" t="n">
+      <c r="AE5" s="1" t="n">
         <v>94.1399</v>
       </c>
-      <c r="AC5" s="1" t="n">
+      <c r="AF5" s="1" t="n">
         <v>94.0789</v>
       </c>
-      <c r="AD5" s="1" t="n">
+      <c r="AG5" s="1" t="n">
         <v>93.57470000000001</v>
       </c>
-      <c r="AE5" s="1" t="n">
+      <c r="AH5" s="1" t="n">
         <v>93.1401</v>
       </c>
-      <c r="AF5" s="1" t="n">
+      <c r="AI5" s="1" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="AG5" s="1" t="n">
+      <c r="AJ5" s="1" t="n">
         <v>94.1309</v>
       </c>
-      <c r="AH5" s="1" t="n">
+      <c r="AK5" s="1" t="n">
         <v>94.4294</v>
       </c>
-      <c r="AI5" s="1" t="n">
+      <c r="AL5" s="1" t="n">
         <v>100.3</v>
       </c>
-      <c r="AJ5" s="1" t="n">
+      <c r="AM5" s="1" t="n">
         <v>101.6</v>
       </c>
-      <c r="AK5" s="1" t="n">
+      <c r="AN5" s="1" t="n">
         <v>101.6</v>
       </c>
     </row>
@@ -9596,48 +9739,57 @@
         <v>109.6978</v>
       </c>
       <c r="W6" s="1" t="n">
+        <v>106.6899</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>102.4904</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>101.1261</v>
+      </c>
+      <c r="Z6" s="1" t="n">
         <v>95.1336</v>
       </c>
-      <c r="X6" s="1" t="n">
+      <c r="AA6" s="1" t="n">
         <v>95.7221</v>
       </c>
-      <c r="Y6" s="1" t="n">
+      <c r="AB6" s="1" t="n">
         <v>97.04340000000001</v>
       </c>
-      <c r="Z6" s="1" t="n">
+      <c r="AC6" s="1" t="n">
         <v>98.175</v>
       </c>
-      <c r="AA6" s="1" t="n">
+      <c r="AD6" s="1" t="n">
         <v>98.2045</v>
       </c>
-      <c r="AB6" s="1" t="n">
+      <c r="AE6" s="1" t="n">
         <v>92.8703</v>
       </c>
-      <c r="AC6" s="1" t="n">
+      <c r="AF6" s="1" t="n">
         <v>92.1768</v>
       </c>
-      <c r="AD6" s="1" t="n">
+      <c r="AG6" s="1" t="n">
         <v>91.7572</v>
       </c>
-      <c r="AE6" s="1" t="n">
+      <c r="AH6" s="1" t="n">
         <v>91.5842</v>
       </c>
-      <c r="AF6" s="1" t="n">
+      <c r="AI6" s="1" t="n">
         <v>91.5</v>
       </c>
-      <c r="AG6" s="1" t="n">
+      <c r="AJ6" s="1" t="n">
         <v>91.82340000000001</v>
       </c>
-      <c r="AH6" s="1" t="n">
+      <c r="AK6" s="1" t="n">
         <v>91.6724</v>
       </c>
-      <c r="AI6" s="1" t="n">
+      <c r="AL6" s="1" t="n">
         <v>103.3</v>
       </c>
-      <c r="AJ6" s="1" t="n">
+      <c r="AM6" s="1" t="n">
         <v>107.4</v>
       </c>
-      <c r="AK6" s="1" t="n">
+      <c r="AN6" s="1" t="n">
         <v>108.1</v>
       </c>
     </row>
@@ -9711,48 +9863,57 @@
         <v>111.6302</v>
       </c>
       <c r="W7" s="1" t="n">
+        <v>109.6921</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>104.7023</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>103.3457</v>
+      </c>
+      <c r="Z7" s="1" t="n">
         <v>93.2577</v>
       </c>
-      <c r="X7" s="1" t="n">
+      <c r="AA7" s="1" t="n">
         <v>92.4097</v>
       </c>
-      <c r="Y7" s="1" t="n">
+      <c r="AB7" s="1" t="n">
         <v>93.37520000000001</v>
       </c>
-      <c r="Z7" s="1" t="n">
+      <c r="AC7" s="1" t="n">
         <v>95.2028</v>
       </c>
-      <c r="AA7" s="1" t="n">
+      <c r="AD7" s="1" t="n">
         <v>95.3318</v>
       </c>
-      <c r="AB7" s="1" t="n">
+      <c r="AE7" s="1" t="n">
         <v>90.8074</v>
       </c>
-      <c r="AC7" s="1" t="n">
+      <c r="AF7" s="1" t="n">
         <v>90.4427</v>
       </c>
-      <c r="AD7" s="1" t="n">
+      <c r="AG7" s="1" t="n">
         <v>90.02500000000001</v>
       </c>
-      <c r="AE7" s="1" t="n">
+      <c r="AH7" s="1" t="n">
         <v>89.97029999999998</v>
       </c>
-      <c r="AF7" s="1" t="n">
+      <c r="AI7" s="1" t="n">
         <v>89.79999999999998</v>
       </c>
-      <c r="AG7" s="1" t="n">
+      <c r="AJ7" s="1" t="n">
         <v>89.71469999999998</v>
       </c>
-      <c r="AH7" s="1" t="n">
+      <c r="AK7" s="1" t="n">
         <v>89.83159999999998</v>
       </c>
-      <c r="AI7" s="1" t="n">
+      <c r="AL7" s="1" t="n">
         <v>101.7</v>
       </c>
-      <c r="AJ7" s="1" t="n">
+      <c r="AM7" s="1" t="n">
         <v>106.2</v>
       </c>
-      <c r="AK7" s="1" t="n">
+      <c r="AN7" s="1" t="n">
         <v>107.3</v>
       </c>
     </row>
@@ -9826,48 +9987,57 @@
         <v>108.5576</v>
       </c>
       <c r="W8" s="1" t="n">
+        <v>107.6014</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>104.0548</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>102.916</v>
+      </c>
+      <c r="Z8" s="1" t="n">
         <v>96.1504</v>
       </c>
-      <c r="X8" s="1" t="n">
+      <c r="AA8" s="1" t="n">
         <v>94.7415</v>
       </c>
-      <c r="Y8" s="1" t="n">
+      <c r="AB8" s="1" t="n">
         <v>94.4943</v>
       </c>
-      <c r="Z8" s="1" t="n">
+      <c r="AC8" s="1" t="n">
         <v>95.6065</v>
       </c>
-      <c r="AA8" s="1" t="n">
+      <c r="AD8" s="1" t="n">
         <v>95.79000000000001</v>
       </c>
-      <c r="AB8" s="1" t="n">
+      <c r="AE8" s="1" t="n">
         <v>93.6027</v>
       </c>
-      <c r="AC8" s="1" t="n">
+      <c r="AF8" s="1" t="n">
         <v>92.9791</v>
       </c>
-      <c r="AD8" s="1" t="n">
+      <c r="AG8" s="1" t="n">
         <v>92.892</v>
       </c>
-      <c r="AE8" s="1" t="n">
+      <c r="AH8" s="1" t="n">
         <v>92.61</v>
       </c>
-      <c r="AF8" s="1" t="n">
+      <c r="AI8" s="1" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="AG8" s="1" t="n">
+      <c r="AJ8" s="1" t="n">
         <v>91.65049999999999</v>
       </c>
-      <c r="AH8" s="1" t="n">
+      <c r="AK8" s="1" t="n">
         <v>90.8592</v>
       </c>
-      <c r="AI8" s="1" t="n">
+      <c r="AL8" s="1" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="AJ8" s="1" t="n">
+      <c r="AM8" s="1" t="n">
         <v>102.3</v>
       </c>
-      <c r="AK8" s="1" t="n">
+      <c r="AN8" s="1" t="n">
         <v>106</v>
       </c>
     </row>
@@ -9941,48 +10111,57 @@
         <v>107.0009</v>
       </c>
       <c r="W9" s="1" t="n">
+        <v>106.4031</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>105.7939</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>105.5579</v>
+      </c>
+      <c r="Z9" s="1" t="n">
         <v>100.4787</v>
       </c>
-      <c r="X9" s="1" t="n">
+      <c r="AA9" s="1" t="n">
         <v>99.6927</v>
       </c>
-      <c r="Y9" s="1" t="n">
+      <c r="AB9" s="1" t="n">
         <v>99.943</v>
       </c>
-      <c r="Z9" s="1" t="n">
+      <c r="AC9" s="1" t="n">
         <v>99.55549999999999</v>
       </c>
-      <c r="AA9" s="1" t="n">
+      <c r="AD9" s="1" t="n">
         <v>99.4258</v>
       </c>
-      <c r="AB9" s="1" t="n">
+      <c r="AE9" s="1" t="n">
         <v>95.968</v>
       </c>
-      <c r="AC9" s="1" t="n">
+      <c r="AF9" s="1" t="n">
         <v>96.13209999999999</v>
       </c>
-      <c r="AD9" s="1" t="n">
+      <c r="AG9" s="1" t="n">
         <v>95.7822</v>
       </c>
-      <c r="AE9" s="1" t="n">
+      <c r="AH9" s="1" t="n">
         <v>95.8147</v>
       </c>
-      <c r="AF9" s="1" t="n">
+      <c r="AI9" s="1" t="n">
         <v>95.7</v>
       </c>
-      <c r="AG9" s="1" t="n">
+      <c r="AJ9" s="1" t="n">
         <v>95.37949999999999</v>
       </c>
-      <c r="AH9" s="1" t="n">
+      <c r="AK9" s="1" t="n">
         <v>94.798</v>
       </c>
-      <c r="AI9" s="1" t="n">
+      <c r="AL9" s="1" t="n">
         <v>100.2</v>
       </c>
-      <c r="AJ9" s="1" t="n">
+      <c r="AM9" s="1" t="n">
         <v>103.9</v>
       </c>
-      <c r="AK9" s="1" t="n">
+      <c r="AN9" s="1" t="n">
         <v>106.2</v>
       </c>
     </row>
@@ -10056,48 +10235,57 @@
         <v>109.0572</v>
       </c>
       <c r="W10" s="1" t="n">
+        <v>107.4347</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>104.5153</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>102.8651</v>
+      </c>
+      <c r="Z10" s="1" t="n">
         <v>97.0311</v>
       </c>
-      <c r="X10" s="1" t="n">
+      <c r="AA10" s="1" t="n">
         <v>97.3227</v>
       </c>
-      <c r="Y10" s="1" t="n">
+      <c r="AB10" s="1" t="n">
         <v>98.06870000000001</v>
       </c>
-      <c r="Z10" s="1" t="n">
+      <c r="AC10" s="1" t="n">
         <v>98.42619999999999</v>
       </c>
-      <c r="AA10" s="1" t="n">
+      <c r="AD10" s="1" t="n">
         <v>98.8326</v>
       </c>
-      <c r="AB10" s="1" t="n">
+      <c r="AE10" s="1" t="n">
         <v>93.8339</v>
       </c>
-      <c r="AC10" s="1" t="n">
+      <c r="AF10" s="1" t="n">
         <v>93.3053</v>
       </c>
-      <c r="AD10" s="1" t="n">
+      <c r="AG10" s="1" t="n">
         <v>92.8353</v>
       </c>
-      <c r="AE10" s="1" t="n">
+      <c r="AH10" s="1" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="AF10" s="1" t="n">
+      <c r="AI10" s="1" t="n">
         <v>92.5</v>
       </c>
-      <c r="AG10" s="1" t="n">
+      <c r="AJ10" s="1" t="n">
         <v>92.7893</v>
       </c>
-      <c r="AH10" s="1" t="n">
+      <c r="AK10" s="1" t="n">
         <v>93.1764</v>
       </c>
-      <c r="AI10" s="1" t="n">
+      <c r="AL10" s="1" t="n">
         <v>102.8</v>
       </c>
-      <c r="AJ10" s="1" t="n">
+      <c r="AM10" s="1" t="n">
         <v>105.4</v>
       </c>
-      <c r="AK10" s="1" t="n">
+      <c r="AN10" s="1" t="n">
         <v>105.6</v>
       </c>
     </row>
@@ -10171,48 +10359,57 @@
         <v>107.1422</v>
       </c>
       <c r="W11" s="1" t="n">
+        <v>106.6074</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>104.8814</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>103.3049</v>
+      </c>
+      <c r="Z11" s="1" t="n">
         <v>97.1311</v>
       </c>
-      <c r="X11" s="1" t="n">
+      <c r="AA11" s="1" t="n">
         <v>97.5694</v>
       </c>
-      <c r="Y11" s="1" t="n">
+      <c r="AB11" s="1" t="n">
         <v>97.78919999999999</v>
       </c>
-      <c r="Z11" s="1" t="n">
+      <c r="AC11" s="1" t="n">
         <v>98.1506</v>
       </c>
-      <c r="AA11" s="1" t="n">
+      <c r="AD11" s="1" t="n">
         <v>98.97150000000001</v>
       </c>
-      <c r="AB11" s="1" t="n">
+      <c r="AE11" s="1" t="n">
         <v>97.00069999999999</v>
       </c>
-      <c r="AC11" s="1" t="n">
+      <c r="AF11" s="1" t="n">
         <v>96.636</v>
       </c>
-      <c r="AD11" s="1" t="n">
+      <c r="AG11" s="1" t="n">
         <v>96.2443</v>
       </c>
-      <c r="AE11" s="1" t="n">
+      <c r="AH11" s="1" t="n">
         <v>96.4837</v>
       </c>
-      <c r="AF11" s="1" t="n">
+      <c r="AI11" s="1" t="n">
         <v>96.2</v>
       </c>
-      <c r="AG11" s="1" t="n">
+      <c r="AJ11" s="1" t="n">
         <v>96.93819999999999</v>
       </c>
-      <c r="AH11" s="1" t="n">
+      <c r="AK11" s="1" t="n">
         <v>97.2213</v>
       </c>
-      <c r="AI11" s="1" t="n">
+      <c r="AL11" s="1" t="n">
         <v>99.5</v>
       </c>
-      <c r="AJ11" s="1" t="n">
+      <c r="AM11" s="1" t="n">
         <v>100.1</v>
       </c>
-      <c r="AK11" s="1" t="n">
+      <c r="AN11" s="1" t="n">
         <v>100.6</v>
       </c>
     </row>
@@ -10286,48 +10483,57 @@
         <v>113.0026</v>
       </c>
       <c r="W12" s="1" t="n">
+        <v>111.3761</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>108.0234</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>107.634</v>
+      </c>
+      <c r="Z12" s="1" t="n">
         <v>94.3297</v>
       </c>
-      <c r="X12" s="1" t="n">
+      <c r="AA12" s="1" t="n">
         <v>96.121</v>
       </c>
-      <c r="Y12" s="1" t="n">
+      <c r="AB12" s="1" t="n">
         <v>97.0506</v>
       </c>
-      <c r="Z12" s="1" t="n">
+      <c r="AC12" s="1" t="n">
         <v>98.5847</v>
       </c>
-      <c r="AA12" s="1" t="n">
+      <c r="AD12" s="1" t="n">
         <v>97.8419</v>
       </c>
-      <c r="AB12" s="1" t="n">
+      <c r="AE12" s="1" t="n">
         <v>88.58920000000001</v>
       </c>
-      <c r="AC12" s="1" t="n">
+      <c r="AF12" s="1" t="n">
         <v>87.97029999999998</v>
       </c>
-      <c r="AD12" s="1" t="n">
+      <c r="AG12" s="1" t="n">
         <v>87.48739999999998</v>
       </c>
-      <c r="AE12" s="1" t="n">
+      <c r="AH12" s="1" t="n">
         <v>88.0997</v>
       </c>
-      <c r="AF12" s="1" t="n">
+      <c r="AI12" s="1" t="n">
         <v>88.29999999999998</v>
       </c>
-      <c r="AG12" s="1" t="n">
+      <c r="AJ12" s="1" t="n">
         <v>89.81539999999998</v>
       </c>
-      <c r="AH12" s="1" t="n">
+      <c r="AK12" s="1" t="n">
         <v>90.572</v>
       </c>
-      <c r="AI12" s="1" t="n">
+      <c r="AL12" s="1" t="n">
         <v>102.6</v>
       </c>
-      <c r="AJ12" s="1" t="n">
+      <c r="AM12" s="1" t="n">
         <v>103.7</v>
       </c>
-      <c r="AK12" s="1" t="n">
+      <c r="AN12" s="1" t="n">
         <v>102.7</v>
       </c>
     </row>
@@ -10401,48 +10607,57 @@
         <v>107.8882</v>
       </c>
       <c r="W13" s="1" t="n">
+        <v>104.7017</v>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>102.7707</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>100.7571</v>
+      </c>
+      <c r="Z13" s="1" t="n">
         <v>91.7657</v>
       </c>
-      <c r="X13" s="1" t="n">
+      <c r="AA13" s="1" t="n">
         <v>92.39660000000001</v>
       </c>
-      <c r="Y13" s="1" t="n">
+      <c r="AB13" s="1" t="n">
         <v>94.54040000000001</v>
       </c>
-      <c r="Z13" s="1" t="n">
+      <c r="AC13" s="1" t="n">
         <v>94.5243</v>
       </c>
-      <c r="AA13" s="1" t="n">
+      <c r="AD13" s="1" t="n">
         <v>95.5527</v>
       </c>
-      <c r="AB13" s="1" t="n">
+      <c r="AE13" s="1" t="n">
         <v>91.474</v>
       </c>
-      <c r="AC13" s="1" t="n">
+      <c r="AF13" s="1" t="n">
         <v>90.254</v>
       </c>
-      <c r="AD13" s="1" t="n">
+      <c r="AG13" s="1" t="n">
         <v>89.62730000000001</v>
       </c>
-      <c r="AE13" s="1" t="n">
+      <c r="AH13" s="1" t="n">
         <v>90.2346</v>
       </c>
-      <c r="AF13" s="1" t="n">
+      <c r="AI13" s="1" t="n">
         <v>90.7</v>
       </c>
-      <c r="AG13" s="1" t="n">
+      <c r="AJ13" s="1" t="n">
         <v>90.32729999999999</v>
       </c>
-      <c r="AH13" s="1" t="n">
+      <c r="AK13" s="1" t="n">
         <v>90.18300000000001</v>
       </c>
-      <c r="AI13" s="1" t="n">
+      <c r="AL13" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="AJ13" s="1" t="n">
+      <c r="AM13" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="AK13" s="1" t="n">
+      <c r="AN13" s="1" t="n">
         <v>105.3</v>
       </c>
     </row>
@@ -10516,48 +10731,57 @@
         <v>109.32</v>
       </c>
       <c r="W14" s="1" t="n">
+        <v>107.1946</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>103.5296</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>101.3451</v>
+      </c>
+      <c r="Z14" s="1" t="n">
         <v>93.2919</v>
       </c>
-      <c r="X14" s="1" t="n">
+      <c r="AA14" s="1" t="n">
         <v>93.54340000000001</v>
       </c>
-      <c r="Y14" s="1" t="n">
+      <c r="AB14" s="1" t="n">
         <v>94.6455</v>
       </c>
-      <c r="Z14" s="1" t="n">
+      <c r="AC14" s="1" t="n">
         <v>95.3199</v>
       </c>
-      <c r="AA14" s="1" t="n">
+      <c r="AD14" s="1" t="n">
         <v>95.9359</v>
       </c>
-      <c r="AB14" s="1" t="n">
+      <c r="AE14" s="1" t="n">
         <v>92.6485</v>
       </c>
-      <c r="AC14" s="1" t="n">
+      <c r="AF14" s="1" t="n">
         <v>92.1053</v>
       </c>
-      <c r="AD14" s="1" t="n">
+      <c r="AG14" s="1" t="n">
         <v>91.45059999999999</v>
       </c>
-      <c r="AE14" s="1" t="n">
+      <c r="AH14" s="1" t="n">
         <v>91.1425</v>
       </c>
-      <c r="AF14" s="1" t="n">
+      <c r="AI14" s="1" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="AG14" s="1" t="n">
+      <c r="AJ14" s="1" t="n">
         <v>91.3802</v>
       </c>
-      <c r="AH14" s="1" t="n">
+      <c r="AK14" s="1" t="n">
         <v>91.52160000000001</v>
       </c>
-      <c r="AI14" s="1" t="n">
+      <c r="AL14" s="1" t="n">
         <v>102.1</v>
       </c>
-      <c r="AJ14" s="1" t="n">
+      <c r="AM14" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="AK14" s="1" t="n">
+      <c r="AN14" s="1" t="n">
         <v>105.4</v>
       </c>
     </row>
@@ -10631,48 +10855,57 @@
         <v>108.7379</v>
       </c>
       <c r="W15" s="1" t="n">
+        <v>106.5994</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>103.5456</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>101.6397</v>
+      </c>
+      <c r="Z15" s="1" t="n">
         <v>94.6071</v>
       </c>
-      <c r="X15" s="1" t="n">
+      <c r="AA15" s="1" t="n">
         <v>94.89239999999999</v>
       </c>
-      <c r="Y15" s="1" t="n">
+      <c r="AB15" s="1" t="n">
         <v>95.9153</v>
       </c>
-      <c r="Z15" s="1" t="n">
+      <c r="AC15" s="1" t="n">
         <v>96.2863</v>
       </c>
-      <c r="AA15" s="1" t="n">
+      <c r="AD15" s="1" t="n">
         <v>97.1592</v>
       </c>
-      <c r="AB15" s="1" t="n">
+      <c r="AE15" s="1" t="n">
         <v>95.2281</v>
       </c>
-      <c r="AC15" s="1" t="n">
+      <c r="AF15" s="1" t="n">
         <v>94.4571</v>
       </c>
-      <c r="AD15" s="1" t="n">
+      <c r="AG15" s="1" t="n">
         <v>93.6858</v>
       </c>
-      <c r="AE15" s="1" t="n">
+      <c r="AH15" s="1" t="n">
         <v>93.24550000000001</v>
       </c>
-      <c r="AF15" s="1" t="n">
+      <c r="AI15" s="1" t="n">
         <v>93.3</v>
       </c>
-      <c r="AG15" s="1" t="n">
+      <c r="AJ15" s="1" t="n">
         <v>93.19670000000001</v>
       </c>
-      <c r="AH15" s="1" t="n">
+      <c r="AK15" s="1" t="n">
         <v>93.10769999999999</v>
       </c>
-      <c r="AI15" s="1" t="n">
+      <c r="AL15" s="1" t="n">
         <v>103.9</v>
       </c>
-      <c r="AJ15" s="1" t="n">
+      <c r="AM15" s="1" t="n">
         <v>107.2</v>
       </c>
-      <c r="AK15" s="1" t="n">
+      <c r="AN15" s="1" t="n">
         <v>107.2</v>
       </c>
     </row>
@@ -10746,48 +10979,57 @@
         <v>111.4121</v>
       </c>
       <c r="W16" s="1" t="n">
+        <v>108.7995</v>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>105.4513</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>103.3631</v>
+      </c>
+      <c r="Z16" s="1" t="n">
         <v>95.7565</v>
       </c>
-      <c r="X16" s="1" t="n">
+      <c r="AA16" s="1" t="n">
         <v>95.8514</v>
       </c>
-      <c r="Y16" s="1" t="n">
+      <c r="AB16" s="1" t="n">
         <v>96.79049999999999</v>
       </c>
-      <c r="Z16" s="1" t="n">
+      <c r="AC16" s="1" t="n">
         <v>97.20010000000001</v>
       </c>
-      <c r="AA16" s="1" t="n">
+      <c r="AD16" s="1" t="n">
         <v>97.51130000000001</v>
       </c>
-      <c r="AB16" s="1" t="n">
+      <c r="AE16" s="1" t="n">
         <v>93.74550000000001</v>
       </c>
-      <c r="AC16" s="1" t="n">
+      <c r="AF16" s="1" t="n">
         <v>93.4121</v>
       </c>
-      <c r="AD16" s="1" t="n">
+      <c r="AG16" s="1" t="n">
         <v>92.884</v>
       </c>
-      <c r="AE16" s="1" t="n">
+      <c r="AH16" s="1" t="n">
         <v>93.012</v>
       </c>
-      <c r="AF16" s="1" t="n">
+      <c r="AI16" s="1" t="n">
         <v>92.8</v>
       </c>
-      <c r="AG16" s="1" t="n">
+      <c r="AJ16" s="1" t="n">
         <v>92.2383</v>
       </c>
-      <c r="AH16" s="1" t="n">
+      <c r="AK16" s="1" t="n">
         <v>92.43389999999999</v>
       </c>
-      <c r="AI16" s="1" t="n">
+      <c r="AL16" s="1" t="n">
         <v>103.1</v>
       </c>
-      <c r="AJ16" s="1" t="n">
+      <c r="AM16" s="1" t="n">
         <v>105.1</v>
       </c>
-      <c r="AK16" s="1" t="n">
+      <c r="AN16" s="1" t="n">
         <v>106</v>
       </c>
     </row>
@@ -10861,48 +11103,57 @@
         <v>109.0472</v>
       </c>
       <c r="W17" s="1" t="n">
+        <v>107.1492</v>
+      </c>
+      <c r="X17" s="1" t="n">
+        <v>103.4657</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>101.8832</v>
+      </c>
+      <c r="Z17" s="1" t="n">
         <v>96.0996</v>
       </c>
-      <c r="X17" s="1" t="n">
+      <c r="AA17" s="1" t="n">
         <v>95.56610000000001</v>
       </c>
-      <c r="Y17" s="1" t="n">
+      <c r="AB17" s="1" t="n">
         <v>96.04859999999999</v>
       </c>
-      <c r="Z17" s="1" t="n">
+      <c r="AC17" s="1" t="n">
         <v>97.176</v>
       </c>
-      <c r="AA17" s="1" t="n">
+      <c r="AD17" s="1" t="n">
         <v>97.8712</v>
       </c>
-      <c r="AB17" s="1" t="n">
+      <c r="AE17" s="1" t="n">
         <v>96.4194</v>
       </c>
-      <c r="AC17" s="1" t="n">
+      <c r="AF17" s="1" t="n">
         <v>96.02160000000001</v>
       </c>
-      <c r="AD17" s="1" t="n">
+      <c r="AG17" s="1" t="n">
         <v>95.5977</v>
       </c>
-      <c r="AE17" s="1" t="n">
+      <c r="AH17" s="1" t="n">
         <v>95.58799999999999</v>
       </c>
-      <c r="AF17" s="1" t="n">
+      <c r="AI17" s="1" t="n">
         <v>95.7</v>
       </c>
-      <c r="AG17" s="1" t="n">
+      <c r="AJ17" s="1" t="n">
         <v>95.5814</v>
       </c>
-      <c r="AH17" s="1" t="n">
+      <c r="AK17" s="1" t="n">
         <v>95.7021</v>
       </c>
-      <c r="AI17" s="1" t="n">
+      <c r="AL17" s="1" t="n">
         <v>103.3</v>
       </c>
-      <c r="AJ17" s="1" t="n">
+      <c r="AM17" s="1" t="n">
         <v>105.9</v>
       </c>
-      <c r="AK17" s="1" t="n">
+      <c r="AN17" s="1" t="n">
         <v>106.8</v>
       </c>
     </row>
@@ -10976,48 +11227,57 @@
         <v>113.9991</v>
       </c>
       <c r="W18" s="1" t="n">
+        <v>111.568</v>
+      </c>
+      <c r="X18" s="1" t="n">
+        <v>107.6035</v>
+      </c>
+      <c r="Y18" s="1" t="n">
+        <v>105.1016</v>
+      </c>
+      <c r="Z18" s="1" t="n">
         <v>94.7593</v>
       </c>
-      <c r="X18" s="1" t="n">
+      <c r="AA18" s="1" t="n">
         <v>95.5825</v>
       </c>
-      <c r="Y18" s="1" t="n">
+      <c r="AB18" s="1" t="n">
         <v>96.4965</v>
       </c>
-      <c r="Z18" s="1" t="n">
+      <c r="AC18" s="1" t="n">
         <v>97.30719999999999</v>
       </c>
-      <c r="AA18" s="1" t="n">
+      <c r="AD18" s="1" t="n">
         <v>98.2081</v>
       </c>
-      <c r="AB18" s="1" t="n">
+      <c r="AE18" s="1" t="n">
         <v>94.2235</v>
       </c>
-      <c r="AC18" s="1" t="n">
+      <c r="AF18" s="1" t="n">
         <v>93.50700000000001</v>
       </c>
-      <c r="AD18" s="1" t="n">
+      <c r="AG18" s="1" t="n">
         <v>92.8652</v>
       </c>
-      <c r="AE18" s="1" t="n">
+      <c r="AH18" s="1" t="n">
         <v>92.89100000000001</v>
       </c>
-      <c r="AF18" s="1" t="n">
+      <c r="AI18" s="1" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="AG18" s="1" t="n">
+      <c r="AJ18" s="1" t="n">
         <v>93.01600000000001</v>
       </c>
-      <c r="AH18" s="1" t="n">
+      <c r="AK18" s="1" t="n">
         <v>93.129</v>
       </c>
-      <c r="AI18" s="1" t="n">
+      <c r="AL18" s="1" t="n">
         <v>111.8</v>
       </c>
-      <c r="AJ18" s="1" t="n">
+      <c r="AM18" s="1" t="n">
         <v>113.4</v>
       </c>
-      <c r="AK18" s="1" t="n">
+      <c r="AN18" s="1" t="n">
         <v>115.2</v>
       </c>
     </row>
@@ -11091,48 +11351,57 @@
         <v>109.9337</v>
       </c>
       <c r="W19" s="1" t="n">
+        <v>108.1749</v>
+      </c>
+      <c r="X19" s="1" t="n">
+        <v>105.3771</v>
+      </c>
+      <c r="Y19" s="1" t="n">
+        <v>104.3991</v>
+      </c>
+      <c r="Z19" s="1" t="n">
         <v>97.2246</v>
       </c>
-      <c r="X19" s="1" t="n">
+      <c r="AA19" s="1" t="n">
         <v>97.1343</v>
       </c>
-      <c r="Y19" s="1" t="n">
+      <c r="AB19" s="1" t="n">
         <v>97.596</v>
       </c>
-      <c r="Z19" s="1" t="n">
+      <c r="AC19" s="1" t="n">
         <v>97.88</v>
       </c>
-      <c r="AA19" s="1" t="n">
+      <c r="AD19" s="1" t="n">
         <v>97.7009</v>
       </c>
-      <c r="AB19" s="1" t="n">
+      <c r="AE19" s="1" t="n">
         <v>95.72369999999999</v>
       </c>
-      <c r="AC19" s="1" t="n">
+      <c r="AF19" s="1" t="n">
         <v>95.2818</v>
       </c>
-      <c r="AD19" s="1" t="n">
+      <c r="AG19" s="1" t="n">
         <v>94.6818</v>
       </c>
-      <c r="AE19" s="1" t="n">
+      <c r="AH19" s="1" t="n">
         <v>94.2189</v>
       </c>
-      <c r="AF19" s="1" t="n">
+      <c r="AI19" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="AG19" s="1" t="n">
+      <c r="AJ19" s="1" t="n">
         <v>94.0157</v>
       </c>
-      <c r="AH19" s="1" t="n">
+      <c r="AK19" s="1" t="n">
         <v>93.86799999999999</v>
       </c>
-      <c r="AI19" s="1" t="n">
+      <c r="AL19" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="AJ19" s="1" t="n">
+      <c r="AM19" s="1" t="n">
         <v>107.1</v>
       </c>
-      <c r="AK19" s="1" t="n">
+      <c r="AN19" s="1" t="n">
         <v>106.6</v>
       </c>
     </row>
@@ -11206,48 +11475,57 @@
         <v>110.9443</v>
       </c>
       <c r="W20" s="1" t="n">
+        <v>108.049</v>
+      </c>
+      <c r="X20" s="1" t="n">
+        <v>105.1485</v>
+      </c>
+      <c r="Y20" s="1" t="n">
+        <v>103.9977</v>
+      </c>
+      <c r="Z20" s="1" t="n">
         <v>96.6951</v>
       </c>
-      <c r="X20" s="1" t="n">
+      <c r="AA20" s="1" t="n">
         <v>96.8884</v>
       </c>
-      <c r="Y20" s="1" t="n">
+      <c r="AB20" s="1" t="n">
         <v>97.9221</v>
       </c>
-      <c r="Z20" s="1" t="n">
+      <c r="AC20" s="1" t="n">
         <v>98.2188</v>
       </c>
-      <c r="AA20" s="1" t="n">
+      <c r="AD20" s="1" t="n">
         <v>98.66370000000001</v>
       </c>
-      <c r="AB20" s="1" t="n">
+      <c r="AE20" s="1" t="n">
         <v>95.80800000000001</v>
       </c>
-      <c r="AC20" s="1" t="n">
+      <c r="AF20" s="1" t="n">
         <v>95.6275</v>
       </c>
-      <c r="AD20" s="1" t="n">
+      <c r="AG20" s="1" t="n">
         <v>94.92400000000001</v>
       </c>
-      <c r="AE20" s="1" t="n">
+      <c r="AH20" s="1" t="n">
         <v>94.5376</v>
       </c>
-      <c r="AF20" s="1" t="n">
+      <c r="AI20" s="1" t="n">
         <v>94.5</v>
       </c>
-      <c r="AG20" s="1" t="n">
+      <c r="AJ20" s="1" t="n">
         <v>94.3563</v>
       </c>
-      <c r="AH20" s="1" t="n">
+      <c r="AK20" s="1" t="n">
         <v>94.2916</v>
       </c>
-      <c r="AI20" s="1" t="n">
+      <c r="AL20" s="1" t="n">
         <v>103.8</v>
       </c>
-      <c r="AJ20" s="1" t="n">
+      <c r="AM20" s="1" t="n">
         <v>105.3</v>
       </c>
-      <c r="AK20" s="1" t="n">
+      <c r="AN20" s="1" t="n">
         <v>106.2</v>
       </c>
     </row>
@@ -11321,48 +11599,57 @@
         <v>111.8008</v>
       </c>
       <c r="W21" s="1" t="n">
+        <v>110.6425</v>
+      </c>
+      <c r="X21" s="1" t="n">
+        <v>108.2575</v>
+      </c>
+      <c r="Y21" s="1" t="n">
+        <v>106.5877</v>
+      </c>
+      <c r="Z21" s="1" t="n">
         <v>96.12009999999999</v>
       </c>
-      <c r="X21" s="1" t="n">
+      <c r="AA21" s="1" t="n">
         <v>95.90940000000001</v>
       </c>
-      <c r="Y21" s="1" t="n">
+      <c r="AB21" s="1" t="n">
         <v>96.2012</v>
       </c>
-      <c r="Z21" s="1" t="n">
+      <c r="AC21" s="1" t="n">
         <v>97.0098</v>
       </c>
-      <c r="AA21" s="1" t="n">
+      <c r="AD21" s="1" t="n">
         <v>97.7881</v>
       </c>
-      <c r="AB21" s="1" t="n">
+      <c r="AE21" s="1" t="n">
         <v>94.07769999999999</v>
       </c>
-      <c r="AC21" s="1" t="n">
+      <c r="AF21" s="1" t="n">
         <v>93.3433</v>
       </c>
-      <c r="AD21" s="1" t="n">
+      <c r="AG21" s="1" t="n">
         <v>92.3984</v>
       </c>
-      <c r="AE21" s="1" t="n">
+      <c r="AH21" s="1" t="n">
         <v>91.262</v>
       </c>
-      <c r="AF21" s="1" t="n">
+      <c r="AI21" s="1" t="n">
         <v>91.3</v>
       </c>
-      <c r="AG21" s="1" t="n">
+      <c r="AJ21" s="1" t="n">
         <v>91.3249</v>
       </c>
-      <c r="AH21" s="1" t="n">
+      <c r="AK21" s="1" t="n">
         <v>91.42140000000001</v>
       </c>
-      <c r="AI21" s="1" t="n">
+      <c r="AL21" s="1" t="n">
         <v>102.6</v>
       </c>
-      <c r="AJ21" s="1" t="n">
+      <c r="AM21" s="1" t="n">
         <v>103.5</v>
       </c>
-      <c r="AK21" s="1" t="n">
+      <c r="AN21" s="1" t="n">
         <v>104.2</v>
       </c>
     </row>
@@ -11436,48 +11723,57 @@
         <v>112.5154</v>
       </c>
       <c r="W22" s="1" t="n">
+        <v>109.6958</v>
+      </c>
+      <c r="X22" s="1" t="n">
+        <v>105.7879</v>
+      </c>
+      <c r="Y22" s="1" t="n">
+        <v>104.1597</v>
+      </c>
+      <c r="Z22" s="1" t="n">
         <v>97.9502</v>
       </c>
-      <c r="X22" s="1" t="n">
+      <c r="AA22" s="1" t="n">
         <v>98.0107</v>
       </c>
-      <c r="Y22" s="1" t="n">
+      <c r="AB22" s="1" t="n">
         <v>98.9451</v>
       </c>
-      <c r="Z22" s="1" t="n">
+      <c r="AC22" s="1" t="n">
         <v>100.1616</v>
       </c>
-      <c r="AA22" s="1" t="n">
+      <c r="AD22" s="1" t="n">
         <v>99.7717</v>
       </c>
-      <c r="AB22" s="1" t="n">
+      <c r="AE22" s="1" t="n">
         <v>95.32559999999999</v>
       </c>
-      <c r="AC22" s="1" t="n">
+      <c r="AF22" s="1" t="n">
         <v>94.8138</v>
       </c>
-      <c r="AD22" s="1" t="n">
+      <c r="AG22" s="1" t="n">
         <v>94.06440000000001</v>
       </c>
-      <c r="AE22" s="1" t="n">
+      <c r="AH22" s="1" t="n">
         <v>93.54689999999999</v>
       </c>
-      <c r="AF22" s="1" t="n">
+      <c r="AI22" s="1" t="n">
         <v>93.5</v>
       </c>
-      <c r="AG22" s="1" t="n">
+      <c r="AJ22" s="1" t="n">
         <v>93.6613</v>
       </c>
-      <c r="AH22" s="1" t="n">
+      <c r="AK22" s="1" t="n">
         <v>93.47320000000001</v>
       </c>
-      <c r="AI22" s="1" t="n">
+      <c r="AL22" s="1" t="n">
         <v>100.6</v>
       </c>
-      <c r="AJ22" s="1" t="n">
+      <c r="AM22" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="AK22" s="1" t="n">
+      <c r="AN22" s="1" t="n">
         <v>102.9</v>
       </c>
     </row>
@@ -11551,48 +11847,57 @@
         <v>108.6773</v>
       </c>
       <c r="W23" s="1" t="n">
+        <v>107.2433</v>
+      </c>
+      <c r="X23" s="1" t="n">
+        <v>105.5337</v>
+      </c>
+      <c r="Y23" s="1" t="n">
+        <v>104.0991</v>
+      </c>
+      <c r="Z23" s="1" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="X23" s="1" t="n">
+      <c r="AA23" s="1" t="n">
         <v>97.4616</v>
       </c>
-      <c r="Y23" s="1" t="n">
+      <c r="AB23" s="1" t="n">
         <v>98.17749999999999</v>
       </c>
-      <c r="Z23" s="1" t="n">
+      <c r="AC23" s="1" t="n">
         <v>98.0806</v>
       </c>
-      <c r="AA23" s="1" t="n">
+      <c r="AD23" s="1" t="n">
         <v>98.3129</v>
       </c>
-      <c r="AB23" s="1" t="n">
+      <c r="AE23" s="1" t="n">
         <v>95.6688</v>
       </c>
-      <c r="AC23" s="1" t="n">
+      <c r="AF23" s="1" t="n">
         <v>95.2084</v>
       </c>
-      <c r="AD23" s="1" t="n">
+      <c r="AG23" s="1" t="n">
         <v>94.9645</v>
       </c>
-      <c r="AE23" s="1" t="n">
+      <c r="AH23" s="1" t="n">
         <v>94.7852</v>
       </c>
-      <c r="AF23" s="1" t="n">
+      <c r="AI23" s="1" t="n">
         <v>94.5</v>
       </c>
-      <c r="AG23" s="1" t="n">
+      <c r="AJ23" s="1" t="n">
         <v>94.38209999999999</v>
       </c>
-      <c r="AH23" s="1" t="n">
+      <c r="AK23" s="1" t="n">
         <v>94.73950000000001</v>
       </c>
-      <c r="AI23" s="1" t="n">
+      <c r="AL23" s="1" t="n">
         <v>102.8</v>
       </c>
-      <c r="AJ23" s="1" t="n">
+      <c r="AM23" s="1" t="n">
         <v>104.6</v>
       </c>
-      <c r="AK23" s="1" t="n">
+      <c r="AN23" s="1" t="n">
         <v>104.9</v>
       </c>
     </row>
@@ -11666,48 +11971,57 @@
         <v>110.1054</v>
       </c>
       <c r="W24" s="1" t="n">
+        <v>107.8254</v>
+      </c>
+      <c r="X24" s="1" t="n">
+        <v>105.8494</v>
+      </c>
+      <c r="Y24" s="1" t="n">
+        <v>104.0593</v>
+      </c>
+      <c r="Z24" s="1" t="n">
         <v>98.3433</v>
       </c>
-      <c r="X24" s="1" t="n">
+      <c r="AA24" s="1" t="n">
         <v>98.01309999999999</v>
       </c>
-      <c r="Y24" s="1" t="n">
+      <c r="AB24" s="1" t="n">
         <v>98.45350000000001</v>
       </c>
-      <c r="Z24" s="1" t="n">
+      <c r="AC24" s="1" t="n">
         <v>98.0916</v>
       </c>
-      <c r="AA24" s="1" t="n">
+      <c r="AD24" s="1" t="n">
         <v>98.11190000000001</v>
       </c>
-      <c r="AB24" s="1" t="n">
+      <c r="AE24" s="1" t="n">
         <v>95.82769999999999</v>
       </c>
-      <c r="AC24" s="1" t="n">
+      <c r="AF24" s="1" t="n">
         <v>95.6521</v>
       </c>
-      <c r="AD24" s="1" t="n">
+      <c r="AG24" s="1" t="n">
         <v>95.3947</v>
       </c>
-      <c r="AE24" s="1" t="n">
+      <c r="AH24" s="1" t="n">
         <v>94.8951</v>
       </c>
-      <c r="AF24" s="1" t="n">
+      <c r="AI24" s="1" t="n">
         <v>94.90000000000001</v>
       </c>
-      <c r="AG24" s="1" t="n">
+      <c r="AJ24" s="1" t="n">
         <v>94.48820000000001</v>
       </c>
-      <c r="AH24" s="1" t="n">
+      <c r="AK24" s="1" t="n">
         <v>94.4823</v>
       </c>
-      <c r="AI24" s="1" t="n">
+      <c r="AL24" s="1" t="n">
         <v>105.9</v>
       </c>
-      <c r="AJ24" s="1" t="n">
+      <c r="AM24" s="1" t="n">
         <v>107.2</v>
       </c>
-      <c r="AK24" s="1" t="n">
+      <c r="AN24" s="1" t="n">
         <v>107.9</v>
       </c>
     </row>
@@ -11781,48 +12095,57 @@
         <v>116.3739</v>
       </c>
       <c r="W25" s="1" t="n">
+        <v>112.9099</v>
+      </c>
+      <c r="X25" s="1" t="n">
+        <v>110.0496</v>
+      </c>
+      <c r="Y25" s="1" t="n">
+        <v>107.0738</v>
+      </c>
+      <c r="Z25" s="1" t="n">
         <v>98.0889</v>
       </c>
-      <c r="X25" s="1" t="n">
+      <c r="AA25" s="1" t="n">
         <v>97.92529999999999</v>
       </c>
-      <c r="Y25" s="1" t="n">
+      <c r="AB25" s="1" t="n">
         <v>98.5164</v>
       </c>
-      <c r="Z25" s="1" t="n">
+      <c r="AC25" s="1" t="n">
         <v>98.0493</v>
       </c>
-      <c r="AA25" s="1" t="n">
+      <c r="AD25" s="1" t="n">
         <v>99.1579</v>
       </c>
-      <c r="AB25" s="1" t="n">
+      <c r="AE25" s="1" t="n">
         <v>88.20449999999998</v>
       </c>
-      <c r="AC25" s="1" t="n">
+      <c r="AF25" s="1" t="n">
         <v>87.611</v>
       </c>
-      <c r="AD25" s="1" t="n">
+      <c r="AG25" s="1" t="n">
         <v>87.6563</v>
       </c>
-      <c r="AE25" s="1" t="n">
+      <c r="AH25" s="1" t="n">
         <v>87.7081</v>
       </c>
-      <c r="AF25" s="1" t="n">
+      <c r="AI25" s="1" t="n">
         <v>87.79999999999998</v>
       </c>
-      <c r="AG25" s="1" t="n">
+      <c r="AJ25" s="1" t="n">
         <v>88.8772</v>
       </c>
-      <c r="AH25" s="1" t="n">
+      <c r="AK25" s="1" t="n">
         <v>92.2878</v>
       </c>
-      <c r="AI25" s="1" t="n">
+      <c r="AL25" s="1" t="n">
         <v>105.7</v>
       </c>
-      <c r="AJ25" s="1" t="n">
+      <c r="AM25" s="1" t="n">
         <v>116.8</v>
       </c>
-      <c r="AK25" s="1" t="n">
+      <c r="AN25" s="1" t="n">
         <v>117.2</v>
       </c>
     </row>
@@ -11896,48 +12219,57 @@
         <v>106.7389</v>
       </c>
       <c r="W26" s="1" t="n">
+        <v>105.9361</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <v>104.2274</v>
+      </c>
+      <c r="Y26" s="1" t="n">
+        <v>103.3166</v>
+      </c>
+      <c r="Z26" s="1" t="n">
         <v>98.27290000000001</v>
       </c>
-      <c r="X26" s="1" t="n">
+      <c r="AA26" s="1" t="n">
         <v>97.7924</v>
       </c>
-      <c r="Y26" s="1" t="n">
+      <c r="AB26" s="1" t="n">
         <v>97.7809</v>
       </c>
-      <c r="Z26" s="1" t="n">
+      <c r="AC26" s="1" t="n">
         <v>98.13330000000001</v>
       </c>
-      <c r="AA26" s="1" t="n">
+      <c r="AD26" s="1" t="n">
         <v>98.2615</v>
       </c>
-      <c r="AB26" s="1" t="n">
+      <c r="AE26" s="1" t="n">
         <v>97.5368</v>
       </c>
-      <c r="AC26" s="1" t="n">
+      <c r="AF26" s="1" t="n">
         <v>97.348</v>
       </c>
-      <c r="AD26" s="1" t="n">
+      <c r="AG26" s="1" t="n">
         <v>96.7901</v>
       </c>
-      <c r="AE26" s="1" t="n">
+      <c r="AH26" s="1" t="n">
         <v>96.74939999999999</v>
       </c>
-      <c r="AF26" s="1" t="n">
+      <c r="AI26" s="1" t="n">
         <v>96.5</v>
       </c>
-      <c r="AG26" s="1" t="n">
+      <c r="AJ26" s="1" t="n">
         <v>96.259</v>
       </c>
-      <c r="AH26" s="1" t="n">
+      <c r="AK26" s="1" t="n">
         <v>96.20999999999999</v>
       </c>
-      <c r="AI26" s="1" t="n">
+      <c r="AL26" s="1" t="n">
         <v>102.1</v>
       </c>
-      <c r="AJ26" s="1" t="n">
+      <c r="AM26" s="1" t="n">
         <v>104.2</v>
       </c>
-      <c r="AK26" s="1" t="n">
+      <c r="AN26" s="1" t="n">
         <v>105.1</v>
       </c>
     </row>
@@ -12011,48 +12343,57 @@
         <v>114.1676</v>
       </c>
       <c r="W27" s="1" t="n">
+        <v>112.9421</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <v>109.2679</v>
+      </c>
+      <c r="Y27" s="1" t="n">
+        <v>105.9576</v>
+      </c>
+      <c r="Z27" s="1" t="n">
         <v>97.3644</v>
       </c>
-      <c r="X27" s="1" t="n">
+      <c r="AA27" s="1" t="n">
         <v>97.0141</v>
       </c>
-      <c r="Y27" s="1" t="n">
+      <c r="AB27" s="1" t="n">
         <v>97.3155</v>
       </c>
-      <c r="Z27" s="1" t="n">
+      <c r="AC27" s="1" t="n">
         <v>98.2043</v>
       </c>
-      <c r="AA27" s="1" t="n">
+      <c r="AD27" s="1" t="n">
         <v>98.84950000000001</v>
       </c>
-      <c r="AB27" s="1" t="n">
+      <c r="AE27" s="1" t="n">
         <v>97.1384</v>
       </c>
-      <c r="AC27" s="1" t="n">
+      <c r="AF27" s="1" t="n">
         <v>96.6833</v>
       </c>
-      <c r="AD27" s="1" t="n">
+      <c r="AG27" s="1" t="n">
         <v>96.8622</v>
       </c>
-      <c r="AE27" s="1" t="n">
+      <c r="AH27" s="1" t="n">
         <v>96.36539999999999</v>
       </c>
-      <c r="AF27" s="1" t="n">
+      <c r="AI27" s="1" t="n">
         <v>96.3</v>
       </c>
-      <c r="AG27" s="1" t="n">
+      <c r="AJ27" s="1" t="n">
         <v>95.8258</v>
       </c>
-      <c r="AH27" s="1" t="n">
+      <c r="AK27" s="1" t="n">
         <v>95.843</v>
       </c>
-      <c r="AI27" s="1" t="n">
+      <c r="AL27" s="1" t="n">
         <v>107.4</v>
       </c>
-      <c r="AJ27" s="1" t="n">
+      <c r="AM27" s="1" t="n">
         <v>109.2</v>
       </c>
-      <c r="AK27" s="1" t="n">
+      <c r="AN27" s="1" t="n">
         <v>110.5</v>
       </c>
     </row>
@@ -12126,48 +12467,57 @@
         <v>118.0434</v>
       </c>
       <c r="W28" s="1" t="n">
+        <v>116.4585</v>
+      </c>
+      <c r="X28" s="1" t="n">
+        <v>115.2421</v>
+      </c>
+      <c r="Y28" s="1" t="n">
+        <v>113.1853</v>
+      </c>
+      <c r="Z28" s="1" t="n">
         <v>99.40179999999999</v>
       </c>
-      <c r="X28" s="1" t="n">
+      <c r="AA28" s="1" t="n">
         <v>96.3079</v>
       </c>
-      <c r="Y28" s="1" t="n">
+      <c r="AB28" s="1" t="n">
         <v>96.9496</v>
       </c>
-      <c r="Z28" s="1" t="n">
+      <c r="AC28" s="1" t="n">
         <v>96.6037</v>
       </c>
-      <c r="AA28" s="1" t="n">
+      <c r="AD28" s="1" t="n">
         <v>96.38849999999999</v>
       </c>
-      <c r="AB28" s="1" t="n">
+      <c r="AE28" s="1" t="n">
         <v>97.1147</v>
       </c>
-      <c r="AC28" s="1" t="n">
+      <c r="AF28" s="1" t="n">
         <v>97.06950000000001</v>
       </c>
-      <c r="AD28" s="1" t="n">
+      <c r="AG28" s="1" t="n">
         <v>96.79389999999999</v>
       </c>
-      <c r="AE28" s="1" t="n">
+      <c r="AH28" s="1" t="n">
         <v>96.51519999999999</v>
       </c>
-      <c r="AF28" s="1" t="n">
+      <c r="AI28" s="1" t="n">
         <v>96.40000000000001</v>
       </c>
-      <c r="AG28" s="1" t="n">
+      <c r="AJ28" s="1" t="n">
         <v>96.06780000000001</v>
       </c>
-      <c r="AH28" s="1" t="n">
+      <c r="AK28" s="1" t="n">
         <v>95.8738</v>
       </c>
-      <c r="AI28" s="1" t="n">
+      <c r="AL28" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="AJ28" s="1" t="n">
+      <c r="AM28" s="1" t="n">
         <v>104.9</v>
       </c>
-      <c r="AK28" s="1" t="n">
+      <c r="AN28" s="1" t="n">
         <v>107.4</v>
       </c>
     </row>
@@ -12241,48 +12591,57 @@
         <v>108.9355</v>
       </c>
       <c r="W29" s="1" t="n">
+        <v>107.339</v>
+      </c>
+      <c r="X29" s="1" t="n">
+        <v>104.869</v>
+      </c>
+      <c r="Y29" s="1" t="n">
+        <v>103.6351</v>
+      </c>
+      <c r="Z29" s="1" t="n">
         <v>97.49420000000001</v>
       </c>
-      <c r="X29" s="1" t="n">
+      <c r="AA29" s="1" t="n">
         <v>97.6109</v>
       </c>
-      <c r="Y29" s="1" t="n">
+      <c r="AB29" s="1" t="n">
         <v>97.93429999999999</v>
       </c>
-      <c r="Z29" s="1" t="n">
+      <c r="AC29" s="1" t="n">
         <v>98.54730000000001</v>
       </c>
-      <c r="AA29" s="1" t="n">
+      <c r="AD29" s="1" t="n">
         <v>98.99290000000001</v>
       </c>
-      <c r="AB29" s="1" t="n">
+      <c r="AE29" s="1" t="n">
         <v>97.529</v>
       </c>
-      <c r="AC29" s="1" t="n">
+      <c r="AF29" s="1" t="n">
         <v>97.20489999999999</v>
       </c>
-      <c r="AD29" s="1" t="n">
+      <c r="AG29" s="1" t="n">
         <v>95.6232</v>
       </c>
-      <c r="AE29" s="1" t="n">
+      <c r="AH29" s="1" t="n">
         <v>95.70610000000001</v>
       </c>
-      <c r="AF29" s="1" t="n">
+      <c r="AI29" s="1" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="AG29" s="1" t="n">
+      <c r="AJ29" s="1" t="n">
         <v>95.04179999999999</v>
       </c>
-      <c r="AH29" s="1" t="n">
+      <c r="AK29" s="1" t="n">
         <v>94.527</v>
       </c>
-      <c r="AI29" s="1" t="n">
+      <c r="AL29" s="1" t="n">
         <v>107.9</v>
       </c>
-      <c r="AJ29" s="1" t="n">
+      <c r="AM29" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="AK29" s="1" t="n">
+      <c r="AN29" s="1" t="n">
         <v>110.7</v>
       </c>
     </row>
@@ -12366,48 +12725,57 @@
         <v>110.1885</v>
       </c>
       <c r="W31" s="1" t="n">
+        <v>108.7475</v>
+      </c>
+      <c r="X31" s="1" t="n">
+        <v>105.3587</v>
+      </c>
+      <c r="Y31" s="1" t="n">
+        <v>104.5629</v>
+      </c>
+      <c r="Z31" s="1" t="n">
         <v>98.04300000000001</v>
       </c>
-      <c r="X31" s="1" t="n">
+      <c r="AA31" s="1" t="n">
         <v>98.2679</v>
       </c>
-      <c r="Y31" s="1" t="n">
+      <c r="AB31" s="1" t="n">
         <v>99.2042</v>
       </c>
-      <c r="Z31" s="1" t="n">
+      <c r="AC31" s="1" t="n">
         <v>99.5578</v>
       </c>
-      <c r="AA31" s="1" t="n">
+      <c r="AD31" s="1" t="n">
         <v>100.0222</v>
       </c>
-      <c r="AB31" s="1" t="n">
+      <c r="AE31" s="1" t="n">
         <v>95.94289999999999</v>
       </c>
-      <c r="AC31" s="1" t="n">
+      <c r="AF31" s="1" t="n">
         <v>95.3959</v>
       </c>
-      <c r="AD31" s="1" t="n">
+      <c r="AG31" s="1" t="n">
         <v>95.00360000000001</v>
       </c>
-      <c r="AE31" s="1" t="n">
+      <c r="AH31" s="1" t="n">
         <v>94.8539</v>
       </c>
-      <c r="AF31" s="1" t="n">
+      <c r="AI31" s="1" t="n">
         <v>94.7</v>
       </c>
-      <c r="AG31" s="1" t="n">
+      <c r="AJ31" s="1" t="n">
         <v>94.51949999999999</v>
       </c>
-      <c r="AH31" s="1" t="n">
+      <c r="AK31" s="1" t="n">
         <v>95.14149999999999</v>
       </c>
-      <c r="AI31" s="1" t="n">
+      <c r="AL31" s="1" t="n">
         <v>103.5</v>
       </c>
-      <c r="AJ31" s="1" t="n">
+      <c r="AM31" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="AK31" s="1" t="n">
+      <c r="AN31" s="1" t="n">
         <v>106.6</v>
       </c>
     </row>
@@ -12481,48 +12849,57 @@
         <v>117.2111</v>
       </c>
       <c r="W32" s="1" t="n">
+        <v>115.9687</v>
+      </c>
+      <c r="X32" s="1" t="n">
+        <v>111.3009</v>
+      </c>
+      <c r="Y32" s="1" t="n">
+        <v>110.545</v>
+      </c>
+      <c r="Z32" s="1" t="n">
         <v>93.6797</v>
       </c>
-      <c r="X32" s="1" t="n">
+      <c r="AA32" s="1" t="n">
         <v>94.5972</v>
       </c>
-      <c r="Y32" s="1" t="n">
+      <c r="AB32" s="1" t="n">
         <v>95.55370000000001</v>
       </c>
-      <c r="Z32" s="1" t="n">
+      <c r="AC32" s="1" t="n">
         <v>97.72029999999999</v>
       </c>
-      <c r="AA32" s="1" t="n">
+      <c r="AD32" s="1" t="n">
         <v>98.4259</v>
       </c>
-      <c r="AB32" s="1" t="n">
+      <c r="AE32" s="1" t="n">
         <v>87.3613</v>
       </c>
-      <c r="AC32" s="1" t="n">
+      <c r="AF32" s="1" t="n">
         <v>87.5201</v>
       </c>
-      <c r="AD32" s="1" t="n">
+      <c r="AG32" s="1" t="n">
         <v>84.8747</v>
       </c>
-      <c r="AE32" s="1" t="n">
+      <c r="AH32" s="1" t="n">
         <v>84.8152</v>
       </c>
-      <c r="AF32" s="1" t="n">
+      <c r="AI32" s="1" t="n">
         <v>85.29999999999998</v>
       </c>
-      <c r="AG32" s="1" t="n">
+      <c r="AJ32" s="1" t="n">
         <v>85.6298</v>
       </c>
-      <c r="AH32" s="1" t="n">
+      <c r="AK32" s="1" t="n">
         <v>86.35980000000001</v>
       </c>
-      <c r="AI32" s="1" t="n">
+      <c r="AL32" s="1" t="n">
         <v>107.4</v>
       </c>
-      <c r="AJ32" s="1" t="n">
+      <c r="AM32" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="AK32" s="1" t="n">
+      <c r="AN32" s="1" t="n">
         <v>108.7</v>
       </c>
     </row>
@@ -12596,48 +12973,57 @@
         <v>107.7336</v>
       </c>
       <c r="W33" s="1" t="n">
+        <v>106.2322</v>
+      </c>
+      <c r="X33" s="1" t="n">
+        <v>105.1907</v>
+      </c>
+      <c r="Y33" s="1" t="n">
+        <v>103.7166</v>
+      </c>
+      <c r="Z33" s="1" t="n">
         <v>97.2846</v>
       </c>
-      <c r="X33" s="1" t="n">
+      <c r="AA33" s="1" t="n">
         <v>96.6421</v>
       </c>
-      <c r="Y33" s="1" t="n">
+      <c r="AB33" s="1" t="n">
         <v>97.0214</v>
       </c>
-      <c r="Z33" s="1" t="n">
+      <c r="AC33" s="1" t="n">
         <v>97.27500000000001</v>
       </c>
-      <c r="AA33" s="1" t="n">
+      <c r="AD33" s="1" t="n">
         <v>98.31440000000001</v>
       </c>
-      <c r="AB33" s="1" t="n">
+      <c r="AE33" s="1" t="n">
         <v>98.91249999999999</v>
       </c>
-      <c r="AC33" s="1" t="n">
+      <c r="AF33" s="1" t="n">
         <v>98.25530000000001</v>
       </c>
-      <c r="AD33" s="1" t="n">
+      <c r="AG33" s="1" t="n">
         <v>98.0016</v>
       </c>
-      <c r="AE33" s="1" t="n">
+      <c r="AH33" s="1" t="n">
         <v>97.0343</v>
       </c>
-      <c r="AF33" s="1" t="n">
+      <c r="AI33" s="1" t="n">
         <v>96.40000000000001</v>
       </c>
-      <c r="AG33" s="1" t="n">
+      <c r="AJ33" s="1" t="n">
         <v>95.5831</v>
       </c>
-      <c r="AH33" s="1" t="n">
+      <c r="AK33" s="1" t="n">
         <v>94.19929999999999</v>
       </c>
-      <c r="AI33" s="1" t="n">
+      <c r="AL33" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="AJ33" s="1" t="n">
+      <c r="AM33" s="1" t="n">
         <v>105.7</v>
       </c>
-      <c r="AK33" s="1" t="n">
+      <c r="AN33" s="1" t="n">
         <v>107.5</v>
       </c>
     </row>
@@ -12711,48 +13097,57 @@
         <v>113.6899</v>
       </c>
       <c r="W34" s="1" t="n">
+        <v>111.7153</v>
+      </c>
+      <c r="X34" s="1" t="n">
+        <v>108.9578</v>
+      </c>
+      <c r="Y34" s="1" t="n">
+        <v>107.1703</v>
+      </c>
+      <c r="Z34" s="1" t="n">
         <v>97.45099999999999</v>
       </c>
-      <c r="X34" s="1" t="n">
+      <c r="AA34" s="1" t="n">
         <v>97.2924</v>
       </c>
-      <c r="Y34" s="1" t="n">
+      <c r="AB34" s="1" t="n">
         <v>96.742</v>
       </c>
-      <c r="Z34" s="1" t="n">
+      <c r="AC34" s="1" t="n">
         <v>96.1765</v>
       </c>
-      <c r="AA34" s="1" t="n">
+      <c r="AD34" s="1" t="n">
         <v>96.0886</v>
       </c>
-      <c r="AB34" s="1" t="n">
+      <c r="AE34" s="1" t="n">
         <v>92.8933</v>
       </c>
-      <c r="AC34" s="1" t="n">
+      <c r="AF34" s="1" t="n">
         <v>92.51900000000001</v>
       </c>
-      <c r="AD34" s="1" t="n">
+      <c r="AG34" s="1" t="n">
         <v>91.8395</v>
       </c>
-      <c r="AE34" s="1" t="n">
+      <c r="AH34" s="1" t="n">
         <v>91.8442</v>
       </c>
-      <c r="AF34" s="1" t="n">
+      <c r="AI34" s="1" t="n">
         <v>90.8</v>
       </c>
-      <c r="AG34" s="1" t="n">
+      <c r="AJ34" s="1" t="n">
         <v>90.5368</v>
       </c>
-      <c r="AH34" s="1" t="n">
+      <c r="AK34" s="1" t="n">
         <v>90.3891</v>
       </c>
-      <c r="AI34" s="1" t="n">
+      <c r="AL34" s="1" t="n">
         <v>107.9</v>
       </c>
-      <c r="AJ34" s="1" t="n">
+      <c r="AM34" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="AK34" s="1" t="n">
+      <c r="AN34" s="1" t="n">
         <v>108.2</v>
       </c>
     </row>
@@ -12826,48 +13221,57 @@
         <v>120.7957</v>
       </c>
       <c r="W35" s="1" t="n">
+        <v>115.9418</v>
+      </c>
+      <c r="X35" s="1" t="n">
+        <v>110.4512</v>
+      </c>
+      <c r="Y35" s="1" t="n">
+        <v>105.7355</v>
+      </c>
+      <c r="Z35" s="1" t="n">
         <v>92.6836</v>
       </c>
-      <c r="X35" s="1" t="n">
+      <c r="AA35" s="1" t="n">
         <v>95.4199</v>
       </c>
-      <c r="Y35" s="1" t="n">
+      <c r="AB35" s="1" t="n">
         <v>97.7251</v>
       </c>
-      <c r="Z35" s="1" t="n">
+      <c r="AC35" s="1" t="n">
         <v>99.2127</v>
       </c>
-      <c r="AA35" s="1" t="n">
+      <c r="AD35" s="1" t="n">
         <v>98.2269</v>
       </c>
-      <c r="AB35" s="1" t="n">
+      <c r="AE35" s="1" t="n">
         <v>84.717</v>
       </c>
-      <c r="AC35" s="1" t="n">
+      <c r="AF35" s="1" t="n">
         <v>84.8837</v>
       </c>
-      <c r="AD35" s="1" t="n">
+      <c r="AG35" s="1" t="n">
         <v>83.15869999999998</v>
       </c>
-      <c r="AE35" s="1" t="n">
+      <c r="AH35" s="1" t="n">
         <v>82.3013</v>
       </c>
-      <c r="AF35" s="1" t="n">
+      <c r="AI35" s="1" t="n">
         <v>82.59999999999998</v>
       </c>
-      <c r="AG35" s="1" t="n">
+      <c r="AJ35" s="1" t="n">
         <v>84.06570000000001</v>
       </c>
-      <c r="AH35" s="1" t="n">
+      <c r="AK35" s="1" t="n">
         <v>85.5318</v>
       </c>
-      <c r="AI35" s="1" t="n">
+      <c r="AL35" s="1" t="n">
         <v>105.2</v>
       </c>
-      <c r="AJ35" s="1" t="n">
+      <c r="AM35" s="1" t="n">
         <v>109.1</v>
       </c>
-      <c r="AK35" s="1" t="n">
+      <c r="AN35" s="1" t="n">
         <v>107.7</v>
       </c>
     </row>
@@ -12882,7 +13286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:BF35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13013,70 +13417,175 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>2012-02</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2012-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2012-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2012-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2012-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2012-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2012-08</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2012-09</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2012-10</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2012-11</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2012-12</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>2013-02</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
         <is>
           <t>2015-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>2015-03</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>2015-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2015-05</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>2016-02</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>2016-03</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2016-04</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -13155,45 +13664,108 @@
         <v>61739.78</v>
       </c>
       <c r="X4" s="1" t="n">
+        <v>5431.4591</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>10927.1652</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>15835.1867</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>22212.9252</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>30609.8286</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>36774.4761</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>43687.8797</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>51045.9254</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>57628.7504</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>64772.4006</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>71803.78690000001</v>
+      </c>
+      <c r="AI4" s="1" t="n">
         <v>6669.7035</v>
       </c>
-      <c r="Y4" s="1" t="n">
+      <c r="AJ4" s="1" t="n">
+        <v>13132.5735</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>19180.1411</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>26797.9733</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>36827.9353</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>44301.575</v>
+      </c>
+      <c r="AO4" s="1" t="n">
+        <v>52119.7659</v>
+      </c>
+      <c r="AP4" s="1" t="n">
+        <v>61119.5474</v>
+      </c>
+      <c r="AQ4" s="1" t="n">
+        <v>68693.182</v>
+      </c>
+      <c r="AR4" s="1" t="n">
+        <v>77412.16409999998</v>
+      </c>
+      <c r="AS4" s="1" t="n">
+        <v>86013.38259999998</v>
+      </c>
+      <c r="AT4" s="1" t="n">
         <v>8786.357900000001</v>
       </c>
-      <c r="Z4" s="1" t="n">
+      <c r="AU4" s="1" t="n">
         <v>16650.6352</v>
       </c>
-      <c r="AA4" s="1" t="n">
+      <c r="AV4" s="1" t="n">
         <v>23669.0414</v>
       </c>
-      <c r="AB4" s="1" t="n">
+      <c r="AW4" s="1" t="n">
         <v>32291.8358</v>
       </c>
-      <c r="AC4" s="1" t="n">
+      <c r="AX4" s="1" t="n">
         <v>43954.9507</v>
       </c>
-      <c r="AD4" s="1" t="n">
+      <c r="AY4" s="1" t="n">
         <v>52562.2224</v>
       </c>
-      <c r="AE4" s="1" t="n">
+      <c r="AZ4" s="1" t="n">
         <v>61062.5425</v>
       </c>
-      <c r="AF4" s="1" t="n">
+      <c r="BA4" s="1" t="n">
         <v>9051.790800000001</v>
       </c>
-      <c r="AG4" s="1" t="n">
+      <c r="BB4" s="1" t="n">
         <v>17676.6202</v>
       </c>
-      <c r="AH4" s="1" t="n">
+      <c r="BC4" s="1" t="n">
         <v>25375.6354</v>
       </c>
-      <c r="AI4" s="1" t="n">
+      <c r="BD4" s="1" t="n">
         <v>23969.4</v>
       </c>
-      <c r="AJ4" s="1" t="n">
+      <c r="BE4" s="1" t="n">
         <v>30355.68</v>
       </c>
-      <c r="AK4" s="1" t="n">
+      <c r="BF4" s="1" t="n">
         <v>38073.7</v>
       </c>
     </row>
@@ -13270,45 +13842,108 @@
         <v>3036.334</v>
       </c>
       <c r="X5" s="1" t="n">
+        <v>187.5599</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>419.9212</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>633.9305000000001</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>927.9479</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>1283.1772</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>1624.3865</v>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>1876.2059</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>2203.719</v>
+      </c>
+      <c r="AF5" s="1" t="n">
+        <v>2518.6094</v>
+      </c>
+      <c r="AG5" s="1" t="n">
+        <v>2810.5433</v>
+      </c>
+      <c r="AH5" s="1" t="n">
+        <v>3153.4419</v>
+      </c>
+      <c r="AI5" s="1" t="n">
         <v>227.0445</v>
       </c>
-      <c r="Y5" s="1" t="n">
+      <c r="AJ5" s="1" t="n">
+        <v>451.9655</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>647.8836</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>932.5097</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>1315.2826</v>
+      </c>
+      <c r="AN5" s="1" t="n">
+        <v>1609.0205</v>
+      </c>
+      <c r="AO5" s="1" t="n">
+        <v>1929.3616</v>
+      </c>
+      <c r="AP5" s="1" t="n">
+        <v>2234.6014</v>
+      </c>
+      <c r="AQ5" s="1" t="n">
+        <v>2475.7625</v>
+      </c>
+      <c r="AR5" s="1" t="n">
+        <v>2864.1043</v>
+      </c>
+      <c r="AS5" s="1" t="n">
+        <v>3483.4045</v>
+      </c>
+      <c r="AT5" s="1" t="n">
         <v>264.3045</v>
       </c>
-      <c r="Z5" s="1" t="n">
+      <c r="AU5" s="1" t="n">
         <v>667.7324</v>
       </c>
-      <c r="AA5" s="1" t="n">
+      <c r="AV5" s="1" t="n">
         <v>949.5753</v>
       </c>
-      <c r="AB5" s="1" t="n">
+      <c r="AW5" s="1" t="n">
         <v>1223.4938</v>
       </c>
-      <c r="AC5" s="1" t="n">
+      <c r="AX5" s="1" t="n">
         <v>1688.0704</v>
       </c>
-      <c r="AD5" s="1" t="n">
+      <c r="AY5" s="1" t="n">
         <v>2093.0282</v>
       </c>
-      <c r="AE5" s="1" t="n">
+      <c r="AZ5" s="1" t="n">
         <v>2449.3065</v>
       </c>
-      <c r="AF5" s="1" t="n">
+      <c r="BA5" s="1" t="n">
         <v>302.7881</v>
       </c>
-      <c r="AG5" s="1" t="n">
+      <c r="BB5" s="1" t="n">
         <v>662.7104</v>
       </c>
-      <c r="AH5" s="1" t="n">
+      <c r="BC5" s="1" t="n">
         <v>933.997</v>
       </c>
-      <c r="AI5" s="1" t="n">
+      <c r="BD5" s="1" t="n">
         <v>1114.66</v>
       </c>
-      <c r="AJ5" s="1" t="n">
+      <c r="BE5" s="1" t="n">
         <v>1445.5</v>
       </c>
-      <c r="AK5" s="1" t="n">
+      <c r="BF5" s="1" t="n">
         <v>1862.11</v>
       </c>
     </row>
@@ -13385,45 +14020,108 @@
         <v>1080.0436</v>
       </c>
       <c r="X6" s="1" t="n">
+        <v>67.515</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>198.6395</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>318.4351</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>445.5903</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>675.8035</v>
+      </c>
+      <c r="AC6" s="1" t="n">
+        <v>757.0866999999998</v>
+      </c>
+      <c r="AD6" s="1" t="n">
+        <v>856.4224</v>
+      </c>
+      <c r="AE6" s="1" t="n">
+        <v>980.7594</v>
+      </c>
+      <c r="AF6" s="1" t="n">
+        <v>1042.9611</v>
+      </c>
+      <c r="AG6" s="1" t="n">
+        <v>1128.6392</v>
+      </c>
+      <c r="AH6" s="1" t="n">
+        <v>1259.9969</v>
+      </c>
+      <c r="AI6" s="1" t="n">
         <v>85.8781</v>
       </c>
-      <c r="Y6" s="1" t="n">
+      <c r="AJ6" s="1" t="n">
+        <v>249.5375</v>
+      </c>
+      <c r="AK6" s="1" t="n">
+        <v>398.7542</v>
+      </c>
+      <c r="AL6" s="1" t="n">
+        <v>568.9986</v>
+      </c>
+      <c r="AM6" s="1" t="n">
+        <v>809.9982</v>
+      </c>
+      <c r="AN6" s="1" t="n">
+        <v>910.086</v>
+      </c>
+      <c r="AO6" s="1" t="n">
+        <v>1020.3737</v>
+      </c>
+      <c r="AP6" s="1" t="n">
+        <v>1158.7303</v>
+      </c>
+      <c r="AQ6" s="1" t="n">
+        <v>1221.6375</v>
+      </c>
+      <c r="AR6" s="1" t="n">
+        <v>1328.4277</v>
+      </c>
+      <c r="AS6" s="1" t="n">
+        <v>1480.8152</v>
+      </c>
+      <c r="AT6" s="1" t="n">
         <v>119.237</v>
       </c>
-      <c r="Z6" s="1" t="n">
+      <c r="AU6" s="1" t="n">
         <v>344.5796</v>
       </c>
-      <c r="AA6" s="1" t="n">
+      <c r="AV6" s="1" t="n">
         <v>540.1039</v>
       </c>
-      <c r="AB6" s="1" t="n">
+      <c r="AW6" s="1" t="n">
         <v>753.1244</v>
       </c>
-      <c r="AC6" s="1" t="n">
+      <c r="AX6" s="1" t="n">
         <v>1039.7283</v>
       </c>
-      <c r="AD6" s="1" t="n">
+      <c r="AY6" s="1" t="n">
         <v>1187.3161</v>
       </c>
-      <c r="AE6" s="1" t="n">
+      <c r="AZ6" s="1" t="n">
         <v>1335.9854</v>
       </c>
-      <c r="AF6" s="1" t="n">
+      <c r="BA6" s="1" t="n">
         <v>137.0541</v>
       </c>
-      <c r="AG6" s="1" t="n">
+      <c r="BB6" s="1" t="n">
         <v>397.8454</v>
       </c>
-      <c r="AH6" s="1" t="n">
+      <c r="BC6" s="1" t="n">
         <v>616.2076</v>
       </c>
-      <c r="AI6" s="1" t="n">
+      <c r="BD6" s="1" t="n">
         <v>407.8</v>
       </c>
-      <c r="AJ6" s="1" t="n">
+      <c r="BE6" s="1" t="n">
         <v>488.25</v>
       </c>
-      <c r="AK6" s="1" t="n">
+      <c r="BF6" s="1" t="n">
         <v>611.24</v>
       </c>
     </row>
@@ -13500,45 +14198,108 @@
         <v>3069.554</v>
       </c>
       <c r="X7" s="1" t="n">
+        <v>125.0491</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>412.9841</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>645.3067</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>944.9340999999999</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>1370.8778</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>1621.9041</v>
+      </c>
+      <c r="AD7" s="1" t="n">
+        <v>1949.862</v>
+      </c>
+      <c r="AE7" s="1" t="n">
+        <v>2286.8291</v>
+      </c>
+      <c r="AF7" s="1" t="n">
+        <v>2602.845</v>
+      </c>
+      <c r="AG7" s="1" t="n">
+        <v>2912.3351</v>
+      </c>
+      <c r="AH7" s="1" t="n">
+        <v>3086.5214</v>
+      </c>
+      <c r="AI7" s="1" t="n">
         <v>145.1008</v>
       </c>
-      <c r="Y7" s="1" t="n">
+      <c r="AJ7" s="1" t="n">
+        <v>455.5338</v>
+      </c>
+      <c r="AK7" s="1" t="n">
+        <v>728.6788</v>
+      </c>
+      <c r="AL7" s="1" t="n">
+        <v>1020.8739</v>
+      </c>
+      <c r="AM7" s="1" t="n">
+        <v>1478.5461</v>
+      </c>
+      <c r="AN7" s="1" t="n">
+        <v>1779.673</v>
+      </c>
+      <c r="AO7" s="1" t="n">
+        <v>2150.034</v>
+      </c>
+      <c r="AP7" s="1" t="n">
+        <v>2517.4865</v>
+      </c>
+      <c r="AQ7" s="1" t="n">
+        <v>2868.4091</v>
+      </c>
+      <c r="AR7" s="1" t="n">
+        <v>3214.5816</v>
+      </c>
+      <c r="AS7" s="1" t="n">
+        <v>3445.4155</v>
+      </c>
+      <c r="AT7" s="1" t="n">
         <v>187.4583</v>
       </c>
-      <c r="Z7" s="1" t="n">
+      <c r="AU7" s="1" t="n">
         <v>619.9032999999999</v>
       </c>
-      <c r="AA7" s="1" t="n">
+      <c r="AV7" s="1" t="n">
         <v>958.492</v>
       </c>
-      <c r="AB7" s="1" t="n">
+      <c r="AW7" s="1" t="n">
         <v>1376.0893</v>
       </c>
-      <c r="AC7" s="1" t="n">
+      <c r="AX7" s="1" t="n">
         <v>1891.5401</v>
       </c>
-      <c r="AD7" s="1" t="n">
+      <c r="AY7" s="1" t="n">
         <v>2265.1635</v>
       </c>
-      <c r="AE7" s="1" t="n">
+      <c r="AZ7" s="1" t="n">
         <v>2677.1783</v>
       </c>
-      <c r="AF7" s="1" t="n">
+      <c r="BA7" s="1" t="n">
         <v>206.5006</v>
       </c>
-      <c r="AG7" s="1" t="n">
+      <c r="BB7" s="1" t="n">
         <v>685.0957</v>
       </c>
-      <c r="AH7" s="1" t="n">
+      <c r="BC7" s="1" t="n">
         <v>1072.0482</v>
       </c>
-      <c r="AI7" s="1" t="n">
+      <c r="BD7" s="1" t="n">
         <v>711</v>
       </c>
-      <c r="AJ7" s="1" t="n">
+      <c r="BE7" s="1" t="n">
         <v>956.53</v>
       </c>
-      <c r="AK7" s="1" t="n">
+      <c r="BF7" s="1" t="n">
         <v>1315.38</v>
       </c>
     </row>
@@ -13615,45 +14376,108 @@
         <v>789.9240999999998</v>
       </c>
       <c r="X8" s="1" t="n">
+        <v>16.3394</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>65.37309999999999</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <v>124.7631</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>202.4972</v>
+      </c>
+      <c r="AB8" s="1" t="n">
+        <v>320.1103</v>
+      </c>
+      <c r="AC8" s="1" t="n">
+        <v>416.779</v>
+      </c>
+      <c r="AD8" s="1" t="n">
+        <v>523.4407</v>
+      </c>
+      <c r="AE8" s="1" t="n">
+        <v>637.5027</v>
+      </c>
+      <c r="AF8" s="1" t="n">
+        <v>740.0819</v>
+      </c>
+      <c r="AG8" s="1" t="n">
+        <v>847.7156</v>
+      </c>
+      <c r="AH8" s="1" t="n">
+        <v>1010.4513</v>
+      </c>
+      <c r="AI8" s="1" t="n">
         <v>21.0423</v>
       </c>
-      <c r="Y8" s="1" t="n">
+      <c r="AJ8" s="1" t="n">
+        <v>80.42499999999998</v>
+      </c>
+      <c r="AK8" s="1" t="n">
+        <v>154.0963</v>
+      </c>
+      <c r="AL8" s="1" t="n">
+        <v>261.2436</v>
+      </c>
+      <c r="AM8" s="1" t="n">
+        <v>413.9349</v>
+      </c>
+      <c r="AN8" s="1" t="n">
+        <v>532.8444</v>
+      </c>
+      <c r="AO8" s="1" t="n">
+        <v>667.6673</v>
+      </c>
+      <c r="AP8" s="1" t="n">
+        <v>826.4343</v>
+      </c>
+      <c r="AQ8" s="1" t="n">
+        <v>972.4675999999999</v>
+      </c>
+      <c r="AR8" s="1" t="n">
+        <v>1127.9594</v>
+      </c>
+      <c r="AS8" s="1" t="n">
+        <v>1308.6275</v>
+      </c>
+      <c r="AT8" s="1" t="n">
         <v>33.9015</v>
       </c>
-      <c r="Z8" s="1" t="n">
+      <c r="AU8" s="1" t="n">
         <v>115.1044</v>
       </c>
-      <c r="AA8" s="1" t="n">
+      <c r="AV8" s="1" t="n">
         <v>196.7842</v>
       </c>
-      <c r="AB8" s="1" t="n">
+      <c r="AW8" s="1" t="n">
         <v>338.9139</v>
       </c>
-      <c r="AC8" s="1" t="n">
+      <c r="AX8" s="1" t="n">
         <v>523.6341</v>
       </c>
-      <c r="AD8" s="1" t="n">
+      <c r="AY8" s="1" t="n">
         <v>682.9160000000001</v>
       </c>
-      <c r="AE8" s="1" t="n">
+      <c r="AZ8" s="1" t="n">
         <v>856.096</v>
       </c>
-      <c r="AF8" s="1" t="n">
+      <c r="BA8" s="1" t="n">
         <v>37.5065</v>
       </c>
-      <c r="AG8" s="1" t="n">
+      <c r="BB8" s="1" t="n">
         <v>131.7734</v>
       </c>
-      <c r="AH8" s="1" t="n">
+      <c r="BC8" s="1" t="n">
         <v>228.2443</v>
       </c>
-      <c r="AI8" s="1" t="n">
+      <c r="BD8" s="1" t="n">
         <v>355.36</v>
       </c>
-      <c r="AJ8" s="1" t="n">
+      <c r="BE8" s="1" t="n">
         <v>457.19</v>
       </c>
-      <c r="AK8" s="1" t="n">
+      <c r="BF8" s="1" t="n">
         <v>599.35</v>
       </c>
     </row>
@@ -13730,45 +14554,108 @@
         <v>1650.0247</v>
       </c>
       <c r="X9" s="1" t="n">
+        <v>1.5312</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>34.1061</v>
+      </c>
+      <c r="Z9" s="1" t="n">
+        <v>111.966</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>256.4358</v>
+      </c>
+      <c r="AB9" s="1" t="n">
+        <v>442.1372</v>
+      </c>
+      <c r="AC9" s="1" t="n">
+        <v>605.0034000000001</v>
+      </c>
+      <c r="AD9" s="1" t="n">
+        <v>821.883</v>
+      </c>
+      <c r="AE9" s="1" t="n">
+        <v>1006.5662</v>
+      </c>
+      <c r="AF9" s="1" t="n">
+        <v>1174.4522</v>
+      </c>
+      <c r="AG9" s="1" t="n">
+        <v>1263.6728</v>
+      </c>
+      <c r="AH9" s="1" t="n">
+        <v>1291.4397</v>
+      </c>
+      <c r="AI9" s="1" t="n">
         <v>5.5054</v>
       </c>
-      <c r="Y9" s="1" t="n">
+      <c r="AJ9" s="1" t="n">
+        <v>40.503</v>
+      </c>
+      <c r="AK9" s="1" t="n">
+        <v>119.1532</v>
+      </c>
+      <c r="AL9" s="1" t="n">
+        <v>261.7268</v>
+      </c>
+      <c r="AM9" s="1" t="n">
+        <v>495.2435</v>
+      </c>
+      <c r="AN9" s="1" t="n">
+        <v>673.0869</v>
+      </c>
+      <c r="AO9" s="1" t="n">
+        <v>880.5176</v>
+      </c>
+      <c r="AP9" s="1" t="n">
+        <v>1116.42</v>
+      </c>
+      <c r="AQ9" s="1" t="n">
+        <v>1334.0944</v>
+      </c>
+      <c r="AR9" s="1" t="n">
+        <v>1438.0465</v>
+      </c>
+      <c r="AS9" s="1" t="n">
+        <v>1479.0074</v>
+      </c>
+      <c r="AT9" s="1" t="n">
         <v>9.660399999999999</v>
       </c>
-      <c r="Z9" s="1" t="n">
+      <c r="AU9" s="1" t="n">
         <v>38.2918</v>
       </c>
-      <c r="AA9" s="1" t="n">
+      <c r="AV9" s="1" t="n">
         <v>88.07380000000001</v>
       </c>
-      <c r="AB9" s="1" t="n">
+      <c r="AW9" s="1" t="n">
         <v>195.6093</v>
       </c>
-      <c r="AC9" s="1" t="n">
+      <c r="AX9" s="1" t="n">
         <v>401.6151</v>
       </c>
-      <c r="AD9" s="1" t="n">
+      <c r="AY9" s="1" t="n">
         <v>555.8388</v>
       </c>
-      <c r="AE9" s="1" t="n">
+      <c r="AZ9" s="1" t="n">
         <v>690.5753</v>
       </c>
-      <c r="AF9" s="1" t="n">
+      <c r="BA9" s="1" t="n">
         <v>7.3169</v>
       </c>
-      <c r="AG9" s="1" t="n">
+      <c r="BB9" s="1" t="n">
         <v>36.8093</v>
       </c>
-      <c r="AH9" s="1" t="n">
+      <c r="BC9" s="1" t="n">
         <v>97.2139</v>
       </c>
-      <c r="AI9" s="1" t="n">
+      <c r="BD9" s="1" t="n">
         <v>141.65</v>
       </c>
-      <c r="AJ9" s="1" t="n">
+      <c r="BE9" s="1" t="n">
         <v>227.12</v>
       </c>
-      <c r="AK9" s="1" t="n">
+      <c r="BF9" s="1" t="n">
         <v>367.07</v>
       </c>
     </row>
@@ -13845,45 +14732,108 @@
         <v>4487.5607</v>
       </c>
       <c r="X10" s="1" t="n">
+        <v>111.1955</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>392.0086</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <v>718.4992999999999</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>1282.1865</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <v>2242.7773</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <v>2776.0917</v>
+      </c>
+      <c r="AD10" s="1" t="n">
+        <v>3371.2874</v>
+      </c>
+      <c r="AE10" s="1" t="n">
+        <v>4057.8798</v>
+      </c>
+      <c r="AF10" s="1" t="n">
+        <v>4659.3675</v>
+      </c>
+      <c r="AG10" s="1" t="n">
+        <v>5126.0007</v>
+      </c>
+      <c r="AH10" s="1" t="n">
+        <v>5455.8196</v>
+      </c>
+      <c r="AI10" s="1" t="n">
         <v>143.8235</v>
       </c>
-      <c r="Y10" s="1" t="n">
+      <c r="AJ10" s="1" t="n">
+        <v>503.1788</v>
+      </c>
+      <c r="AK10" s="1" t="n">
+        <v>913.7299</v>
+      </c>
+      <c r="AL10" s="1" t="n">
+        <v>1663.2198</v>
+      </c>
+      <c r="AM10" s="1" t="n">
+        <v>2721.1524</v>
+      </c>
+      <c r="AN10" s="1" t="n">
+        <v>3433.7452</v>
+      </c>
+      <c r="AO10" s="1" t="n">
+        <v>4090.0251</v>
+      </c>
+      <c r="AP10" s="1" t="n">
+        <v>5023.4148</v>
+      </c>
+      <c r="AQ10" s="1" t="n">
+        <v>5630.7755</v>
+      </c>
+      <c r="AR10" s="1" t="n">
+        <v>6159.3791</v>
+      </c>
+      <c r="AS10" s="1" t="n">
+        <v>6450.7513</v>
+      </c>
+      <c r="AT10" s="1" t="n">
         <v>161.0711</v>
       </c>
-      <c r="Z10" s="1" t="n">
+      <c r="AU10" s="1" t="n">
         <v>476.0095</v>
       </c>
-      <c r="AA10" s="1" t="n">
+      <c r="AV10" s="1" t="n">
         <v>840.8533</v>
       </c>
-      <c r="AB10" s="1" t="n">
+      <c r="AW10" s="1" t="n">
         <v>1377.8154</v>
       </c>
-      <c r="AC10" s="1" t="n">
+      <c r="AX10" s="1" t="n">
         <v>2101.6638</v>
       </c>
-      <c r="AD10" s="1" t="n">
+      <c r="AY10" s="1" t="n">
         <v>2579.4002</v>
       </c>
-      <c r="AE10" s="1" t="n">
+      <c r="AZ10" s="1" t="n">
         <v>2975.1341</v>
       </c>
-      <c r="AF10" s="1" t="n">
+      <c r="BA10" s="1" t="n">
         <v>145.9277</v>
       </c>
-      <c r="AG10" s="1" t="n">
+      <c r="BB10" s="1" t="n">
         <v>439.3409</v>
       </c>
-      <c r="AH10" s="1" t="n">
+      <c r="BC10" s="1" t="n">
         <v>722.157</v>
       </c>
-      <c r="AI10" s="1" t="n">
+      <c r="BD10" s="1" t="n">
         <v>185.51</v>
       </c>
-      <c r="AJ10" s="1" t="n">
+      <c r="BE10" s="1" t="n">
         <v>254.08</v>
       </c>
-      <c r="AK10" s="1" t="n">
+      <c r="BF10" s="1" t="n">
         <v>360.76</v>
       </c>
     </row>
@@ -13957,45 +14907,108 @@
         <v>1165.3918</v>
       </c>
       <c r="X11" s="1" t="n">
+        <v>4.4249</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>7.5456</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <v>45.4395</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>187.9074</v>
+      </c>
+      <c r="AB11" s="1" t="n">
+        <v>417.1619</v>
+      </c>
+      <c r="AC11" s="1" t="n">
+        <v>579.3004</v>
+      </c>
+      <c r="AD11" s="1" t="n">
+        <v>750.6875999999999</v>
+      </c>
+      <c r="AE11" s="1" t="n">
+        <v>935.2687</v>
+      </c>
+      <c r="AF11" s="1" t="n">
+        <v>1075.4789</v>
+      </c>
+      <c r="AG11" s="1" t="n">
+        <v>1223.3949</v>
+      </c>
+      <c r="AH11" s="1" t="n">
+        <v>1310.0259</v>
+      </c>
+      <c r="AI11" s="1" t="n">
         <v>13.3624</v>
       </c>
-      <c r="Y11" s="1" t="n">
+      <c r="AJ11" s="1" t="n">
+        <v>30.5188</v>
+      </c>
+      <c r="AK11" s="1" t="n">
+        <v>77.36539999999998</v>
+      </c>
+      <c r="AL11" s="1" t="n">
+        <v>175.3514</v>
+      </c>
+      <c r="AM11" s="1" t="n">
+        <v>351.8022</v>
+      </c>
+      <c r="AN11" s="1" t="n">
+        <v>515.6133</v>
+      </c>
+      <c r="AO11" s="1" t="n">
+        <v>664.6629</v>
+      </c>
+      <c r="AP11" s="1" t="n">
+        <v>866.2735</v>
+      </c>
+      <c r="AQ11" s="1" t="n">
+        <v>1019.7901</v>
+      </c>
+      <c r="AR11" s="1" t="n">
+        <v>1213.3025</v>
+      </c>
+      <c r="AS11" s="1" t="n">
+        <v>1252.4257</v>
+      </c>
+      <c r="AT11" s="1" t="n">
         <v>9.7384</v>
       </c>
-      <c r="Z11" s="1" t="n">
+      <c r="AU11" s="1" t="n">
         <v>25.3741</v>
       </c>
-      <c r="AA11" s="1" t="n">
+      <c r="AV11" s="1" t="n">
         <v>67.3903</v>
       </c>
-      <c r="AB11" s="1" t="n">
+      <c r="AW11" s="1" t="n">
         <v>143.0953</v>
       </c>
-      <c r="AC11" s="1" t="n">
+      <c r="AX11" s="1" t="n">
         <v>243.4314</v>
       </c>
-      <c r="AD11" s="1" t="n">
+      <c r="AY11" s="1" t="n">
         <v>409.0578</v>
       </c>
-      <c r="AE11" s="1" t="n">
+      <c r="AZ11" s="1" t="n">
         <v>545.9666999999999</v>
       </c>
-      <c r="AF11" s="1" t="n">
+      <c r="BA11" s="1" t="n">
         <v>9.3597</v>
       </c>
-      <c r="AG11" s="1" t="n">
+      <c r="BB11" s="1" t="n">
         <v>29.7167</v>
       </c>
-      <c r="AH11" s="1" t="n">
+      <c r="BC11" s="1" t="n">
         <v>85.5635</v>
       </c>
-      <c r="AI11" s="1" t="n">
+      <c r="BD11" s="1" t="n">
         <v>64.18000000000001</v>
       </c>
-      <c r="AJ11" s="1" t="n">
+      <c r="BE11" s="1" t="n">
         <v>116.27</v>
       </c>
-      <c r="AK11" s="1" t="n">
+      <c r="BF11" s="1" t="n">
         <v>170.04</v>
       </c>
     </row>
@@ -14072,45 +15085,108 @@
         <v>1219.3669</v>
       </c>
       <c r="X12" s="1" t="n">
+        <v>8.2865</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>27.2004</v>
+      </c>
+      <c r="Z12" s="1" t="n">
+        <v>82.98820000000001</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>198.3427</v>
+      </c>
+      <c r="AB12" s="1" t="n">
+        <v>378.2098</v>
+      </c>
+      <c r="AC12" s="1" t="n">
+        <v>568.4569</v>
+      </c>
+      <c r="AD12" s="1" t="n">
+        <v>805.3174</v>
+      </c>
+      <c r="AE12" s="1" t="n">
+        <v>999.4921000000001</v>
+      </c>
+      <c r="AF12" s="1" t="n">
+        <v>1196.8345</v>
+      </c>
+      <c r="AG12" s="1" t="n">
+        <v>1343.5125</v>
+      </c>
+      <c r="AH12" s="1" t="n">
+        <v>1535.8438</v>
+      </c>
+      <c r="AI12" s="1" t="n">
         <v>8.531000000000001</v>
       </c>
-      <c r="Y12" s="1" t="n">
+      <c r="AJ12" s="1" t="n">
+        <v>34.7606</v>
+      </c>
+      <c r="AK12" s="1" t="n">
+        <v>115.2515</v>
+      </c>
+      <c r="AL12" s="1" t="n">
+        <v>254.5196</v>
+      </c>
+      <c r="AM12" s="1" t="n">
+        <v>454.1255</v>
+      </c>
+      <c r="AN12" s="1" t="n">
+        <v>645.9049</v>
+      </c>
+      <c r="AO12" s="1" t="n">
+        <v>840.4403999999998</v>
+      </c>
+      <c r="AP12" s="1" t="n">
+        <v>1048.494</v>
+      </c>
+      <c r="AQ12" s="1" t="n">
+        <v>1253.5567</v>
+      </c>
+      <c r="AR12" s="1" t="n">
+        <v>1454.7406</v>
+      </c>
+      <c r="AS12" s="1" t="n">
+        <v>1604.833</v>
+      </c>
+      <c r="AT12" s="1" t="n">
         <v>5.4189</v>
       </c>
-      <c r="Z12" s="1" t="n">
+      <c r="AU12" s="1" t="n">
         <v>16.9226</v>
       </c>
-      <c r="AA12" s="1" t="n">
+      <c r="AV12" s="1" t="n">
         <v>58.5011</v>
       </c>
-      <c r="AB12" s="1" t="n">
+      <c r="AW12" s="1" t="n">
         <v>157.4279</v>
       </c>
-      <c r="AC12" s="1" t="n">
+      <c r="AX12" s="1" t="n">
         <v>332.856</v>
       </c>
-      <c r="AD12" s="1" t="n">
+      <c r="AY12" s="1" t="n">
         <v>438.2424</v>
       </c>
-      <c r="AE12" s="1" t="n">
+      <c r="AZ12" s="1" t="n">
         <v>547.4684</v>
       </c>
-      <c r="AF12" s="1" t="n">
+      <c r="BA12" s="1" t="n">
         <v>3.7037</v>
       </c>
-      <c r="AG12" s="1" t="n">
+      <c r="BB12" s="1" t="n">
         <v>16.9447</v>
       </c>
-      <c r="AH12" s="1" t="n">
+      <c r="BC12" s="1" t="n">
         <v>57.3575</v>
       </c>
-      <c r="AI12" s="1" t="n">
+      <c r="BD12" s="1" t="n">
         <v>46.7</v>
       </c>
-      <c r="AJ12" s="1" t="n">
+      <c r="BE12" s="1" t="n">
         <v>68.75</v>
       </c>
-      <c r="AK12" s="1" t="n">
+      <c r="BF12" s="1" t="n">
         <v>109.72</v>
       </c>
     </row>
@@ -14187,45 +15263,108 @@
         <v>2170.3103</v>
       </c>
       <c r="X13" s="1" t="n">
+        <v>315.8574</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>471.8066</v>
+      </c>
+      <c r="Z13" s="1" t="n">
+        <v>613.1838</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>821.121</v>
+      </c>
+      <c r="AB13" s="1" t="n">
+        <v>1042.4255</v>
+      </c>
+      <c r="AC13" s="1" t="n">
+        <v>1231.5687</v>
+      </c>
+      <c r="AD13" s="1" t="n">
+        <v>1449.0376</v>
+      </c>
+      <c r="AE13" s="1" t="n">
+        <v>1664.8561</v>
+      </c>
+      <c r="AF13" s="1" t="n">
+        <v>1894.649</v>
+      </c>
+      <c r="AG13" s="1" t="n">
+        <v>2150.0667</v>
+      </c>
+      <c r="AH13" s="1" t="n">
+        <v>2381.3574</v>
+      </c>
+      <c r="AI13" s="1" t="n">
         <v>380.1675</v>
       </c>
-      <c r="Y13" s="1" t="n">
+      <c r="AJ13" s="1" t="n">
+        <v>575.2039</v>
+      </c>
+      <c r="AK13" s="1" t="n">
+        <v>787.8533</v>
+      </c>
+      <c r="AL13" s="1" t="n">
+        <v>1015.5821</v>
+      </c>
+      <c r="AM13" s="1" t="n">
+        <v>1268.8705</v>
+      </c>
+      <c r="AN13" s="1" t="n">
+        <v>1493.3271</v>
+      </c>
+      <c r="AO13" s="1" t="n">
+        <v>1752.9776</v>
+      </c>
+      <c r="AP13" s="1" t="n">
+        <v>2010.2076</v>
+      </c>
+      <c r="AQ13" s="1" t="n">
+        <v>2279.6886</v>
+      </c>
+      <c r="AR13" s="1" t="n">
+        <v>2565.2366</v>
+      </c>
+      <c r="AS13" s="1" t="n">
+        <v>2819.5915</v>
+      </c>
+      <c r="AT13" s="1" t="n">
         <v>453.0848</v>
       </c>
-      <c r="Z13" s="1" t="n">
+      <c r="AU13" s="1" t="n">
         <v>713.0199</v>
       </c>
-      <c r="AA13" s="1" t="n">
+      <c r="AV13" s="1" t="n">
         <v>950.4052</v>
       </c>
-      <c r="AB13" s="1" t="n">
+      <c r="AW13" s="1" t="n">
         <v>1220.1418</v>
       </c>
-      <c r="AC13" s="1" t="n">
+      <c r="AX13" s="1" t="n">
         <v>1550.0154</v>
       </c>
-      <c r="AD13" s="1" t="n">
+      <c r="AY13" s="1" t="n">
         <v>1835.4498</v>
       </c>
-      <c r="AE13" s="1" t="n">
+      <c r="AZ13" s="1" t="n">
         <v>2085.6711</v>
       </c>
-      <c r="AF13" s="1" t="n">
+      <c r="BA13" s="1" t="n">
         <v>499.8124</v>
       </c>
-      <c r="AG13" s="1" t="n">
+      <c r="BB13" s="1" t="n">
         <v>800.5042999999998</v>
       </c>
-      <c r="AH13" s="1" t="n">
+      <c r="BC13" s="1" t="n">
         <v>1060.2072</v>
       </c>
-      <c r="AI13" s="1" t="n">
+      <c r="BD13" s="1" t="n">
         <v>1838.56</v>
       </c>
-      <c r="AJ13" s="1" t="n">
+      <c r="BE13" s="1" t="n">
         <v>2271.16</v>
       </c>
-      <c r="AK13" s="1" t="n">
+      <c r="BF13" s="1" t="n">
         <v>2747.1</v>
       </c>
     </row>
@@ -14302,45 +15441,108 @@
         <v>5552.6859</v>
       </c>
       <c r="X14" s="1" t="n">
+        <v>755.9272999999998</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>1306.6257</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <v>1764.3396</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>2291.7322</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>2902.2455</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>3450.8461</v>
+      </c>
+      <c r="AD14" s="1" t="n">
+        <v>3996.9846</v>
+      </c>
+      <c r="AE14" s="1" t="n">
+        <v>4502.8813</v>
+      </c>
+      <c r="AF14" s="1" t="n">
+        <v>4979.2197</v>
+      </c>
+      <c r="AG14" s="1" t="n">
+        <v>5553.56</v>
+      </c>
+      <c r="AH14" s="1" t="n">
+        <v>6206.0953</v>
+      </c>
+      <c r="AI14" s="1" t="n">
         <v>857.0866999999998</v>
       </c>
-      <c r="Y14" s="1" t="n">
+      <c r="AJ14" s="1" t="n">
+        <v>1476.6726</v>
+      </c>
+      <c r="AK14" s="1" t="n">
+        <v>2051.4457</v>
+      </c>
+      <c r="AL14" s="1" t="n">
+        <v>2701.822</v>
+      </c>
+      <c r="AM14" s="1" t="n">
+        <v>3386.3539</v>
+      </c>
+      <c r="AN14" s="1" t="n">
+        <v>4001.9197</v>
+      </c>
+      <c r="AO14" s="1" t="n">
+        <v>4592.1757</v>
+      </c>
+      <c r="AP14" s="1" t="n">
+        <v>5202.6377</v>
+      </c>
+      <c r="AQ14" s="1" t="n">
+        <v>5756.1041</v>
+      </c>
+      <c r="AR14" s="1" t="n">
+        <v>6460.6361</v>
+      </c>
+      <c r="AS14" s="1" t="n">
+        <v>7241.4512</v>
+      </c>
+      <c r="AT14" s="1" t="n">
         <v>1115.4358</v>
       </c>
-      <c r="Z14" s="1" t="n">
+      <c r="AU14" s="1" t="n">
         <v>1846.579</v>
       </c>
-      <c r="AA14" s="1" t="n">
+      <c r="AV14" s="1" t="n">
         <v>2497.8473</v>
       </c>
-      <c r="AB14" s="1" t="n">
+      <c r="AW14" s="1" t="n">
         <v>3240.3904</v>
       </c>
-      <c r="AC14" s="1" t="n">
+      <c r="AX14" s="1" t="n">
         <v>4161.8344</v>
       </c>
-      <c r="AD14" s="1" t="n">
+      <c r="AY14" s="1" t="n">
         <v>4843.7827</v>
       </c>
-      <c r="AE14" s="1" t="n">
+      <c r="AZ14" s="1" t="n">
         <v>5493.0431</v>
       </c>
-      <c r="AF14" s="1" t="n">
+      <c r="BA14" s="1" t="n">
         <v>1161.4919</v>
       </c>
-      <c r="AG14" s="1" t="n">
+      <c r="BB14" s="1" t="n">
         <v>1981.5363</v>
       </c>
-      <c r="AH14" s="1" t="n">
+      <c r="BC14" s="1" t="n">
         <v>2687.5838</v>
       </c>
-      <c r="AI14" s="1" t="n">
+      <c r="BD14" s="1" t="n">
         <v>2640.19</v>
       </c>
-      <c r="AJ14" s="1" t="n">
+      <c r="BE14" s="1" t="n">
         <v>3233.88</v>
       </c>
-      <c r="AK14" s="1" t="n">
+      <c r="BF14" s="1" t="n">
         <v>3801.93</v>
       </c>
     </row>
@@ -14417,45 +15619,108 @@
         <v>4137.254</v>
       </c>
       <c r="X15" s="1" t="n">
+        <v>530.8907</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>960.3184</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <v>1327.0146</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>1790.9731</v>
+      </c>
+      <c r="AB15" s="1" t="n">
+        <v>2335.099</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <v>2803.9704</v>
+      </c>
+      <c r="AD15" s="1" t="n">
+        <v>3269.3789</v>
+      </c>
+      <c r="AE15" s="1" t="n">
+        <v>3792.087</v>
+      </c>
+      <c r="AF15" s="1" t="n">
+        <v>4282.1589</v>
+      </c>
+      <c r="AG15" s="1" t="n">
+        <v>4747.2124</v>
+      </c>
+      <c r="AH15" s="1" t="n">
+        <v>5226.2667</v>
+      </c>
+      <c r="AI15" s="1" t="n">
         <v>676.7829</v>
       </c>
-      <c r="Y15" s="1" t="n">
+      <c r="AJ15" s="1" t="n">
+        <v>1192.1928</v>
+      </c>
+      <c r="AK15" s="1" t="n">
+        <v>1645.4645</v>
+      </c>
+      <c r="AL15" s="1" t="n">
+        <v>2151.2596</v>
+      </c>
+      <c r="AM15" s="1" t="n">
+        <v>2832.8554</v>
+      </c>
+      <c r="AN15" s="1" t="n">
+        <v>3342.0902</v>
+      </c>
+      <c r="AO15" s="1" t="n">
+        <v>3853.2084</v>
+      </c>
+      <c r="AP15" s="1" t="n">
+        <v>4475.3759</v>
+      </c>
+      <c r="AQ15" s="1" t="n">
+        <v>4974.4621</v>
+      </c>
+      <c r="AR15" s="1" t="n">
+        <v>5497.2769</v>
+      </c>
+      <c r="AS15" s="1" t="n">
+        <v>6216.2493</v>
+      </c>
+      <c r="AT15" s="1" t="n">
         <v>845.8920000000001</v>
       </c>
-      <c r="Z15" s="1" t="n">
+      <c r="AU15" s="1" t="n">
         <v>1481.8343</v>
       </c>
-      <c r="AA15" s="1" t="n">
+      <c r="AV15" s="1" t="n">
         <v>2024.5794</v>
       </c>
-      <c r="AB15" s="1" t="n">
+      <c r="AW15" s="1" t="n">
         <v>2679.031</v>
       </c>
-      <c r="AC15" s="1" t="n">
+      <c r="AX15" s="1" t="n">
         <v>3530.7064</v>
       </c>
-      <c r="AD15" s="1" t="n">
+      <c r="AY15" s="1" t="n">
         <v>4133.416</v>
       </c>
-      <c r="AE15" s="1" t="n">
+      <c r="AZ15" s="1" t="n">
         <v>4703.4852</v>
       </c>
-      <c r="AF15" s="1" t="n">
+      <c r="BA15" s="1" t="n">
         <v>789.4792999999999</v>
       </c>
-      <c r="AG15" s="1" t="n">
+      <c r="BB15" s="1" t="n">
         <v>1457.3669</v>
       </c>
-      <c r="AH15" s="1" t="n">
+      <c r="BC15" s="1" t="n">
         <v>2017.2453</v>
       </c>
-      <c r="AI15" s="1" t="n">
+      <c r="BD15" s="1" t="n">
         <v>2498.33</v>
       </c>
-      <c r="AJ15" s="1" t="n">
+      <c r="BE15" s="1" t="n">
         <v>3147.88</v>
       </c>
-      <c r="AK15" s="1" t="n">
+      <c r="BF15" s="1" t="n">
         <v>3944.7</v>
       </c>
     </row>
@@ -14532,45 +15797,108 @@
         <v>2590.0724</v>
       </c>
       <c r="X16" s="1" t="n">
+        <v>375.1768</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>609.8827</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <v>863.0684</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>1127.0772</v>
+      </c>
+      <c r="AB16" s="1" t="n">
+        <v>1436.0415</v>
+      </c>
+      <c r="AC16" s="1" t="n">
+        <v>1669.9365</v>
+      </c>
+      <c r="AD16" s="1" t="n">
+        <v>2011.9636</v>
+      </c>
+      <c r="AE16" s="1" t="n">
+        <v>2314.4024</v>
+      </c>
+      <c r="AF16" s="1" t="n">
+        <v>2572.6083</v>
+      </c>
+      <c r="AG16" s="1" t="n">
+        <v>2894.6013</v>
+      </c>
+      <c r="AH16" s="1" t="n">
+        <v>3151.6065</v>
+      </c>
+      <c r="AI16" s="1" t="n">
         <v>392.7641</v>
       </c>
-      <c r="Y16" s="1" t="n">
+      <c r="AJ16" s="1" t="n">
+        <v>700.2545</v>
+      </c>
+      <c r="AK16" s="1" t="n">
+        <v>1002.8617</v>
+      </c>
+      <c r="AL16" s="1" t="n">
+        <v>1372.8558</v>
+      </c>
+      <c r="AM16" s="1" t="n">
+        <v>1757.5533</v>
+      </c>
+      <c r="AN16" s="1" t="n">
+        <v>2065.6758</v>
+      </c>
+      <c r="AO16" s="1" t="n">
+        <v>2488.9727</v>
+      </c>
+      <c r="AP16" s="1" t="n">
+        <v>2875.5846</v>
+      </c>
+      <c r="AQ16" s="1" t="n">
+        <v>3215.6727</v>
+      </c>
+      <c r="AR16" s="1" t="n">
+        <v>3618.2512</v>
+      </c>
+      <c r="AS16" s="1" t="n">
+        <v>3946.2264</v>
+      </c>
+      <c r="AT16" s="1" t="n">
         <v>477.9503</v>
       </c>
-      <c r="Z16" s="1" t="n">
+      <c r="AU16" s="1" t="n">
         <v>842.4367999999998</v>
       </c>
-      <c r="AA16" s="1" t="n">
+      <c r="AV16" s="1" t="n">
         <v>1166.3418</v>
       </c>
-      <c r="AB16" s="1" t="n">
+      <c r="AW16" s="1" t="n">
         <v>1560.5479</v>
       </c>
-      <c r="AC16" s="1" t="n">
+      <c r="AX16" s="1" t="n">
         <v>2016.9882</v>
       </c>
-      <c r="AD16" s="1" t="n">
+      <c r="AY16" s="1" t="n">
         <v>2411.6804</v>
       </c>
-      <c r="AE16" s="1" t="n">
+      <c r="AZ16" s="1" t="n">
         <v>2821.3573</v>
       </c>
-      <c r="AF16" s="1" t="n">
+      <c r="BA16" s="1" t="n">
         <v>499.8409</v>
       </c>
-      <c r="AG16" s="1" t="n">
+      <c r="BB16" s="1" t="n">
         <v>915.6013</v>
       </c>
-      <c r="AH16" s="1" t="n">
+      <c r="BC16" s="1" t="n">
         <v>1287.5627</v>
       </c>
-      <c r="AI16" s="1" t="n">
+      <c r="BD16" s="1" t="n">
         <v>902.92</v>
       </c>
-      <c r="AJ16" s="1" t="n">
+      <c r="BE16" s="1" t="n">
         <v>1095.12</v>
       </c>
-      <c r="AK16" s="1" t="n">
+      <c r="BF16" s="1" t="n">
         <v>1270.06</v>
       </c>
     </row>
@@ -14647,45 +15975,108 @@
         <v>2402.6056</v>
       </c>
       <c r="X17" s="1" t="n">
+        <v>283.0088</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>586.8704</v>
+      </c>
+      <c r="Z17" s="1" t="n">
+        <v>776.1377</v>
+      </c>
+      <c r="AA17" s="1" t="n">
+        <v>1036.6991</v>
+      </c>
+      <c r="AB17" s="1" t="n">
+        <v>1335.9444</v>
+      </c>
+      <c r="AC17" s="1" t="n">
+        <v>1520.236</v>
+      </c>
+      <c r="AD17" s="1" t="n">
+        <v>1742.9321</v>
+      </c>
+      <c r="AE17" s="1" t="n">
+        <v>2016.1062</v>
+      </c>
+      <c r="AF17" s="1" t="n">
+        <v>2225.0978</v>
+      </c>
+      <c r="AG17" s="1" t="n">
+        <v>2495.1809</v>
+      </c>
+      <c r="AH17" s="1" t="n">
+        <v>2824.1249</v>
+      </c>
+      <c r="AI17" s="1" t="n">
         <v>368.6536</v>
       </c>
-      <c r="Y17" s="1" t="n">
+      <c r="AJ17" s="1" t="n">
+        <v>700.3939</v>
+      </c>
+      <c r="AK17" s="1" t="n">
+        <v>996.2665</v>
+      </c>
+      <c r="AL17" s="1" t="n">
+        <v>1333.1189</v>
+      </c>
+      <c r="AM17" s="1" t="n">
+        <v>1790.4811</v>
+      </c>
+      <c r="AN17" s="1" t="n">
+        <v>2046.0616</v>
+      </c>
+      <c r="AO17" s="1" t="n">
+        <v>2333.6295</v>
+      </c>
+      <c r="AP17" s="1" t="n">
+        <v>2693.3574</v>
+      </c>
+      <c r="AQ17" s="1" t="n">
+        <v>2980.4595</v>
+      </c>
+      <c r="AR17" s="1" t="n">
+        <v>3341.3918</v>
+      </c>
+      <c r="AS17" s="1" t="n">
+        <v>3702.9727</v>
+      </c>
+      <c r="AT17" s="1" t="n">
         <v>596.6861</v>
       </c>
-      <c r="Z17" s="1" t="n">
+      <c r="AU17" s="1" t="n">
         <v>1044.2265</v>
       </c>
-      <c r="AA17" s="1" t="n">
+      <c r="AV17" s="1" t="n">
         <v>1361.3283</v>
       </c>
-      <c r="AB17" s="1" t="n">
+      <c r="AW17" s="1" t="n">
         <v>1761.71</v>
       </c>
-      <c r="AC17" s="1" t="n">
+      <c r="AX17" s="1" t="n">
         <v>2331.9866</v>
       </c>
-      <c r="AD17" s="1" t="n">
+      <c r="AY17" s="1" t="n">
         <v>2652.9348</v>
       </c>
-      <c r="AE17" s="1" t="n">
+      <c r="AZ17" s="1" t="n">
         <v>2996.5501</v>
       </c>
-      <c r="AF17" s="1" t="n">
+      <c r="BA17" s="1" t="n">
         <v>596.1528</v>
       </c>
-      <c r="AG17" s="1" t="n">
+      <c r="BB17" s="1" t="n">
         <v>1095.4642</v>
       </c>
-      <c r="AH17" s="1" t="n">
+      <c r="BC17" s="1" t="n">
         <v>1418.8192</v>
       </c>
-      <c r="AI17" s="1" t="n">
+      <c r="BD17" s="1" t="n">
         <v>800.53</v>
       </c>
-      <c r="AJ17" s="1" t="n">
+      <c r="BE17" s="1" t="n">
         <v>958.33</v>
       </c>
-      <c r="AK17" s="1" t="n">
+      <c r="BF17" s="1" t="n">
         <v>1131.69</v>
       </c>
     </row>
@@ -14762,45 +16153,108 @@
         <v>852.6883</v>
       </c>
       <c r="X18" s="1" t="n">
+        <v>87.70010000000001</v>
+      </c>
+      <c r="Y18" s="1" t="n">
+        <v>165.3713</v>
+      </c>
+      <c r="Z18" s="1" t="n">
+        <v>248.3004</v>
+      </c>
+      <c r="AA18" s="1" t="n">
+        <v>339.8166</v>
+      </c>
+      <c r="AB18" s="1" t="n">
+        <v>431.0787</v>
+      </c>
+      <c r="AC18" s="1" t="n">
+        <v>507.225</v>
+      </c>
+      <c r="AD18" s="1" t="n">
+        <v>589.431</v>
+      </c>
+      <c r="AE18" s="1" t="n">
+        <v>701.7345</v>
+      </c>
+      <c r="AF18" s="1" t="n">
+        <v>784.0582000000001</v>
+      </c>
+      <c r="AG18" s="1" t="n">
+        <v>875.5168999999999</v>
+      </c>
+      <c r="AH18" s="1" t="n">
+        <v>969.6176</v>
+      </c>
+      <c r="AI18" s="1" t="n">
         <v>130.3625</v>
       </c>
-      <c r="Y18" s="1" t="n">
+      <c r="AJ18" s="1" t="n">
+        <v>217.071</v>
+      </c>
+      <c r="AK18" s="1" t="n">
+        <v>298.8802</v>
+      </c>
+      <c r="AL18" s="1" t="n">
+        <v>404.4801</v>
+      </c>
+      <c r="AM18" s="1" t="n">
+        <v>505.1209</v>
+      </c>
+      <c r="AN18" s="1" t="n">
+        <v>596.8287</v>
+      </c>
+      <c r="AO18" s="1" t="n">
+        <v>704.5674</v>
+      </c>
+      <c r="AP18" s="1" t="n">
+        <v>829.0451</v>
+      </c>
+      <c r="AQ18" s="1" t="n">
+        <v>929.8973</v>
+      </c>
+      <c r="AR18" s="1" t="n">
+        <v>1060.2646</v>
+      </c>
+      <c r="AS18" s="1" t="n">
+        <v>1174.5768</v>
+      </c>
+      <c r="AT18" s="1" t="n">
         <v>166.4562</v>
       </c>
-      <c r="Z18" s="1" t="n">
+      <c r="AU18" s="1" t="n">
         <v>273.1064</v>
       </c>
-      <c r="AA18" s="1" t="n">
+      <c r="AV18" s="1" t="n">
         <v>377.4364</v>
       </c>
-      <c r="AB18" s="1" t="n">
+      <c r="AW18" s="1" t="n">
         <v>486.4091</v>
       </c>
-      <c r="AC18" s="1" t="n">
+      <c r="AX18" s="1" t="n">
         <v>641.0638</v>
       </c>
-      <c r="AD18" s="1" t="n">
+      <c r="AY18" s="1" t="n">
         <v>768.7782999999998</v>
       </c>
-      <c r="AE18" s="1" t="n">
+      <c r="AZ18" s="1" t="n">
         <v>920.6261</v>
       </c>
-      <c r="AF18" s="1" t="n">
+      <c r="BA18" s="1" t="n">
         <v>189.6595</v>
       </c>
-      <c r="AG18" s="1" t="n">
+      <c r="BB18" s="1" t="n">
         <v>312.3605</v>
       </c>
-      <c r="AH18" s="1" t="n">
+      <c r="BC18" s="1" t="n">
         <v>440.4727</v>
       </c>
-      <c r="AI18" s="1" t="n">
+      <c r="BD18" s="1" t="n">
         <v>444.35</v>
       </c>
-      <c r="AJ18" s="1" t="n">
+      <c r="BE18" s="1" t="n">
         <v>564.95</v>
       </c>
-      <c r="AK18" s="1" t="n">
+      <c r="BF18" s="1" t="n">
         <v>685.85</v>
       </c>
     </row>
@@ -14877,45 +16331,108 @@
         <v>4108.0778</v>
       </c>
       <c r="X19" s="1" t="n">
+        <v>335.1767</v>
+      </c>
+      <c r="Y19" s="1" t="n">
+        <v>745.0567</v>
+      </c>
+      <c r="Z19" s="1" t="n">
+        <v>1068.767</v>
+      </c>
+      <c r="AA19" s="1" t="n">
+        <v>1492.7733</v>
+      </c>
+      <c r="AB19" s="1" t="n">
+        <v>2039.8375</v>
+      </c>
+      <c r="AC19" s="1" t="n">
+        <v>2467.3382</v>
+      </c>
+      <c r="AD19" s="1" t="n">
+        <v>2922.1273</v>
+      </c>
+      <c r="AE19" s="1" t="n">
+        <v>3374.3271</v>
+      </c>
+      <c r="AF19" s="1" t="n">
+        <v>3788.5937</v>
+      </c>
+      <c r="AG19" s="1" t="n">
+        <v>4251.4106</v>
+      </c>
+      <c r="AH19" s="1" t="n">
+        <v>4708.3068</v>
+      </c>
+      <c r="AI19" s="1" t="n">
         <v>402.9231</v>
       </c>
-      <c r="Y19" s="1" t="n">
+      <c r="AJ19" s="1" t="n">
+        <v>857.9973</v>
+      </c>
+      <c r="AK19" s="1" t="n">
+        <v>1254.8854</v>
+      </c>
+      <c r="AL19" s="1" t="n">
+        <v>1724.1125</v>
+      </c>
+      <c r="AM19" s="1" t="n">
+        <v>2327.68</v>
+      </c>
+      <c r="AN19" s="1" t="n">
+        <v>2814.829</v>
+      </c>
+      <c r="AO19" s="1" t="n">
+        <v>3297.697</v>
+      </c>
+      <c r="AP19" s="1" t="n">
+        <v>3838.6911</v>
+      </c>
+      <c r="AQ19" s="1" t="n">
+        <v>4318.6857</v>
+      </c>
+      <c r="AR19" s="1" t="n">
+        <v>4864.3749</v>
+      </c>
+      <c r="AS19" s="1" t="n">
+        <v>5444.5312</v>
+      </c>
+      <c r="AT19" s="1" t="n">
         <v>498.4137</v>
       </c>
-      <c r="Z19" s="1" t="n">
+      <c r="AU19" s="1" t="n">
         <v>990.258</v>
       </c>
-      <c r="AA19" s="1" t="n">
+      <c r="AV19" s="1" t="n">
         <v>1461.4088</v>
       </c>
-      <c r="AB19" s="1" t="n">
+      <c r="AW19" s="1" t="n">
         <v>2004.0368</v>
       </c>
-      <c r="AC19" s="1" t="n">
+      <c r="AX19" s="1" t="n">
         <v>2654.1094</v>
       </c>
-      <c r="AD19" s="1" t="n">
+      <c r="AY19" s="1" t="n">
         <v>3194.5291</v>
       </c>
-      <c r="AE19" s="1" t="n">
+      <c r="AZ19" s="1" t="n">
         <v>3715.745</v>
       </c>
-      <c r="AF19" s="1" t="n">
+      <c r="BA19" s="1" t="n">
         <v>527.0735</v>
       </c>
-      <c r="AG19" s="1" t="n">
+      <c r="BB19" s="1" t="n">
         <v>1059.3349</v>
       </c>
-      <c r="AH19" s="1" t="n">
+      <c r="BC19" s="1" t="n">
         <v>1601.0519</v>
       </c>
-      <c r="AI19" s="1" t="n">
+      <c r="BD19" s="1" t="n">
         <v>1823.27</v>
       </c>
-      <c r="AJ19" s="1" t="n">
+      <c r="BE19" s="1" t="n">
         <v>2360.49</v>
       </c>
-      <c r="AK19" s="1" t="n">
+      <c r="BF19" s="1" t="n">
         <v>2996.27</v>
       </c>
     </row>
@@ -14992,45 +16509,108 @@
         <v>2620.0097</v>
       </c>
       <c r="X20" s="1" t="n">
+        <v>167.9439</v>
+      </c>
+      <c r="Y20" s="1" t="n">
+        <v>417.3573</v>
+      </c>
+      <c r="Z20" s="1" t="n">
+        <v>689.2553</v>
+      </c>
+      <c r="AA20" s="1" t="n">
+        <v>942.9962</v>
+      </c>
+      <c r="AB20" s="1" t="n">
+        <v>1271.8374</v>
+      </c>
+      <c r="AC20" s="1" t="n">
+        <v>1529.7639</v>
+      </c>
+      <c r="AD20" s="1" t="n">
+        <v>1811.0181</v>
+      </c>
+      <c r="AE20" s="1" t="n">
+        <v>2100.0748</v>
+      </c>
+      <c r="AF20" s="1" t="n">
+        <v>2359.9119</v>
+      </c>
+      <c r="AG20" s="1" t="n">
+        <v>2696.1485</v>
+      </c>
+      <c r="AH20" s="1" t="n">
+        <v>3035.2884</v>
+      </c>
+      <c r="AI20" s="1" t="n">
         <v>219.5908</v>
       </c>
-      <c r="Y20" s="1" t="n">
+      <c r="AJ20" s="1" t="n">
+        <v>520.3831</v>
+      </c>
+      <c r="AK20" s="1" t="n">
+        <v>836.6815</v>
+      </c>
+      <c r="AL20" s="1" t="n">
+        <v>1180.1042</v>
+      </c>
+      <c r="AM20" s="1" t="n">
+        <v>1597.936</v>
+      </c>
+      <c r="AN20" s="1" t="n">
+        <v>1910.7346</v>
+      </c>
+      <c r="AO20" s="1" t="n">
+        <v>2225.1584</v>
+      </c>
+      <c r="AP20" s="1" t="n">
+        <v>2610.3983</v>
+      </c>
+      <c r="AQ20" s="1" t="n">
+        <v>2933.263</v>
+      </c>
+      <c r="AR20" s="1" t="n">
+        <v>3385.0499</v>
+      </c>
+      <c r="AS20" s="1" t="n">
+        <v>3843.759</v>
+      </c>
+      <c r="AT20" s="1" t="n">
         <v>323.6915</v>
       </c>
-      <c r="Z20" s="1" t="n">
+      <c r="AU20" s="1" t="n">
         <v>697.1774</v>
       </c>
-      <c r="AA20" s="1" t="n">
+      <c r="AV20" s="1" t="n">
         <v>1053.2863</v>
       </c>
-      <c r="AB20" s="1" t="n">
+      <c r="AW20" s="1" t="n">
         <v>1479.8946</v>
       </c>
-      <c r="AC20" s="1" t="n">
+      <c r="AX20" s="1" t="n">
         <v>2040.5409</v>
       </c>
-      <c r="AD20" s="1" t="n">
+      <c r="AY20" s="1" t="n">
         <v>2465.5561</v>
       </c>
-      <c r="AE20" s="1" t="n">
+      <c r="AZ20" s="1" t="n">
         <v>2876.661</v>
       </c>
-      <c r="AF20" s="1" t="n">
+      <c r="BA20" s="1" t="n">
         <v>363.2482</v>
       </c>
-      <c r="AG20" s="1" t="n">
+      <c r="BB20" s="1" t="n">
         <v>803.6064</v>
       </c>
-      <c r="AH20" s="1" t="n">
+      <c r="BC20" s="1" t="n">
         <v>1261.955</v>
       </c>
-      <c r="AI20" s="1" t="n">
+      <c r="BD20" s="1" t="n">
         <v>1116.4</v>
       </c>
-      <c r="AJ20" s="1" t="n">
+      <c r="BE20" s="1" t="n">
         <v>1390.6</v>
       </c>
-      <c r="AK20" s="1" t="n">
+      <c r="BF20" s="1" t="n">
         <v>1721.76</v>
       </c>
     </row>
@@ -15107,45 +16687,108 @@
         <v>2063.2122</v>
       </c>
       <c r="X21" s="1" t="n">
+        <v>157.9955</v>
+      </c>
+      <c r="Y21" s="1" t="n">
+        <v>408.2679</v>
+      </c>
+      <c r="Z21" s="1" t="n">
+        <v>581.2654</v>
+      </c>
+      <c r="AA21" s="1" t="n">
+        <v>778.3080999999999</v>
+      </c>
+      <c r="AB21" s="1" t="n">
+        <v>1159.6503</v>
+      </c>
+      <c r="AC21" s="1" t="n">
+        <v>1342.6013</v>
+      </c>
+      <c r="AD21" s="1" t="n">
+        <v>1556.7501</v>
+      </c>
+      <c r="AE21" s="1" t="n">
+        <v>1768.7892</v>
+      </c>
+      <c r="AF21" s="1" t="n">
+        <v>1981.8845</v>
+      </c>
+      <c r="AG21" s="1" t="n">
+        <v>2223.1607</v>
+      </c>
+      <c r="AH21" s="1" t="n">
+        <v>2539.4649</v>
+      </c>
+      <c r="AI21" s="1" t="n">
         <v>220.705</v>
       </c>
-      <c r="Y21" s="1" t="n">
+      <c r="AJ21" s="1" t="n">
+        <v>513.2274</v>
+      </c>
+      <c r="AK21" s="1" t="n">
+        <v>732.2673999999998</v>
+      </c>
+      <c r="AL21" s="1" t="n">
+        <v>990.1365</v>
+      </c>
+      <c r="AM21" s="1" t="n">
+        <v>1472.1568</v>
+      </c>
+      <c r="AN21" s="1" t="n">
+        <v>1721.7488</v>
+      </c>
+      <c r="AO21" s="1" t="n">
+        <v>1994.3511</v>
+      </c>
+      <c r="AP21" s="1" t="n">
+        <v>2296.5074</v>
+      </c>
+      <c r="AQ21" s="1" t="n">
+        <v>2565.3933</v>
+      </c>
+      <c r="AR21" s="1" t="n">
+        <v>2882.7686</v>
+      </c>
+      <c r="AS21" s="1" t="n">
+        <v>3286.0234</v>
+      </c>
+      <c r="AT21" s="1" t="n">
         <v>316.0484</v>
       </c>
-      <c r="Z21" s="1" t="n">
+      <c r="AU21" s="1" t="n">
         <v>656.9538</v>
       </c>
-      <c r="AA21" s="1" t="n">
+      <c r="AV21" s="1" t="n">
         <v>928.607</v>
       </c>
-      <c r="AB21" s="1" t="n">
+      <c r="AW21" s="1" t="n">
         <v>1259.7687</v>
       </c>
-      <c r="AC21" s="1" t="n">
+      <c r="AX21" s="1" t="n">
         <v>1879.4739</v>
       </c>
-      <c r="AD21" s="1" t="n">
+      <c r="AY21" s="1" t="n">
         <v>2210.9539</v>
       </c>
-      <c r="AE21" s="1" t="n">
+      <c r="AZ21" s="1" t="n">
         <v>2548.7745</v>
       </c>
-      <c r="AF21" s="1" t="n">
+      <c r="BA21" s="1" t="n">
         <v>324.6281</v>
       </c>
-      <c r="AG21" s="1" t="n">
+      <c r="BB21" s="1" t="n">
         <v>698.1613</v>
       </c>
-      <c r="AH21" s="1" t="n">
+      <c r="BC21" s="1" t="n">
         <v>1009.3123</v>
       </c>
-      <c r="AI21" s="1" t="n">
+      <c r="BD21" s="1" t="n">
         <v>1321.65</v>
       </c>
-      <c r="AJ21" s="1" t="n">
+      <c r="BE21" s="1" t="n">
         <v>1740.37</v>
       </c>
-      <c r="AK21" s="1" t="n">
+      <c r="BF21" s="1" t="n">
         <v>2193.2</v>
       </c>
     </row>
@@ -15222,45 +16865,108 @@
         <v>1896.6647</v>
       </c>
       <c r="X22" s="1" t="n">
+        <v>178.2109</v>
+      </c>
+      <c r="Y22" s="1" t="n">
+        <v>369.2622</v>
+      </c>
+      <c r="Z22" s="1" t="n">
+        <v>523.4361</v>
+      </c>
+      <c r="AA22" s="1" t="n">
+        <v>694.6777</v>
+      </c>
+      <c r="AB22" s="1" t="n">
+        <v>913.6775</v>
+      </c>
+      <c r="AC22" s="1" t="n">
+        <v>1071.6732</v>
+      </c>
+      <c r="AD22" s="1" t="n">
+        <v>1264.4625</v>
+      </c>
+      <c r="AE22" s="1" t="n">
+        <v>1486.3875</v>
+      </c>
+      <c r="AF22" s="1" t="n">
+        <v>1684.4434</v>
+      </c>
+      <c r="AG22" s="1" t="n">
+        <v>1930.9846</v>
+      </c>
+      <c r="AH22" s="1" t="n">
+        <v>2210.5229</v>
+      </c>
+      <c r="AI22" s="1" t="n">
         <v>234.9489</v>
       </c>
-      <c r="Y22" s="1" t="n">
+      <c r="AJ22" s="1" t="n">
+        <v>424.643</v>
+      </c>
+      <c r="AK22" s="1" t="n">
+        <v>586.3318</v>
+      </c>
+      <c r="AL22" s="1" t="n">
+        <v>806.5403</v>
+      </c>
+      <c r="AM22" s="1" t="n">
+        <v>1092.1788</v>
+      </c>
+      <c r="AN22" s="1" t="n">
+        <v>1309.1066</v>
+      </c>
+      <c r="AO22" s="1" t="n">
+        <v>1530.4285</v>
+      </c>
+      <c r="AP22" s="1" t="n">
+        <v>1774.1842</v>
+      </c>
+      <c r="AQ22" s="1" t="n">
+        <v>2000.2666</v>
+      </c>
+      <c r="AR22" s="1" t="n">
+        <v>2342.1051</v>
+      </c>
+      <c r="AS22" s="1" t="n">
+        <v>2628.3245</v>
+      </c>
+      <c r="AT22" s="1" t="n">
         <v>275.4221</v>
       </c>
-      <c r="Z22" s="1" t="n">
+      <c r="AU22" s="1" t="n">
         <v>488.9126</v>
       </c>
-      <c r="AA22" s="1" t="n">
+      <c r="AV22" s="1" t="n">
         <v>668.7761</v>
       </c>
-      <c r="AB22" s="1" t="n">
+      <c r="AW22" s="1" t="n">
         <v>882.7491999999999</v>
       </c>
-      <c r="AC22" s="1" t="n">
+      <c r="AX22" s="1" t="n">
         <v>1185.5969</v>
       </c>
-      <c r="AD22" s="1" t="n">
+      <c r="AY22" s="1" t="n">
         <v>1393.923</v>
       </c>
-      <c r="AE22" s="1" t="n">
+      <c r="AZ22" s="1" t="n">
         <v>1599.7355</v>
       </c>
-      <c r="AF22" s="1" t="n">
+      <c r="BA22" s="1" t="n">
         <v>249.6448</v>
       </c>
-      <c r="AG22" s="1" t="n">
+      <c r="BB22" s="1" t="n">
         <v>502.9117</v>
       </c>
-      <c r="AH22" s="1" t="n">
+      <c r="BC22" s="1" t="n">
         <v>700.0788</v>
       </c>
-      <c r="AI22" s="1" t="n">
+      <c r="BD22" s="1" t="n">
         <v>661.92</v>
       </c>
-      <c r="AJ22" s="1" t="n">
+      <c r="BE22" s="1" t="n">
         <v>798.51</v>
       </c>
-      <c r="AK22" s="1" t="n">
+      <c r="BF22" s="1" t="n">
         <v>993.5700000000001</v>
       </c>
     </row>
@@ -15337,45 +17043,108 @@
         <v>4899.1884</v>
       </c>
       <c r="X23" s="1" t="n">
+        <v>523.0531</v>
+      </c>
+      <c r="Y23" s="1" t="n">
+        <v>945.1206</v>
+      </c>
+      <c r="Z23" s="1" t="n">
+        <v>1276.1582</v>
+      </c>
+      <c r="AA23" s="1" t="n">
+        <v>1708.8428</v>
+      </c>
+      <c r="AB23" s="1" t="n">
+        <v>2193.3909</v>
+      </c>
+      <c r="AC23" s="1" t="n">
+        <v>2593.9233</v>
+      </c>
+      <c r="AD23" s="1" t="n">
+        <v>3142.997</v>
+      </c>
+      <c r="AE23" s="1" t="n">
+        <v>3672.0932</v>
+      </c>
+      <c r="AF23" s="1" t="n">
+        <v>4133.0205</v>
+      </c>
+      <c r="AG23" s="1" t="n">
+        <v>4745.2271</v>
+      </c>
+      <c r="AH23" s="1" t="n">
+        <v>5352.7853</v>
+      </c>
+      <c r="AI23" s="1" t="n">
         <v>611.4949</v>
       </c>
-      <c r="Y23" s="1" t="n">
+      <c r="AJ23" s="1" t="n">
+        <v>1105.1533</v>
+      </c>
+      <c r="AK23" s="1" t="n">
+        <v>1533.6158</v>
+      </c>
+      <c r="AL23" s="1" t="n">
+        <v>2031.4624</v>
+      </c>
+      <c r="AM23" s="1" t="n">
+        <v>2708.3644</v>
+      </c>
+      <c r="AN23" s="1" t="n">
+        <v>3231.4506</v>
+      </c>
+      <c r="AO23" s="1" t="n">
+        <v>3773.7758</v>
+      </c>
+      <c r="AP23" s="1" t="n">
+        <v>4444.0194</v>
+      </c>
+      <c r="AQ23" s="1" t="n">
+        <v>5017.6933</v>
+      </c>
+      <c r="AR23" s="1" t="n">
+        <v>5714.7696</v>
+      </c>
+      <c r="AS23" s="1" t="n">
+        <v>6489.592</v>
+      </c>
+      <c r="AT23" s="1" t="n">
         <v>934.6569</v>
       </c>
-      <c r="Z23" s="1" t="n">
+      <c r="AU23" s="1" t="n">
         <v>1548.5877</v>
       </c>
-      <c r="AA23" s="1" t="n">
+      <c r="AV23" s="1" t="n">
         <v>2129.176</v>
       </c>
-      <c r="AB23" s="1" t="n">
+      <c r="AW23" s="1" t="n">
         <v>2802.6905</v>
       </c>
-      <c r="AC23" s="1" t="n">
+      <c r="AX23" s="1" t="n">
         <v>3736.658</v>
       </c>
-      <c r="AD23" s="1" t="n">
+      <c r="AY23" s="1" t="n">
         <v>4502.1337</v>
       </c>
-      <c r="AE23" s="1" t="n">
+      <c r="AZ23" s="1" t="n">
         <v>5280.3519</v>
       </c>
-      <c r="AF23" s="1" t="n">
+      <c r="BA23" s="1" t="n">
         <v>991.8961</v>
       </c>
-      <c r="AG23" s="1" t="n">
+      <c r="BB23" s="1" t="n">
         <v>1646.5467</v>
       </c>
-      <c r="AH23" s="1" t="n">
+      <c r="BC23" s="1" t="n">
         <v>2356.3201</v>
       </c>
-      <c r="AI23" s="1" t="n">
+      <c r="BD23" s="1" t="n">
         <v>2477.43</v>
       </c>
-      <c r="AJ23" s="1" t="n">
+      <c r="BE23" s="1" t="n">
         <v>3088.59</v>
       </c>
-      <c r="AK23" s="1" t="n">
+      <c r="BF23" s="1" t="n">
         <v>3967.96</v>
       </c>
     </row>
@@ -15452,45 +17221,108 @@
         <v>1500.4585</v>
       </c>
       <c r="X24" s="1" t="n">
+        <v>149.5022</v>
+      </c>
+      <c r="Y24" s="1" t="n">
+        <v>307.343</v>
+      </c>
+      <c r="Z24" s="1" t="n">
+        <v>406.0607</v>
+      </c>
+      <c r="AA24" s="1" t="n">
+        <v>547.3792</v>
+      </c>
+      <c r="AB24" s="1" t="n">
+        <v>769.9107</v>
+      </c>
+      <c r="AC24" s="1" t="n">
+        <v>863.3192</v>
+      </c>
+      <c r="AD24" s="1" t="n">
+        <v>970.8185</v>
+      </c>
+      <c r="AE24" s="1" t="n">
+        <v>1083.3539</v>
+      </c>
+      <c r="AF24" s="1" t="n">
+        <v>1229.9444</v>
+      </c>
+      <c r="AG24" s="1" t="n">
+        <v>1383.3825</v>
+      </c>
+      <c r="AH24" s="1" t="n">
+        <v>1554.9388</v>
+      </c>
+      <c r="AI24" s="1" t="n">
         <v>135.2589</v>
       </c>
-      <c r="Y24" s="1" t="n">
+      <c r="AJ24" s="1" t="n">
+        <v>267.7526</v>
+      </c>
+      <c r="AK24" s="1" t="n">
+        <v>379.9534</v>
+      </c>
+      <c r="AL24" s="1" t="n">
+        <v>521.6876</v>
+      </c>
+      <c r="AM24" s="1" t="n">
+        <v>719.0921</v>
+      </c>
+      <c r="AN24" s="1" t="n">
+        <v>824.2020999999999</v>
+      </c>
+      <c r="AO24" s="1" t="n">
+        <v>938.3128</v>
+      </c>
+      <c r="AP24" s="1" t="n">
+        <v>1070.0038</v>
+      </c>
+      <c r="AQ24" s="1" t="n">
+        <v>1213.6256</v>
+      </c>
+      <c r="AR24" s="1" t="n">
+        <v>1427.0829</v>
+      </c>
+      <c r="AS24" s="1" t="n">
+        <v>1614.6322</v>
+      </c>
+      <c r="AT24" s="1" t="n">
         <v>162.4115</v>
       </c>
-      <c r="Z24" s="1" t="n">
+      <c r="AU24" s="1" t="n">
         <v>307.2608</v>
       </c>
-      <c r="AA24" s="1" t="n">
+      <c r="AV24" s="1" t="n">
         <v>424.995</v>
       </c>
-      <c r="AB24" s="1" t="n">
+      <c r="AW24" s="1" t="n">
         <v>564.0249</v>
       </c>
-      <c r="AC24" s="1" t="n">
+      <c r="AX24" s="1" t="n">
         <v>800.8123000000001</v>
       </c>
-      <c r="AD24" s="1" t="n">
+      <c r="AY24" s="1" t="n">
         <v>940.1053000000001</v>
       </c>
-      <c r="AE24" s="1" t="n">
+      <c r="AZ24" s="1" t="n">
         <v>1070.7219</v>
       </c>
-      <c r="AF24" s="1" t="n">
+      <c r="BA24" s="1" t="n">
         <v>171.1329</v>
       </c>
-      <c r="AG24" s="1" t="n">
+      <c r="BB24" s="1" t="n">
         <v>351.7993</v>
       </c>
-      <c r="AH24" s="1" t="n">
+      <c r="BC24" s="1" t="n">
         <v>508.1643</v>
       </c>
-      <c r="AI24" s="1" t="n">
+      <c r="BD24" s="1" t="n">
         <v>250.7</v>
       </c>
-      <c r="AJ24" s="1" t="n">
+      <c r="BE24" s="1" t="n">
         <v>304.15</v>
       </c>
-      <c r="AK24" s="1" t="n">
+      <c r="BF24" s="1" t="n">
         <v>383.36</v>
       </c>
     </row>
@@ -15567,45 +17399,108 @@
         <v>663.0486</v>
       </c>
       <c r="X25" s="1" t="n">
+        <v>91.88939999999999</v>
+      </c>
+      <c r="Y25" s="1" t="n">
+        <v>153.2341</v>
+      </c>
+      <c r="Z25" s="1" t="n">
+        <v>212.1007</v>
+      </c>
+      <c r="AA25" s="1" t="n">
+        <v>293.0989</v>
+      </c>
+      <c r="AB25" s="1" t="n">
+        <v>387.431</v>
+      </c>
+      <c r="AC25" s="1" t="n">
+        <v>447.3876</v>
+      </c>
+      <c r="AD25" s="1" t="n">
+        <v>538.8810999999999</v>
+      </c>
+      <c r="AE25" s="1" t="n">
+        <v>621.9088</v>
+      </c>
+      <c r="AF25" s="1" t="n">
+        <v>696.6375</v>
+      </c>
+      <c r="AG25" s="1" t="n">
+        <v>799.1796000000001</v>
+      </c>
+      <c r="AH25" s="1" t="n">
+        <v>886.644</v>
+      </c>
+      <c r="AI25" s="1" t="n">
         <v>124.6931</v>
       </c>
-      <c r="Y25" s="1" t="n">
+      <c r="AJ25" s="1" t="n">
+        <v>198.6208</v>
+      </c>
+      <c r="AK25" s="1" t="n">
+        <v>282.3159</v>
+      </c>
+      <c r="AL25" s="1" t="n">
+        <v>375.1525</v>
+      </c>
+      <c r="AM25" s="1" t="n">
+        <v>500.4734</v>
+      </c>
+      <c r="AN25" s="1" t="n">
+        <v>602.1794</v>
+      </c>
+      <c r="AO25" s="1" t="n">
+        <v>704.9562</v>
+      </c>
+      <c r="AP25" s="1" t="n">
+        <v>814.4507</v>
+      </c>
+      <c r="AQ25" s="1" t="n">
+        <v>919.3453</v>
+      </c>
+      <c r="AR25" s="1" t="n">
+        <v>1058.2258</v>
+      </c>
+      <c r="AS25" s="1" t="n">
+        <v>1196.7581</v>
+      </c>
+      <c r="AT25" s="1" t="n">
         <v>161.6805</v>
       </c>
-      <c r="Z25" s="1" t="n">
+      <c r="AU25" s="1" t="n">
         <v>270.7443</v>
       </c>
-      <c r="AA25" s="1" t="n">
+      <c r="AV25" s="1" t="n">
         <v>395.1906</v>
       </c>
-      <c r="AB25" s="1" t="n">
+      <c r="AW25" s="1" t="n">
         <v>545.1629</v>
       </c>
-      <c r="AC25" s="1" t="n">
+      <c r="AX25" s="1" t="n">
         <v>735.0154</v>
       </c>
-      <c r="AD25" s="1" t="n">
+      <c r="AY25" s="1" t="n">
         <v>898.3941999999998</v>
       </c>
-      <c r="AE25" s="1" t="n">
+      <c r="AZ25" s="1" t="n">
         <v>1042.0387</v>
       </c>
-      <c r="AF25" s="1" t="n">
+      <c r="BA25" s="1" t="n">
         <v>177.8309</v>
       </c>
-      <c r="AG25" s="1" t="n">
+      <c r="BB25" s="1" t="n">
         <v>313.37</v>
       </c>
-      <c r="AH25" s="1" t="n">
+      <c r="BC25" s="1" t="n">
         <v>441.733</v>
       </c>
-      <c r="AI25" s="1" t="n">
+      <c r="BD25" s="1" t="n">
         <v>238.32</v>
       </c>
-      <c r="AJ25" s="1" t="n">
+      <c r="BE25" s="1" t="n">
         <v>283.22</v>
       </c>
-      <c r="AK25" s="1" t="n">
+      <c r="BF25" s="1" t="n">
         <v>341.45</v>
       </c>
     </row>
@@ -15682,45 +17577,108 @@
         <v>2015.0883</v>
       </c>
       <c r="X26" s="1" t="n">
+        <v>247.5685</v>
+      </c>
+      <c r="Y26" s="1" t="n">
+        <v>436.6191</v>
+      </c>
+      <c r="Z26" s="1" t="n">
+        <v>584.0242</v>
+      </c>
+      <c r="AA26" s="1" t="n">
+        <v>783.2496999999998</v>
+      </c>
+      <c r="AB26" s="1" t="n">
+        <v>996.1575</v>
+      </c>
+      <c r="AC26" s="1" t="n">
+        <v>1218.9178</v>
+      </c>
+      <c r="AD26" s="1" t="n">
+        <v>1454.3493</v>
+      </c>
+      <c r="AE26" s="1" t="n">
+        <v>1751.4424</v>
+      </c>
+      <c r="AF26" s="1" t="n">
+        <v>1949.3358</v>
+      </c>
+      <c r="AG26" s="1" t="n">
+        <v>2203.0429</v>
+      </c>
+      <c r="AH26" s="1" t="n">
+        <v>2508.35</v>
+      </c>
+      <c r="AI26" s="1" t="n">
         <v>298.2648</v>
       </c>
-      <c r="Y26" s="1" t="n">
+      <c r="AJ26" s="1" t="n">
+        <v>547.2518</v>
+      </c>
+      <c r="AK26" s="1" t="n">
+        <v>747.1672999999998</v>
+      </c>
+      <c r="AL26" s="1" t="n">
+        <v>988.5694</v>
+      </c>
+      <c r="AM26" s="1" t="n">
+        <v>1272.2791</v>
+      </c>
+      <c r="AN26" s="1" t="n">
+        <v>1500.3526</v>
+      </c>
+      <c r="AO26" s="1" t="n">
+        <v>1774.4014</v>
+      </c>
+      <c r="AP26" s="1" t="n">
+        <v>2112.1901</v>
+      </c>
+      <c r="AQ26" s="1" t="n">
+        <v>2329.8987</v>
+      </c>
+      <c r="AR26" s="1" t="n">
+        <v>2645.0988</v>
+      </c>
+      <c r="AS26" s="1" t="n">
+        <v>3012.7838</v>
+      </c>
+      <c r="AT26" s="1" t="n">
         <v>435.138</v>
       </c>
-      <c r="Z26" s="1" t="n">
+      <c r="AU26" s="1" t="n">
         <v>761.9207</v>
       </c>
-      <c r="AA26" s="1" t="n">
+      <c r="AV26" s="1" t="n">
         <v>1006.7654</v>
       </c>
-      <c r="AB26" s="1" t="n">
+      <c r="AW26" s="1" t="n">
         <v>1344.2471</v>
       </c>
-      <c r="AC26" s="1" t="n">
+      <c r="AX26" s="1" t="n">
         <v>1715.8209</v>
       </c>
-      <c r="AD26" s="1" t="n">
+      <c r="AY26" s="1" t="n">
         <v>2012.1675</v>
       </c>
-      <c r="AE26" s="1" t="n">
+      <c r="AZ26" s="1" t="n">
         <v>2340.1324</v>
       </c>
-      <c r="AF26" s="1" t="n">
+      <c r="BA26" s="1" t="n">
         <v>400.2674</v>
       </c>
-      <c r="AG26" s="1" t="n">
+      <c r="BB26" s="1" t="n">
         <v>746.8062999999999</v>
       </c>
-      <c r="AH26" s="1" t="n">
+      <c r="BC26" s="1" t="n">
         <v>1012.2007</v>
       </c>
-      <c r="AI26" s="1" t="n">
+      <c r="BD26" s="1" t="n">
         <v>655.3200000000001</v>
       </c>
-      <c r="AJ26" s="1" t="n">
+      <c r="BE26" s="1" t="n">
         <v>814.7</v>
       </c>
-      <c r="AK26" s="1" t="n">
+      <c r="BF26" s="1" t="n">
         <v>942.48</v>
       </c>
     </row>
@@ -15797,45 +17755,108 @@
         <v>2836.7129</v>
       </c>
       <c r="X27" s="1" t="n">
+        <v>345.6669</v>
+      </c>
+      <c r="Y27" s="1" t="n">
+        <v>665.3267</v>
+      </c>
+      <c r="Z27" s="1" t="n">
+        <v>911.77</v>
+      </c>
+      <c r="AA27" s="1" t="n">
+        <v>1193.9909</v>
+      </c>
+      <c r="AB27" s="1" t="n">
+        <v>1551.4771</v>
+      </c>
+      <c r="AC27" s="1" t="n">
+        <v>1823.0523</v>
+      </c>
+      <c r="AD27" s="1" t="n">
+        <v>2074.12</v>
+      </c>
+      <c r="AE27" s="1" t="n">
+        <v>2352.5818</v>
+      </c>
+      <c r="AF27" s="1" t="n">
+        <v>2644.5464</v>
+      </c>
+      <c r="AG27" s="1" t="n">
+        <v>2939.5037</v>
+      </c>
+      <c r="AH27" s="1" t="n">
+        <v>3266.397</v>
+      </c>
+      <c r="AI27" s="1" t="n">
         <v>407.2592</v>
       </c>
-      <c r="Y27" s="1" t="n">
+      <c r="AJ27" s="1" t="n">
+        <v>772.9023999999998</v>
+      </c>
+      <c r="AK27" s="1" t="n">
+        <v>1053.6911</v>
+      </c>
+      <c r="AL27" s="1" t="n">
+        <v>1407.4502</v>
+      </c>
+      <c r="AM27" s="1" t="n">
+        <v>1823.7945</v>
+      </c>
+      <c r="AN27" s="1" t="n">
+        <v>2152.4641</v>
+      </c>
+      <c r="AO27" s="1" t="n">
+        <v>2455.1217</v>
+      </c>
+      <c r="AP27" s="1" t="n">
+        <v>2811.2643</v>
+      </c>
+      <c r="AQ27" s="1" t="n">
+        <v>3118.3032</v>
+      </c>
+      <c r="AR27" s="1" t="n">
+        <v>3449.8408</v>
+      </c>
+      <c r="AS27" s="1" t="n">
+        <v>3852.9951</v>
+      </c>
+      <c r="AT27" s="1" t="n">
         <v>535.1501</v>
       </c>
-      <c r="Z27" s="1" t="n">
+      <c r="AU27" s="1" t="n">
         <v>1021.5721</v>
       </c>
-      <c r="AA27" s="1" t="n">
+      <c r="AV27" s="1" t="n">
         <v>1384.5898</v>
       </c>
-      <c r="AB27" s="1" t="n">
+      <c r="AW27" s="1" t="n">
         <v>1838.6435</v>
       </c>
-      <c r="AC27" s="1" t="n">
+      <c r="AX27" s="1" t="n">
         <v>2370.0803</v>
       </c>
-      <c r="AD27" s="1" t="n">
+      <c r="AY27" s="1" t="n">
         <v>2770.461</v>
       </c>
-      <c r="AE27" s="1" t="n">
+      <c r="AZ27" s="1" t="n">
         <v>3218.7141</v>
       </c>
-      <c r="AF27" s="1" t="n">
+      <c r="BA27" s="1" t="n">
         <v>604.4391000000001</v>
       </c>
-      <c r="AG27" s="1" t="n">
+      <c r="BB27" s="1" t="n">
         <v>1168.7381</v>
       </c>
-      <c r="AH27" s="1" t="n">
+      <c r="BC27" s="1" t="n">
         <v>1563.1767</v>
       </c>
-      <c r="AI27" s="1" t="n">
+      <c r="BD27" s="1" t="n">
         <v>1313.11</v>
       </c>
-      <c r="AJ27" s="1" t="n">
+      <c r="BE27" s="1" t="n">
         <v>1713.79</v>
       </c>
-      <c r="AK27" s="1" t="n">
+      <c r="BF27" s="1" t="n">
         <v>2154.84</v>
       </c>
     </row>
@@ -15912,45 +17933,108 @@
         <v>878.6671</v>
       </c>
       <c r="X28" s="1" t="n">
+        <v>81.5271</v>
+      </c>
+      <c r="Y28" s="1" t="n">
+        <v>219.8063</v>
+      </c>
+      <c r="Z28" s="1" t="n">
+        <v>322.1699</v>
+      </c>
+      <c r="AA28" s="1" t="n">
+        <v>436.6323</v>
+      </c>
+      <c r="AB28" s="1" t="n">
+        <v>574.7891</v>
+      </c>
+      <c r="AC28" s="1" t="n">
+        <v>699.2304</v>
+      </c>
+      <c r="AD28" s="1" t="n">
+        <v>832.5829</v>
+      </c>
+      <c r="AE28" s="1" t="n">
+        <v>1000.3241</v>
+      </c>
+      <c r="AF28" s="1" t="n">
+        <v>1139.7686</v>
+      </c>
+      <c r="AG28" s="1" t="n">
+        <v>1329.0542</v>
+      </c>
+      <c r="AH28" s="1" t="n">
+        <v>1467.596</v>
+      </c>
+      <c r="AI28" s="1" t="n">
         <v>152.2357</v>
       </c>
-      <c r="Y28" s="1" t="n">
+      <c r="AJ28" s="1" t="n">
+        <v>383.0529</v>
+      </c>
+      <c r="AK28" s="1" t="n">
+        <v>496.133</v>
+      </c>
+      <c r="AL28" s="1" t="n">
+        <v>664.7686</v>
+      </c>
+      <c r="AM28" s="1" t="n">
+        <v>859.5798</v>
+      </c>
+      <c r="AN28" s="1" t="n">
+        <v>1028.1271</v>
+      </c>
+      <c r="AO28" s="1" t="n">
+        <v>1211.8071</v>
+      </c>
+      <c r="AP28" s="1" t="n">
+        <v>1420.6713</v>
+      </c>
+      <c r="AQ28" s="1" t="n">
+        <v>1598.6025</v>
+      </c>
+      <c r="AR28" s="1" t="n">
+        <v>1778.4148</v>
+      </c>
+      <c r="AS28" s="1" t="n">
+        <v>1942.5435</v>
+      </c>
+      <c r="AT28" s="1" t="n">
         <v>247.8663</v>
       </c>
-      <c r="Z28" s="1" t="n">
+      <c r="AU28" s="1" t="n">
         <v>462.6392</v>
       </c>
-      <c r="AA28" s="1" t="n">
+      <c r="AV28" s="1" t="n">
         <v>613.8</v>
       </c>
-      <c r="AB28" s="1" t="n">
+      <c r="AW28" s="1" t="n">
         <v>806.5546000000001</v>
       </c>
-      <c r="AC28" s="1" t="n">
+      <c r="AX28" s="1" t="n">
         <v>1072.4312</v>
       </c>
-      <c r="AD28" s="1" t="n">
+      <c r="AY28" s="1" t="n">
         <v>1248.7406</v>
       </c>
-      <c r="AE28" s="1" t="n">
+      <c r="AZ28" s="1" t="n">
         <v>1427.5177</v>
       </c>
-      <c r="AF28" s="1" t="n">
+      <c r="BA28" s="1" t="n">
         <v>210.3799</v>
       </c>
-      <c r="AG28" s="1" t="n">
+      <c r="BB28" s="1" t="n">
         <v>427.4238</v>
       </c>
-      <c r="AH28" s="1" t="n">
+      <c r="BC28" s="1" t="n">
         <v>608.1145</v>
       </c>
-      <c r="AI28" s="1" t="n">
+      <c r="BD28" s="1" t="n">
         <v>385.18</v>
       </c>
-      <c r="AJ28" s="1" t="n">
+      <c r="BE28" s="1" t="n">
         <v>465.16</v>
       </c>
-      <c r="AK28" s="1" t="n">
+      <c r="BF28" s="1" t="n">
         <v>552.7</v>
       </c>
     </row>
@@ -16027,45 +18111,108 @@
         <v>1272.7171</v>
       </c>
       <c r="X29" s="1" t="n">
+        <v>150.8033</v>
+      </c>
+      <c r="Y29" s="1" t="n">
+        <v>289.6692</v>
+      </c>
+      <c r="Z29" s="1" t="n">
+        <v>431.5448</v>
+      </c>
+      <c r="AA29" s="1" t="n">
+        <v>585.1332</v>
+      </c>
+      <c r="AB29" s="1" t="n">
+        <v>792.2693</v>
+      </c>
+      <c r="AC29" s="1" t="n">
+        <v>923.2006</v>
+      </c>
+      <c r="AD29" s="1" t="n">
+        <v>1061.564</v>
+      </c>
+      <c r="AE29" s="1" t="n">
+        <v>1246.9756</v>
+      </c>
+      <c r="AF29" s="1" t="n">
+        <v>1385.4316</v>
+      </c>
+      <c r="AG29" s="1" t="n">
+        <v>1573.3691</v>
+      </c>
+      <c r="AH29" s="1" t="n">
+        <v>1782.1351</v>
+      </c>
+      <c r="AI29" s="1" t="n">
         <v>218.0659</v>
       </c>
-      <c r="Y29" s="1" t="n">
+      <c r="AJ29" s="1" t="n">
+        <v>410.6194</v>
+      </c>
+      <c r="AK29" s="1" t="n">
+        <v>587.0279</v>
+      </c>
+      <c r="AL29" s="1" t="n">
+        <v>810.4556</v>
+      </c>
+      <c r="AM29" s="1" t="n">
+        <v>1084.4303</v>
+      </c>
+      <c r="AN29" s="1" t="n">
+        <v>1272.3294</v>
+      </c>
+      <c r="AO29" s="1" t="n">
+        <v>1470.0274</v>
+      </c>
+      <c r="AP29" s="1" t="n">
+        <v>1737.5133</v>
+      </c>
+      <c r="AQ29" s="1" t="n">
+        <v>1989.7647</v>
+      </c>
+      <c r="AR29" s="1" t="n">
+        <v>2189.4794</v>
+      </c>
+      <c r="AS29" s="1" t="n">
+        <v>2488.3284</v>
+      </c>
+      <c r="AT29" s="1" t="n">
         <v>239.4925</v>
       </c>
-      <c r="Z29" s="1" t="n">
+      <c r="AU29" s="1" t="n">
         <v>478.032</v>
       </c>
-      <c r="AA29" s="1" t="n">
+      <c r="AV29" s="1" t="n">
         <v>666.8313000000001</v>
       </c>
-      <c r="AB29" s="1" t="n">
+      <c r="AW29" s="1" t="n">
         <v>867.9811999999998</v>
       </c>
-      <c r="AC29" s="1" t="n">
+      <c r="AX29" s="1" t="n">
         <v>1227.4794</v>
       </c>
-      <c r="AD29" s="1" t="n">
+      <c r="AY29" s="1" t="n">
         <v>1420.2291</v>
       </c>
-      <c r="AE29" s="1" t="n">
+      <c r="AZ29" s="1" t="n">
         <v>1641.5218</v>
       </c>
-      <c r="AF29" s="1" t="n">
+      <c r="BA29" s="1" t="n">
         <v>240.4501</v>
       </c>
-      <c r="AG29" s="1" t="n">
+      <c r="BB29" s="1" t="n">
         <v>485.3637</v>
       </c>
-      <c r="AH29" s="1" t="n">
+      <c r="BC29" s="1" t="n">
         <v>695.9169000000001</v>
       </c>
-      <c r="AI29" s="1" t="n">
+      <c r="BD29" s="1" t="n">
         <v>384.64</v>
       </c>
-      <c r="AJ29" s="1" t="n">
+      <c r="BE29" s="1" t="n">
         <v>473.69</v>
       </c>
-      <c r="AK29" s="1" t="n">
+      <c r="BF29" s="1" t="n">
         <v>581.25</v>
       </c>
     </row>
@@ -16136,45 +18283,108 @@
         <v>5.1342</v>
       </c>
       <c r="X30" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="Y30" s="1" t="n">
+        <v>0.4606</v>
+      </c>
+      <c r="Z30" s="1" t="n">
+        <v>0.8895999999999999</v>
+      </c>
+      <c r="AA30" s="1" t="n">
+        <v>1.1555</v>
+      </c>
+      <c r="AB30" s="1" t="n">
+        <v>2.2073</v>
+      </c>
+      <c r="AC30" s="1" t="n">
+        <v>3.0992</v>
+      </c>
+      <c r="AD30" s="1" t="n">
+        <v>3.9665</v>
+      </c>
+      <c r="AE30" s="1" t="n">
+        <v>4.665</v>
+      </c>
+      <c r="AF30" s="1" t="n">
+        <v>5.3149</v>
+      </c>
+      <c r="AG30" s="1" t="n">
+        <v>6.3261</v>
+      </c>
+      <c r="AH30" s="1" t="n">
+        <v>6.8719</v>
+      </c>
+      <c r="AI30" s="1" t="n">
         <v>0.018</v>
       </c>
-      <c r="Y30" s="1" t="n">
+      <c r="AJ30" s="1" t="n">
+        <v>0.6308</v>
+      </c>
+      <c r="AK30" s="1" t="n">
+        <v>1.3016</v>
+      </c>
+      <c r="AL30" s="1" t="n">
+        <v>2.3531</v>
+      </c>
+      <c r="AM30" s="1" t="n">
+        <v>3.3094</v>
+      </c>
+      <c r="AN30" s="1" t="n">
+        <v>4.4597</v>
+      </c>
+      <c r="AO30" s="1" t="n">
+        <v>5.5058</v>
+      </c>
+      <c r="AP30" s="1" t="n">
+        <v>6.2909</v>
+      </c>
+      <c r="AQ30" s="1" t="n">
+        <v>7.6762</v>
+      </c>
+      <c r="AR30" s="1" t="n">
+        <v>8.481400000000001</v>
+      </c>
+      <c r="AS30" s="1" t="n">
+        <v>9.6777</v>
+      </c>
+      <c r="AT30" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="Z30" s="1" t="n">
+      <c r="AU30" s="1" t="n">
         <v>0.759</v>
       </c>
-      <c r="AA30" s="1" t="n">
+      <c r="AV30" s="1" t="n">
         <v>4.8376</v>
       </c>
-      <c r="AB30" s="1" t="n">
+      <c r="AW30" s="1" t="n">
         <v>8.112399999999999</v>
       </c>
-      <c r="AC30" s="1" t="n">
+      <c r="AX30" s="1" t="n">
         <v>14.4584</v>
       </c>
-      <c r="AD30" s="1" t="n">
+      <c r="AY30" s="1" t="n">
         <v>20.3346</v>
       </c>
-      <c r="AE30" s="1" t="n">
+      <c r="AZ30" s="1" t="n">
         <v>28.816</v>
       </c>
-      <c r="AF30" s="1" t="n">
+      <c r="BA30" s="1" t="n">
         <v>0.13</v>
       </c>
-      <c r="AG30" s="1" t="n">
+      <c r="BB30" s="1" t="n">
         <v>2.1034</v>
       </c>
-      <c r="AH30" s="1" t="n">
+      <c r="BC30" s="1" t="n">
         <v>5.8283</v>
       </c>
-      <c r="AI30" s="1" t="n">
+      <c r="BD30" s="1" t="n">
         <v>10.59</v>
       </c>
-      <c r="AJ30" s="1" t="n">
+      <c r="BE30" s="1" t="n">
         <v>15.95</v>
       </c>
-      <c r="AK30" s="1" t="n">
+      <c r="BF30" s="1" t="n">
         <v>23.72</v>
       </c>
     </row>
@@ -16251,45 +18461,108 @@
         <v>1420.5279</v>
       </c>
       <c r="X31" s="1" t="n">
+        <v>119.4244</v>
+      </c>
+      <c r="Y31" s="1" t="n">
+        <v>224.6475</v>
+      </c>
+      <c r="Z31" s="1" t="n">
+        <v>335.1262</v>
+      </c>
+      <c r="AA31" s="1" t="n">
+        <v>506.7371</v>
+      </c>
+      <c r="AB31" s="1" t="n">
+        <v>734.9229</v>
+      </c>
+      <c r="AC31" s="1" t="n">
+        <v>856.0947999999999</v>
+      </c>
+      <c r="AD31" s="1" t="n">
+        <v>1019.109</v>
+      </c>
+      <c r="AE31" s="1" t="n">
+        <v>1226.389</v>
+      </c>
+      <c r="AF31" s="1" t="n">
+        <v>1408.3508</v>
+      </c>
+      <c r="AG31" s="1" t="n">
+        <v>1636.1568</v>
+      </c>
+      <c r="AH31" s="1" t="n">
+        <v>1835.9321</v>
+      </c>
+      <c r="AI31" s="1" t="n">
         <v>162.069</v>
       </c>
-      <c r="Y31" s="1" t="n">
+      <c r="AJ31" s="1" t="n">
+        <v>302.7732</v>
+      </c>
+      <c r="AK31" s="1" t="n">
+        <v>460.1099</v>
+      </c>
+      <c r="AL31" s="1" t="n">
+        <v>665.6034</v>
+      </c>
+      <c r="AM31" s="1" t="n">
+        <v>976.2127</v>
+      </c>
+      <c r="AN31" s="1" t="n">
+        <v>1175.0061</v>
+      </c>
+      <c r="AO31" s="1" t="n">
+        <v>1362.8609</v>
+      </c>
+      <c r="AP31" s="1" t="n">
+        <v>1561.7315</v>
+      </c>
+      <c r="AQ31" s="1" t="n">
+        <v>1766.7418</v>
+      </c>
+      <c r="AR31" s="1" t="n">
+        <v>2064.63</v>
+      </c>
+      <c r="AS31" s="1" t="n">
+        <v>2240.1692</v>
+      </c>
+      <c r="AT31" s="1" t="n">
         <v>180.5453</v>
       </c>
-      <c r="Z31" s="1" t="n">
+      <c r="AU31" s="1" t="n">
         <v>328.5662</v>
       </c>
-      <c r="AA31" s="1" t="n">
+      <c r="AV31" s="1" t="n">
         <v>523.3627</v>
       </c>
-      <c r="AB31" s="1" t="n">
+      <c r="AW31" s="1" t="n">
         <v>763.6382</v>
       </c>
-      <c r="AC31" s="1" t="n">
+      <c r="AX31" s="1" t="n">
         <v>1093.6738</v>
       </c>
-      <c r="AD31" s="1" t="n">
+      <c r="AY31" s="1" t="n">
         <v>1311.6524</v>
       </c>
-      <c r="AE31" s="1" t="n">
+      <c r="AZ31" s="1" t="n">
         <v>1537.0265</v>
       </c>
-      <c r="AF31" s="1" t="n">
+      <c r="BA31" s="1" t="n">
         <v>166.2645</v>
       </c>
-      <c r="AG31" s="1" t="n">
+      <c r="BB31" s="1" t="n">
         <v>340.1913</v>
       </c>
-      <c r="AH31" s="1" t="n">
+      <c r="BC31" s="1" t="n">
         <v>503.454</v>
       </c>
-      <c r="AI31" s="1" t="n">
+      <c r="BD31" s="1" t="n">
         <v>802.1</v>
       </c>
-      <c r="AJ31" s="1" t="n">
+      <c r="BE31" s="1" t="n">
         <v>1039.95</v>
       </c>
-      <c r="AK31" s="1" t="n">
+      <c r="BF31" s="1" t="n">
         <v>1339.73</v>
       </c>
     </row>
@@ -16366,45 +18639,108 @@
         <v>362.882</v>
       </c>
       <c r="X32" s="1" t="n">
+        <v>7.0772</v>
+      </c>
+      <c r="Y32" s="1" t="n">
+        <v>41.1823</v>
+      </c>
+      <c r="Z32" s="1" t="n">
+        <v>89.1888</v>
+      </c>
+      <c r="AA32" s="1" t="n">
+        <v>146.9263</v>
+      </c>
+      <c r="AB32" s="1" t="n">
+        <v>221.5956</v>
+      </c>
+      <c r="AC32" s="1" t="n">
+        <v>278.7699</v>
+      </c>
+      <c r="AD32" s="1" t="n">
+        <v>341.1084</v>
+      </c>
+      <c r="AE32" s="1" t="n">
+        <v>416.2748</v>
+      </c>
+      <c r="AF32" s="1" t="n">
+        <v>477.1044</v>
+      </c>
+      <c r="AG32" s="1" t="n">
+        <v>528.5386999999999</v>
+      </c>
+      <c r="AH32" s="1" t="n">
+        <v>561.0185</v>
+      </c>
+      <c r="AI32" s="1" t="n">
         <v>17.3335</v>
       </c>
-      <c r="Y32" s="1" t="n">
+      <c r="AJ32" s="1" t="n">
+        <v>58.2021</v>
+      </c>
+      <c r="AK32" s="1" t="n">
+        <v>116.3643</v>
+      </c>
+      <c r="AL32" s="1" t="n">
+        <v>189.2415</v>
+      </c>
+      <c r="AM32" s="1" t="n">
+        <v>291.2993</v>
+      </c>
+      <c r="AN32" s="1" t="n">
+        <v>368.8196</v>
+      </c>
+      <c r="AO32" s="1" t="n">
+        <v>448.3303</v>
+      </c>
+      <c r="AP32" s="1" t="n">
+        <v>549.3108</v>
+      </c>
+      <c r="AQ32" s="1" t="n">
+        <v>627.5828</v>
+      </c>
+      <c r="AR32" s="1" t="n">
+        <v>693.4517</v>
+      </c>
+      <c r="AS32" s="1" t="n">
+        <v>724.649</v>
+      </c>
+      <c r="AT32" s="1" t="n">
         <v>15.5452</v>
       </c>
-      <c r="Z32" s="1" t="n">
+      <c r="AU32" s="1" t="n">
         <v>52.8724</v>
       </c>
-      <c r="AA32" s="1" t="n">
+      <c r="AV32" s="1" t="n">
         <v>103.9602</v>
       </c>
-      <c r="AB32" s="1" t="n">
+      <c r="AW32" s="1" t="n">
         <v>187.6314</v>
       </c>
-      <c r="AC32" s="1" t="n">
+      <c r="AX32" s="1" t="n">
         <v>296.1537</v>
       </c>
-      <c r="AD32" s="1" t="n">
+      <c r="AY32" s="1" t="n">
         <v>378.3305</v>
       </c>
-      <c r="AE32" s="1" t="n">
+      <c r="AZ32" s="1" t="n">
         <v>462.8996</v>
       </c>
-      <c r="AF32" s="1" t="n">
+      <c r="BA32" s="1" t="n">
         <v>19.7274</v>
       </c>
-      <c r="AG32" s="1" t="n">
+      <c r="BB32" s="1" t="n">
         <v>68.2141</v>
       </c>
-      <c r="AH32" s="1" t="n">
+      <c r="BC32" s="1" t="n">
         <v>130.2626</v>
       </c>
-      <c r="AI32" s="1" t="n">
+      <c r="BD32" s="1" t="n">
         <v>187.64</v>
       </c>
-      <c r="AJ32" s="1" t="n">
+      <c r="BE32" s="1" t="n">
         <v>264.42</v>
       </c>
-      <c r="AK32" s="1" t="n">
+      <c r="BF32" s="1" t="n">
         <v>409.39</v>
       </c>
     </row>
@@ -16477,46 +18813,106 @@
       <c r="W33" s="1" t="n">
         <v>144.7702</v>
       </c>
-      <c r="X33" s="1" t="n">
+      <c r="Y33" s="1" t="n">
+        <v>7.0996</v>
+      </c>
+      <c r="Z33" s="1" t="n">
+        <v>22.3704</v>
+      </c>
+      <c r="AA33" s="1" t="n">
+        <v>41.1701</v>
+      </c>
+      <c r="AB33" s="1" t="n">
+        <v>65.7051</v>
+      </c>
+      <c r="AC33" s="1" t="n">
+        <v>90.3511</v>
+      </c>
+      <c r="AD33" s="1" t="n">
+        <v>112.9779</v>
+      </c>
+      <c r="AE33" s="1" t="n">
+        <v>136.4158</v>
+      </c>
+      <c r="AF33" s="1" t="n">
+        <v>171.003</v>
+      </c>
+      <c r="AG33" s="1" t="n">
+        <v>185.9902</v>
+      </c>
+      <c r="AH33" s="1" t="n">
+        <v>189.6795</v>
+      </c>
+      <c r="AI33" s="1" t="n">
         <v>0.9696</v>
       </c>
-      <c r="Y33" s="1" t="n">
+      <c r="AJ33" s="1" t="n">
+        <v>13.9168</v>
+      </c>
+      <c r="AK33" s="1" t="n">
+        <v>36.9627</v>
+      </c>
+      <c r="AL33" s="1" t="n">
+        <v>60.9918</v>
+      </c>
+      <c r="AM33" s="1" t="n">
+        <v>85.6662</v>
+      </c>
+      <c r="AN33" s="1" t="n">
+        <v>129.3621</v>
+      </c>
+      <c r="AO33" s="1" t="n">
+        <v>156.6181</v>
+      </c>
+      <c r="AP33" s="1" t="n">
+        <v>196.7843</v>
+      </c>
+      <c r="AQ33" s="1" t="n">
+        <v>226.9215</v>
+      </c>
+      <c r="AR33" s="1" t="n">
+        <v>244.796</v>
+      </c>
+      <c r="AS33" s="1" t="n">
+        <v>247.6138</v>
+      </c>
+      <c r="AT33" s="1" t="n">
         <v>2.3023</v>
       </c>
-      <c r="Z33" s="1" t="n">
+      <c r="AU33" s="1" t="n">
         <v>12.673</v>
       </c>
-      <c r="AA33" s="1" t="n">
+      <c r="AV33" s="1" t="n">
         <v>45.2642</v>
       </c>
-      <c r="AB33" s="1" t="n">
+      <c r="AW33" s="1" t="n">
         <v>82.6315</v>
       </c>
-      <c r="AC33" s="1" t="n">
+      <c r="AX33" s="1" t="n">
         <v>130.564</v>
       </c>
-      <c r="AD33" s="1" t="n">
+      <c r="AY33" s="1" t="n">
         <v>174.5603</v>
       </c>
-      <c r="AE33" s="1" t="n">
+      <c r="AZ33" s="1" t="n">
         <v>211.9767</v>
       </c>
-      <c r="AF33" s="1" t="n">
+      <c r="BA33" s="1" t="n">
         <v>2.6115</v>
       </c>
-      <c r="AG33" s="1" t="n">
+      <c r="BB33" s="1" t="n">
         <v>14.429</v>
       </c>
-      <c r="AH33" s="1" t="n">
+      <c r="BC33" s="1" t="n">
         <v>50.5359</v>
       </c>
-      <c r="AI33" s="1" t="n">
+      <c r="BD33" s="1" t="n">
         <v>14.72</v>
       </c>
-      <c r="AJ33" s="1" t="n">
+      <c r="BE33" s="1" t="n">
         <v>24.98</v>
       </c>
-      <c r="AK33" s="1" t="n">
+      <c r="BF33" s="1" t="n">
         <v>36.16</v>
       </c>
     </row>
@@ -16593,45 +18989,108 @@
         <v>330.5522</v>
       </c>
       <c r="X34" s="1" t="n">
+        <v>0.9797</v>
+      </c>
+      <c r="Y34" s="1" t="n">
+        <v>20.7655</v>
+      </c>
+      <c r="Z34" s="1" t="n">
+        <v>53.3366</v>
+      </c>
+      <c r="AA34" s="1" t="n">
+        <v>93.85850000000001</v>
+      </c>
+      <c r="AB34" s="1" t="n">
+        <v>142.1723</v>
+      </c>
+      <c r="AC34" s="1" t="n">
+        <v>188.2168</v>
+      </c>
+      <c r="AD34" s="1" t="n">
+        <v>235.7331</v>
+      </c>
+      <c r="AE34" s="1" t="n">
+        <v>292.5451</v>
+      </c>
+      <c r="AF34" s="1" t="n">
+        <v>343.9445</v>
+      </c>
+      <c r="AG34" s="1" t="n">
+        <v>398.8263</v>
+      </c>
+      <c r="AH34" s="1" t="n">
+        <v>429.1529</v>
+      </c>
+      <c r="AI34" s="1" t="n">
         <v>1.5864</v>
       </c>
-      <c r="Y34" s="1" t="n">
+      <c r="AJ34" s="1" t="n">
+        <v>25.917</v>
+      </c>
+      <c r="AK34" s="1" t="n">
+        <v>64.7698</v>
+      </c>
+      <c r="AL34" s="1" t="n">
+        <v>116.1358</v>
+      </c>
+      <c r="AM34" s="1" t="n">
+        <v>189.8222</v>
+      </c>
+      <c r="AN34" s="1" t="n">
+        <v>257.6807</v>
+      </c>
+      <c r="AO34" s="1" t="n">
+        <v>324.2614</v>
+      </c>
+      <c r="AP34" s="1" t="n">
+        <v>399.6571</v>
+      </c>
+      <c r="AQ34" s="1" t="n">
+        <v>465.0777</v>
+      </c>
+      <c r="AR34" s="1" t="n">
+        <v>530.8017</v>
+      </c>
+      <c r="AS34" s="1" t="n">
+        <v>558.9682</v>
+      </c>
+      <c r="AT34" s="1" t="n">
         <v>3.6092</v>
       </c>
-      <c r="Z34" s="1" t="n">
+      <c r="AU34" s="1" t="n">
         <v>38.9866</v>
       </c>
-      <c r="AA34" s="1" t="n">
+      <c r="AV34" s="1" t="n">
         <v>87.4507</v>
       </c>
-      <c r="AB34" s="1" t="n">
+      <c r="AW34" s="1" t="n">
         <v>141.806</v>
       </c>
-      <c r="AC34" s="1" t="n">
+      <c r="AX34" s="1" t="n">
         <v>211.326</v>
       </c>
-      <c r="AD34" s="1" t="n">
+      <c r="AY34" s="1" t="n">
         <v>288.7241</v>
       </c>
-      <c r="AE34" s="1" t="n">
+      <c r="AZ34" s="1" t="n">
         <v>360.3279</v>
       </c>
-      <c r="AF34" s="1" t="n">
+      <c r="BA34" s="1" t="n">
         <v>3.8284</v>
       </c>
-      <c r="AG34" s="1" t="n">
+      <c r="BB34" s="1" t="n">
         <v>49.2384</v>
       </c>
-      <c r="AH34" s="1" t="n">
+      <c r="BC34" s="1" t="n">
         <v>99.3961</v>
       </c>
-      <c r="AI34" s="1" t="n">
+      <c r="BD34" s="1" t="n">
         <v>47.73</v>
       </c>
-      <c r="AJ34" s="1" t="n">
+      <c r="BE34" s="1" t="n">
         <v>66.16</v>
       </c>
-      <c r="AK34" s="1" t="n">
+      <c r="BF34" s="1" t="n">
         <v>102.39</v>
       </c>
     </row>
@@ -16708,45 +19167,108 @@
         <v>518.2560999999999</v>
       </c>
       <c r="X35" s="1" t="n">
+        <v>4.1617</v>
+      </c>
+      <c r="Y35" s="1" t="n">
+        <v>17.2929</v>
+      </c>
+      <c r="Z35" s="1" t="n">
+        <v>54.3499</v>
+      </c>
+      <c r="AA35" s="1" t="n">
+        <v>112.7343</v>
+      </c>
+      <c r="AB35" s="1" t="n">
+        <v>179.7075</v>
+      </c>
+      <c r="AC35" s="1" t="n">
+        <v>244.7451</v>
+      </c>
+      <c r="AD35" s="1" t="n">
+        <v>330.4798</v>
+      </c>
+      <c r="AE35" s="1" t="n">
+        <v>411.2928</v>
+      </c>
+      <c r="AF35" s="1" t="n">
+        <v>481.0921</v>
+      </c>
+      <c r="AG35" s="1" t="n">
+        <v>570.1467</v>
+      </c>
+      <c r="AH35" s="1" t="n">
+        <v>606.0939</v>
+      </c>
+      <c r="AI35" s="1" t="n">
         <v>6.1814</v>
       </c>
-      <c r="Y35" s="1" t="n">
+      <c r="AJ35" s="1" t="n">
+        <v>21.3179</v>
+      </c>
+      <c r="AK35" s="1" t="n">
+        <v>72.8775</v>
+      </c>
+      <c r="AL35" s="1" t="n">
+        <v>145.646</v>
+      </c>
+      <c r="AM35" s="1" t="n">
+        <v>242.3398</v>
+      </c>
+      <c r="AN35" s="1" t="n">
+        <v>352.8452</v>
+      </c>
+      <c r="AO35" s="1" t="n">
+        <v>477.5381</v>
+      </c>
+      <c r="AP35" s="1" t="n">
+        <v>597.8158</v>
+      </c>
+      <c r="AQ35" s="1" t="n">
+        <v>681.5624</v>
+      </c>
+      <c r="AR35" s="1" t="n">
+        <v>789.1938</v>
+      </c>
+      <c r="AS35" s="1" t="n">
+        <v>825.6855</v>
+      </c>
+      <c r="AT35" s="1" t="n">
         <v>8.0791</v>
       </c>
-      <c r="Z35" s="1" t="n">
+      <c r="AU35" s="1" t="n">
         <v>27.5988</v>
       </c>
-      <c r="AA35" s="1" t="n">
+      <c r="AV35" s="1" t="n">
         <v>93.0274</v>
       </c>
-      <c r="AB35" s="1" t="n">
+      <c r="AW35" s="1" t="n">
         <v>198.4628</v>
       </c>
-      <c r="AC35" s="1" t="n">
+      <c r="AX35" s="1" t="n">
         <v>335.6222</v>
       </c>
-      <c r="AD35" s="1" t="n">
+      <c r="AY35" s="1" t="n">
         <v>474.422</v>
       </c>
-      <c r="AE35" s="1" t="n">
+      <c r="AZ35" s="1" t="n">
         <v>601.1377</v>
       </c>
-      <c r="AF35" s="1" t="n">
+      <c r="BA35" s="1" t="n">
         <v>11.6439</v>
       </c>
-      <c r="AG35" s="1" t="n">
+      <c r="BB35" s="1" t="n">
         <v>35.3118</v>
       </c>
-      <c r="AH35" s="1" t="n">
+      <c r="BC35" s="1" t="n">
         <v>103.4544</v>
       </c>
-      <c r="AI35" s="1" t="n">
+      <c r="BD35" s="1" t="n">
         <v>126.94</v>
       </c>
-      <c r="AJ35" s="1" t="n">
+      <c r="BE35" s="1" t="n">
         <v>225.96</v>
       </c>
-      <c r="AK35" s="1" t="n">
+      <c r="BF35" s="1" t="n">
         <v>356.47</v>
       </c>
     </row>
@@ -30930,7 +33452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30960,6 +33482,56 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>2010-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2010-04</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2010-05</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2010-06</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2010-07</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2010-08</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2010-09</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2010-10</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2010-11</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2010-12</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -31117,7 +33689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA4"/>
+  <dimension ref="A1:BL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -31303,95 +33875,150 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>2013-02</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
           <t>2015-02</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>2015-03</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>2015-04</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2015-05</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>2015-09</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>2015-10</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2015-11</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>2015-12</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2018-07</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>2018-08</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2018-09</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>2018-10</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>2018-11</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>2018-12</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -31415,7 +34042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD4"/>
+  <dimension ref="A1:BO4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -31601,110 +34228,165 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>2013-02</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
           <t>2015-02</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>2015-03</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>2015-04</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2015-05</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>2015-09</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>2015-10</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2015-11</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>2015-12</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2016-02</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>2016-03</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2016-04</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>2016-05</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>2016-06</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>2016-07</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>2017-02</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>2017-03</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -31728,7 +34410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ4"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -31914,175 +34596,230 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>2013-02</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
           <t>2015-02</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>2015-03</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>2015-04</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2015-05</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>2015-09</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>2015-10</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2015-11</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>2015-12</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2016-03</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>2016-04</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2016-05</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>2016-06</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>2016-07</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>2016-08</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>2016-09</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>2016-10</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>2016-11</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>2016-12</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2017-02</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>2017-03</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2017-04</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>2017-05</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2017-06</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>2017-07</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>2017-08</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>2017-09</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>2017-10</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>2017-11</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>2017-12</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -32194,108 +34931,141 @@
         <v>71803.78690000001</v>
       </c>
       <c r="AI4" s="1" t="n">
+        <v>6669.7035</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>13132.5735</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>19180.1411</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>26797.9733</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>36827.9353</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>44301.575</v>
+      </c>
+      <c r="AO4" s="1" t="n">
+        <v>52119.7659</v>
+      </c>
+      <c r="AP4" s="1" t="n">
+        <v>61119.5474</v>
+      </c>
+      <c r="AQ4" s="1" t="n">
+        <v>68693.182</v>
+      </c>
+      <c r="AR4" s="1" t="n">
+        <v>77412.16409999998</v>
+      </c>
+      <c r="AS4" s="1" t="n">
+        <v>86013.38259999998</v>
+      </c>
+      <c r="AT4" s="1" t="n">
         <v>8786.357900000001</v>
       </c>
-      <c r="AJ4" s="1" t="n">
+      <c r="AU4" s="1" t="n">
         <v>16650.6352</v>
       </c>
-      <c r="AK4" s="1" t="n">
+      <c r="AV4" s="1" t="n">
         <v>23669.0414</v>
       </c>
-      <c r="AL4" s="1" t="n">
+      <c r="AW4" s="1" t="n">
         <v>32291.8358</v>
       </c>
-      <c r="AM4" s="1" t="n">
+      <c r="AX4" s="1" t="n">
         <v>43954.9507</v>
       </c>
-      <c r="AN4" s="1" t="n">
+      <c r="AY4" s="1" t="n">
         <v>52562.2224</v>
       </c>
-      <c r="AO4" s="1" t="n">
+      <c r="AZ4" s="1" t="n">
         <v>61062.5425</v>
       </c>
-      <c r="AP4" s="1" t="n">
+      <c r="BA4" s="1" t="n">
         <v>70535.0705</v>
       </c>
-      <c r="AQ4" s="1" t="n">
+      <c r="BB4" s="1" t="n">
         <v>78800.7363</v>
       </c>
-      <c r="AR4" s="1" t="n">
+      <c r="BC4" s="1" t="n">
         <v>87702.38039999998</v>
       </c>
-      <c r="AS4" s="1" t="n">
+      <c r="BD4" s="1" t="n">
         <v>95978.8458</v>
       </c>
-      <c r="AT4" s="1" t="n">
+      <c r="BE4" s="1" t="n">
         <v>17676.6202</v>
       </c>
-      <c r="AU4" s="1" t="n">
+      <c r="BF4" s="1" t="n">
         <v>25375.6354</v>
       </c>
-      <c r="AV4" s="1" t="n">
+      <c r="BG4" s="1" t="n">
         <v>34564.1056</v>
       </c>
-      <c r="AW4" s="1" t="n">
+      <c r="BH4" s="1" t="n">
         <v>46630.5204</v>
       </c>
-      <c r="AX4" s="1" t="n">
+      <c r="BI4" s="1" t="n">
         <v>55360.5005</v>
       </c>
-      <c r="AY4" s="1" t="n">
+      <c r="BJ4" s="1" t="n">
         <v>64386.7376</v>
       </c>
-      <c r="AZ4" s="1" t="n">
+      <c r="BK4" s="1" t="n">
         <v>74597.58960000001</v>
       </c>
-      <c r="BA4" s="1" t="n">
+      <c r="BL4" s="1" t="n">
         <v>83974.61289999998</v>
       </c>
-      <c r="BB4" s="1" t="n">
+      <c r="BM4" s="1" t="n">
         <v>93387.0808</v>
       </c>
-      <c r="BC4" s="1" t="n">
+      <c r="BN4" s="1" t="n">
         <v>102581</v>
       </c>
-      <c r="BD4" s="1" t="n">
+      <c r="BO4" s="1" t="n">
         <v>9854.3388</v>
       </c>
-      <c r="BE4" s="1" t="n">
+      <c r="BP4" s="1" t="n">
         <v>19291.9181</v>
       </c>
-      <c r="BF4" s="1" t="n">
+      <c r="BQ4" s="1" t="n">
         <v>27731.5764</v>
       </c>
-      <c r="BG4" s="1" t="n">
+      <c r="BR4" s="1" t="n">
         <v>37594.6757</v>
       </c>
-      <c r="BH4" s="1" t="n">
+      <c r="BS4" s="1" t="n">
         <v>50610.2227</v>
       </c>
-      <c r="BI4" s="1" t="n">
+      <c r="BT4" s="1" t="n">
         <v>59761.0771</v>
       </c>
-      <c r="BJ4" s="1" t="n">
+      <c r="BU4" s="1" t="n">
         <v>69493.8821</v>
       </c>
-      <c r="BK4" s="1" t="n">
+      <c r="BV4" s="1" t="n">
         <v>80644.44629999998</v>
       </c>
-      <c r="BL4" s="1" t="n">
+      <c r="BW4" s="1" t="n">
         <v>90544.3579</v>
       </c>
-      <c r="BM4" s="1" t="n">
+      <c r="BX4" s="1" t="n">
         <v>100386.5483</v>
       </c>
-      <c r="BN4" s="1" t="n">
+      <c r="BY4" s="1" t="n">
         <v>109798.5288</v>
       </c>
-      <c r="BO4" s="1" t="n">
+      <c r="BZ4" s="1" t="n">
         <v>23969.4</v>
       </c>
-      <c r="BP4" s="1" t="n">
+      <c r="CA4" s="1" t="n">
         <v>30355.68</v>
       </c>
-      <c r="BQ4" s="1" t="n">
+      <c r="CB4" s="1" t="n">
         <v>38073.7</v>
       </c>
     </row>
@@ -32827,7 +35597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:CE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -32908,290 +35678,350 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>2011-01</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2011-02</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2011-03</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2011-04</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2011-05</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2011-06</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2011-07</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2011-08</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2011-09</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2011-11</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>2012-01</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>2012-02</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2012-03</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>2012-04</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2012-05</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2021-09</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>2022-03</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>2022-04</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>2022-05</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>2022-06</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>2022-07</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>2022-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>2022-09</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>2022-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>2022-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>2022-12</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>2023-01</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>2023-02</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>2023-03</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>2023-04</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>2023-05</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>2023-06</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>2023-07</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2023-08</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>2023-09</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>2023-10</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>2023-11</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>2023-12</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>2024-01</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2024-02</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>2024-03</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2024-04</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>2024-05</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2024-06</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>2024-07</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>2024-08</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>2024-09</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>2024-11</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2025-02</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>2025-03</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025-06</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>2025-07</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -33240,177 +36070,213 @@
         <v>102.82</v>
       </c>
       <c r="N4" s="1" t="n">
+        <v>104.4325</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>104.8464</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>105.084</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>105.1886</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>105.0506</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>105.044</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>105.0852</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>105.1045</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>104.7419</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>103.9059</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>102.6649</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>101.8527</v>
+      </c>
+      <c r="Z4" s="1" t="n">
         <v>101.035</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="AA4" s="1" t="n">
         <v>100.4421</v>
       </c>
-      <c r="P4" s="1" t="n">
+      <c r="AB4" s="1" t="n">
         <v>99.57940000000001</v>
       </c>
-      <c r="Q4" s="1" t="n">
+      <c r="AC4" s="1" t="n">
         <v>99.0932</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="AD4" s="1" t="n">
         <v>98.9306</v>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="AE4" s="1" t="n">
         <v>104.9</v>
       </c>
-      <c r="T4" s="1" t="n">
+      <c r="AF4" s="1" t="n">
         <v>103.8</v>
       </c>
-      <c r="U4" s="1" t="n">
+      <c r="AG4" s="1" t="n">
         <v>103.4</v>
       </c>
-      <c r="V4" s="1" t="n">
+      <c r="AH4" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="W4" s="1" t="n">
+      <c r="AI4" s="1" t="n">
         <v>102.6</v>
       </c>
-      <c r="X4" s="1" t="n">
+      <c r="AJ4" s="1" t="n">
         <v>101.8</v>
       </c>
-      <c r="Y4" s="1" t="n">
+      <c r="AK4" s="1" t="n">
         <v>101.1</v>
       </c>
-      <c r="Z4" s="1" t="n">
+      <c r="AL4" s="1" t="n">
         <v>100.9</v>
       </c>
-      <c r="AA4" s="1" t="n">
+      <c r="AM4" s="1" t="n">
         <v>100.5</v>
       </c>
-      <c r="AB4" s="1" t="n">
+      <c r="AN4" s="1" t="n">
         <v>100.6</v>
       </c>
-      <c r="AC4" s="1" t="n">
+      <c r="AO4" s="1" t="n">
         <v>100.7</v>
       </c>
-      <c r="AD4" s="1" t="n">
+      <c r="AP4" s="1" t="n">
         <v>100.3</v>
       </c>
-      <c r="AE4" s="1" t="n">
+      <c r="AQ4" s="1" t="n">
         <v>99.7</v>
       </c>
-      <c r="AF4" s="1" t="n">
+      <c r="AR4" s="1" t="n">
         <v>99.7</v>
       </c>
-      <c r="AG4" s="1" t="n">
+      <c r="AS4" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="AH4" s="1" t="n">
+      <c r="AT4" s="1" t="n">
         <v>98.2</v>
       </c>
-      <c r="AI4" s="1" t="n">
+      <c r="AU4" s="1" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="AJ4" s="1" t="n">
+      <c r="AV4" s="1" t="n">
         <v>98.2</v>
       </c>
-      <c r="AK4" s="1" t="n">
+      <c r="AW4" s="1" t="n">
         <v>98.2</v>
       </c>
-      <c r="AL4" s="1" t="n">
+      <c r="AX4" s="1" t="n">
         <v>98.2</v>
       </c>
-      <c r="AM4" s="1" t="n">
+      <c r="AY4" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="AN4" s="1" t="n">
+      <c r="AZ4" s="1" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="AO4" s="1" t="n">
+      <c r="BA4" s="1" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="AP4" s="1" t="n">
+      <c r="BB4" s="1" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="AQ4" s="1" t="n">
+      <c r="BC4" s="1" t="n">
         <v>98.3</v>
       </c>
-      <c r="AR4" s="1" t="n">
+      <c r="BD4" s="1" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="AS4" s="1" t="n">
+      <c r="BE4" s="1" t="n">
         <v>98.2</v>
       </c>
-      <c r="AT4" s="1" t="n">
+      <c r="BF4" s="1" t="n">
         <v>98.5</v>
       </c>
-      <c r="AU4" s="1" t="n">
+      <c r="BG4" s="1" t="n">
         <v>98.7</v>
       </c>
-      <c r="AV4" s="1" t="n">
+      <c r="BH4" s="1" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="AW4" s="1" t="n">
+      <c r="BI4" s="1" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="AX4" s="1" t="n">
+      <c r="BJ4" s="1" t="n">
         <v>98.3</v>
       </c>
-      <c r="AY4" s="1" t="n">
+      <c r="BK4" s="1" t="n">
         <v>98.3</v>
       </c>
-      <c r="AZ4" s="1" t="n">
+      <c r="BL4" s="1" t="n">
         <v>98.5</v>
       </c>
-      <c r="BA4" s="1" t="n">
+      <c r="BM4" s="1" t="n">
         <v>98.7</v>
       </c>
-      <c r="BB4" s="1" t="n">
+      <c r="BN4" s="1" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="BC4" s="1" t="n">
+      <c r="BO4" s="1" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="BD4" s="1" t="n">
+      <c r="BP4" s="1" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="BE4" s="1" t="n">
+      <c r="BQ4" s="1" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="BF4" s="1" t="n">
+      <c r="BR4" s="1" t="n">
         <v>98.2</v>
       </c>
-      <c r="BG4" s="1" t="n">
+      <c r="BS4" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="BH4" s="1" t="n">
+      <c r="BT4" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="BI4" s="1" t="n">
+      <c r="BU4" s="1" t="n">
         <v>98.2</v>
       </c>
-      <c r="BJ4" s="1" t="n">
+      <c r="BV4" s="1" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="BK4" s="1" t="n">
+      <c r="BW4" s="1" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="BL4" s="1" t="n">
+      <c r="BX4" s="1" t="n">
         <v>98.8</v>
       </c>
-      <c r="BM4" s="1" t="n">
+      <c r="BY4" s="1" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="BN4" s="1" t="n">
+      <c r="BZ4" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="BO4" s="1" t="n">
+      <c r="CA4" s="1" t="n">
         <v>99.7</v>
       </c>
-      <c r="BP4" s="1" t="n">
+      <c r="CB4" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="BQ4" s="1" t="n">
+      <c r="CC4" s="1" t="n">
         <v>100.3</v>
       </c>
-      <c r="BR4" s="1" t="n">
+      <c r="CD4" s="1" t="n">
         <v>101.1</v>
       </c>
-      <c r="BS4" s="1" t="n">
+      <c r="CE4" s="1" t="n">
         <v>101.5</v>
       </c>
     </row>
@@ -33679,7 +36545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ4"/>
+  <dimension ref="A1:BY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -33825,215 +36691,255 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
+          <t>2012-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2012-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2012-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2012-08</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2012-09</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2012-10</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2012-11</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2012-12</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>2013-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>2013-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>2013-04</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>2013-05</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>2013-06</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>2013-07</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>2013-08</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>2013-09</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>2013-10</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>2013-11</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>2013-12</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>2015-02</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>2015-03</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>2015-04</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2015-05</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>2015-09</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>2015-10</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2015-11</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>2015-12</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2016-06</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>2016-07</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2016-08</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>2016-09</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>2016-10</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>2016-11</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>2016-12</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>2017-02</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>2017-03</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>2017-04</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2017-05</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>2017-06</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2017-07</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>2017-08</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2017-09</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>2017-10</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>2017-11</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>2017-12</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -34121,132 +37027,156 @@
         <v>15835.1867</v>
       </c>
       <c r="AA4" s="1" t="n">
+        <v>22212.9252</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>30609.8286</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>36774.4761</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>43687.8797</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>51045.9254</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>57628.7504</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>64772.4006</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>71803.78690000001</v>
+      </c>
+      <c r="AI4" s="1" t="n">
         <v>6669.7035</v>
       </c>
-      <c r="AB4" s="1" t="n">
+      <c r="AJ4" s="1" t="n">
         <v>13132.5735</v>
       </c>
-      <c r="AC4" s="1" t="n">
+      <c r="AK4" s="1" t="n">
         <v>19180.1411</v>
       </c>
-      <c r="AD4" s="1" t="n">
+      <c r="AL4" s="1" t="n">
         <v>26797.9733</v>
       </c>
-      <c r="AE4" s="1" t="n">
+      <c r="AM4" s="1" t="n">
         <v>36827.9353</v>
       </c>
-      <c r="AF4" s="1" t="n">
+      <c r="AN4" s="1" t="n">
         <v>44301.575</v>
       </c>
-      <c r="AG4" s="1" t="n">
+      <c r="AO4" s="1" t="n">
         <v>52119.7659</v>
       </c>
-      <c r="AH4" s="1" t="n">
+      <c r="AP4" s="1" t="n">
         <v>61119.5474</v>
       </c>
-      <c r="AI4" s="1" t="n">
+      <c r="AQ4" s="1" t="n">
         <v>68693.182</v>
       </c>
-      <c r="AJ4" s="1" t="n">
+      <c r="AR4" s="1" t="n">
         <v>77412.16409999998</v>
       </c>
-      <c r="AK4" s="1" t="n">
+      <c r="AS4" s="1" t="n">
         <v>86013.38259999998</v>
       </c>
-      <c r="AL4" s="1" t="n">
+      <c r="AT4" s="1" t="n">
         <v>8786.357900000001</v>
       </c>
-      <c r="AM4" s="1" t="n">
+      <c r="AU4" s="1" t="n">
         <v>16650.6352</v>
       </c>
-      <c r="AN4" s="1" t="n">
+      <c r="AV4" s="1" t="n">
         <v>23669.0414</v>
       </c>
-      <c r="AO4" s="1" t="n">
+      <c r="AW4" s="1" t="n">
         <v>32291.8358</v>
       </c>
-      <c r="AP4" s="1" t="n">
+      <c r="AX4" s="1" t="n">
         <v>43954.9507</v>
       </c>
-      <c r="AQ4" s="1" t="n">
+      <c r="AY4" s="1" t="n">
         <v>52562.2224</v>
       </c>
-      <c r="AR4" s="1" t="n">
+      <c r="AZ4" s="1" t="n">
         <v>61062.5425</v>
       </c>
-      <c r="AS4" s="1" t="n">
+      <c r="BA4" s="1" t="n">
         <v>70535.0705</v>
       </c>
-      <c r="AT4" s="1" t="n">
+      <c r="BB4" s="1" t="n">
         <v>78800.7363</v>
       </c>
-      <c r="AU4" s="1" t="n">
+      <c r="BC4" s="1" t="n">
         <v>87702.38039999998</v>
       </c>
-      <c r="AV4" s="1" t="n">
+      <c r="BD4" s="1" t="n">
         <v>95978.8458</v>
       </c>
-      <c r="AW4" s="1" t="n">
+      <c r="BE4" s="1" t="n">
         <v>46630.5204</v>
       </c>
-      <c r="AX4" s="1" t="n">
+      <c r="BF4" s="1" t="n">
         <v>55360.5005</v>
       </c>
-      <c r="AY4" s="1" t="n">
+      <c r="BG4" s="1" t="n">
         <v>64386.7376</v>
       </c>
-      <c r="AZ4" s="1" t="n">
+      <c r="BH4" s="1" t="n">
         <v>74597.58960000001</v>
       </c>
-      <c r="BA4" s="1" t="n">
+      <c r="BI4" s="1" t="n">
         <v>83974.61289999998</v>
       </c>
-      <c r="BB4" s="1" t="n">
+      <c r="BJ4" s="1" t="n">
         <v>93387.0808</v>
       </c>
-      <c r="BC4" s="1" t="n">
+      <c r="BK4" s="1" t="n">
         <v>102581</v>
       </c>
-      <c r="BD4" s="1" t="n">
+      <c r="BL4" s="1" t="n">
         <v>9854.3388</v>
       </c>
-      <c r="BE4" s="1" t="n">
+      <c r="BM4" s="1" t="n">
         <v>19291.9181</v>
       </c>
-      <c r="BF4" s="1" t="n">
+      <c r="BN4" s="1" t="n">
         <v>27731.5764</v>
       </c>
-      <c r="BG4" s="1" t="n">
+      <c r="BO4" s="1" t="n">
         <v>37594.6757</v>
       </c>
-      <c r="BH4" s="1" t="n">
+      <c r="BP4" s="1" t="n">
         <v>50610.2227</v>
       </c>
-      <c r="BI4" s="1" t="n">
+      <c r="BQ4" s="1" t="n">
         <v>59761.0771</v>
       </c>
-      <c r="BJ4" s="1" t="n">
+      <c r="BR4" s="1" t="n">
         <v>69493.8821</v>
       </c>
-      <c r="BK4" s="1" t="n">
+      <c r="BS4" s="1" t="n">
         <v>80644.44629999998</v>
       </c>
-      <c r="BL4" s="1" t="n">
+      <c r="BT4" s="1" t="n">
         <v>90544.3579</v>
       </c>
-      <c r="BM4" s="1" t="n">
+      <c r="BU4" s="1" t="n">
         <v>100386.5483</v>
       </c>
-      <c r="BN4" s="1" t="n">
+      <c r="BV4" s="1" t="n">
         <v>109798.5288</v>
       </c>
-      <c r="BO4" s="1" t="n">
+      <c r="BW4" s="1" t="n">
         <v>23969.4</v>
       </c>
-      <c r="BP4" s="1" t="n">
+      <c r="BX4" s="1" t="n">
         <v>30355.68</v>
       </c>
-      <c r="BQ4" s="1" t="n">
+      <c r="BY4" s="1" t="n">
         <v>38073.7</v>
       </c>
     </row>
@@ -34261,7 +37191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD4"/>
+  <dimension ref="A1:CO4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -34447,240 +37377,295 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>2013-02</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
           <t>2015-02</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>2015-03</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>2015-04</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2015-05</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>2015-09</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>2015-10</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2015-11</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>2015-12</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2016-02</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>2016-03</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2016-04</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>2016-05</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>2016-06</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>2016-07</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>2016-08</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>2016-09</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>2016-10</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>2016-11</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2016-12</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>2017-02</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2017-03</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>2017-04</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2017-05</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>2017-06</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>2017-07</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>2017-08</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>2019-02</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>2019-03</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>2019-04</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>2019-05</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>2019-06</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>2019-07</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>2020-02</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>2020-03</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>2020-04</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>2020-05</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>2020-06</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>2021-02</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>2021-03</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>2021-04</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>2021-05</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>2021-06</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -34704,7 +37689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:BV4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -34845,135 +37830,245 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>2012-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2012-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2012-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2012-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2012-06</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2012-07</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2012-08</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2012-09</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2012-10</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2012-11</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2012-12</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2013-02</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
           <t>2015-02</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2015-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>2015-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>2015-05</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2016-10</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>2016-11</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2016-12</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>2017-06</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2017-07</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>2017-08</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>2017-09</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>2017-10</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>2017-11</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>2017-12</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>2021-02</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>2021-03</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2021-04</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>2021-05</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2021-06</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>2021-07</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2021-08</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -35058,84 +38153,150 @@
         <v>17739.7</v>
       </c>
       <c r="Z4" s="1" t="n">
+        <v>33668.6</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>15650.2</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>15603.1</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>16714.8</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>16584.9</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>16314.9</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>16658.9</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>18226.6</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>18933.8</v>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>18476.7</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>20334.2</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>37809.8378</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>17641.2</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>17600.2968</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>18886.3</v>
+      </c>
+      <c r="AO4" s="1" t="n">
+        <v>18826.682611566</v>
+      </c>
+      <c r="AP4" s="1" t="n">
+        <v>18513.1615437625</v>
+      </c>
+      <c r="AQ4" s="1" t="n">
+        <v>18886.2154651754</v>
+      </c>
+      <c r="AR4" s="1" t="n">
+        <v>20653.3</v>
+      </c>
+      <c r="AS4" s="1" t="n">
+        <v>21491.281429538</v>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>21011.9344366549</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>23059.7</v>
+      </c>
+      <c r="AV4" s="1" t="n">
         <v>47992.5090274846</v>
       </c>
-      <c r="AA4" s="1" t="n">
+      <c r="AW4" s="1" t="n">
         <v>22722.8149340663</v>
       </c>
-      <c r="AB4" s="1" t="n">
+      <c r="AX4" s="1" t="n">
         <v>22386.7143520077</v>
       </c>
-      <c r="AC4" s="1" t="n">
+      <c r="AY4" s="1" t="n">
         <v>24194.8230632128</v>
       </c>
-      <c r="AD4" s="1" t="n">
+      <c r="AZ4" s="1" t="n">
         <v>24280.2708775</v>
       </c>
-      <c r="AE4" s="1" t="n">
+      <c r="BA4" s="1" t="n">
         <v>24338.77761836049</v>
       </c>
-      <c r="AF4" s="1" t="n">
+      <c r="BB4" s="1" t="n">
         <v>24893.3647423717</v>
       </c>
-      <c r="AG4" s="1" t="n">
+      <c r="BC4" s="1" t="n">
         <v>31119.2</v>
       </c>
-      <c r="AH4" s="1" t="n">
+      <c r="BD4" s="1" t="n">
         <v>30958.5</v>
       </c>
-      <c r="AI4" s="1" t="n">
+      <c r="BE4" s="1" t="n">
         <v>31757</v>
       </c>
-      <c r="AJ4" s="1" t="n">
+      <c r="BF4" s="1" t="n">
         <v>29807.6</v>
       </c>
-      <c r="AK4" s="1" t="n">
+      <c r="BG4" s="1" t="n">
         <v>29609.8</v>
       </c>
-      <c r="AL4" s="1" t="n">
+      <c r="BH4" s="1" t="n">
         <v>30329.7</v>
       </c>
-      <c r="AM4" s="1" t="n">
+      <c r="BI4" s="1" t="n">
         <v>30870.3</v>
       </c>
-      <c r="AN4" s="1" t="n">
+      <c r="BJ4" s="1" t="n">
         <v>34240.9</v>
       </c>
-      <c r="AO4" s="1" t="n">
+      <c r="BK4" s="1" t="n">
         <v>34108.2</v>
       </c>
-      <c r="AP4" s="1" t="n">
+      <c r="BL4" s="1" t="n">
         <v>34734.1</v>
       </c>
-      <c r="AQ4" s="1" t="n">
+      <c r="BM4" s="1" t="n">
         <v>69736.8</v>
       </c>
-      <c r="AR4" s="1" t="n">
+      <c r="BN4" s="1" t="n">
         <v>35484.1</v>
       </c>
-      <c r="AS4" s="1" t="n">
+      <c r="BO4" s="1" t="n">
         <v>33152.6</v>
       </c>
-      <c r="AT4" s="1" t="n">
+      <c r="BP4" s="1" t="n">
         <v>35945.1</v>
       </c>
-      <c r="AU4" s="1" t="n">
+      <c r="BQ4" s="1" t="n">
         <v>37585.8</v>
       </c>
-      <c r="AV4" s="1" t="n">
+      <c r="BR4" s="1" t="n">
         <v>34925.1</v>
       </c>
-      <c r="AW4" s="1" t="n">
+      <c r="BS4" s="1" t="n">
         <v>34394.9</v>
       </c>
-      <c r="AX4" s="1" t="n">
+      <c r="BT4" s="1" t="n">
         <v>37246.5</v>
       </c>
-      <c r="AY4" s="1" t="n">
+      <c r="BU4" s="1" t="n">
         <v>41090</v>
       </c>
-      <c r="AZ4" s="1" t="n">
+      <c r="BV4" s="1" t="n">
         <v>42690.7</v>
       </c>
     </row>

--- a/output/china_dg_all.xlsx
+++ b/output/china_dg_all.xlsx
@@ -7549,7 +7549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH35"/>
+  <dimension ref="A1:CC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7845,20 +7845,125 @@
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
           <t>2018-12</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -8099,7 +8204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF35"/>
+  <dimension ref="A1:CP35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8455,80 +8560,130 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>2019-10</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>2019-11</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>2019-12</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
         <is>
           <t>2020-08</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>2020-09</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>2020-10</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>2020-11</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>2020-12</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>2021-08</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>2021-09</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>2021-10</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>2021-11</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>2021-12</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -13286,7 +13441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF35"/>
+  <dimension ref="A1:BT35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13577,15 +13732,85 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -13760,12 +13985,54 @@
         <v>25375.6354</v>
       </c>
       <c r="BD4" s="1" t="n">
+        <v>10831.0878</v>
+      </c>
+      <c r="BE4" s="1" t="n">
+        <v>21291.2911</v>
+      </c>
+      <c r="BF4" s="1" t="n">
+        <v>30591.9486</v>
+      </c>
+      <c r="BG4" s="1" t="n">
+        <v>41420.2686</v>
+      </c>
+      <c r="BH4" s="1" t="n">
+        <v>55530.962</v>
+      </c>
+      <c r="BI4" s="1" t="n">
+        <v>65885.7066</v>
+      </c>
+      <c r="BJ4" s="1" t="n">
+        <v>76518.8414</v>
+      </c>
+      <c r="BK4" s="1" t="n">
+        <v>61609.3028</v>
+      </c>
+      <c r="BL4" s="1" t="n">
+        <v>72843.118</v>
+      </c>
+      <c r="BM4" s="1" t="n">
+        <v>84589.05740000001</v>
+      </c>
+      <c r="BN4" s="1" t="n">
+        <v>98007.6669</v>
+      </c>
+      <c r="BO4" s="1" t="n">
+        <v>109603.4475</v>
+      </c>
+      <c r="BP4" s="1" t="n">
+        <v>121265.0472</v>
+      </c>
+      <c r="BQ4" s="1" t="n">
+        <v>132194.2649</v>
+      </c>
+      <c r="BR4" s="1" t="n">
         <v>23969.4</v>
       </c>
-      <c r="BE4" s="1" t="n">
+      <c r="BS4" s="1" t="n">
         <v>30355.68</v>
       </c>
-      <c r="BF4" s="1" t="n">
+      <c r="BT4" s="1" t="n">
         <v>38073.7</v>
       </c>
     </row>
@@ -13938,12 +14205,54 @@
         <v>933.997</v>
       </c>
       <c r="BD5" s="1" t="n">
+        <v>281.4554</v>
+      </c>
+      <c r="BE5" s="1" t="n">
+        <v>531.3999</v>
+      </c>
+      <c r="BF5" s="1" t="n">
+        <v>708.942</v>
+      </c>
+      <c r="BG5" s="1" t="n">
+        <v>1052.1258</v>
+      </c>
+      <c r="BH5" s="1" t="n">
+        <v>1429.8792</v>
+      </c>
+      <c r="BI5" s="1" t="n">
+        <v>1766.6439</v>
+      </c>
+      <c r="BJ5" s="1" t="n">
+        <v>2114.9898</v>
+      </c>
+      <c r="BK5" s="1" t="n">
+        <v>1664.3267</v>
+      </c>
+      <c r="BL5" s="1" t="n">
+        <v>2031.9508</v>
+      </c>
+      <c r="BM5" s="1" t="n">
+        <v>2346.4573</v>
+      </c>
+      <c r="BN5" s="1" t="n">
+        <v>2740.8934</v>
+      </c>
+      <c r="BO5" s="1" t="n">
+        <v>3116.3822</v>
+      </c>
+      <c r="BP5" s="1" t="n">
+        <v>3489.9707</v>
+      </c>
+      <c r="BQ5" s="1" t="n">
+        <v>3838.3805</v>
+      </c>
+      <c r="BR5" s="1" t="n">
         <v>1114.66</v>
       </c>
-      <c r="BE5" s="1" t="n">
+      <c r="BS5" s="1" t="n">
         <v>1445.5</v>
       </c>
-      <c r="BF5" s="1" t="n">
+      <c r="BT5" s="1" t="n">
         <v>1862.11</v>
       </c>
     </row>
@@ -14116,12 +14425,54 @@
         <v>616.2076</v>
       </c>
       <c r="BD6" s="1" t="n">
+        <v>173.0955</v>
+      </c>
+      <c r="BE6" s="1" t="n">
+        <v>460.7246</v>
+      </c>
+      <c r="BF6" s="1" t="n">
+        <v>694.8412</v>
+      </c>
+      <c r="BG6" s="1" t="n">
+        <v>980.7501999999999</v>
+      </c>
+      <c r="BH6" s="1" t="n">
+        <v>1301.3731</v>
+      </c>
+      <c r="BI6" s="1" t="n">
+        <v>1489.2187</v>
+      </c>
+      <c r="BJ6" s="1" t="n">
+        <v>1651.6343</v>
+      </c>
+      <c r="BK6" s="1" t="n">
+        <v>1549.3604</v>
+      </c>
+      <c r="BL6" s="1" t="n">
+        <v>1772.7494</v>
+      </c>
+      <c r="BM6" s="1" t="n">
+        <v>1970.4558</v>
+      </c>
+      <c r="BN6" s="1" t="n">
+        <v>2261.8284</v>
+      </c>
+      <c r="BO6" s="1" t="n">
+        <v>2423.8093</v>
+      </c>
+      <c r="BP6" s="1" t="n">
+        <v>2569.6942</v>
+      </c>
+      <c r="BQ6" s="1" t="n">
+        <v>2727.8199</v>
+      </c>
+      <c r="BR6" s="1" t="n">
         <v>407.8</v>
       </c>
-      <c r="BE6" s="1" t="n">
+      <c r="BS6" s="1" t="n">
         <v>488.25</v>
       </c>
-      <c r="BF6" s="1" t="n">
+      <c r="BT6" s="1" t="n">
         <v>611.24</v>
       </c>
     </row>
@@ -14294,12 +14645,54 @@
         <v>1072.0482</v>
       </c>
       <c r="BD7" s="1" t="n">
+        <v>208.5376</v>
+      </c>
+      <c r="BE7" s="1" t="n">
+        <v>600.1655</v>
+      </c>
+      <c r="BF7" s="1" t="n">
+        <v>961.764</v>
+      </c>
+      <c r="BG7" s="1" t="n">
+        <v>1405.3679</v>
+      </c>
+      <c r="BH7" s="1" t="n">
+        <v>1963.9893</v>
+      </c>
+      <c r="BI7" s="1" t="n">
+        <v>2423.1278</v>
+      </c>
+      <c r="BJ7" s="1" t="n">
+        <v>2905.7576</v>
+      </c>
+      <c r="BK7" s="1" t="n">
+        <v>2104.8643</v>
+      </c>
+      <c r="BL7" s="1" t="n">
+        <v>2545.56</v>
+      </c>
+      <c r="BM7" s="1" t="n">
+        <v>2962.4778</v>
+      </c>
+      <c r="BN7" s="1" t="n">
+        <v>3400.1212</v>
+      </c>
+      <c r="BO7" s="1" t="n">
+        <v>3762.0251</v>
+      </c>
+      <c r="BP7" s="1" t="n">
+        <v>4112.5478</v>
+      </c>
+      <c r="BQ7" s="1" t="n">
+        <v>4347.054</v>
+      </c>
+      <c r="BR7" s="1" t="n">
         <v>711</v>
       </c>
-      <c r="BE7" s="1" t="n">
+      <c r="BS7" s="1" t="n">
         <v>956.53</v>
       </c>
-      <c r="BF7" s="1" t="n">
+      <c r="BT7" s="1" t="n">
         <v>1315.38</v>
       </c>
     </row>
@@ -14472,12 +14865,54 @@
         <v>228.2443</v>
       </c>
       <c r="BD8" s="1" t="n">
+        <v>47.4944</v>
+      </c>
+      <c r="BE8" s="1" t="n">
+        <v>161.73</v>
+      </c>
+      <c r="BF8" s="1" t="n">
+        <v>274.385</v>
+      </c>
+      <c r="BG8" s="1" t="n">
+        <v>420.3798</v>
+      </c>
+      <c r="BH8" s="1" t="n">
+        <v>642.1949</v>
+      </c>
+      <c r="BI8" s="1" t="n">
+        <v>771.1499</v>
+      </c>
+      <c r="BJ8" s="1" t="n">
+        <v>921.2184</v>
+      </c>
+      <c r="BK8" s="1" t="n">
+        <v>753.2674</v>
+      </c>
+      <c r="BL8" s="1" t="n">
+        <v>916.5306</v>
+      </c>
+      <c r="BM8" s="1" t="n">
+        <v>1073.2813</v>
+      </c>
+      <c r="BN8" s="1" t="n">
+        <v>1240.1738</v>
+      </c>
+      <c r="BO8" s="1" t="n">
+        <v>1391.1474</v>
+      </c>
+      <c r="BP8" s="1" t="n">
+        <v>1521.9604</v>
+      </c>
+      <c r="BQ8" s="1" t="n">
+        <v>1656.5005</v>
+      </c>
+      <c r="BR8" s="1" t="n">
         <v>355.36</v>
       </c>
-      <c r="BE8" s="1" t="n">
+      <c r="BS8" s="1" t="n">
         <v>457.19</v>
       </c>
-      <c r="BF8" s="1" t="n">
+      <c r="BT8" s="1" t="n">
         <v>599.35</v>
       </c>
     </row>
@@ -14650,12 +15085,54 @@
         <v>97.2139</v>
       </c>
       <c r="BD9" s="1" t="n">
+        <v>8.1898</v>
+      </c>
+      <c r="BE9" s="1" t="n">
+        <v>39.6087</v>
+      </c>
+      <c r="BF9" s="1" t="n">
+        <v>93.3494</v>
+      </c>
+      <c r="BG9" s="1" t="n">
+        <v>185.2671</v>
+      </c>
+      <c r="BH9" s="1" t="n">
+        <v>341.2202</v>
+      </c>
+      <c r="BI9" s="1" t="n">
+        <v>483.9874</v>
+      </c>
+      <c r="BJ9" s="1" t="n">
+        <v>605.6374</v>
+      </c>
+      <c r="BK9" s="1" t="n">
+        <v>360.9991</v>
+      </c>
+      <c r="BL9" s="1" t="n">
+        <v>520.28</v>
+      </c>
+      <c r="BM9" s="1" t="n">
+        <v>677.942</v>
+      </c>
+      <c r="BN9" s="1" t="n">
+        <v>851.4805</v>
+      </c>
+      <c r="BO9" s="1" t="n">
+        <v>957.6004</v>
+      </c>
+      <c r="BP9" s="1" t="n">
+        <v>1026.0799</v>
+      </c>
+      <c r="BQ9" s="1" t="n">
+        <v>1041.9497</v>
+      </c>
+      <c r="BR9" s="1" t="n">
         <v>141.65</v>
       </c>
-      <c r="BE9" s="1" t="n">
+      <c r="BS9" s="1" t="n">
         <v>227.12</v>
       </c>
-      <c r="BF9" s="1" t="n">
+      <c r="BT9" s="1" t="n">
         <v>367.07</v>
       </c>
     </row>
@@ -14828,12 +15305,54 @@
         <v>722.157</v>
       </c>
       <c r="BD10" s="1" t="n">
+        <v>119.8364</v>
+      </c>
+      <c r="BE10" s="1" t="n">
+        <v>388.4677</v>
+      </c>
+      <c r="BF10" s="1" t="n">
+        <v>651.7551999999999</v>
+      </c>
+      <c r="BG10" s="1" t="n">
+        <v>971.5592</v>
+      </c>
+      <c r="BH10" s="1" t="n">
+        <v>1364.5294</v>
+      </c>
+      <c r="BI10" s="1" t="n">
+        <v>1616.732</v>
+      </c>
+      <c r="BJ10" s="1" t="n">
+        <v>1883.4608</v>
+      </c>
+      <c r="BK10" s="1" t="n">
+        <v>1487.1906</v>
+      </c>
+      <c r="BL10" s="1" t="n">
+        <v>1769.6838</v>
+      </c>
+      <c r="BM10" s="1" t="n">
+        <v>2040.2389</v>
+      </c>
+      <c r="BN10" s="1" t="n">
+        <v>2372.8153</v>
+      </c>
+      <c r="BO10" s="1" t="n">
+        <v>2602.8313</v>
+      </c>
+      <c r="BP10" s="1" t="n">
+        <v>2763.9211</v>
+      </c>
+      <c r="BQ10" s="1" t="n">
+        <v>2833.9503</v>
+      </c>
+      <c r="BR10" s="1" t="n">
         <v>185.51</v>
       </c>
-      <c r="BE10" s="1" t="n">
+      <c r="BS10" s="1" t="n">
         <v>254.08</v>
       </c>
-      <c r="BF10" s="1" t="n">
+      <c r="BT10" s="1" t="n">
         <v>360.76</v>
       </c>
     </row>
@@ -15003,12 +15522,54 @@
         <v>85.5635</v>
       </c>
       <c r="BD11" s="1" t="n">
+        <v>10.4389</v>
+      </c>
+      <c r="BE11" s="1" t="n">
+        <v>35.7783</v>
+      </c>
+      <c r="BF11" s="1" t="n">
+        <v>98.3338</v>
+      </c>
+      <c r="BG11" s="1" t="n">
+        <v>253.7204</v>
+      </c>
+      <c r="BH11" s="1" t="n">
+        <v>375.9577</v>
+      </c>
+      <c r="BI11" s="1" t="n">
+        <v>532.8577</v>
+      </c>
+      <c r="BJ11" s="1" t="n">
+        <v>696.8611</v>
+      </c>
+      <c r="BK11" s="1" t="n">
+        <v>477.4939</v>
+      </c>
+      <c r="BL11" s="1" t="n">
+        <v>633.5031</v>
+      </c>
+      <c r="BM11" s="1" t="n">
+        <v>830.4023999999999</v>
+      </c>
+      <c r="BN11" s="1" t="n">
+        <v>1014.4162</v>
+      </c>
+      <c r="BO11" s="1" t="n">
+        <v>1164.1421</v>
+      </c>
+      <c r="BP11" s="1" t="n">
+        <v>1263.3654</v>
+      </c>
+      <c r="BQ11" s="1" t="n">
+        <v>1315.522</v>
+      </c>
+      <c r="BR11" s="1" t="n">
         <v>64.18000000000001</v>
       </c>
-      <c r="BE11" s="1" t="n">
+      <c r="BS11" s="1" t="n">
         <v>116.27</v>
       </c>
-      <c r="BF11" s="1" t="n">
+      <c r="BT11" s="1" t="n">
         <v>170.04</v>
       </c>
     </row>
@@ -15181,12 +15742,54 @@
         <v>57.3575</v>
       </c>
       <c r="BD12" s="1" t="n">
+        <v>2.0376</v>
+      </c>
+      <c r="BE12" s="1" t="n">
+        <v>24.6858</v>
+      </c>
+      <c r="BF12" s="1" t="n">
+        <v>76.7346</v>
+      </c>
+      <c r="BG12" s="1" t="n">
+        <v>171.9393</v>
+      </c>
+      <c r="BH12" s="1" t="n">
+        <v>303.768</v>
+      </c>
+      <c r="BI12" s="1" t="n">
+        <v>414.2757</v>
+      </c>
+      <c r="BJ12" s="1" t="n">
+        <v>533.8824</v>
+      </c>
+      <c r="BK12" s="1" t="n">
+        <v>339.1663</v>
+      </c>
+      <c r="BL12" s="1" t="n">
+        <v>441.7863</v>
+      </c>
+      <c r="BM12" s="1" t="n">
+        <v>546.9347</v>
+      </c>
+      <c r="BN12" s="1" t="n">
+        <v>705.7483999999999</v>
+      </c>
+      <c r="BO12" s="1" t="n">
+        <v>811.6767</v>
+      </c>
+      <c r="BP12" s="1" t="n">
+        <v>911.3123000000001</v>
+      </c>
+      <c r="BQ12" s="1" t="n">
+        <v>958.0066</v>
+      </c>
+      <c r="BR12" s="1" t="n">
         <v>46.7</v>
       </c>
-      <c r="BE12" s="1" t="n">
+      <c r="BS12" s="1" t="n">
         <v>68.75</v>
       </c>
-      <c r="BF12" s="1" t="n">
+      <c r="BT12" s="1" t="n">
         <v>109.72</v>
       </c>
     </row>
@@ -15359,12 +15962,54 @@
         <v>1060.2072</v>
       </c>
       <c r="BD13" s="1" t="n">
+        <v>605.4403</v>
+      </c>
+      <c r="BE13" s="1" t="n">
+        <v>909.3862</v>
+      </c>
+      <c r="BF13" s="1" t="n">
+        <v>1182.3855</v>
+      </c>
+      <c r="BG13" s="1" t="n">
+        <v>1478.1702</v>
+      </c>
+      <c r="BH13" s="1" t="n">
+        <v>1816.9121</v>
+      </c>
+      <c r="BI13" s="1" t="n">
+        <v>2153.9724</v>
+      </c>
+      <c r="BJ13" s="1" t="n">
+        <v>2491.1393</v>
+      </c>
+      <c r="BK13" s="1" t="n">
+        <v>1883.144</v>
+      </c>
+      <c r="BL13" s="1" t="n">
+        <v>2230.3038</v>
+      </c>
+      <c r="BM13" s="1" t="n">
+        <v>2584.2312</v>
+      </c>
+      <c r="BN13" s="1" t="n">
+        <v>2966.4188</v>
+      </c>
+      <c r="BO13" s="1" t="n">
+        <v>3348.7605</v>
+      </c>
+      <c r="BP13" s="1" t="n">
+        <v>3749.9584</v>
+      </c>
+      <c r="BQ13" s="1" t="n">
+        <v>4231.3761</v>
+      </c>
+      <c r="BR13" s="1" t="n">
         <v>1838.56</v>
       </c>
-      <c r="BE13" s="1" t="n">
+      <c r="BS13" s="1" t="n">
         <v>2271.16</v>
       </c>
-      <c r="BF13" s="1" t="n">
+      <c r="BT13" s="1" t="n">
         <v>2747.1</v>
       </c>
     </row>
@@ -15537,12 +16182,54 @@
         <v>2687.5838</v>
       </c>
       <c r="BD14" s="1" t="n">
+        <v>1467.79</v>
+      </c>
+      <c r="BE14" s="1" t="n">
+        <v>2603.6502</v>
+      </c>
+      <c r="BF14" s="1" t="n">
+        <v>3526.8864</v>
+      </c>
+      <c r="BG14" s="1" t="n">
+        <v>4632.7369</v>
+      </c>
+      <c r="BH14" s="1" t="n">
+        <v>5653.3405</v>
+      </c>
+      <c r="BI14" s="1" t="n">
+        <v>6699.1832</v>
+      </c>
+      <c r="BJ14" s="1" t="n">
+        <v>7580.5473</v>
+      </c>
+      <c r="BK14" s="1" t="n">
+        <v>6090.8601</v>
+      </c>
+      <c r="BL14" s="1" t="n">
+        <v>7150.0596</v>
+      </c>
+      <c r="BM14" s="1" t="n">
+        <v>8139.4743</v>
+      </c>
+      <c r="BN14" s="1" t="n">
+        <v>9239.159799999999</v>
+      </c>
+      <c r="BO14" s="1" t="n">
+        <v>10226.9891</v>
+      </c>
+      <c r="BP14" s="1" t="n">
+        <v>11202.5769</v>
+      </c>
+      <c r="BQ14" s="1" t="n">
+        <v>12009.3475</v>
+      </c>
+      <c r="BR14" s="1" t="n">
         <v>2640.19</v>
       </c>
-      <c r="BE14" s="1" t="n">
+      <c r="BS14" s="1" t="n">
         <v>3233.88</v>
       </c>
-      <c r="BF14" s="1" t="n">
+      <c r="BT14" s="1" t="n">
         <v>3801.93</v>
       </c>
     </row>
@@ -15715,12 +16402,54 @@
         <v>2017.2453</v>
       </c>
       <c r="BD15" s="1" t="n">
+        <v>1010.5442</v>
+      </c>
+      <c r="BE15" s="1" t="n">
+        <v>1899.5384</v>
+      </c>
+      <c r="BF15" s="1" t="n">
+        <v>2664.7329</v>
+      </c>
+      <c r="BG15" s="1" t="n">
+        <v>3569.3685</v>
+      </c>
+      <c r="BH15" s="1" t="n">
+        <v>4795.0283</v>
+      </c>
+      <c r="BI15" s="1" t="n">
+        <v>5610.3893</v>
+      </c>
+      <c r="BJ15" s="1" t="n">
+        <v>6462.6226</v>
+      </c>
+      <c r="BK15" s="1" t="n">
+        <v>5166.8744</v>
+      </c>
+      <c r="BL15" s="1" t="n">
+        <v>6043.0388</v>
+      </c>
+      <c r="BM15" s="1" t="n">
+        <v>6960.0159</v>
+      </c>
+      <c r="BN15" s="1" t="n">
+        <v>8055.4849</v>
+      </c>
+      <c r="BO15" s="1" t="n">
+        <v>8984.134700000001</v>
+      </c>
+      <c r="BP15" s="1" t="n">
+        <v>9958.0998</v>
+      </c>
+      <c r="BQ15" s="1" t="n">
+        <v>10682.9713</v>
+      </c>
+      <c r="BR15" s="1" t="n">
         <v>2498.33</v>
       </c>
-      <c r="BE15" s="1" t="n">
+      <c r="BS15" s="1" t="n">
         <v>3147.88</v>
       </c>
-      <c r="BF15" s="1" t="n">
+      <c r="BT15" s="1" t="n">
         <v>3944.7</v>
       </c>
     </row>
@@ -15893,12 +16622,54 @@
         <v>1287.5627</v>
       </c>
       <c r="BD16" s="1" t="n">
+        <v>650.8596</v>
+      </c>
+      <c r="BE16" s="1" t="n">
+        <v>1222.8281</v>
+      </c>
+      <c r="BF16" s="1" t="n">
+        <v>1782.4165</v>
+      </c>
+      <c r="BG16" s="1" t="n">
+        <v>2405.5964</v>
+      </c>
+      <c r="BH16" s="1" t="n">
+        <v>3067.7573</v>
+      </c>
+      <c r="BI16" s="1" t="n">
+        <v>3623.8346</v>
+      </c>
+      <c r="BJ16" s="1" t="n">
+        <v>4208.3249</v>
+      </c>
+      <c r="BK16" s="1" t="n">
+        <v>3387.0738</v>
+      </c>
+      <c r="BL16" s="1" t="n">
+        <v>4022.9433</v>
+      </c>
+      <c r="BM16" s="1" t="n">
+        <v>4671.7852</v>
+      </c>
+      <c r="BN16" s="1" t="n">
+        <v>5278.9535</v>
+      </c>
+      <c r="BO16" s="1" t="n">
+        <v>5722.9806</v>
+      </c>
+      <c r="BP16" s="1" t="n">
+        <v>6160.1311</v>
+      </c>
+      <c r="BQ16" s="1" t="n">
+        <v>6670.4785</v>
+      </c>
+      <c r="BR16" s="1" t="n">
         <v>902.92</v>
       </c>
-      <c r="BE16" s="1" t="n">
+      <c r="BS16" s="1" t="n">
         <v>1095.12</v>
       </c>
-      <c r="BF16" s="1" t="n">
+      <c r="BT16" s="1" t="n">
         <v>1270.06</v>
       </c>
     </row>
@@ -16071,12 +16842,54 @@
         <v>1418.8192</v>
       </c>
       <c r="BD17" s="1" t="n">
+        <v>550.7912</v>
+      </c>
+      <c r="BE17" s="1" t="n">
+        <v>1109.319</v>
+      </c>
+      <c r="BF17" s="1" t="n">
+        <v>1502.5949</v>
+      </c>
+      <c r="BG17" s="1" t="n">
+        <v>1898.4759</v>
+      </c>
+      <c r="BH17" s="1" t="n">
+        <v>2404.9236</v>
+      </c>
+      <c r="BI17" s="1" t="n">
+        <v>2804.8439</v>
+      </c>
+      <c r="BJ17" s="1" t="n">
+        <v>3186.2848</v>
+      </c>
+      <c r="BK17" s="1" t="n">
+        <v>2826.8979</v>
+      </c>
+      <c r="BL17" s="1" t="n">
+        <v>3290.8329</v>
+      </c>
+      <c r="BM17" s="1" t="n">
+        <v>3730.7401</v>
+      </c>
+      <c r="BN17" s="1" t="n">
+        <v>4303.2291</v>
+      </c>
+      <c r="BO17" s="1" t="n">
+        <v>4773.6335</v>
+      </c>
+      <c r="BP17" s="1" t="n">
+        <v>5252.9574</v>
+      </c>
+      <c r="BQ17" s="1" t="n">
+        <v>5673.1288</v>
+      </c>
+      <c r="BR17" s="1" t="n">
         <v>800.53</v>
       </c>
-      <c r="BE17" s="1" t="n">
+      <c r="BS17" s="1" t="n">
         <v>958.33</v>
       </c>
-      <c r="BF17" s="1" t="n">
+      <c r="BT17" s="1" t="n">
         <v>1131.69</v>
       </c>
     </row>
@@ -16249,12 +17062,54 @@
         <v>440.4727</v>
       </c>
       <c r="BD18" s="1" t="n">
+        <v>226.9471</v>
+      </c>
+      <c r="BE18" s="1" t="n">
+        <v>405.4974</v>
+      </c>
+      <c r="BF18" s="1" t="n">
+        <v>569.8703</v>
+      </c>
+      <c r="BG18" s="1" t="n">
+        <v>750.0631</v>
+      </c>
+      <c r="BH18" s="1" t="n">
+        <v>973.0121</v>
+      </c>
+      <c r="BI18" s="1" t="n">
+        <v>1173.1141</v>
+      </c>
+      <c r="BJ18" s="1" t="n">
+        <v>1378.7684</v>
+      </c>
+      <c r="BK18" s="1" t="n">
+        <v>1025.1144</v>
+      </c>
+      <c r="BL18" s="1" t="n">
+        <v>1247.7205</v>
+      </c>
+      <c r="BM18" s="1" t="n">
+        <v>1477.4854</v>
+      </c>
+      <c r="BN18" s="1" t="n">
+        <v>1709.7371</v>
+      </c>
+      <c r="BO18" s="1" t="n">
+        <v>1895.2201</v>
+      </c>
+      <c r="BP18" s="1" t="n">
+        <v>2083.2327</v>
+      </c>
+      <c r="BQ18" s="1" t="n">
+        <v>2239.1084</v>
+      </c>
+      <c r="BR18" s="1" t="n">
         <v>444.35</v>
       </c>
-      <c r="BE18" s="1" t="n">
+      <c r="BS18" s="1" t="n">
         <v>564.95</v>
       </c>
-      <c r="BF18" s="1" t="n">
+      <c r="BT18" s="1" t="n">
         <v>685.85</v>
       </c>
     </row>
@@ -16427,12 +17282,54 @@
         <v>1601.0519</v>
       </c>
       <c r="BD19" s="1" t="n">
+        <v>614.9979</v>
+      </c>
+      <c r="BE19" s="1" t="n">
+        <v>1287.0028</v>
+      </c>
+      <c r="BF19" s="1" t="n">
+        <v>1933.8147</v>
+      </c>
+      <c r="BG19" s="1" t="n">
+        <v>2641.1319</v>
+      </c>
+      <c r="BH19" s="1" t="n">
+        <v>3550.3143</v>
+      </c>
+      <c r="BI19" s="1" t="n">
+        <v>4243.9028</v>
+      </c>
+      <c r="BJ19" s="1" t="n">
+        <v>4888.0392</v>
+      </c>
+      <c r="BK19" s="1" t="n">
+        <v>4072.7077</v>
+      </c>
+      <c r="BL19" s="1" t="n">
+        <v>4854.9526</v>
+      </c>
+      <c r="BM19" s="1" t="n">
+        <v>5588.1442</v>
+      </c>
+      <c r="BN19" s="1" t="n">
+        <v>6384.8901</v>
+      </c>
+      <c r="BO19" s="1" t="n">
+        <v>7179.8717</v>
+      </c>
+      <c r="BP19" s="1" t="n">
+        <v>7948.4754</v>
+      </c>
+      <c r="BQ19" s="1" t="n">
+        <v>8614.8945</v>
+      </c>
+      <c r="BR19" s="1" t="n">
         <v>1823.27</v>
       </c>
-      <c r="BE19" s="1" t="n">
+      <c r="BS19" s="1" t="n">
         <v>2360.49</v>
       </c>
-      <c r="BF19" s="1" t="n">
+      <c r="BT19" s="1" t="n">
         <v>2996.27</v>
       </c>
     </row>
@@ -16605,12 +17502,54 @@
         <v>1261.955</v>
       </c>
       <c r="BD20" s="1" t="n">
+        <v>511.1378</v>
+      </c>
+      <c r="BE20" s="1" t="n">
+        <v>1138.6497</v>
+      </c>
+      <c r="BF20" s="1" t="n">
+        <v>1781.9226</v>
+      </c>
+      <c r="BG20" s="1" t="n">
+        <v>2417.7471</v>
+      </c>
+      <c r="BH20" s="1" t="n">
+        <v>3131.3238</v>
+      </c>
+      <c r="BI20" s="1" t="n">
+        <v>3664.1178</v>
+      </c>
+      <c r="BJ20" s="1" t="n">
+        <v>4212.2677</v>
+      </c>
+      <c r="BK20" s="1" t="n">
+        <v>3261.1244</v>
+      </c>
+      <c r="BL20" s="1" t="n">
+        <v>3871.2961</v>
+      </c>
+      <c r="BM20" s="1" t="n">
+        <v>4499.9816</v>
+      </c>
+      <c r="BN20" s="1" t="n">
+        <v>5194.013</v>
+      </c>
+      <c r="BO20" s="1" t="n">
+        <v>5879.158</v>
+      </c>
+      <c r="BP20" s="1" t="n">
+        <v>6631.2605</v>
+      </c>
+      <c r="BQ20" s="1" t="n">
+        <v>7464.5887</v>
+      </c>
+      <c r="BR20" s="1" t="n">
         <v>1116.4</v>
       </c>
-      <c r="BE20" s="1" t="n">
+      <c r="BS20" s="1" t="n">
         <v>1390.6</v>
       </c>
-      <c r="BF20" s="1" t="n">
+      <c r="BT20" s="1" t="n">
         <v>1721.76</v>
       </c>
     </row>
@@ -16783,12 +17722,54 @@
         <v>1009.3123</v>
       </c>
       <c r="BD21" s="1" t="n">
+        <v>394.4007</v>
+      </c>
+      <c r="BE21" s="1" t="n">
+        <v>915.49</v>
+      </c>
+      <c r="BF21" s="1" t="n">
+        <v>1317.0126</v>
+      </c>
+      <c r="BG21" s="1" t="n">
+        <v>1714.5683</v>
+      </c>
+      <c r="BH21" s="1" t="n">
+        <v>2409.341</v>
+      </c>
+      <c r="BI21" s="1" t="n">
+        <v>2757.3412</v>
+      </c>
+      <c r="BJ21" s="1" t="n">
+        <v>3177.427</v>
+      </c>
+      <c r="BK21" s="1" t="n">
+        <v>2599.7396</v>
+      </c>
+      <c r="BL21" s="1" t="n">
+        <v>2969.1658</v>
+      </c>
+      <c r="BM21" s="1" t="n">
+        <v>3432.7411</v>
+      </c>
+      <c r="BN21" s="1" t="n">
+        <v>3927.5544</v>
+      </c>
+      <c r="BO21" s="1" t="n">
+        <v>4356.8791</v>
+      </c>
+      <c r="BP21" s="1" t="n">
+        <v>4699.571</v>
+      </c>
+      <c r="BQ21" s="1" t="n">
+        <v>5111.7254</v>
+      </c>
+      <c r="BR21" s="1" t="n">
         <v>1321.65</v>
       </c>
-      <c r="BE21" s="1" t="n">
+      <c r="BS21" s="1" t="n">
         <v>1740.37</v>
       </c>
-      <c r="BF21" s="1" t="n">
+      <c r="BT21" s="1" t="n">
         <v>2193.2</v>
       </c>
     </row>
@@ -16961,12 +17942,54 @@
         <v>700.0788</v>
       </c>
       <c r="BD22" s="1" t="n">
+        <v>316.4505</v>
+      </c>
+      <c r="BE22" s="1" t="n">
+        <v>598.7093</v>
+      </c>
+      <c r="BF22" s="1" t="n">
+        <v>878.2184</v>
+      </c>
+      <c r="BG22" s="1" t="n">
+        <v>1186.2545</v>
+      </c>
+      <c r="BH22" s="1" t="n">
+        <v>1614.9309</v>
+      </c>
+      <c r="BI22" s="1" t="n">
+        <v>1930.2882</v>
+      </c>
+      <c r="BJ22" s="1" t="n">
+        <v>2314.5632</v>
+      </c>
+      <c r="BK22" s="1" t="n">
+        <v>1867.6564</v>
+      </c>
+      <c r="BL22" s="1" t="n">
+        <v>2220.3776</v>
+      </c>
+      <c r="BM22" s="1" t="n">
+        <v>2653.3632</v>
+      </c>
+      <c r="BN22" s="1" t="n">
+        <v>3130.8499</v>
+      </c>
+      <c r="BO22" s="1" t="n">
+        <v>3576.9251</v>
+      </c>
+      <c r="BP22" s="1" t="n">
+        <v>4005.5343</v>
+      </c>
+      <c r="BQ22" s="1" t="n">
+        <v>4445.4659</v>
+      </c>
+      <c r="BR22" s="1" t="n">
         <v>661.92</v>
       </c>
-      <c r="BE22" s="1" t="n">
+      <c r="BS22" s="1" t="n">
         <v>798.51</v>
       </c>
-      <c r="BF22" s="1" t="n">
+      <c r="BT22" s="1" t="n">
         <v>993.5700000000001</v>
       </c>
     </row>
@@ -17139,12 +18162,54 @@
         <v>2356.3201</v>
       </c>
       <c r="BD23" s="1" t="n">
+        <v>1354.2483</v>
+      </c>
+      <c r="BE23" s="1" t="n">
+        <v>2462.3795</v>
+      </c>
+      <c r="BF23" s="1" t="n">
+        <v>3461.3386</v>
+      </c>
+      <c r="BG23" s="1" t="n">
+        <v>4657.0637</v>
+      </c>
+      <c r="BH23" s="1" t="n">
+        <v>6454.5594</v>
+      </c>
+      <c r="BI23" s="1" t="n">
+        <v>7606.0474</v>
+      </c>
+      <c r="BJ23" s="1" t="n">
+        <v>8869.0731</v>
+      </c>
+      <c r="BK23" s="1" t="n">
+        <v>7255.5958</v>
+      </c>
+      <c r="BL23" s="1" t="n">
+        <v>8462.7886</v>
+      </c>
+      <c r="BM23" s="1" t="n">
+        <v>9820.936799999999</v>
+      </c>
+      <c r="BN23" s="1" t="n">
+        <v>11464.4409</v>
+      </c>
+      <c r="BO23" s="1" t="n">
+        <v>12811.8919</v>
+      </c>
+      <c r="BP23" s="1" t="n">
+        <v>14343.817</v>
+      </c>
+      <c r="BQ23" s="1" t="n">
+        <v>15852.162</v>
+      </c>
+      <c r="BR23" s="1" t="n">
         <v>2477.43</v>
       </c>
-      <c r="BE23" s="1" t="n">
+      <c r="BS23" s="1" t="n">
         <v>3088.59</v>
       </c>
-      <c r="BF23" s="1" t="n">
+      <c r="BT23" s="1" t="n">
         <v>3967.96</v>
       </c>
     </row>
@@ -17317,12 +18382,54 @@
         <v>508.1643</v>
       </c>
       <c r="BD24" s="1" t="n">
+        <v>233.8771</v>
+      </c>
+      <c r="BE24" s="1" t="n">
+        <v>512.8942</v>
+      </c>
+      <c r="BF24" s="1" t="n">
+        <v>750.4374</v>
+      </c>
+      <c r="BG24" s="1" t="n">
+        <v>997.563</v>
+      </c>
+      <c r="BH24" s="1" t="n">
+        <v>1367.6813</v>
+      </c>
+      <c r="BI24" s="1" t="n">
+        <v>1557.513</v>
+      </c>
+      <c r="BJ24" s="1" t="n">
+        <v>1761.725</v>
+      </c>
+      <c r="BK24" s="1" t="n">
+        <v>1738.2592</v>
+      </c>
+      <c r="BL24" s="1" t="n">
+        <v>1957.0021</v>
+      </c>
+      <c r="BM24" s="1" t="n">
+        <v>2264.5778</v>
+      </c>
+      <c r="BN24" s="1" t="n">
+        <v>2574.8165</v>
+      </c>
+      <c r="BO24" s="1" t="n">
+        <v>2903.6425</v>
+      </c>
+      <c r="BP24" s="1" t="n">
+        <v>3323.4118</v>
+      </c>
+      <c r="BQ24" s="1" t="n">
+        <v>3814.4125</v>
+      </c>
+      <c r="BR24" s="1" t="n">
         <v>250.7</v>
       </c>
-      <c r="BE24" s="1" t="n">
+      <c r="BS24" s="1" t="n">
         <v>304.15</v>
       </c>
-      <c r="BF24" s="1" t="n">
+      <c r="BT24" s="1" t="n">
         <v>383.36</v>
       </c>
     </row>
@@ -17495,12 +18602,54 @@
         <v>441.733</v>
       </c>
       <c r="BD25" s="1" t="n">
+        <v>229.9142</v>
+      </c>
+      <c r="BE25" s="1" t="n">
+        <v>413.5396</v>
+      </c>
+      <c r="BF25" s="1" t="n">
+        <v>543.5941</v>
+      </c>
+      <c r="BG25" s="1" t="n">
+        <v>677.143</v>
+      </c>
+      <c r="BH25" s="1" t="n">
+        <v>823.8615</v>
+      </c>
+      <c r="BI25" s="1" t="n">
+        <v>957.8437</v>
+      </c>
+      <c r="BJ25" s="1" t="n">
+        <v>1087.281</v>
+      </c>
+      <c r="BK25" s="1" t="n">
+        <v>565.3280999999999</v>
+      </c>
+      <c r="BL25" s="1" t="n">
+        <v>659.5191</v>
+      </c>
+      <c r="BM25" s="1" t="n">
+        <v>753.8681</v>
+      </c>
+      <c r="BN25" s="1" t="n">
+        <v>863.3535000000001</v>
+      </c>
+      <c r="BO25" s="1" t="n">
+        <v>987.2691</v>
+      </c>
+      <c r="BP25" s="1" t="n">
+        <v>1141.9704</v>
+      </c>
+      <c r="BQ25" s="1" t="n">
+        <v>1336.1768</v>
+      </c>
+      <c r="BR25" s="1" t="n">
         <v>238.32</v>
       </c>
-      <c r="BE25" s="1" t="n">
+      <c r="BS25" s="1" t="n">
         <v>283.22</v>
       </c>
-      <c r="BF25" s="1" t="n">
+      <c r="BT25" s="1" t="n">
         <v>341.45</v>
       </c>
     </row>
@@ -17673,12 +18822,54 @@
         <v>1012.2007</v>
       </c>
       <c r="BD26" s="1" t="n">
+        <v>413.6426</v>
+      </c>
+      <c r="BE26" s="1" t="n">
+        <v>798.1156</v>
+      </c>
+      <c r="BF26" s="1" t="n">
+        <v>1099.6617</v>
+      </c>
+      <c r="BG26" s="1" t="n">
+        <v>1461.7206</v>
+      </c>
+      <c r="BH26" s="1" t="n">
+        <v>1967.8549</v>
+      </c>
+      <c r="BI26" s="1" t="n">
+        <v>2272.6059</v>
+      </c>
+      <c r="BJ26" s="1" t="n">
+        <v>2632.019</v>
+      </c>
+      <c r="BK26" s="1" t="n">
+        <v>2127.9302</v>
+      </c>
+      <c r="BL26" s="1" t="n">
+        <v>2454.1705</v>
+      </c>
+      <c r="BM26" s="1" t="n">
+        <v>2829.9666</v>
+      </c>
+      <c r="BN26" s="1" t="n">
+        <v>3321.82</v>
+      </c>
+      <c r="BO26" s="1" t="n">
+        <v>3669.239</v>
+      </c>
+      <c r="BP26" s="1" t="n">
+        <v>4034.9471</v>
+      </c>
+      <c r="BQ26" s="1" t="n">
+        <v>4439.3034</v>
+      </c>
+      <c r="BR26" s="1" t="n">
         <v>655.3200000000001</v>
       </c>
-      <c r="BE26" s="1" t="n">
+      <c r="BS26" s="1" t="n">
         <v>814.7</v>
       </c>
-      <c r="BF26" s="1" t="n">
+      <c r="BT26" s="1" t="n">
         <v>942.48</v>
       </c>
     </row>
@@ -17851,12 +19042,54 @@
         <v>1563.1767</v>
       </c>
       <c r="BD27" s="1" t="n">
+        <v>652.6145</v>
+      </c>
+      <c r="BE27" s="1" t="n">
+        <v>1125.6075</v>
+      </c>
+      <c r="BF27" s="1" t="n">
+        <v>1571.1122</v>
+      </c>
+      <c r="BG27" s="1" t="n">
+        <v>2065.458</v>
+      </c>
+      <c r="BH27" s="1" t="n">
+        <v>2646.5367</v>
+      </c>
+      <c r="BI27" s="1" t="n">
+        <v>3076.7723</v>
+      </c>
+      <c r="BJ27" s="1" t="n">
+        <v>3563.3777</v>
+      </c>
+      <c r="BK27" s="1" t="n">
+        <v>3101.1063</v>
+      </c>
+      <c r="BL27" s="1" t="n">
+        <v>3615.8022</v>
+      </c>
+      <c r="BM27" s="1" t="n">
+        <v>4215.6642</v>
+      </c>
+      <c r="BN27" s="1" t="n">
+        <v>4872.4485</v>
+      </c>
+      <c r="BO27" s="1" t="n">
+        <v>5474.7924</v>
+      </c>
+      <c r="BP27" s="1" t="n">
+        <v>6011.5283</v>
+      </c>
+      <c r="BQ27" s="1" t="n">
+        <v>6573.2391</v>
+      </c>
+      <c r="BR27" s="1" t="n">
         <v>1313.11</v>
       </c>
-      <c r="BE27" s="1" t="n">
+      <c r="BS27" s="1" t="n">
         <v>1713.79</v>
       </c>
-      <c r="BF27" s="1" t="n">
+      <c r="BT27" s="1" t="n">
         <v>2154.84</v>
       </c>
     </row>
@@ -18029,12 +19262,54 @@
         <v>608.1145</v>
       </c>
       <c r="BD28" s="1" t="n">
+        <v>233.5929</v>
+      </c>
+      <c r="BE28" s="1" t="n">
+        <v>479.8447</v>
+      </c>
+      <c r="BF28" s="1" t="n">
+        <v>670.0847</v>
+      </c>
+      <c r="BG28" s="1" t="n">
+        <v>879.1796000000001</v>
+      </c>
+      <c r="BH28" s="1" t="n">
+        <v>1182.5562</v>
+      </c>
+      <c r="BI28" s="1" t="n">
+        <v>1387.9834</v>
+      </c>
+      <c r="BJ28" s="1" t="n">
+        <v>1574.8904</v>
+      </c>
+      <c r="BK28" s="1" t="n">
+        <v>1404.2818</v>
+      </c>
+      <c r="BL28" s="1" t="n">
+        <v>1655.5087</v>
+      </c>
+      <c r="BM28" s="1" t="n">
+        <v>1937.8807</v>
+      </c>
+      <c r="BN28" s="1" t="n">
+        <v>2194.2062</v>
+      </c>
+      <c r="BO28" s="1" t="n">
+        <v>2471.8956</v>
+      </c>
+      <c r="BP28" s="1" t="n">
+        <v>2769.5667</v>
+      </c>
+      <c r="BQ28" s="1" t="n">
+        <v>2990.8139</v>
+      </c>
+      <c r="BR28" s="1" t="n">
         <v>385.18</v>
       </c>
-      <c r="BE28" s="1" t="n">
+      <c r="BS28" s="1" t="n">
         <v>465.16</v>
       </c>
-      <c r="BF28" s="1" t="n">
+      <c r="BT28" s="1" t="n">
         <v>552.7</v>
       </c>
     </row>
@@ -18207,12 +19482,54 @@
         <v>695.9169000000001</v>
       </c>
       <c r="BD29" s="1" t="n">
+        <v>265.3924</v>
+      </c>
+      <c r="BE29" s="1" t="n">
+        <v>571.7096</v>
+      </c>
+      <c r="BF29" s="1" t="n">
+        <v>779.855</v>
+      </c>
+      <c r="BG29" s="1" t="n">
+        <v>989.2129</v>
+      </c>
+      <c r="BH29" s="1" t="n">
+        <v>1342.2137</v>
+      </c>
+      <c r="BI29" s="1" t="n">
+        <v>1598.336</v>
+      </c>
+      <c r="BJ29" s="1" t="n">
+        <v>1832.3491</v>
+      </c>
+      <c r="BK29" s="1" t="n">
+        <v>1729.106</v>
+      </c>
+      <c r="BL29" s="1" t="n">
+        <v>2043.4472</v>
+      </c>
+      <c r="BM29" s="1" t="n">
+        <v>2407.8468</v>
+      </c>
+      <c r="BN29" s="1" t="n">
+        <v>2843.9346</v>
+      </c>
+      <c r="BO29" s="1" t="n">
+        <v>3200.2112</v>
+      </c>
+      <c r="BP29" s="1" t="n">
+        <v>3658.0604</v>
+      </c>
+      <c r="BQ29" s="1" t="n">
+        <v>4151.4085</v>
+      </c>
+      <c r="BR29" s="1" t="n">
         <v>384.64</v>
       </c>
-      <c r="BE29" s="1" t="n">
+      <c r="BS29" s="1" t="n">
         <v>473.69</v>
       </c>
-      <c r="BF29" s="1" t="n">
+      <c r="BT29" s="1" t="n">
         <v>581.25</v>
       </c>
     </row>
@@ -18379,12 +19696,54 @@
         <v>5.8283</v>
       </c>
       <c r="BD30" s="1" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="BE30" s="1" t="n">
+        <v>3.421</v>
+      </c>
+      <c r="BF30" s="1" t="n">
+        <v>5.6941</v>
+      </c>
+      <c r="BG30" s="1" t="n">
+        <v>9.9945</v>
+      </c>
+      <c r="BH30" s="1" t="n">
+        <v>27.6581</v>
+      </c>
+      <c r="BI30" s="1" t="n">
+        <v>40.6545</v>
+      </c>
+      <c r="BJ30" s="1" t="n">
+        <v>53.3767</v>
+      </c>
+      <c r="BK30" s="1" t="n">
+        <v>38.0519</v>
+      </c>
+      <c r="BL30" s="1" t="n">
+        <v>54.7453</v>
+      </c>
+      <c r="BM30" s="1" t="n">
+        <v>69.53449999999999</v>
+      </c>
+      <c r="BN30" s="1" t="n">
+        <v>85.7863</v>
+      </c>
+      <c r="BO30" s="1" t="n">
+        <v>105.2434</v>
+      </c>
+      <c r="BP30" s="1" t="n">
+        <v>124.1005</v>
+      </c>
+      <c r="BQ30" s="1" t="n">
+        <v>129.5559</v>
+      </c>
+      <c r="BR30" s="1" t="n">
         <v>10.59</v>
       </c>
-      <c r="BE30" s="1" t="n">
+      <c r="BS30" s="1" t="n">
         <v>15.95</v>
       </c>
-      <c r="BF30" s="1" t="n">
+      <c r="BT30" s="1" t="n">
         <v>23.72</v>
       </c>
     </row>
@@ -18557,12 +19916,54 @@
         <v>503.454</v>
       </c>
       <c r="BD31" s="1" t="n">
+        <v>197.7271</v>
+      </c>
+      <c r="BE31" s="1" t="n">
+        <v>416.6669</v>
+      </c>
+      <c r="BF31" s="1" t="n">
+        <v>630.9001</v>
+      </c>
+      <c r="BG31" s="1" t="n">
+        <v>930.3087</v>
+      </c>
+      <c r="BH31" s="1" t="n">
+        <v>1513.8679</v>
+      </c>
+      <c r="BI31" s="1" t="n">
+        <v>1817.1052</v>
+      </c>
+      <c r="BJ31" s="1" t="n">
+        <v>2160.236</v>
+      </c>
+      <c r="BK31" s="1" t="n">
+        <v>1681.6116</v>
+      </c>
+      <c r="BL31" s="1" t="n">
+        <v>1985.0995</v>
+      </c>
+      <c r="BM31" s="1" t="n">
+        <v>2324.7106</v>
+      </c>
+      <c r="BN31" s="1" t="n">
+        <v>2788.2273</v>
+      </c>
+      <c r="BO31" s="1" t="n">
+        <v>3167.6566</v>
+      </c>
+      <c r="BP31" s="1" t="n">
+        <v>3531.7209</v>
+      </c>
+      <c r="BQ31" s="1" t="n">
+        <v>3903.6487</v>
+      </c>
+      <c r="BR31" s="1" t="n">
         <v>802.1</v>
       </c>
-      <c r="BE31" s="1" t="n">
+      <c r="BS31" s="1" t="n">
         <v>1039.95</v>
       </c>
-      <c r="BF31" s="1" t="n">
+      <c r="BT31" s="1" t="n">
         <v>1339.73</v>
       </c>
     </row>
@@ -18735,12 +20136,54 @@
         <v>130.2626</v>
       </c>
       <c r="BD32" s="1" t="n">
+        <v>28.9271</v>
+      </c>
+      <c r="BE32" s="1" t="n">
+        <v>89.10429999999999</v>
+      </c>
+      <c r="BF32" s="1" t="n">
+        <v>167.7348</v>
+      </c>
+      <c r="BG32" s="1" t="n">
+        <v>267.6232</v>
+      </c>
+      <c r="BH32" s="1" t="n">
+        <v>461.2319</v>
+      </c>
+      <c r="BI32" s="1" t="n">
+        <v>572.8707000000001</v>
+      </c>
+      <c r="BJ32" s="1" t="n">
+        <v>696.8342</v>
+      </c>
+      <c r="BK32" s="1" t="n">
+        <v>480.0238</v>
+      </c>
+      <c r="BL32" s="1" t="n">
+        <v>604.9867</v>
+      </c>
+      <c r="BM32" s="1" t="n">
+        <v>739.7646999999999</v>
+      </c>
+      <c r="BN32" s="1" t="n">
+        <v>923.1895</v>
+      </c>
+      <c r="BO32" s="1" t="n">
+        <v>1055.7345</v>
+      </c>
+      <c r="BP32" s="1" t="n">
+        <v>1172.4698</v>
+      </c>
+      <c r="BQ32" s="1" t="n">
+        <v>1257.8484</v>
+      </c>
+      <c r="BR32" s="1" t="n">
         <v>187.64</v>
       </c>
-      <c r="BE32" s="1" t="n">
+      <c r="BS32" s="1" t="n">
         <v>264.42</v>
       </c>
-      <c r="BF32" s="1" t="n">
+      <c r="BT32" s="1" t="n">
         <v>409.39</v>
       </c>
     </row>
@@ -18907,12 +20350,54 @@
         <v>50.5359</v>
       </c>
       <c r="BD33" s="1" t="n">
+        <v>1.5579</v>
+      </c>
+      <c r="BE33" s="1" t="n">
+        <v>18.7019</v>
+      </c>
+      <c r="BF33" s="1" t="n">
+        <v>54.5746</v>
+      </c>
+      <c r="BG33" s="1" t="n">
+        <v>99.4935</v>
+      </c>
+      <c r="BH33" s="1" t="n">
+        <v>161.4395</v>
+      </c>
+      <c r="BI33" s="1" t="n">
+        <v>213.3758</v>
+      </c>
+      <c r="BJ33" s="1" t="n">
+        <v>262.1819</v>
+      </c>
+      <c r="BK33" s="1" t="n">
+        <v>159.4126</v>
+      </c>
+      <c r="BL33" s="1" t="n">
+        <v>211.8021</v>
+      </c>
+      <c r="BM33" s="1" t="n">
+        <v>250.2274</v>
+      </c>
+      <c r="BN33" s="1" t="n">
+        <v>288.9207</v>
+      </c>
+      <c r="BO33" s="1" t="n">
+        <v>340.2464</v>
+      </c>
+      <c r="BP33" s="1" t="n">
+        <v>394.8496</v>
+      </c>
+      <c r="BQ33" s="1" t="n">
+        <v>406.2924</v>
+      </c>
+      <c r="BR33" s="1" t="n">
         <v>14.72</v>
       </c>
-      <c r="BE33" s="1" t="n">
+      <c r="BS33" s="1" t="n">
         <v>24.98</v>
       </c>
-      <c r="BF33" s="1" t="n">
+      <c r="BT33" s="1" t="n">
         <v>36.16</v>
       </c>
     </row>
@@ -19085,12 +20570,54 @@
         <v>99.3961</v>
       </c>
       <c r="BD34" s="1" t="n">
+        <v>5.7573</v>
+      </c>
+      <c r="BE34" s="1" t="n">
+        <v>37.6625</v>
+      </c>
+      <c r="BF34" s="1" t="n">
+        <v>86.8536</v>
+      </c>
+      <c r="BG34" s="1" t="n">
+        <v>127.8101</v>
+      </c>
+      <c r="BH34" s="1" t="n">
+        <v>198.2141</v>
+      </c>
+      <c r="BI34" s="1" t="n">
+        <v>245.1362</v>
+      </c>
+      <c r="BJ34" s="1" t="n">
+        <v>291.2991</v>
+      </c>
+      <c r="BK34" s="1" t="n">
+        <v>157.1482</v>
+      </c>
+      <c r="BL34" s="1" t="n">
+        <v>204.7193</v>
+      </c>
+      <c r="BM34" s="1" t="n">
+        <v>248.8423</v>
+      </c>
+      <c r="BN34" s="1" t="n">
+        <v>306.6965</v>
+      </c>
+      <c r="BO34" s="1" t="n">
+        <v>345.3722</v>
+      </c>
+      <c r="BP34" s="1" t="n">
+        <v>380.1601</v>
+      </c>
+      <c r="BQ34" s="1" t="n">
+        <v>403.0911</v>
+      </c>
+      <c r="BR34" s="1" t="n">
         <v>47.73</v>
       </c>
-      <c r="BE34" s="1" t="n">
+      <c r="BS34" s="1" t="n">
         <v>66.16</v>
       </c>
-      <c r="BF34" s="1" t="n">
+      <c r="BT34" s="1" t="n">
         <v>102.39</v>
       </c>
     </row>
@@ -19263,12 +20790,54 @@
         <v>103.4544</v>
       </c>
       <c r="BD35" s="1" t="n">
+        <v>13.2776</v>
+      </c>
+      <c r="BE35" s="1" t="n">
+        <v>29.0122</v>
+      </c>
+      <c r="BF35" s="1" t="n">
+        <v>70.1477</v>
+      </c>
+      <c r="BG35" s="1" t="n">
+        <v>122.4753</v>
+      </c>
+      <c r="BH35" s="1" t="n">
+        <v>243.4911</v>
+      </c>
+      <c r="BI35" s="1" t="n">
+        <v>380.4819</v>
+      </c>
+      <c r="BJ35" s="1" t="n">
+        <v>520.772</v>
+      </c>
+      <c r="BK35" s="1" t="n">
+        <v>253.5859</v>
+      </c>
+      <c r="BL35" s="1" t="n">
+        <v>400.7917</v>
+      </c>
+      <c r="BM35" s="1" t="n">
+        <v>539.0845</v>
+      </c>
+      <c r="BN35" s="1" t="n">
+        <v>702.0586</v>
+      </c>
+      <c r="BO35" s="1" t="n">
+        <v>896.0857999999999</v>
+      </c>
+      <c r="BP35" s="1" t="n">
+        <v>1027.7953</v>
+      </c>
+      <c r="BQ35" s="1" t="n">
+        <v>1074.0436</v>
+      </c>
+      <c r="BR35" s="1" t="n">
         <v>126.94</v>
       </c>
-      <c r="BE35" s="1" t="n">
+      <c r="BS35" s="1" t="n">
         <v>225.96</v>
       </c>
-      <c r="BF35" s="1" t="n">
+      <c r="BT35" s="1" t="n">
         <v>356.47</v>
       </c>
     </row>
@@ -33689,7 +35258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL4"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -33985,40 +35554,120 @@
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
           <t>2018-07</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>2018-08</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>2018-09</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>2018-10</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>2018-11</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2018-12</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -34042,7 +35691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO4"/>
+  <dimension ref="A1:CK4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -34378,15 +36027,125 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -34410,7 +36169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -34811,15 +36570,125 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CX3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -35060,12 +36929,78 @@
         <v>109798.5288</v>
       </c>
       <c r="BZ4" s="1" t="n">
+        <v>10831.0878</v>
+      </c>
+      <c r="CA4" s="1" t="n">
+        <v>21291.2911</v>
+      </c>
+      <c r="CB4" s="1" t="n">
+        <v>30591.9486</v>
+      </c>
+      <c r="CC4" s="1" t="n">
+        <v>41420.2686</v>
+      </c>
+      <c r="CD4" s="1" t="n">
+        <v>55530.962</v>
+      </c>
+      <c r="CE4" s="1" t="n">
+        <v>65885.7066</v>
+      </c>
+      <c r="CF4" s="1" t="n">
+        <v>76518.8414</v>
+      </c>
+      <c r="CG4" s="1" t="n">
+        <v>88665.0355</v>
+      </c>
+      <c r="CH4" s="1" t="n">
+        <v>99324.9154</v>
+      </c>
+      <c r="CI4" s="1" t="n">
+        <v>110083.0033</v>
+      </c>
+      <c r="CJ4" s="1" t="n">
+        <v>120263.5146</v>
+      </c>
+      <c r="CK4" s="1" t="n">
+        <v>10115.4174</v>
+      </c>
+      <c r="CL4" s="1" t="n">
+        <v>21962.6085</v>
+      </c>
+      <c r="CM4" s="1" t="n">
+        <v>33102.8406</v>
+      </c>
+      <c r="CN4" s="1" t="n">
+        <v>45919.5905</v>
+      </c>
+      <c r="CO4" s="1" t="n">
+        <v>62780.2095</v>
+      </c>
+      <c r="CP4" s="1" t="n">
+        <v>75324.6079</v>
+      </c>
+      <c r="CQ4" s="1" t="n">
+        <v>88454.14449999999</v>
+      </c>
+      <c r="CR4" s="1" t="n">
+        <v>103484.1959</v>
+      </c>
+      <c r="CS4" s="1" t="n">
+        <v>116555.7566</v>
+      </c>
+      <c r="CT4" s="1" t="n">
+        <v>129492.364</v>
+      </c>
+      <c r="CU4" s="1" t="n">
+        <v>141442.9455</v>
+      </c>
+      <c r="CV4" s="1" t="n">
         <v>23969.4</v>
       </c>
-      <c r="CA4" s="1" t="n">
+      <c r="CW4" s="1" t="n">
         <v>30355.68</v>
       </c>
-      <c r="CB4" s="1" t="n">
+      <c r="CX4" s="1" t="n">
         <v>38073.7</v>
       </c>
     </row>
@@ -36545,7 +38480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY4"/>
+  <dimension ref="A1:CM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -36931,15 +38866,85 @@
       </c>
       <c r="BW3" t="inlineStr">
         <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -37171,12 +39176,54 @@
         <v>109798.5288</v>
       </c>
       <c r="BW4" s="1" t="n">
+        <v>10831.0878</v>
+      </c>
+      <c r="BX4" s="1" t="n">
+        <v>21291.2911</v>
+      </c>
+      <c r="BY4" s="1" t="n">
+        <v>30591.9486</v>
+      </c>
+      <c r="BZ4" s="1" t="n">
+        <v>41420.2686</v>
+      </c>
+      <c r="CA4" s="1" t="n">
+        <v>55530.962</v>
+      </c>
+      <c r="CB4" s="1" t="n">
+        <v>65885.7066</v>
+      </c>
+      <c r="CC4" s="1" t="n">
+        <v>76518.8414</v>
+      </c>
+      <c r="CD4" s="1" t="n">
+        <v>88665.0355</v>
+      </c>
+      <c r="CE4" s="1" t="n">
+        <v>99324.9154</v>
+      </c>
+      <c r="CF4" s="1" t="n">
+        <v>110083.0033</v>
+      </c>
+      <c r="CG4" s="1" t="n">
+        <v>120263.5146</v>
+      </c>
+      <c r="CH4" s="1" t="n">
+        <v>10115.4174</v>
+      </c>
+      <c r="CI4" s="1" t="n">
+        <v>21962.6085</v>
+      </c>
+      <c r="CJ4" s="1" t="n">
+        <v>33102.8406</v>
+      </c>
+      <c r="CK4" s="1" t="n">
         <v>23969.4</v>
       </c>
-      <c r="BX4" s="1" t="n">
+      <c r="CL4" s="1" t="n">
         <v>30355.68</v>
       </c>
-      <c r="BY4" s="1" t="n">
+      <c r="CM4" s="1" t="n">
         <v>38073.7</v>
       </c>
     </row>
@@ -37191,7 +39238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO4"/>
+  <dimension ref="A1:DF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -37577,95 +39624,180 @@
       </c>
       <c r="BW3" t="inlineStr">
         <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>2019-02</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>2019-03</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>2019-04</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>2019-05</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>2019-06</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>2019-07</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>2020-02</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>2020-03</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>2020-04</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>2020-05</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>2020-06</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
         <is>
           <t>2021-02</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CZ3" t="inlineStr">
         <is>
           <t>2021-03</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="DA3" t="inlineStr">
         <is>
           <t>2021-04</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="DB3" t="inlineStr">
         <is>
           <t>2021-05</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="DC3" t="inlineStr">
         <is>
           <t>2021-06</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="DD3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="DE3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="DF3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -37689,7 +39821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV4"/>
+  <dimension ref="A1:CG4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -38025,50 +40157,105 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
           <t>2021-02</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>2021-03</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>2021-04</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>2021-05</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>2021-06</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>2021-07</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>2021-08</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -38270,33 +40457,66 @@
         <v>34734.1</v>
       </c>
       <c r="BM4" s="1" t="n">
+        <v>66064</v>
+      </c>
+      <c r="BN4" s="1" t="n">
+        <v>31725.7</v>
+      </c>
+      <c r="BO4" s="1" t="n">
+        <v>30586.1</v>
+      </c>
+      <c r="BP4" s="1" t="n">
+        <v>32955.7</v>
+      </c>
+      <c r="BQ4" s="1" t="n">
+        <v>33878.1</v>
+      </c>
+      <c r="BR4" s="1" t="n">
+        <v>33073.3</v>
+      </c>
+      <c r="BS4" s="1" t="n">
+        <v>33896.3</v>
+      </c>
+      <c r="BT4" s="1" t="n">
+        <v>34494.9</v>
+      </c>
+      <c r="BU4" s="1" t="n">
+        <v>38104.3</v>
+      </c>
+      <c r="BV4" s="1" t="n">
+        <v>38093.8</v>
+      </c>
+      <c r="BW4" s="1" t="n">
+        <v>38776.7</v>
+      </c>
+      <c r="BX4" s="1" t="n">
         <v>69736.8</v>
       </c>
-      <c r="BN4" s="1" t="n">
+      <c r="BY4" s="1" t="n">
         <v>35484.1</v>
       </c>
-      <c r="BO4" s="1" t="n">
+      <c r="BZ4" s="1" t="n">
         <v>33152.6</v>
       </c>
-      <c r="BP4" s="1" t="n">
+      <c r="CA4" s="1" t="n">
         <v>35945.1</v>
       </c>
-      <c r="BQ4" s="1" t="n">
+      <c r="CB4" s="1" t="n">
         <v>37585.8</v>
       </c>
-      <c r="BR4" s="1" t="n">
+      <c r="CC4" s="1" t="n">
         <v>34925.1</v>
       </c>
-      <c r="BS4" s="1" t="n">
+      <c r="CD4" s="1" t="n">
         <v>34394.9</v>
       </c>
-      <c r="BT4" s="1" t="n">
+      <c r="CE4" s="1" t="n">
         <v>37246.5</v>
       </c>
-      <c r="BU4" s="1" t="n">
+      <c r="CF4" s="1" t="n">
         <v>41090</v>
       </c>
-      <c r="BV4" s="1" t="n">
+      <c r="CG4" s="1" t="n">
         <v>42690.7</v>
       </c>
     </row>

--- a/output/china_dg_all.xlsx
+++ b/output/china_dg_all.xlsx
@@ -7549,7 +7549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC35"/>
+  <dimension ref="A1:CN35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7955,15 +7955,70 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -8204,7 +8259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP35"/>
+  <dimension ref="A1:CV35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8650,40 +8705,70 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
           <t>2021-08</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>2021-09</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>2021-10</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>2021-11</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>2021-12</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -13441,7 +13526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT35"/>
+  <dimension ref="A1:CI35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13767,50 +13852,125 @@
       </c>
       <c r="BK3" t="inlineStr">
         <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
           <t>2019-06</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>2019-07</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2019-08</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>2019-09</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2019-10</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>2019-11</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>2019-12</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -14006,33 +14166,78 @@
         <v>76518.8414</v>
       </c>
       <c r="BK4" s="1" t="n">
+        <v>88665.0355</v>
+      </c>
+      <c r="BL4" s="1" t="n">
+        <v>99324.9154</v>
+      </c>
+      <c r="BM4" s="1" t="n">
+        <v>110083.0033</v>
+      </c>
+      <c r="BN4" s="1" t="n">
+        <v>120263.5146</v>
+      </c>
+      <c r="BO4" s="1" t="n">
         <v>61609.3028</v>
       </c>
-      <c r="BL4" s="1" t="n">
+      <c r="BP4" s="1" t="n">
         <v>72843.118</v>
       </c>
-      <c r="BM4" s="1" t="n">
+      <c r="BQ4" s="1" t="n">
         <v>84589.05740000001</v>
       </c>
-      <c r="BN4" s="1" t="n">
+      <c r="BR4" s="1" t="n">
         <v>98007.6669</v>
       </c>
-      <c r="BO4" s="1" t="n">
+      <c r="BS4" s="1" t="n">
         <v>109603.4475</v>
       </c>
-      <c r="BP4" s="1" t="n">
+      <c r="BT4" s="1" t="n">
         <v>121265.0472</v>
       </c>
-      <c r="BQ4" s="1" t="n">
+      <c r="BU4" s="1" t="n">
         <v>132194.2649</v>
       </c>
-      <c r="BR4" s="1" t="n">
+      <c r="BV4" s="1" t="n">
+        <v>10115.4174</v>
+      </c>
+      <c r="BW4" s="1" t="n">
+        <v>21962.6085</v>
+      </c>
+      <c r="BX4" s="1" t="n">
+        <v>33102.8406</v>
+      </c>
+      <c r="BY4" s="1" t="n">
+        <v>45919.5905</v>
+      </c>
+      <c r="BZ4" s="1" t="n">
+        <v>62780.2095</v>
+      </c>
+      <c r="CA4" s="1" t="n">
+        <v>75324.6079</v>
+      </c>
+      <c r="CB4" s="1" t="n">
+        <v>88454.14449999999</v>
+      </c>
+      <c r="CC4" s="1" t="n">
+        <v>103484.1959</v>
+      </c>
+      <c r="CD4" s="1" t="n">
+        <v>116555.7566</v>
+      </c>
+      <c r="CE4" s="1" t="n">
+        <v>129492.364</v>
+      </c>
+      <c r="CF4" s="1" t="n">
+        <v>141442.9455</v>
+      </c>
+      <c r="CG4" s="1" t="n">
         <v>23969.4</v>
       </c>
-      <c r="BS4" s="1" t="n">
+      <c r="CH4" s="1" t="n">
         <v>30355.68</v>
       </c>
-      <c r="BT4" s="1" t="n">
+      <c r="CI4" s="1" t="n">
         <v>38073.7</v>
       </c>
     </row>
@@ -14226,33 +14431,78 @@
         <v>2114.9898</v>
       </c>
       <c r="BK5" s="1" t="n">
+        <v>2565.4758</v>
+      </c>
+      <c r="BL5" s="1" t="n">
+        <v>3002.9351</v>
+      </c>
+      <c r="BM5" s="1" t="n">
+        <v>3409.4668</v>
+      </c>
+      <c r="BN5" s="1" t="n">
+        <v>3873.3513</v>
+      </c>
+      <c r="BO5" s="1" t="n">
         <v>1664.3267</v>
       </c>
-      <c r="BL5" s="1" t="n">
+      <c r="BP5" s="1" t="n">
         <v>2031.9508</v>
       </c>
-      <c r="BM5" s="1" t="n">
+      <c r="BQ5" s="1" t="n">
         <v>2346.4573</v>
       </c>
-      <c r="BN5" s="1" t="n">
+      <c r="BR5" s="1" t="n">
         <v>2740.8934</v>
       </c>
-      <c r="BO5" s="1" t="n">
+      <c r="BS5" s="1" t="n">
         <v>3116.3822</v>
       </c>
-      <c r="BP5" s="1" t="n">
+      <c r="BT5" s="1" t="n">
         <v>3489.9707</v>
       </c>
-      <c r="BQ5" s="1" t="n">
+      <c r="BU5" s="1" t="n">
         <v>3838.3805</v>
       </c>
-      <c r="BR5" s="1" t="n">
+      <c r="BV5" s="1" t="n">
+        <v>302.3609</v>
+      </c>
+      <c r="BW5" s="1" t="n">
+        <v>616.3508</v>
+      </c>
+      <c r="BX5" s="1" t="n">
+        <v>878.0779</v>
+      </c>
+      <c r="BY5" s="1" t="n">
+        <v>1256.4697</v>
+      </c>
+      <c r="BZ5" s="1" t="n">
+        <v>1730.2521</v>
+      </c>
+      <c r="CA5" s="1" t="n">
+        <v>2119.2472</v>
+      </c>
+      <c r="CB5" s="1" t="n">
+        <v>2479.7992</v>
+      </c>
+      <c r="CC5" s="1" t="n">
+        <v>2918.8044</v>
+      </c>
+      <c r="CD5" s="1" t="n">
+        <v>3330.2827</v>
+      </c>
+      <c r="CE5" s="1" t="n">
+        <v>3617.3284</v>
+      </c>
+      <c r="CF5" s="1" t="n">
+        <v>3938.7093</v>
+      </c>
+      <c r="CG5" s="1" t="n">
         <v>1114.66</v>
       </c>
-      <c r="BS5" s="1" t="n">
+      <c r="CH5" s="1" t="n">
         <v>1445.5</v>
       </c>
-      <c r="BT5" s="1" t="n">
+      <c r="CI5" s="1" t="n">
         <v>1862.11</v>
       </c>
     </row>
@@ -14446,33 +14696,78 @@
         <v>1651.6343</v>
       </c>
       <c r="BK6" s="1" t="n">
+        <v>1893.3975</v>
+      </c>
+      <c r="BL6" s="1" t="n">
+        <v>2087.517</v>
+      </c>
+      <c r="BM6" s="1" t="n">
+        <v>2231.1793</v>
+      </c>
+      <c r="BN6" s="1" t="n">
+        <v>2424.4892</v>
+      </c>
+      <c r="BO6" s="1" t="n">
         <v>1549.3604</v>
       </c>
-      <c r="BL6" s="1" t="n">
+      <c r="BP6" s="1" t="n">
         <v>1772.7494</v>
       </c>
-      <c r="BM6" s="1" t="n">
+      <c r="BQ6" s="1" t="n">
         <v>1970.4558</v>
       </c>
-      <c r="BN6" s="1" t="n">
+      <c r="BR6" s="1" t="n">
         <v>2261.8284</v>
       </c>
-      <c r="BO6" s="1" t="n">
+      <c r="BS6" s="1" t="n">
         <v>2423.8093</v>
       </c>
-      <c r="BP6" s="1" t="n">
+      <c r="BT6" s="1" t="n">
         <v>2569.6942</v>
       </c>
-      <c r="BQ6" s="1" t="n">
+      <c r="BU6" s="1" t="n">
         <v>2727.8199</v>
       </c>
-      <c r="BR6" s="1" t="n">
+      <c r="BV6" s="1" t="n">
+        <v>186.4798</v>
+      </c>
+      <c r="BW6" s="1" t="n">
+        <v>481.8743</v>
+      </c>
+      <c r="BX6" s="1" t="n">
+        <v>733.5337</v>
+      </c>
+      <c r="BY6" s="1" t="n">
+        <v>1088.3714</v>
+      </c>
+      <c r="BZ6" s="1" t="n">
+        <v>1452.4835</v>
+      </c>
+      <c r="CA6" s="1" t="n">
+        <v>1660.1203</v>
+      </c>
+      <c r="CB6" s="1" t="n">
+        <v>1863.8416</v>
+      </c>
+      <c r="CC6" s="1" t="n">
+        <v>2124.799</v>
+      </c>
+      <c r="CD6" s="1" t="n">
+        <v>2301.5225</v>
+      </c>
+      <c r="CE6" s="1" t="n">
+        <v>2468.1568</v>
+      </c>
+      <c r="CF6" s="1" t="n">
+        <v>2608.5378</v>
+      </c>
+      <c r="CG6" s="1" t="n">
         <v>407.8</v>
       </c>
-      <c r="BS6" s="1" t="n">
+      <c r="CH6" s="1" t="n">
         <v>488.25</v>
       </c>
-      <c r="BT6" s="1" t="n">
+      <c r="CI6" s="1" t="n">
         <v>611.24</v>
       </c>
     </row>
@@ -14666,33 +14961,78 @@
         <v>2905.7576</v>
       </c>
       <c r="BK7" s="1" t="n">
+        <v>3438.0326</v>
+      </c>
+      <c r="BL7" s="1" t="n">
+        <v>3844.954</v>
+      </c>
+      <c r="BM7" s="1" t="n">
+        <v>4182.5543</v>
+      </c>
+      <c r="BN7" s="1" t="n">
+        <v>4476.4037</v>
+      </c>
+      <c r="BO7" s="1" t="n">
         <v>2104.8643</v>
       </c>
-      <c r="BL7" s="1" t="n">
+      <c r="BP7" s="1" t="n">
         <v>2545.56</v>
       </c>
-      <c r="BM7" s="1" t="n">
+      <c r="BQ7" s="1" t="n">
         <v>2962.4778</v>
       </c>
-      <c r="BN7" s="1" t="n">
+      <c r="BR7" s="1" t="n">
         <v>3400.1212</v>
       </c>
-      <c r="BO7" s="1" t="n">
+      <c r="BS7" s="1" t="n">
         <v>3762.0251</v>
       </c>
-      <c r="BP7" s="1" t="n">
+      <c r="BT7" s="1" t="n">
         <v>4112.5478</v>
       </c>
-      <c r="BQ7" s="1" t="n">
+      <c r="BU7" s="1" t="n">
         <v>4347.054</v>
       </c>
-      <c r="BR7" s="1" t="n">
+      <c r="BV7" s="1" t="n">
+        <v>146.962</v>
+      </c>
+      <c r="BW7" s="1" t="n">
+        <v>557.4908</v>
+      </c>
+      <c r="BX7" s="1" t="n">
+        <v>908.1106</v>
+      </c>
+      <c r="BY7" s="1" t="n">
+        <v>1364.5879</v>
+      </c>
+      <c r="BZ7" s="1" t="n">
+        <v>2118.1069</v>
+      </c>
+      <c r="CA7" s="1" t="n">
+        <v>2584.6963</v>
+      </c>
+      <c r="CB7" s="1" t="n">
+        <v>3042.1122</v>
+      </c>
+      <c r="CC7" s="1" t="n">
+        <v>3520.8292</v>
+      </c>
+      <c r="CD7" s="1" t="n">
+        <v>3929.575</v>
+      </c>
+      <c r="CE7" s="1" t="n">
+        <v>4326.8777</v>
+      </c>
+      <c r="CF7" s="1" t="n">
+        <v>4601.1346</v>
+      </c>
+      <c r="CG7" s="1" t="n">
         <v>711</v>
       </c>
-      <c r="BS7" s="1" t="n">
+      <c r="CH7" s="1" t="n">
         <v>956.53</v>
       </c>
-      <c r="BT7" s="1" t="n">
+      <c r="CI7" s="1" t="n">
         <v>1315.38</v>
       </c>
     </row>
@@ -14886,33 +15226,78 @@
         <v>921.2184</v>
       </c>
       <c r="BK8" s="1" t="n">
+        <v>1055.6625</v>
+      </c>
+      <c r="BL8" s="1" t="n">
+        <v>1167.1429</v>
+      </c>
+      <c r="BM8" s="1" t="n">
+        <v>1267.7648</v>
+      </c>
+      <c r="BN8" s="1" t="n">
+        <v>1376.5885</v>
+      </c>
+      <c r="BO8" s="1" t="n">
         <v>753.2674</v>
       </c>
-      <c r="BL8" s="1" t="n">
+      <c r="BP8" s="1" t="n">
         <v>916.5306</v>
       </c>
-      <c r="BM8" s="1" t="n">
+      <c r="BQ8" s="1" t="n">
         <v>1073.2813</v>
       </c>
-      <c r="BN8" s="1" t="n">
+      <c r="BR8" s="1" t="n">
         <v>1240.1738</v>
       </c>
-      <c r="BO8" s="1" t="n">
+      <c r="BS8" s="1" t="n">
         <v>1391.1474</v>
       </c>
-      <c r="BP8" s="1" t="n">
+      <c r="BT8" s="1" t="n">
         <v>1521.9604</v>
       </c>
-      <c r="BQ8" s="1" t="n">
+      <c r="BU8" s="1" t="n">
         <v>1656.5005</v>
       </c>
-      <c r="BR8" s="1" t="n">
+      <c r="BV8" s="1" t="n">
+        <v>60.3721</v>
+      </c>
+      <c r="BW8" s="1" t="n">
+        <v>195.0618</v>
+      </c>
+      <c r="BX8" s="1" t="n">
+        <v>329.1546</v>
+      </c>
+      <c r="BY8" s="1" t="n">
+        <v>512.1138</v>
+      </c>
+      <c r="BZ8" s="1" t="n">
+        <v>815.2402</v>
+      </c>
+      <c r="CA8" s="1" t="n">
+        <v>990.9857</v>
+      </c>
+      <c r="CB8" s="1" t="n">
+        <v>1155.5257</v>
+      </c>
+      <c r="CC8" s="1" t="n">
+        <v>1379.8144</v>
+      </c>
+      <c r="CD8" s="1" t="n">
+        <v>1559.9447</v>
+      </c>
+      <c r="CE8" s="1" t="n">
+        <v>1708.9429</v>
+      </c>
+      <c r="CF8" s="1" t="n">
+        <v>1830.364</v>
+      </c>
+      <c r="CG8" s="1" t="n">
         <v>355.36</v>
       </c>
-      <c r="BS8" s="1" t="n">
+      <c r="CH8" s="1" t="n">
         <v>457.19</v>
       </c>
-      <c r="BT8" s="1" t="n">
+      <c r="CI8" s="1" t="n">
         <v>599.35</v>
       </c>
     </row>
@@ -15106,33 +15491,78 @@
         <v>605.6374</v>
       </c>
       <c r="BK9" s="1" t="n">
+        <v>744.3805</v>
+      </c>
+      <c r="BL9" s="1" t="n">
+        <v>827.0376</v>
+      </c>
+      <c r="BM9" s="1" t="n">
+        <v>875.1373</v>
+      </c>
+      <c r="BN9" s="1" t="n">
+        <v>882.8479</v>
+      </c>
+      <c r="BO9" s="1" t="n">
         <v>360.9991</v>
       </c>
-      <c r="BL9" s="1" t="n">
+      <c r="BP9" s="1" t="n">
         <v>520.28</v>
       </c>
-      <c r="BM9" s="1" t="n">
+      <c r="BQ9" s="1" t="n">
         <v>677.942</v>
       </c>
-      <c r="BN9" s="1" t="n">
+      <c r="BR9" s="1" t="n">
         <v>851.4805</v>
       </c>
-      <c r="BO9" s="1" t="n">
+      <c r="BS9" s="1" t="n">
         <v>957.6004</v>
       </c>
-      <c r="BP9" s="1" t="n">
+      <c r="BT9" s="1" t="n">
         <v>1026.0799</v>
       </c>
-      <c r="BQ9" s="1" t="n">
+      <c r="BU9" s="1" t="n">
         <v>1041.9497</v>
       </c>
-      <c r="BR9" s="1" t="n">
+      <c r="BV9" s="1" t="n">
+        <v>5.6055</v>
+      </c>
+      <c r="BW9" s="1" t="n">
+        <v>46.4601</v>
+      </c>
+      <c r="BX9" s="1" t="n">
+        <v>117.0135</v>
+      </c>
+      <c r="BY9" s="1" t="n">
+        <v>224.7055</v>
+      </c>
+      <c r="BZ9" s="1" t="n">
+        <v>390.8461</v>
+      </c>
+      <c r="CA9" s="1" t="n">
+        <v>562.098</v>
+      </c>
+      <c r="CB9" s="1" t="n">
+        <v>725.7313</v>
+      </c>
+      <c r="CC9" s="1" t="n">
+        <v>927.3303</v>
+      </c>
+      <c r="CD9" s="1" t="n">
+        <v>1063.4453</v>
+      </c>
+      <c r="CE9" s="1" t="n">
+        <v>1154.9562</v>
+      </c>
+      <c r="CF9" s="1" t="n">
+        <v>1176.4822</v>
+      </c>
+      <c r="CG9" s="1" t="n">
         <v>141.65</v>
       </c>
-      <c r="BS9" s="1" t="n">
+      <c r="CH9" s="1" t="n">
         <v>227.12</v>
       </c>
-      <c r="BT9" s="1" t="n">
+      <c r="CI9" s="1" t="n">
         <v>367.07</v>
       </c>
     </row>
@@ -15326,33 +15756,78 @@
         <v>1883.4608</v>
       </c>
       <c r="BK10" s="1" t="n">
+        <v>2169.199</v>
+      </c>
+      <c r="BL10" s="1" t="n">
+        <v>2365.2791</v>
+      </c>
+      <c r="BM10" s="1" t="n">
+        <v>2502.1567</v>
+      </c>
+      <c r="BN10" s="1" t="n">
+        <v>2599.2713</v>
+      </c>
+      <c r="BO10" s="1" t="n">
         <v>1487.1906</v>
       </c>
-      <c r="BL10" s="1" t="n">
+      <c r="BP10" s="1" t="n">
         <v>1769.6838</v>
       </c>
-      <c r="BM10" s="1" t="n">
+      <c r="BQ10" s="1" t="n">
         <v>2040.2389</v>
       </c>
-      <c r="BN10" s="1" t="n">
+      <c r="BR10" s="1" t="n">
         <v>2372.8153</v>
       </c>
-      <c r="BO10" s="1" t="n">
+      <c r="BS10" s="1" t="n">
         <v>2602.8313</v>
       </c>
-      <c r="BP10" s="1" t="n">
+      <c r="BT10" s="1" t="n">
         <v>2763.9211</v>
       </c>
-      <c r="BQ10" s="1" t="n">
+      <c r="BU10" s="1" t="n">
         <v>2833.9503</v>
       </c>
-      <c r="BR10" s="1" t="n">
+      <c r="BV10" s="1" t="n">
+        <v>110.1994</v>
+      </c>
+      <c r="BW10" s="1" t="n">
+        <v>402.3221</v>
+      </c>
+      <c r="BX10" s="1" t="n">
+        <v>700.4512</v>
+      </c>
+      <c r="BY10" s="1" t="n">
+        <v>997.8713</v>
+      </c>
+      <c r="BZ10" s="1" t="n">
+        <v>1477.5871</v>
+      </c>
+      <c r="CA10" s="1" t="n">
+        <v>1746.6626</v>
+      </c>
+      <c r="CB10" s="1" t="n">
+        <v>2041.8478</v>
+      </c>
+      <c r="CC10" s="1" t="n">
+        <v>2407.818</v>
+      </c>
+      <c r="CD10" s="1" t="n">
+        <v>2687.1412</v>
+      </c>
+      <c r="CE10" s="1" t="n">
+        <v>2885.6296</v>
+      </c>
+      <c r="CF10" s="1" t="n">
+        <v>2978.8629</v>
+      </c>
+      <c r="CG10" s="1" t="n">
         <v>185.51</v>
       </c>
-      <c r="BS10" s="1" t="n">
+      <c r="CH10" s="1" t="n">
         <v>254.08</v>
       </c>
-      <c r="BT10" s="1" t="n">
+      <c r="CI10" s="1" t="n">
         <v>360.76</v>
       </c>
     </row>
@@ -15543,33 +16018,78 @@
         <v>696.8611</v>
       </c>
       <c r="BK11" s="1" t="n">
+        <v>869.3222</v>
+      </c>
+      <c r="BL11" s="1" t="n">
+        <v>1007.4549</v>
+      </c>
+      <c r="BM11" s="1" t="n">
+        <v>1129.859</v>
+      </c>
+      <c r="BN11" s="1" t="n">
+        <v>1175.8793</v>
+      </c>
+      <c r="BO11" s="1" t="n">
         <v>477.4939</v>
       </c>
-      <c r="BL11" s="1" t="n">
+      <c r="BP11" s="1" t="n">
         <v>633.5031</v>
       </c>
-      <c r="BM11" s="1" t="n">
+      <c r="BQ11" s="1" t="n">
         <v>830.4023999999999</v>
       </c>
-      <c r="BN11" s="1" t="n">
+      <c r="BR11" s="1" t="n">
         <v>1014.4162</v>
       </c>
-      <c r="BO11" s="1" t="n">
+      <c r="BS11" s="1" t="n">
         <v>1164.1421</v>
       </c>
-      <c r="BP11" s="1" t="n">
+      <c r="BT11" s="1" t="n">
         <v>1263.3654</v>
       </c>
-      <c r="BQ11" s="1" t="n">
+      <c r="BU11" s="1" t="n">
         <v>1315.522</v>
       </c>
-      <c r="BR11" s="1" t="n">
+      <c r="BV11" s="1" t="n">
+        <v>11.6689</v>
+      </c>
+      <c r="BW11" s="1" t="n">
+        <v>46.5721</v>
+      </c>
+      <c r="BX11" s="1" t="n">
+        <v>130.0138</v>
+      </c>
+      <c r="BY11" s="1" t="n">
+        <v>356.5036</v>
+      </c>
+      <c r="BZ11" s="1" t="n">
+        <v>545.2777</v>
+      </c>
+      <c r="CA11" s="1" t="n">
+        <v>749.8876</v>
+      </c>
+      <c r="CB11" s="1" t="n">
+        <v>966.5164</v>
+      </c>
+      <c r="CC11" s="1" t="n">
+        <v>1167.5094</v>
+      </c>
+      <c r="CD11" s="1" t="n">
+        <v>1329.9829</v>
+      </c>
+      <c r="CE11" s="1" t="n">
+        <v>1433.1235</v>
+      </c>
+      <c r="CF11" s="1" t="n">
+        <v>1460.7761</v>
+      </c>
+      <c r="CG11" s="1" t="n">
         <v>64.18000000000001</v>
       </c>
-      <c r="BS11" s="1" t="n">
+      <c r="CH11" s="1" t="n">
         <v>116.27</v>
       </c>
-      <c r="BT11" s="1" t="n">
+      <c r="CI11" s="1" t="n">
         <v>170.04</v>
       </c>
     </row>
@@ -15763,33 +16283,78 @@
         <v>533.8824</v>
       </c>
       <c r="BK12" s="1" t="n">
+        <v>686.8334</v>
+      </c>
+      <c r="BL12" s="1" t="n">
+        <v>807.3795</v>
+      </c>
+      <c r="BM12" s="1" t="n">
+        <v>901.5086</v>
+      </c>
+      <c r="BN12" s="1" t="n">
+        <v>944.4049</v>
+      </c>
+      <c r="BO12" s="1" t="n">
         <v>339.1663</v>
       </c>
-      <c r="BL12" s="1" t="n">
+      <c r="BP12" s="1" t="n">
         <v>441.7863</v>
       </c>
-      <c r="BM12" s="1" t="n">
+      <c r="BQ12" s="1" t="n">
         <v>546.9347</v>
       </c>
-      <c r="BN12" s="1" t="n">
+      <c r="BR12" s="1" t="n">
         <v>705.7483999999999</v>
       </c>
-      <c r="BO12" s="1" t="n">
+      <c r="BS12" s="1" t="n">
         <v>811.6767</v>
       </c>
-      <c r="BP12" s="1" t="n">
+      <c r="BT12" s="1" t="n">
         <v>911.3123000000001</v>
       </c>
-      <c r="BQ12" s="1" t="n">
+      <c r="BU12" s="1" t="n">
         <v>958.0066</v>
       </c>
-      <c r="BR12" s="1" t="n">
+      <c r="BV12" s="1" t="n">
+        <v>1.1712</v>
+      </c>
+      <c r="BW12" s="1" t="n">
+        <v>21.2098</v>
+      </c>
+      <c r="BX12" s="1" t="n">
+        <v>69.5599</v>
+      </c>
+      <c r="BY12" s="1" t="n">
+        <v>149.85</v>
+      </c>
+      <c r="BZ12" s="1" t="n">
+        <v>303.0006</v>
+      </c>
+      <c r="CA12" s="1" t="n">
+        <v>419.3788</v>
+      </c>
+      <c r="CB12" s="1" t="n">
+        <v>545.3278</v>
+      </c>
+      <c r="CC12" s="1" t="n">
+        <v>698.0077</v>
+      </c>
+      <c r="CD12" s="1" t="n">
+        <v>816.4799</v>
+      </c>
+      <c r="CE12" s="1" t="n">
+        <v>926.6733</v>
+      </c>
+      <c r="CF12" s="1" t="n">
+        <v>982.9165</v>
+      </c>
+      <c r="CG12" s="1" t="n">
         <v>46.7</v>
       </c>
-      <c r="BS12" s="1" t="n">
+      <c r="CH12" s="1" t="n">
         <v>68.75</v>
       </c>
-      <c r="BT12" s="1" t="n">
+      <c r="CI12" s="1" t="n">
         <v>109.72</v>
       </c>
     </row>
@@ -15983,33 +16548,78 @@
         <v>2491.1393</v>
       </c>
       <c r="BK13" s="1" t="n">
+        <v>2853.6613</v>
+      </c>
+      <c r="BL13" s="1" t="n">
+        <v>3201.4421</v>
+      </c>
+      <c r="BM13" s="1" t="n">
+        <v>3573.5614</v>
+      </c>
+      <c r="BN13" s="1" t="n">
+        <v>4033.1832</v>
+      </c>
+      <c r="BO13" s="1" t="n">
         <v>1883.144</v>
       </c>
-      <c r="BL13" s="1" t="n">
+      <c r="BP13" s="1" t="n">
         <v>2230.3038</v>
       </c>
-      <c r="BM13" s="1" t="n">
+      <c r="BQ13" s="1" t="n">
         <v>2584.2312</v>
       </c>
-      <c r="BN13" s="1" t="n">
+      <c r="BR13" s="1" t="n">
         <v>2966.4188</v>
       </c>
-      <c r="BO13" s="1" t="n">
+      <c r="BS13" s="1" t="n">
         <v>3348.7605</v>
       </c>
-      <c r="BP13" s="1" t="n">
+      <c r="BT13" s="1" t="n">
         <v>3749.9584</v>
       </c>
-      <c r="BQ13" s="1" t="n">
+      <c r="BU13" s="1" t="n">
         <v>4231.3761</v>
       </c>
-      <c r="BR13" s="1" t="n">
+      <c r="BV13" s="1" t="n">
+        <v>575.3746</v>
+      </c>
+      <c r="BW13" s="1" t="n">
+        <v>859.965</v>
+      </c>
+      <c r="BX13" s="1" t="n">
+        <v>1194.7842</v>
+      </c>
+      <c r="BY13" s="1" t="n">
+        <v>1594.1142</v>
+      </c>
+      <c r="BZ13" s="1" t="n">
+        <v>2014.5417</v>
+      </c>
+      <c r="CA13" s="1" t="n">
+        <v>2419.1005</v>
+      </c>
+      <c r="CB13" s="1" t="n">
+        <v>2835.657</v>
+      </c>
+      <c r="CC13" s="1" t="n">
+        <v>3261.7396</v>
+      </c>
+      <c r="CD13" s="1" t="n">
+        <v>3691.9842</v>
+      </c>
+      <c r="CE13" s="1" t="n">
+        <v>4135.6927</v>
+      </c>
+      <c r="CF13" s="1" t="n">
+        <v>4698.7486</v>
+      </c>
+      <c r="CG13" s="1" t="n">
         <v>1838.56</v>
       </c>
-      <c r="BS13" s="1" t="n">
+      <c r="CH13" s="1" t="n">
         <v>2271.16</v>
       </c>
-      <c r="BT13" s="1" t="n">
+      <c r="CI13" s="1" t="n">
         <v>2747.1</v>
       </c>
     </row>
@@ -16203,33 +16813,78 @@
         <v>7580.5473</v>
       </c>
       <c r="BK14" s="1" t="n">
+        <v>8625.216200000001</v>
+      </c>
+      <c r="BL14" s="1" t="n">
+        <v>9447.659600000001</v>
+      </c>
+      <c r="BM14" s="1" t="n">
+        <v>10300.5737</v>
+      </c>
+      <c r="BN14" s="1" t="n">
+        <v>10982.3369</v>
+      </c>
+      <c r="BO14" s="1" t="n">
         <v>6090.8601</v>
       </c>
-      <c r="BL14" s="1" t="n">
+      <c r="BP14" s="1" t="n">
         <v>7150.0596</v>
       </c>
-      <c r="BM14" s="1" t="n">
+      <c r="BQ14" s="1" t="n">
         <v>8139.4743</v>
       </c>
-      <c r="BN14" s="1" t="n">
+      <c r="BR14" s="1" t="n">
         <v>9239.159799999999</v>
       </c>
-      <c r="BO14" s="1" t="n">
+      <c r="BS14" s="1" t="n">
         <v>10226.9891</v>
       </c>
-      <c r="BP14" s="1" t="n">
+      <c r="BT14" s="1" t="n">
         <v>11202.5769</v>
       </c>
-      <c r="BQ14" s="1" t="n">
+      <c r="BU14" s="1" t="n">
         <v>12009.3475</v>
       </c>
-      <c r="BR14" s="1" t="n">
+      <c r="BV14" s="1" t="n">
+        <v>1333.967</v>
+      </c>
+      <c r="BW14" s="1" t="n">
+        <v>2717.8193</v>
+      </c>
+      <c r="BX14" s="1" t="n">
+        <v>3790.4037</v>
+      </c>
+      <c r="BY14" s="1" t="n">
+        <v>4964.9387</v>
+      </c>
+      <c r="BZ14" s="1" t="n">
+        <v>6277.3765</v>
+      </c>
+      <c r="CA14" s="1" t="n">
+        <v>7509.0139</v>
+      </c>
+      <c r="CB14" s="1" t="n">
+        <v>8777.6101</v>
+      </c>
+      <c r="CC14" s="1" t="n">
+        <v>10052.6994</v>
+      </c>
+      <c r="CD14" s="1" t="n">
+        <v>11166.0281</v>
+      </c>
+      <c r="CE14" s="1" t="n">
+        <v>12253.3932</v>
+      </c>
+      <c r="CF14" s="1" t="n">
+        <v>13171.2702</v>
+      </c>
+      <c r="CG14" s="1" t="n">
         <v>2640.19</v>
       </c>
-      <c r="BS14" s="1" t="n">
+      <c r="CH14" s="1" t="n">
         <v>3233.88</v>
       </c>
-      <c r="BT14" s="1" t="n">
+      <c r="CI14" s="1" t="n">
         <v>3801.93</v>
       </c>
     </row>
@@ -16423,33 +17078,78 @@
         <v>6462.6226</v>
       </c>
       <c r="BK15" s="1" t="n">
+        <v>7454.9738</v>
+      </c>
+      <c r="BL15" s="1" t="n">
+        <v>8325.5862</v>
+      </c>
+      <c r="BM15" s="1" t="n">
+        <v>9271.6991</v>
+      </c>
+      <c r="BN15" s="1" t="n">
+        <v>9944.934800000001</v>
+      </c>
+      <c r="BO15" s="1" t="n">
         <v>5166.8744</v>
       </c>
-      <c r="BL15" s="1" t="n">
+      <c r="BP15" s="1" t="n">
         <v>6043.0388</v>
       </c>
-      <c r="BM15" s="1" t="n">
+      <c r="BQ15" s="1" t="n">
         <v>6960.0159</v>
       </c>
-      <c r="BN15" s="1" t="n">
+      <c r="BR15" s="1" t="n">
         <v>8055.4849</v>
       </c>
-      <c r="BO15" s="1" t="n">
+      <c r="BS15" s="1" t="n">
         <v>8984.134700000001</v>
       </c>
-      <c r="BP15" s="1" t="n">
+      <c r="BT15" s="1" t="n">
         <v>9958.0998</v>
       </c>
-      <c r="BQ15" s="1" t="n">
+      <c r="BU15" s="1" t="n">
         <v>10682.9713</v>
       </c>
-      <c r="BR15" s="1" t="n">
+      <c r="BV15" s="1" t="n">
+        <v>1089.4757</v>
+      </c>
+      <c r="BW15" s="1" t="n">
+        <v>2044.6521</v>
+      </c>
+      <c r="BX15" s="1" t="n">
+        <v>2968.3669</v>
+      </c>
+      <c r="BY15" s="1" t="n">
+        <v>3993.2959</v>
+      </c>
+      <c r="BZ15" s="1" t="n">
+        <v>5308.8371</v>
+      </c>
+      <c r="CA15" s="1" t="n">
+        <v>6300.7858</v>
+      </c>
+      <c r="CB15" s="1" t="n">
+        <v>7321.7283</v>
+      </c>
+      <c r="CC15" s="1" t="n">
+        <v>8536.7003</v>
+      </c>
+      <c r="CD15" s="1" t="n">
+        <v>9567.249</v>
+      </c>
+      <c r="CE15" s="1" t="n">
+        <v>10634.5743</v>
+      </c>
+      <c r="CF15" s="1" t="n">
+        <v>11413.6556</v>
+      </c>
+      <c r="CG15" s="1" t="n">
         <v>2498.33</v>
       </c>
-      <c r="BS15" s="1" t="n">
+      <c r="CH15" s="1" t="n">
         <v>3147.88</v>
       </c>
-      <c r="BT15" s="1" t="n">
+      <c r="CI15" s="1" t="n">
         <v>3944.7</v>
       </c>
     </row>
@@ -16643,33 +17343,78 @@
         <v>4208.3249</v>
       </c>
       <c r="BK16" s="1" t="n">
+        <v>4748.5628</v>
+      </c>
+      <c r="BL16" s="1" t="n">
+        <v>5161.6618</v>
+      </c>
+      <c r="BM16" s="1" t="n">
+        <v>5538.0215</v>
+      </c>
+      <c r="BN16" s="1" t="n">
+        <v>5974.1086</v>
+      </c>
+      <c r="BO16" s="1" t="n">
         <v>3387.0738</v>
       </c>
-      <c r="BL16" s="1" t="n">
+      <c r="BP16" s="1" t="n">
         <v>4022.9433</v>
       </c>
-      <c r="BM16" s="1" t="n">
+      <c r="BQ16" s="1" t="n">
         <v>4671.7852</v>
       </c>
-      <c r="BN16" s="1" t="n">
+      <c r="BR16" s="1" t="n">
         <v>5278.9535</v>
       </c>
-      <c r="BO16" s="1" t="n">
+      <c r="BS16" s="1" t="n">
         <v>5722.9806</v>
       </c>
-      <c r="BP16" s="1" t="n">
+      <c r="BT16" s="1" t="n">
         <v>6160.1311</v>
       </c>
-      <c r="BQ16" s="1" t="n">
+      <c r="BU16" s="1" t="n">
         <v>6670.4785</v>
       </c>
-      <c r="BR16" s="1" t="n">
+      <c r="BV16" s="1" t="n">
+        <v>569.5878</v>
+      </c>
+      <c r="BW16" s="1" t="n">
+        <v>1216.5308</v>
+      </c>
+      <c r="BX16" s="1" t="n">
+        <v>1920.8034</v>
+      </c>
+      <c r="BY16" s="1" t="n">
+        <v>2638.7145</v>
+      </c>
+      <c r="BZ16" s="1" t="n">
+        <v>3450.264</v>
+      </c>
+      <c r="CA16" s="1" t="n">
+        <v>4095.3453</v>
+      </c>
+      <c r="CB16" s="1" t="n">
+        <v>4796.7807</v>
+      </c>
+      <c r="CC16" s="1" t="n">
+        <v>5456.2578</v>
+      </c>
+      <c r="CD16" s="1" t="n">
+        <v>5966.0771</v>
+      </c>
+      <c r="CE16" s="1" t="n">
+        <v>6471.3629</v>
+      </c>
+      <c r="CF16" s="1" t="n">
+        <v>7042.2934</v>
+      </c>
+      <c r="CG16" s="1" t="n">
         <v>902.92</v>
       </c>
-      <c r="BS16" s="1" t="n">
+      <c r="CH16" s="1" t="n">
         <v>1095.12</v>
       </c>
-      <c r="BT16" s="1" t="n">
+      <c r="CI16" s="1" t="n">
         <v>1270.06</v>
       </c>
     </row>
@@ -16863,33 +17608,78 @@
         <v>3186.2848</v>
       </c>
       <c r="BK17" s="1" t="n">
+        <v>3685.1091</v>
+      </c>
+      <c r="BL17" s="1" t="n">
+        <v>4112.2427</v>
+      </c>
+      <c r="BM17" s="1" t="n">
+        <v>4522.269</v>
+      </c>
+      <c r="BN17" s="1" t="n">
+        <v>4940.338</v>
+      </c>
+      <c r="BO17" s="1" t="n">
         <v>2826.8979</v>
       </c>
-      <c r="BL17" s="1" t="n">
+      <c r="BP17" s="1" t="n">
         <v>3290.8329</v>
       </c>
-      <c r="BM17" s="1" t="n">
+      <c r="BQ17" s="1" t="n">
         <v>3730.7401</v>
       </c>
-      <c r="BN17" s="1" t="n">
+      <c r="BR17" s="1" t="n">
         <v>4303.2291</v>
       </c>
-      <c r="BO17" s="1" t="n">
+      <c r="BS17" s="1" t="n">
         <v>4773.6335</v>
       </c>
-      <c r="BP17" s="1" t="n">
+      <c r="BT17" s="1" t="n">
         <v>5252.9574</v>
       </c>
-      <c r="BQ17" s="1" t="n">
+      <c r="BU17" s="1" t="n">
         <v>5673.1288</v>
       </c>
-      <c r="BR17" s="1" t="n">
+      <c r="BV17" s="1" t="n">
+        <v>525.2369</v>
+      </c>
+      <c r="BW17" s="1" t="n">
+        <v>1132.9312</v>
+      </c>
+      <c r="BX17" s="1" t="n">
+        <v>1661.6057</v>
+      </c>
+      <c r="BY17" s="1" t="n">
+        <v>2254.1204</v>
+      </c>
+      <c r="BZ17" s="1" t="n">
+        <v>2905.6497</v>
+      </c>
+      <c r="CA17" s="1" t="n">
+        <v>3452.1566</v>
+      </c>
+      <c r="CB17" s="1" t="n">
+        <v>3966.2676</v>
+      </c>
+      <c r="CC17" s="1" t="n">
+        <v>4605.1381</v>
+      </c>
+      <c r="CD17" s="1" t="n">
+        <v>5107.6831</v>
+      </c>
+      <c r="CE17" s="1" t="n">
+        <v>5581.0132</v>
+      </c>
+      <c r="CF17" s="1" t="n">
+        <v>6026.8029</v>
+      </c>
+      <c r="CG17" s="1" t="n">
         <v>800.53</v>
       </c>
-      <c r="BS17" s="1" t="n">
+      <c r="CH17" s="1" t="n">
         <v>958.33</v>
       </c>
-      <c r="BT17" s="1" t="n">
+      <c r="CI17" s="1" t="n">
         <v>1131.69</v>
       </c>
     </row>
@@ -17083,33 +17873,78 @@
         <v>1378.7684</v>
       </c>
       <c r="BK18" s="1" t="n">
+        <v>1620.7265</v>
+      </c>
+      <c r="BL18" s="1" t="n">
+        <v>1818.3909</v>
+      </c>
+      <c r="BM18" s="1" t="n">
+        <v>2019.5297</v>
+      </c>
+      <c r="BN18" s="1" t="n">
+        <v>2174.9319</v>
+      </c>
+      <c r="BO18" s="1" t="n">
         <v>1025.1144</v>
       </c>
-      <c r="BL18" s="1" t="n">
+      <c r="BP18" s="1" t="n">
         <v>1247.7205</v>
       </c>
-      <c r="BM18" s="1" t="n">
+      <c r="BQ18" s="1" t="n">
         <v>1477.4854</v>
       </c>
-      <c r="BN18" s="1" t="n">
+      <c r="BR18" s="1" t="n">
         <v>1709.7371</v>
       </c>
-      <c r="BO18" s="1" t="n">
+      <c r="BS18" s="1" t="n">
         <v>1895.2201</v>
       </c>
-      <c r="BP18" s="1" t="n">
+      <c r="BT18" s="1" t="n">
         <v>2083.2327</v>
       </c>
-      <c r="BQ18" s="1" t="n">
+      <c r="BU18" s="1" t="n">
         <v>2239.1084</v>
       </c>
-      <c r="BR18" s="1" t="n">
+      <c r="BV18" s="1" t="n">
+        <v>223.9908</v>
+      </c>
+      <c r="BW18" s="1" t="n">
+        <v>424.1934</v>
+      </c>
+      <c r="BX18" s="1" t="n">
+        <v>626.9134</v>
+      </c>
+      <c r="BY18" s="1" t="n">
+        <v>836.4037</v>
+      </c>
+      <c r="BZ18" s="1" t="n">
+        <v>1063.7544</v>
+      </c>
+      <c r="CA18" s="1" t="n">
+        <v>1294.3787</v>
+      </c>
+      <c r="CB18" s="1" t="n">
+        <v>1546.5838</v>
+      </c>
+      <c r="CC18" s="1" t="n">
+        <v>1794.6414</v>
+      </c>
+      <c r="CD18" s="1" t="n">
+        <v>1996.2777</v>
+      </c>
+      <c r="CE18" s="1" t="n">
+        <v>2204.5139</v>
+      </c>
+      <c r="CF18" s="1" t="n">
+        <v>2378.0804</v>
+      </c>
+      <c r="CG18" s="1" t="n">
         <v>444.35</v>
       </c>
-      <c r="BS18" s="1" t="n">
+      <c r="CH18" s="1" t="n">
         <v>564.95</v>
       </c>
-      <c r="BT18" s="1" t="n">
+      <c r="CI18" s="1" t="n">
         <v>685.85</v>
       </c>
     </row>
@@ -17303,33 +18138,78 @@
         <v>4888.0392</v>
       </c>
       <c r="BK19" s="1" t="n">
+        <v>5590.8347</v>
+      </c>
+      <c r="BL19" s="1" t="n">
+        <v>6250.4568</v>
+      </c>
+      <c r="BM19" s="1" t="n">
+        <v>6921.8942</v>
+      </c>
+      <c r="BN19" s="1" t="n">
+        <v>7552.9666</v>
+      </c>
+      <c r="BO19" s="1" t="n">
         <v>4072.7077</v>
       </c>
-      <c r="BL19" s="1" t="n">
+      <c r="BP19" s="1" t="n">
         <v>4854.9526</v>
       </c>
-      <c r="BM19" s="1" t="n">
+      <c r="BQ19" s="1" t="n">
         <v>5588.1442</v>
       </c>
-      <c r="BN19" s="1" t="n">
+      <c r="BR19" s="1" t="n">
         <v>6384.8901</v>
       </c>
-      <c r="BO19" s="1" t="n">
+      <c r="BS19" s="1" t="n">
         <v>7179.8717</v>
       </c>
-      <c r="BP19" s="1" t="n">
+      <c r="BT19" s="1" t="n">
         <v>7948.4754</v>
       </c>
-      <c r="BQ19" s="1" t="n">
+      <c r="BU19" s="1" t="n">
         <v>8614.8945</v>
       </c>
-      <c r="BR19" s="1" t="n">
+      <c r="BV19" s="1" t="n">
+        <v>733.829</v>
+      </c>
+      <c r="BW19" s="1" t="n">
+        <v>1538.6551</v>
+      </c>
+      <c r="BX19" s="1" t="n">
+        <v>2264.1079</v>
+      </c>
+      <c r="BY19" s="1" t="n">
+        <v>3099.4348</v>
+      </c>
+      <c r="BZ19" s="1" t="n">
+        <v>4191.4142</v>
+      </c>
+      <c r="CA19" s="1" t="n">
+        <v>5065.515</v>
+      </c>
+      <c r="CB19" s="1" t="n">
+        <v>5901.0061</v>
+      </c>
+      <c r="CC19" s="1" t="n">
+        <v>6865.3487</v>
+      </c>
+      <c r="CD19" s="1" t="n">
+        <v>7780.1722</v>
+      </c>
+      <c r="CE19" s="1" t="n">
+        <v>8668.8086</v>
+      </c>
+      <c r="CF19" s="1" t="n">
+        <v>9450.4902</v>
+      </c>
+      <c r="CG19" s="1" t="n">
         <v>1823.27</v>
       </c>
-      <c r="BS19" s="1" t="n">
+      <c r="CH19" s="1" t="n">
         <v>2360.49</v>
       </c>
-      <c r="BT19" s="1" t="n">
+      <c r="CI19" s="1" t="n">
         <v>2996.27</v>
       </c>
     </row>
@@ -17523,33 +18403,78 @@
         <v>4212.2677</v>
       </c>
       <c r="BK20" s="1" t="n">
+        <v>4840.2283</v>
+      </c>
+      <c r="BL20" s="1" t="n">
+        <v>5472.8986</v>
+      </c>
+      <c r="BM20" s="1" t="n">
+        <v>6226.4826</v>
+      </c>
+      <c r="BN20" s="1" t="n">
+        <v>7015.4731</v>
+      </c>
+      <c r="BO20" s="1" t="n">
         <v>3261.1244</v>
       </c>
-      <c r="BL20" s="1" t="n">
+      <c r="BP20" s="1" t="n">
         <v>3871.2961</v>
       </c>
-      <c r="BM20" s="1" t="n">
+      <c r="BQ20" s="1" t="n">
         <v>4499.9816</v>
       </c>
-      <c r="BN20" s="1" t="n">
+      <c r="BR20" s="1" t="n">
         <v>5194.013</v>
       </c>
-      <c r="BO20" s="1" t="n">
+      <c r="BS20" s="1" t="n">
         <v>5879.158</v>
       </c>
-      <c r="BP20" s="1" t="n">
+      <c r="BT20" s="1" t="n">
         <v>6631.2605</v>
       </c>
-      <c r="BQ20" s="1" t="n">
+      <c r="BU20" s="1" t="n">
         <v>7464.5887</v>
       </c>
-      <c r="BR20" s="1" t="n">
+      <c r="BV20" s="1" t="n">
+        <v>416.6278</v>
+      </c>
+      <c r="BW20" s="1" t="n">
+        <v>1168.8649</v>
+      </c>
+      <c r="BX20" s="1" t="n">
+        <v>1831.185</v>
+      </c>
+      <c r="BY20" s="1" t="n">
+        <v>2585.7895</v>
+      </c>
+      <c r="BZ20" s="1" t="n">
+        <v>3346.1375</v>
+      </c>
+      <c r="CA20" s="1" t="n">
+        <v>4004.767</v>
+      </c>
+      <c r="CB20" s="1" t="n">
+        <v>4657.0959</v>
+      </c>
+      <c r="CC20" s="1" t="n">
+        <v>5391.3221</v>
+      </c>
+      <c r="CD20" s="1" t="n">
+        <v>6112.2297</v>
+      </c>
+      <c r="CE20" s="1" t="n">
+        <v>6911.302</v>
+      </c>
+      <c r="CF20" s="1" t="n">
+        <v>7782.2869</v>
+      </c>
+      <c r="CG20" s="1" t="n">
         <v>1116.4</v>
       </c>
-      <c r="BS20" s="1" t="n">
+      <c r="CH20" s="1" t="n">
         <v>1390.6</v>
       </c>
-      <c r="BT20" s="1" t="n">
+      <c r="CI20" s="1" t="n">
         <v>1721.76</v>
       </c>
     </row>
@@ -17743,33 +18668,78 @@
         <v>3177.427</v>
       </c>
       <c r="BK21" s="1" t="n">
+        <v>3608.6945</v>
+      </c>
+      <c r="BL21" s="1" t="n">
+        <v>3991.9571</v>
+      </c>
+      <c r="BM21" s="1" t="n">
+        <v>4303.2918</v>
+      </c>
+      <c r="BN21" s="1" t="n">
+        <v>4693.1172</v>
+      </c>
+      <c r="BO21" s="1" t="n">
         <v>2599.7396</v>
       </c>
-      <c r="BL21" s="1" t="n">
+      <c r="BP21" s="1" t="n">
         <v>2969.1658</v>
       </c>
-      <c r="BM21" s="1" t="n">
+      <c r="BQ21" s="1" t="n">
         <v>3432.7411</v>
       </c>
-      <c r="BN21" s="1" t="n">
+      <c r="BR21" s="1" t="n">
         <v>3927.5544</v>
       </c>
-      <c r="BO21" s="1" t="n">
+      <c r="BS21" s="1" t="n">
         <v>4356.8791</v>
       </c>
-      <c r="BP21" s="1" t="n">
+      <c r="BT21" s="1" t="n">
         <v>4699.571</v>
       </c>
-      <c r="BQ21" s="1" t="n">
+      <c r="BU21" s="1" t="n">
         <v>5111.7254</v>
       </c>
-      <c r="BR21" s="1" t="n">
+      <c r="BV21" s="1" t="n">
+        <v>127.3853</v>
+      </c>
+      <c r="BW21" s="1" t="n">
+        <v>257.2178</v>
+      </c>
+      <c r="BX21" s="1" t="n">
+        <v>647.4562</v>
+      </c>
+      <c r="BY21" s="1" t="n">
+        <v>1020.7733</v>
+      </c>
+      <c r="BZ21" s="1" t="n">
+        <v>1604.5057</v>
+      </c>
+      <c r="CA21" s="1" t="n">
+        <v>2018.1998</v>
+      </c>
+      <c r="CB21" s="1" t="n">
+        <v>2602.6772</v>
+      </c>
+      <c r="CC21" s="1" t="n">
+        <v>3261.6175</v>
+      </c>
+      <c r="CD21" s="1" t="n">
+        <v>3843.4239</v>
+      </c>
+      <c r="CE21" s="1" t="n">
+        <v>4338.8736</v>
+      </c>
+      <c r="CF21" s="1" t="n">
+        <v>4888.8684</v>
+      </c>
+      <c r="CG21" s="1" t="n">
         <v>1321.65</v>
       </c>
-      <c r="BS21" s="1" t="n">
+      <c r="CH21" s="1" t="n">
         <v>1740.37</v>
       </c>
-      <c r="BT21" s="1" t="n">
+      <c r="CI21" s="1" t="n">
         <v>2193.2</v>
       </c>
     </row>
@@ -17963,33 +18933,78 @@
         <v>2314.5632</v>
       </c>
       <c r="BK22" s="1" t="n">
+        <v>2738.4736</v>
+      </c>
+      <c r="BL22" s="1" t="n">
+        <v>3142.8733</v>
+      </c>
+      <c r="BM22" s="1" t="n">
+        <v>3531.1744</v>
+      </c>
+      <c r="BN22" s="1" t="n">
+        <v>3945.9495</v>
+      </c>
+      <c r="BO22" s="1" t="n">
         <v>1867.6564</v>
       </c>
-      <c r="BL22" s="1" t="n">
+      <c r="BP22" s="1" t="n">
         <v>2220.3776</v>
       </c>
-      <c r="BM22" s="1" t="n">
+      <c r="BQ22" s="1" t="n">
         <v>2653.3632</v>
       </c>
-      <c r="BN22" s="1" t="n">
+      <c r="BR22" s="1" t="n">
         <v>3130.8499</v>
       </c>
-      <c r="BO22" s="1" t="n">
+      <c r="BS22" s="1" t="n">
         <v>3576.9251</v>
       </c>
-      <c r="BP22" s="1" t="n">
+      <c r="BT22" s="1" t="n">
         <v>4005.5343</v>
       </c>
-      <c r="BQ22" s="1" t="n">
+      <c r="BU22" s="1" t="n">
         <v>4445.4659</v>
       </c>
-      <c r="BR22" s="1" t="n">
+      <c r="BV22" s="1" t="n">
+        <v>333.0843</v>
+      </c>
+      <c r="BW22" s="1" t="n">
+        <v>655.3239</v>
+      </c>
+      <c r="BX22" s="1" t="n">
+        <v>1062.1031</v>
+      </c>
+      <c r="BY22" s="1" t="n">
+        <v>1457.1067</v>
+      </c>
+      <c r="BZ22" s="1" t="n">
+        <v>1992.3882</v>
+      </c>
+      <c r="CA22" s="1" t="n">
+        <v>2368.4144</v>
+      </c>
+      <c r="CB22" s="1" t="n">
+        <v>2846.5118</v>
+      </c>
+      <c r="CC22" s="1" t="n">
+        <v>3386.293</v>
+      </c>
+      <c r="CD22" s="1" t="n">
+        <v>3894.2057</v>
+      </c>
+      <c r="CE22" s="1" t="n">
+        <v>4377.2666</v>
+      </c>
+      <c r="CF22" s="1" t="n">
+        <v>4880.4403</v>
+      </c>
+      <c r="CG22" s="1" t="n">
         <v>661.92</v>
       </c>
-      <c r="BS22" s="1" t="n">
+      <c r="CH22" s="1" t="n">
         <v>798.51</v>
       </c>
-      <c r="BT22" s="1" t="n">
+      <c r="CI22" s="1" t="n">
         <v>993.5700000000001</v>
       </c>
     </row>
@@ -18183,33 +19198,78 @@
         <v>8869.0731</v>
       </c>
       <c r="BK23" s="1" t="n">
+        <v>10295.1467</v>
+      </c>
+      <c r="BL23" s="1" t="n">
+        <v>11524.1125</v>
+      </c>
+      <c r="BM23" s="1" t="n">
+        <v>12918.8647</v>
+      </c>
+      <c r="BN23" s="1" t="n">
+        <v>14412.1933</v>
+      </c>
+      <c r="BO23" s="1" t="n">
         <v>7255.5958</v>
       </c>
-      <c r="BL23" s="1" t="n">
+      <c r="BP23" s="1" t="n">
         <v>8462.7886</v>
       </c>
-      <c r="BM23" s="1" t="n">
+      <c r="BQ23" s="1" t="n">
         <v>9820.936799999999</v>
       </c>
-      <c r="BN23" s="1" t="n">
+      <c r="BR23" s="1" t="n">
         <v>11464.4409</v>
       </c>
-      <c r="BO23" s="1" t="n">
+      <c r="BS23" s="1" t="n">
         <v>12811.8919</v>
       </c>
-      <c r="BP23" s="1" t="n">
+      <c r="BT23" s="1" t="n">
         <v>14343.817</v>
       </c>
-      <c r="BQ23" s="1" t="n">
+      <c r="BU23" s="1" t="n">
         <v>15852.162</v>
       </c>
-      <c r="BR23" s="1" t="n">
+      <c r="BV23" s="1" t="n">
+        <v>1309.5673</v>
+      </c>
+      <c r="BW23" s="1" t="n">
+        <v>2548.8348</v>
+      </c>
+      <c r="BX23" s="1" t="n">
+        <v>3752.8039</v>
+      </c>
+      <c r="BY23" s="1" t="n">
+        <v>5186.7414</v>
+      </c>
+      <c r="BZ23" s="1" t="n">
+        <v>7433.8878</v>
+      </c>
+      <c r="CA23" s="1" t="n">
+        <v>8899.268</v>
+      </c>
+      <c r="CB23" s="1" t="n">
+        <v>10414.8706</v>
+      </c>
+      <c r="CC23" s="1" t="n">
+        <v>12276.8539</v>
+      </c>
+      <c r="CD23" s="1" t="n">
+        <v>13843.4163</v>
+      </c>
+      <c r="CE23" s="1" t="n">
+        <v>15644.2007</v>
+      </c>
+      <c r="CF23" s="1" t="n">
+        <v>17312.7415</v>
+      </c>
+      <c r="CG23" s="1" t="n">
         <v>2477.43</v>
       </c>
-      <c r="BS23" s="1" t="n">
+      <c r="CH23" s="1" t="n">
         <v>3088.59</v>
       </c>
-      <c r="BT23" s="1" t="n">
+      <c r="CI23" s="1" t="n">
         <v>3967.96</v>
       </c>
     </row>
@@ -18403,33 +19463,78 @@
         <v>1761.725</v>
       </c>
       <c r="BK24" s="1" t="n">
+        <v>2000.4418</v>
+      </c>
+      <c r="BL24" s="1" t="n">
+        <v>2303.6253</v>
+      </c>
+      <c r="BM24" s="1" t="n">
+        <v>2632.5696</v>
+      </c>
+      <c r="BN24" s="1" t="n">
+        <v>3004.1257</v>
+      </c>
+      <c r="BO24" s="1" t="n">
         <v>1738.2592</v>
       </c>
-      <c r="BL24" s="1" t="n">
+      <c r="BP24" s="1" t="n">
         <v>1957.0021</v>
       </c>
-      <c r="BM24" s="1" t="n">
+      <c r="BQ24" s="1" t="n">
         <v>2264.5778</v>
       </c>
-      <c r="BN24" s="1" t="n">
+      <c r="BR24" s="1" t="n">
         <v>2574.8165</v>
       </c>
-      <c r="BO24" s="1" t="n">
+      <c r="BS24" s="1" t="n">
         <v>2903.6425</v>
       </c>
-      <c r="BP24" s="1" t="n">
+      <c r="BT24" s="1" t="n">
         <v>3323.4118</v>
       </c>
-      <c r="BQ24" s="1" t="n">
+      <c r="BU24" s="1" t="n">
         <v>3814.4125</v>
       </c>
-      <c r="BR24" s="1" t="n">
+      <c r="BV24" s="1" t="n">
+        <v>260.9228</v>
+      </c>
+      <c r="BW24" s="1" t="n">
+        <v>652.102</v>
+      </c>
+      <c r="BX24" s="1" t="n">
+        <v>990.9353</v>
+      </c>
+      <c r="BY24" s="1" t="n">
+        <v>1338.789</v>
+      </c>
+      <c r="BZ24" s="1" t="n">
+        <v>1830.6391</v>
+      </c>
+      <c r="CA24" s="1" t="n">
+        <v>2049.8094</v>
+      </c>
+      <c r="CB24" s="1" t="n">
+        <v>2287.4554</v>
+      </c>
+      <c r="CC24" s="1" t="n">
+        <v>2630.6858</v>
+      </c>
+      <c r="CD24" s="1" t="n">
+        <v>2966.1383</v>
+      </c>
+      <c r="CE24" s="1" t="n">
+        <v>3353.4498</v>
+      </c>
+      <c r="CF24" s="1" t="n">
+        <v>3845.6156</v>
+      </c>
+      <c r="CG24" s="1" t="n">
         <v>250.7</v>
       </c>
-      <c r="BS24" s="1" t="n">
+      <c r="CH24" s="1" t="n">
         <v>304.15</v>
       </c>
-      <c r="BT24" s="1" t="n">
+      <c r="CI24" s="1" t="n">
         <v>383.36</v>
       </c>
     </row>
@@ -18623,33 +19728,78 @@
         <v>1087.281</v>
       </c>
       <c r="BK25" s="1" t="n">
+        <v>1200.8325</v>
+      </c>
+      <c r="BL25" s="1" t="n">
+        <v>1339.3516</v>
+      </c>
+      <c r="BM25" s="1" t="n">
+        <v>1525.0322</v>
+      </c>
+      <c r="BN25" s="1" t="n">
+        <v>1715.0418</v>
+      </c>
+      <c r="BO25" s="1" t="n">
         <v>565.3280999999999</v>
       </c>
-      <c r="BL25" s="1" t="n">
+      <c r="BP25" s="1" t="n">
         <v>659.5191</v>
       </c>
-      <c r="BM25" s="1" t="n">
+      <c r="BQ25" s="1" t="n">
         <v>753.8681</v>
       </c>
-      <c r="BN25" s="1" t="n">
+      <c r="BR25" s="1" t="n">
         <v>863.3535000000001</v>
       </c>
-      <c r="BO25" s="1" t="n">
+      <c r="BS25" s="1" t="n">
         <v>987.2691</v>
       </c>
-      <c r="BP25" s="1" t="n">
+      <c r="BT25" s="1" t="n">
         <v>1141.9704</v>
       </c>
-      <c r="BQ25" s="1" t="n">
+      <c r="BU25" s="1" t="n">
         <v>1336.1768</v>
       </c>
-      <c r="BR25" s="1" t="n">
+      <c r="BV25" s="1" t="n">
+        <v>105.1338</v>
+      </c>
+      <c r="BW25" s="1" t="n">
+        <v>215.5315</v>
+      </c>
+      <c r="BX25" s="1" t="n">
+        <v>291.7818</v>
+      </c>
+      <c r="BY25" s="1" t="n">
+        <v>387.8324</v>
+      </c>
+      <c r="BZ25" s="1" t="n">
+        <v>507.6647</v>
+      </c>
+      <c r="CA25" s="1" t="n">
+        <v>611.5227</v>
+      </c>
+      <c r="CB25" s="1" t="n">
+        <v>726.5321</v>
+      </c>
+      <c r="CC25" s="1" t="n">
+        <v>860.313</v>
+      </c>
+      <c r="CD25" s="1" t="n">
+        <v>996.4998000000001</v>
+      </c>
+      <c r="CE25" s="1" t="n">
+        <v>1158.1955</v>
+      </c>
+      <c r="CF25" s="1" t="n">
+        <v>1341.6668</v>
+      </c>
+      <c r="CG25" s="1" t="n">
         <v>238.32</v>
       </c>
-      <c r="BS25" s="1" t="n">
+      <c r="CH25" s="1" t="n">
         <v>283.22</v>
       </c>
-      <c r="BT25" s="1" t="n">
+      <c r="CI25" s="1" t="n">
         <v>341.45</v>
       </c>
     </row>
@@ -18843,33 +19993,78 @@
         <v>2632.019</v>
       </c>
       <c r="BK26" s="1" t="n">
+        <v>3134.6528</v>
+      </c>
+      <c r="BL26" s="1" t="n">
+        <v>3469.4712</v>
+      </c>
+      <c r="BM26" s="1" t="n">
+        <v>3861.2471</v>
+      </c>
+      <c r="BN26" s="1" t="n">
+        <v>4248.7612</v>
+      </c>
+      <c r="BO26" s="1" t="n">
         <v>2127.9302</v>
       </c>
-      <c r="BL26" s="1" t="n">
+      <c r="BP26" s="1" t="n">
         <v>2454.1705</v>
       </c>
-      <c r="BM26" s="1" t="n">
+      <c r="BQ26" s="1" t="n">
         <v>2829.9666</v>
       </c>
-      <c r="BN26" s="1" t="n">
+      <c r="BR26" s="1" t="n">
         <v>3321.82</v>
       </c>
-      <c r="BO26" s="1" t="n">
+      <c r="BS26" s="1" t="n">
         <v>3669.239</v>
       </c>
-      <c r="BP26" s="1" t="n">
+      <c r="BT26" s="1" t="n">
         <v>4034.9471</v>
       </c>
-      <c r="BQ26" s="1" t="n">
+      <c r="BU26" s="1" t="n">
         <v>4439.3034</v>
       </c>
-      <c r="BR26" s="1" t="n">
+      <c r="BV26" s="1" t="n">
+        <v>286.0916</v>
+      </c>
+      <c r="BW26" s="1" t="n">
+        <v>764.5525</v>
+      </c>
+      <c r="BX26" s="1" t="n">
+        <v>1113.1892</v>
+      </c>
+      <c r="BY26" s="1" t="n">
+        <v>1541.0597</v>
+      </c>
+      <c r="BZ26" s="1" t="n">
+        <v>2143.0459</v>
+      </c>
+      <c r="CA26" s="1" t="n">
+        <v>2493.0352</v>
+      </c>
+      <c r="CB26" s="1" t="n">
+        <v>2842.0911</v>
+      </c>
+      <c r="CC26" s="1" t="n">
+        <v>3285.2785</v>
+      </c>
+      <c r="CD26" s="1" t="n">
+        <v>3621.1897</v>
+      </c>
+      <c r="CE26" s="1" t="n">
+        <v>3975.2255</v>
+      </c>
+      <c r="CF26" s="1" t="n">
+        <v>4351.9565</v>
+      </c>
+      <c r="CG26" s="1" t="n">
         <v>655.3200000000001</v>
       </c>
-      <c r="BS26" s="1" t="n">
+      <c r="CH26" s="1" t="n">
         <v>814.7</v>
       </c>
-      <c r="BT26" s="1" t="n">
+      <c r="CI26" s="1" t="n">
         <v>942.48</v>
       </c>
     </row>
@@ -19063,33 +20258,78 @@
         <v>3563.3777</v>
       </c>
       <c r="BK27" s="1" t="n">
+        <v>4158.621</v>
+      </c>
+      <c r="BL27" s="1" t="n">
+        <v>4657.4916</v>
+      </c>
+      <c r="BM27" s="1" t="n">
+        <v>5178.3249</v>
+      </c>
+      <c r="BN27" s="1" t="n">
+        <v>5697.8652</v>
+      </c>
+      <c r="BO27" s="1" t="n">
         <v>3101.1063</v>
       </c>
-      <c r="BL27" s="1" t="n">
+      <c r="BP27" s="1" t="n">
         <v>3615.8022</v>
       </c>
-      <c r="BM27" s="1" t="n">
+      <c r="BQ27" s="1" t="n">
         <v>4215.6642</v>
       </c>
-      <c r="BN27" s="1" t="n">
+      <c r="BR27" s="1" t="n">
         <v>4872.4485</v>
       </c>
-      <c r="BO27" s="1" t="n">
+      <c r="BS27" s="1" t="n">
         <v>5474.7924</v>
       </c>
-      <c r="BP27" s="1" t="n">
+      <c r="BT27" s="1" t="n">
         <v>6011.5283</v>
       </c>
-      <c r="BQ27" s="1" t="n">
+      <c r="BU27" s="1" t="n">
         <v>6573.2391</v>
       </c>
-      <c r="BR27" s="1" t="n">
+      <c r="BV27" s="1" t="n">
+        <v>672.6098</v>
+      </c>
+      <c r="BW27" s="1" t="n">
+        <v>1332.3518</v>
+      </c>
+      <c r="BX27" s="1" t="n">
+        <v>1950.1877</v>
+      </c>
+      <c r="BY27" s="1" t="n">
+        <v>2570.0147</v>
+      </c>
+      <c r="BZ27" s="1" t="n">
+        <v>3360.5003</v>
+      </c>
+      <c r="CA27" s="1" t="n">
+        <v>3946.0865</v>
+      </c>
+      <c r="CB27" s="1" t="n">
+        <v>4632.6255</v>
+      </c>
+      <c r="CC27" s="1" t="n">
+        <v>5340.7763</v>
+      </c>
+      <c r="CD27" s="1" t="n">
+        <v>6012.5084</v>
+      </c>
+      <c r="CE27" s="1" t="n">
+        <v>6659.278</v>
+      </c>
+      <c r="CF27" s="1" t="n">
+        <v>7315.3072</v>
+      </c>
+      <c r="CG27" s="1" t="n">
         <v>1313.11</v>
       </c>
-      <c r="BS27" s="1" t="n">
+      <c r="CH27" s="1" t="n">
         <v>1713.79</v>
       </c>
-      <c r="BT27" s="1" t="n">
+      <c r="CI27" s="1" t="n">
         <v>2154.84</v>
       </c>
     </row>
@@ -19283,33 +20523,78 @@
         <v>1574.8904</v>
       </c>
       <c r="BK28" s="1" t="n">
+        <v>1728.8098</v>
+      </c>
+      <c r="BL28" s="1" t="n">
+        <v>1915.9075</v>
+      </c>
+      <c r="BM28" s="1" t="n">
+        <v>2196.5382</v>
+      </c>
+      <c r="BN28" s="1" t="n">
+        <v>2349.2273</v>
+      </c>
+      <c r="BO28" s="1" t="n">
         <v>1404.2818</v>
       </c>
-      <c r="BL28" s="1" t="n">
+      <c r="BP28" s="1" t="n">
         <v>1655.5087</v>
       </c>
-      <c r="BM28" s="1" t="n">
+      <c r="BQ28" s="1" t="n">
         <v>1937.8807</v>
       </c>
-      <c r="BN28" s="1" t="n">
+      <c r="BR28" s="1" t="n">
         <v>2194.2062</v>
       </c>
-      <c r="BO28" s="1" t="n">
+      <c r="BS28" s="1" t="n">
         <v>2471.8956</v>
       </c>
-      <c r="BP28" s="1" t="n">
+      <c r="BT28" s="1" t="n">
         <v>2769.5667</v>
       </c>
-      <c r="BQ28" s="1" t="n">
+      <c r="BU28" s="1" t="n">
         <v>2990.8139</v>
       </c>
-      <c r="BR28" s="1" t="n">
+      <c r="BV28" s="1" t="n">
+        <v>247.425</v>
+      </c>
+      <c r="BW28" s="1" t="n">
+        <v>600.5486</v>
+      </c>
+      <c r="BX28" s="1" t="n">
+        <v>832.1751</v>
+      </c>
+      <c r="BY28" s="1" t="n">
+        <v>1098.5865</v>
+      </c>
+      <c r="BZ28" s="1" t="n">
+        <v>1495.1402</v>
+      </c>
+      <c r="CA28" s="1" t="n">
+        <v>1808.0819</v>
+      </c>
+      <c r="CB28" s="1" t="n">
+        <v>2149.6928</v>
+      </c>
+      <c r="CC28" s="1" t="n">
+        <v>2482.3587</v>
+      </c>
+      <c r="CD28" s="1" t="n">
+        <v>2821.4677</v>
+      </c>
+      <c r="CE28" s="1" t="n">
+        <v>3162.5041</v>
+      </c>
+      <c r="CF28" s="1" t="n">
+        <v>3418.7451</v>
+      </c>
+      <c r="CG28" s="1" t="n">
         <v>385.18</v>
       </c>
-      <c r="BS28" s="1" t="n">
+      <c r="CH28" s="1" t="n">
         <v>465.16</v>
       </c>
-      <c r="BT28" s="1" t="n">
+      <c r="CI28" s="1" t="n">
         <v>552.7</v>
       </c>
     </row>
@@ -19503,33 +20788,78 @@
         <v>1832.3491</v>
       </c>
       <c r="BK29" s="1" t="n">
+        <v>2192.8632</v>
+      </c>
+      <c r="BL29" s="1" t="n">
+        <v>2576.9641</v>
+      </c>
+      <c r="BM29" s="1" t="n">
+        <v>2915.669</v>
+      </c>
+      <c r="BN29" s="1" t="n">
+        <v>3247.2329</v>
+      </c>
+      <c r="BO29" s="1" t="n">
         <v>1729.106</v>
       </c>
-      <c r="BL29" s="1" t="n">
+      <c r="BP29" s="1" t="n">
         <v>2043.4472</v>
       </c>
-      <c r="BM29" s="1" t="n">
+      <c r="BQ29" s="1" t="n">
         <v>2407.8468</v>
       </c>
-      <c r="BN29" s="1" t="n">
+      <c r="BR29" s="1" t="n">
         <v>2843.9346</v>
       </c>
-      <c r="BO29" s="1" t="n">
+      <c r="BS29" s="1" t="n">
         <v>3200.2112</v>
       </c>
-      <c r="BP29" s="1" t="n">
+      <c r="BT29" s="1" t="n">
         <v>3658.0604</v>
       </c>
-      <c r="BQ29" s="1" t="n">
+      <c r="BU29" s="1" t="n">
         <v>4151.4085</v>
       </c>
-      <c r="BR29" s="1" t="n">
+      <c r="BV29" s="1" t="n">
+        <v>242.6311</v>
+      </c>
+      <c r="BW29" s="1" t="n">
+        <v>749.7573</v>
+      </c>
+      <c r="BX29" s="1" t="n">
+        <v>1087.9695</v>
+      </c>
+      <c r="BY29" s="1" t="n">
+        <v>1449.1346</v>
+      </c>
+      <c r="BZ29" s="1" t="n">
+        <v>1955.6895</v>
+      </c>
+      <c r="CA29" s="1" t="n">
+        <v>2306.5588</v>
+      </c>
+      <c r="CB29" s="1" t="n">
+        <v>2699.6027</v>
+      </c>
+      <c r="CC29" s="1" t="n">
+        <v>3160.0545</v>
+      </c>
+      <c r="CD29" s="1" t="n">
+        <v>3578.0394</v>
+      </c>
+      <c r="CE29" s="1" t="n">
+        <v>4018.8729</v>
+      </c>
+      <c r="CF29" s="1" t="n">
+        <v>4505.1875</v>
+      </c>
+      <c r="CG29" s="1" t="n">
         <v>384.64</v>
       </c>
-      <c r="BS29" s="1" t="n">
+      <c r="CH29" s="1" t="n">
         <v>473.69</v>
       </c>
-      <c r="BT29" s="1" t="n">
+      <c r="CI29" s="1" t="n">
         <v>581.25</v>
       </c>
     </row>
@@ -19717,33 +21047,78 @@
         <v>53.3767</v>
       </c>
       <c r="BK30" s="1" t="n">
+        <v>60.8674</v>
+      </c>
+      <c r="BL30" s="1" t="n">
+        <v>75.09739999999999</v>
+      </c>
+      <c r="BM30" s="1" t="n">
+        <v>91.747</v>
+      </c>
+      <c r="BN30" s="1" t="n">
+        <v>92.6036</v>
+      </c>
+      <c r="BO30" s="1" t="n">
         <v>38.0519</v>
       </c>
-      <c r="BL30" s="1" t="n">
+      <c r="BP30" s="1" t="n">
         <v>54.7453</v>
       </c>
-      <c r="BM30" s="1" t="n">
+      <c r="BQ30" s="1" t="n">
         <v>69.53449999999999</v>
       </c>
-      <c r="BN30" s="1" t="n">
+      <c r="BR30" s="1" t="n">
         <v>85.7863</v>
       </c>
-      <c r="BO30" s="1" t="n">
+      <c r="BS30" s="1" t="n">
         <v>105.2434</v>
       </c>
-      <c r="BP30" s="1" t="n">
+      <c r="BT30" s="1" t="n">
         <v>124.1005</v>
       </c>
-      <c r="BQ30" s="1" t="n">
+      <c r="BU30" s="1" t="n">
         <v>129.5559</v>
       </c>
-      <c r="BR30" s="1" t="n">
+      <c r="BV30" s="1" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="BW30" s="1" t="n">
+        <v>6.6395</v>
+      </c>
+      <c r="BX30" s="1" t="n">
+        <v>17.1717</v>
+      </c>
+      <c r="BY30" s="1" t="n">
+        <v>39.6309</v>
+      </c>
+      <c r="BZ30" s="1" t="n">
+        <v>59.4021</v>
+      </c>
+      <c r="CA30" s="1" t="n">
+        <v>72.26179999999999</v>
+      </c>
+      <c r="CB30" s="1" t="n">
+        <v>89.88209999999999</v>
+      </c>
+      <c r="CC30" s="1" t="n">
+        <v>111.2782</v>
+      </c>
+      <c r="CD30" s="1" t="n">
+        <v>128.7353</v>
+      </c>
+      <c r="CE30" s="1" t="n">
+        <v>155.4961</v>
+      </c>
+      <c r="CF30" s="1" t="n">
+        <v>165.4676</v>
+      </c>
+      <c r="CG30" s="1" t="n">
         <v>10.59</v>
       </c>
-      <c r="BS30" s="1" t="n">
+      <c r="CH30" s="1" t="n">
         <v>15.95</v>
       </c>
-      <c r="BT30" s="1" t="n">
+      <c r="CI30" s="1" t="n">
         <v>23.72</v>
       </c>
     </row>
@@ -19937,33 +21312,78 @@
         <v>2160.236</v>
       </c>
       <c r="BK31" s="1" t="n">
+        <v>2589.9488</v>
+      </c>
+      <c r="BL31" s="1" t="n">
+        <v>2913.0173</v>
+      </c>
+      <c r="BM31" s="1" t="n">
+        <v>3241.9132</v>
+      </c>
+      <c r="BN31" s="1" t="n">
+        <v>3534.6664</v>
+      </c>
+      <c r="BO31" s="1" t="n">
         <v>1681.6116</v>
       </c>
-      <c r="BL31" s="1" t="n">
+      <c r="BP31" s="1" t="n">
         <v>1985.0995</v>
       </c>
-      <c r="BM31" s="1" t="n">
+      <c r="BQ31" s="1" t="n">
         <v>2324.7106</v>
       </c>
-      <c r="BN31" s="1" t="n">
+      <c r="BR31" s="1" t="n">
         <v>2788.2273</v>
       </c>
-      <c r="BO31" s="1" t="n">
+      <c r="BS31" s="1" t="n">
         <v>3167.6566</v>
       </c>
-      <c r="BP31" s="1" t="n">
+      <c r="BT31" s="1" t="n">
         <v>3531.7209</v>
       </c>
-      <c r="BQ31" s="1" t="n">
+      <c r="BU31" s="1" t="n">
         <v>3903.6487</v>
       </c>
-      <c r="BR31" s="1" t="n">
+      <c r="BV31" s="1" t="n">
+        <v>191.9716</v>
+      </c>
+      <c r="BW31" s="1" t="n">
+        <v>518.5812</v>
+      </c>
+      <c r="BX31" s="1" t="n">
+        <v>821.0171</v>
+      </c>
+      <c r="BY31" s="1" t="n">
+        <v>1192.1621</v>
+      </c>
+      <c r="BZ31" s="1" t="n">
+        <v>1807.5276</v>
+      </c>
+      <c r="CA31" s="1" t="n">
+        <v>2154.319</v>
+      </c>
+      <c r="CB31" s="1" t="n">
+        <v>2560.2311</v>
+      </c>
+      <c r="CC31" s="1" t="n">
+        <v>3098.5138</v>
+      </c>
+      <c r="CD31" s="1" t="n">
+        <v>3504.4533</v>
+      </c>
+      <c r="CE31" s="1" t="n">
+        <v>3972.8269</v>
+      </c>
+      <c r="CF31" s="1" t="n">
+        <v>4404.3898</v>
+      </c>
+      <c r="CG31" s="1" t="n">
         <v>802.1</v>
       </c>
-      <c r="BS31" s="1" t="n">
+      <c r="CH31" s="1" t="n">
         <v>1039.95</v>
       </c>
-      <c r="BT31" s="1" t="n">
+      <c r="CI31" s="1" t="n">
         <v>1339.73</v>
       </c>
     </row>
@@ -20157,33 +21577,78 @@
         <v>696.8342</v>
       </c>
       <c r="BK32" s="1" t="n">
+        <v>849.4885</v>
+      </c>
+      <c r="BL32" s="1" t="n">
+        <v>965.8515</v>
+      </c>
+      <c r="BM32" s="1" t="n">
+        <v>1054.7225</v>
+      </c>
+      <c r="BN32" s="1" t="n">
+        <v>1116.3933</v>
+      </c>
+      <c r="BO32" s="1" t="n">
         <v>480.0238</v>
       </c>
-      <c r="BL32" s="1" t="n">
+      <c r="BP32" s="1" t="n">
         <v>604.9867</v>
       </c>
-      <c r="BM32" s="1" t="n">
+      <c r="BQ32" s="1" t="n">
         <v>739.7646999999999</v>
       </c>
-      <c r="BN32" s="1" t="n">
+      <c r="BR32" s="1" t="n">
         <v>923.1895</v>
       </c>
-      <c r="BO32" s="1" t="n">
+      <c r="BS32" s="1" t="n">
         <v>1055.7345</v>
       </c>
-      <c r="BP32" s="1" t="n">
+      <c r="BT32" s="1" t="n">
         <v>1172.4698</v>
       </c>
-      <c r="BQ32" s="1" t="n">
+      <c r="BU32" s="1" t="n">
         <v>1257.8484</v>
       </c>
-      <c r="BR32" s="1" t="n">
+      <c r="BV32" s="1" t="n">
+        <v>31.5394</v>
+      </c>
+      <c r="BW32" s="1" t="n">
+        <v>105.545</v>
+      </c>
+      <c r="BX32" s="1" t="n">
+        <v>201.7576</v>
+      </c>
+      <c r="BY32" s="1" t="n">
+        <v>333.7467</v>
+      </c>
+      <c r="BZ32" s="1" t="n">
+        <v>527.606</v>
+      </c>
+      <c r="CA32" s="1" t="n">
+        <v>666.2533</v>
+      </c>
+      <c r="CB32" s="1" t="n">
+        <v>813.4085</v>
+      </c>
+      <c r="CC32" s="1" t="n">
+        <v>986.2467</v>
+      </c>
+      <c r="CD32" s="1" t="n">
+        <v>1129.5058</v>
+      </c>
+      <c r="CE32" s="1" t="n">
+        <v>1262.2143</v>
+      </c>
+      <c r="CF32" s="1" t="n">
+        <v>1355.6405</v>
+      </c>
+      <c r="CG32" s="1" t="n">
         <v>187.64</v>
       </c>
-      <c r="BS32" s="1" t="n">
+      <c r="CH32" s="1" t="n">
         <v>264.42</v>
       </c>
-      <c r="BT32" s="1" t="n">
+      <c r="CI32" s="1" t="n">
         <v>409.39</v>
       </c>
     </row>
@@ -20371,33 +21836,78 @@
         <v>262.1819</v>
       </c>
       <c r="BK33" s="1" t="n">
+        <v>272.1828</v>
+      </c>
+      <c r="BL33" s="1" t="n">
+        <v>310.6635</v>
+      </c>
+      <c r="BM33" s="1" t="n">
+        <v>344.3326</v>
+      </c>
+      <c r="BN33" s="1" t="n">
+        <v>351.8188</v>
+      </c>
+      <c r="BO33" s="1" t="n">
         <v>159.4126</v>
       </c>
-      <c r="BL33" s="1" t="n">
+      <c r="BP33" s="1" t="n">
         <v>211.8021</v>
       </c>
-      <c r="BM33" s="1" t="n">
+      <c r="BQ33" s="1" t="n">
         <v>250.2274</v>
       </c>
-      <c r="BN33" s="1" t="n">
+      <c r="BR33" s="1" t="n">
         <v>288.9207</v>
       </c>
-      <c r="BO33" s="1" t="n">
+      <c r="BS33" s="1" t="n">
         <v>340.2464</v>
       </c>
-      <c r="BP33" s="1" t="n">
+      <c r="BT33" s="1" t="n">
         <v>394.8496</v>
       </c>
-      <c r="BQ33" s="1" t="n">
+      <c r="BU33" s="1" t="n">
         <v>406.2924</v>
       </c>
-      <c r="BR33" s="1" t="n">
+      <c r="BV33" s="1" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="BW33" s="1" t="n">
+        <v>16.5754</v>
+      </c>
+      <c r="BX33" s="1" t="n">
+        <v>50.4587</v>
+      </c>
+      <c r="BY33" s="1" t="n">
+        <v>95.3723</v>
+      </c>
+      <c r="BZ33" s="1" t="n">
+        <v>171.9173</v>
+      </c>
+      <c r="CA33" s="1" t="n">
+        <v>230.1523</v>
+      </c>
+      <c r="CB33" s="1" t="n">
+        <v>280.178</v>
+      </c>
+      <c r="CC33" s="1" t="n">
+        <v>327.8389</v>
+      </c>
+      <c r="CD33" s="1" t="n">
+        <v>376.6966</v>
+      </c>
+      <c r="CE33" s="1" t="n">
+        <v>409.4499</v>
+      </c>
+      <c r="CF33" s="1" t="n">
+        <v>421.346</v>
+      </c>
+      <c r="CG33" s="1" t="n">
         <v>14.72</v>
       </c>
-      <c r="BS33" s="1" t="n">
+      <c r="CH33" s="1" t="n">
         <v>24.98</v>
       </c>
-      <c r="BT33" s="1" t="n">
+      <c r="CI33" s="1" t="n">
         <v>36.16</v>
       </c>
     </row>
@@ -20591,33 +22101,78 @@
         <v>291.2991</v>
       </c>
       <c r="BK34" s="1" t="n">
+        <v>342.3908</v>
+      </c>
+      <c r="BL34" s="1" t="n">
+        <v>387.0303</v>
+      </c>
+      <c r="BM34" s="1" t="n">
+        <v>430.1798</v>
+      </c>
+      <c r="BN34" s="1" t="n">
+        <v>449.5685</v>
+      </c>
+      <c r="BO34" s="1" t="n">
         <v>157.1482</v>
       </c>
-      <c r="BL34" s="1" t="n">
+      <c r="BP34" s="1" t="n">
         <v>204.7193</v>
       </c>
-      <c r="BM34" s="1" t="n">
+      <c r="BQ34" s="1" t="n">
         <v>248.8423</v>
       </c>
-      <c r="BN34" s="1" t="n">
+      <c r="BR34" s="1" t="n">
         <v>306.6965</v>
       </c>
-      <c r="BO34" s="1" t="n">
+      <c r="BS34" s="1" t="n">
         <v>345.3722</v>
       </c>
-      <c r="BP34" s="1" t="n">
+      <c r="BT34" s="1" t="n">
         <v>380.1601</v>
       </c>
-      <c r="BQ34" s="1" t="n">
+      <c r="BU34" s="1" t="n">
         <v>403.0911</v>
       </c>
-      <c r="BR34" s="1" t="n">
+      <c r="BV34" s="1" t="n">
+        <v>5.3605</v>
+      </c>
+      <c r="BW34" s="1" t="n">
+        <v>34.2893</v>
+      </c>
+      <c r="BX34" s="1" t="n">
+        <v>73.2655</v>
+      </c>
+      <c r="BY34" s="1" t="n">
+        <v>115.4331</v>
+      </c>
+      <c r="BZ34" s="1" t="n">
+        <v>179.8966</v>
+      </c>
+      <c r="CA34" s="1" t="n">
+        <v>222.4491</v>
+      </c>
+      <c r="CB34" s="1" t="n">
+        <v>267.9659</v>
+      </c>
+      <c r="CC34" s="1" t="n">
+        <v>323.8522</v>
+      </c>
+      <c r="CD34" s="1" t="n">
+        <v>367.8757</v>
+      </c>
+      <c r="CE34" s="1" t="n">
+        <v>407.948</v>
+      </c>
+      <c r="CF34" s="1" t="n">
+        <v>433.2733</v>
+      </c>
+      <c r="CG34" s="1" t="n">
         <v>47.73</v>
       </c>
-      <c r="BS34" s="1" t="n">
+      <c r="CH34" s="1" t="n">
         <v>66.16</v>
       </c>
-      <c r="BT34" s="1" t="n">
+      <c r="CI34" s="1" t="n">
         <v>102.39</v>
       </c>
     </row>
@@ -20811,33 +22366,78 @@
         <v>520.772</v>
       </c>
       <c r="BK35" s="1" t="n">
+        <v>650.0051</v>
+      </c>
+      <c r="BL35" s="1" t="n">
+        <v>851.4624</v>
+      </c>
+      <c r="BM35" s="1" t="n">
+        <v>983.7383</v>
+      </c>
+      <c r="BN35" s="1" t="n">
+        <v>1033.4407</v>
+      </c>
+      <c r="BO35" s="1" t="n">
         <v>253.5859</v>
       </c>
-      <c r="BL35" s="1" t="n">
+      <c r="BP35" s="1" t="n">
         <v>400.7917</v>
       </c>
-      <c r="BM35" s="1" t="n">
+      <c r="BQ35" s="1" t="n">
         <v>539.0845</v>
       </c>
-      <c r="BN35" s="1" t="n">
+      <c r="BR35" s="1" t="n">
         <v>702.0586</v>
       </c>
-      <c r="BO35" s="1" t="n">
+      <c r="BS35" s="1" t="n">
         <v>896.0857999999999</v>
       </c>
-      <c r="BP35" s="1" t="n">
+      <c r="BT35" s="1" t="n">
         <v>1027.7953</v>
       </c>
-      <c r="BQ35" s="1" t="n">
+      <c r="BU35" s="1" t="n">
         <v>1074.0436</v>
       </c>
-      <c r="BR35" s="1" t="n">
+      <c r="BV35" s="1" t="n">
+        <v>8.239699999999999</v>
+      </c>
+      <c r="BW35" s="1" t="n">
+        <v>33.8043</v>
+      </c>
+      <c r="BX35" s="1" t="n">
+        <v>86.4828</v>
+      </c>
+      <c r="BY35" s="1" t="n">
+        <v>175.9222</v>
+      </c>
+      <c r="BZ35" s="1" t="n">
+        <v>319.6292</v>
+      </c>
+      <c r="CA35" s="1" t="n">
+        <v>504.0564</v>
+      </c>
+      <c r="CB35" s="1" t="n">
+        <v>616.9882</v>
+      </c>
+      <c r="CC35" s="1" t="n">
+        <v>843.4751</v>
+      </c>
+      <c r="CD35" s="1" t="n">
+        <v>1065.5254</v>
+      </c>
+      <c r="CE35" s="1" t="n">
+        <v>1214.2129</v>
+      </c>
+      <c r="CF35" s="1" t="n">
+        <v>1260.8878</v>
+      </c>
+      <c r="CG35" s="1" t="n">
         <v>126.94</v>
       </c>
-      <c r="BS35" s="1" t="n">
+      <c r="CH35" s="1" t="n">
         <v>225.96</v>
       </c>
-      <c r="BT35" s="1" t="n">
+      <c r="CI35" s="1" t="n">
         <v>356.47</v>
       </c>
     </row>
@@ -35258,7 +36858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CO4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -35609,65 +37209,130 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>2020-02</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2020-03</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>2020-04</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>2020-05</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>2020-06</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>2020-07</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>2020-08</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>2020-09</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>2020-10</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>2020-11</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>2020-12</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -35691,7 +37356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK4"/>
+  <dimension ref="A1:DG4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -36082,70 +37747,180 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
           <t>2020-02</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>2020-03</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>2020-04</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>2020-05</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>2020-06</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>2020-07</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>2020-08</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>2020-09</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>2020-10</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>2020-11</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>2020-12</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="DF3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="DG3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -36169,7 +37944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX4"/>
+  <dimension ref="A1:DT4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -36625,70 +38400,180 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
           <t>2020-02</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>2020-03</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CX3" t="inlineStr">
         <is>
           <t>2020-04</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CY3" t="inlineStr">
         <is>
           <t>2020-05</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CZ3" t="inlineStr">
         <is>
           <t>2020-06</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="DA3" t="inlineStr">
         <is>
           <t>2020-07</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="DB3" t="inlineStr">
         <is>
           <t>2020-08</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="DC3" t="inlineStr">
         <is>
           <t>2020-09</t>
         </is>
       </c>
-      <c r="CS3" t="inlineStr">
+      <c r="DD3" t="inlineStr">
         <is>
           <t>2020-10</t>
         </is>
       </c>
-      <c r="CT3" t="inlineStr">
+      <c r="DE3" t="inlineStr">
         <is>
           <t>2020-11</t>
         </is>
       </c>
-      <c r="CU3" t="inlineStr">
+      <c r="DF3" t="inlineStr">
         <is>
           <t>2020-12</t>
         </is>
       </c>
-      <c r="CV3" t="inlineStr">
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="CW3" t="inlineStr">
+      <c r="DS3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="CX3" t="inlineStr">
+      <c r="DT3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -36962,45 +38847,111 @@
         <v>120263.5146</v>
       </c>
       <c r="CK4" s="1" t="n">
+        <v>12089.8397</v>
+      </c>
+      <c r="CL4" s="1" t="n">
+        <v>23802.9199</v>
+      </c>
+      <c r="CM4" s="1" t="n">
+        <v>34217.45</v>
+      </c>
+      <c r="CN4" s="1" t="n">
+        <v>46074.8881</v>
+      </c>
+      <c r="CO4" s="1" t="n">
+        <v>61609.3028</v>
+      </c>
+      <c r="CP4" s="1" t="n">
+        <v>72843.118</v>
+      </c>
+      <c r="CQ4" s="1" t="n">
+        <v>84589.05740000001</v>
+      </c>
+      <c r="CR4" s="1" t="n">
+        <v>98007.6669</v>
+      </c>
+      <c r="CS4" s="1" t="n">
+        <v>109603.4475</v>
+      </c>
+      <c r="CT4" s="1" t="n">
+        <v>121265.0472</v>
+      </c>
+      <c r="CU4" s="1" t="n">
+        <v>132194.2649</v>
+      </c>
+      <c r="CV4" s="1" t="n">
         <v>10115.4174</v>
       </c>
-      <c r="CL4" s="1" t="n">
+      <c r="CW4" s="1" t="n">
         <v>21962.6085</v>
       </c>
-      <c r="CM4" s="1" t="n">
+      <c r="CX4" s="1" t="n">
         <v>33102.8406</v>
       </c>
-      <c r="CN4" s="1" t="n">
+      <c r="CY4" s="1" t="n">
         <v>45919.5905</v>
       </c>
-      <c r="CO4" s="1" t="n">
+      <c r="CZ4" s="1" t="n">
         <v>62780.2095</v>
       </c>
-      <c r="CP4" s="1" t="n">
+      <c r="DA4" s="1" t="n">
         <v>75324.6079</v>
       </c>
-      <c r="CQ4" s="1" t="n">
+      <c r="DB4" s="1" t="n">
         <v>88454.14449999999</v>
       </c>
-      <c r="CR4" s="1" t="n">
+      <c r="DC4" s="1" t="n">
         <v>103484.1959</v>
       </c>
-      <c r="CS4" s="1" t="n">
+      <c r="DD4" s="1" t="n">
         <v>116555.7566</v>
       </c>
-      <c r="CT4" s="1" t="n">
+      <c r="DE4" s="1" t="n">
         <v>129492.364</v>
       </c>
-      <c r="CU4" s="1" t="n">
+      <c r="DF4" s="1" t="n">
         <v>141442.9455</v>
       </c>
-      <c r="CV4" s="1" t="n">
+      <c r="DG4" s="1" t="n">
+        <v>13985.8657</v>
+      </c>
+      <c r="DH4" s="1" t="n">
+        <v>27575.8249</v>
+      </c>
+      <c r="DI4" s="1" t="n">
+        <v>40239.7557</v>
+      </c>
+      <c r="DJ4" s="1" t="n">
+        <v>54318.0785</v>
+      </c>
+      <c r="DK4" s="1" t="n">
+        <v>72179.07120000001</v>
+      </c>
+      <c r="DL4" s="1" t="n">
+        <v>84895.4072</v>
+      </c>
+      <c r="DM4" s="1" t="n">
+        <v>98059.72629999999</v>
+      </c>
+      <c r="DN4" s="1" t="n">
+        <v>112568.069</v>
+      </c>
+      <c r="DO4" s="1" t="n">
+        <v>124933.6196</v>
+      </c>
+      <c r="DP4" s="1" t="n">
+        <v>137313.9585</v>
+      </c>
+      <c r="DQ4" s="1" t="n">
+        <v>147602.0767</v>
+      </c>
+      <c r="DR4" s="1" t="n">
         <v>23969.4</v>
       </c>
-      <c r="CW4" s="1" t="n">
+      <c r="DS4" s="1" t="n">
         <v>30355.68</v>
       </c>
-      <c r="CX4" s="1" t="n">
+      <c r="DT4" s="1" t="n">
         <v>38073.7</v>
       </c>
     </row>
@@ -38480,7 +40431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM4"/>
+  <dimension ref="A1:CT4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -38936,15 +40887,50 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -39218,12 +41204,33 @@
         <v>33102.8406</v>
       </c>
       <c r="CK4" s="1" t="n">
+        <v>75324.6079</v>
+      </c>
+      <c r="CL4" s="1" t="n">
+        <v>88454.14449999999</v>
+      </c>
+      <c r="CM4" s="1" t="n">
+        <v>103484.1959</v>
+      </c>
+      <c r="CN4" s="1" t="n">
+        <v>116555.7566</v>
+      </c>
+      <c r="CO4" s="1" t="n">
+        <v>129492.364</v>
+      </c>
+      <c r="CP4" s="1" t="n">
+        <v>141442.9455</v>
+      </c>
+      <c r="CQ4" s="1" t="n">
+        <v>13985.8657</v>
+      </c>
+      <c r="CR4" s="1" t="n">
         <v>23969.4</v>
       </c>
-      <c r="CL4" s="1" t="n">
+      <c r="CS4" s="1" t="n">
         <v>30355.68</v>
       </c>
-      <c r="CM4" s="1" t="n">
+      <c r="CT4" s="1" t="n">
         <v>38073.7</v>
       </c>
     </row>
@@ -39238,7 +41245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DF4"/>
+  <dimension ref="A1:DL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -39789,15 +41796,45 @@
       </c>
       <c r="DD3" t="inlineStr">
         <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="DE3" t="inlineStr">
+      <c r="DK3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="DF3" t="inlineStr">
+      <c r="DL3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -39821,7 +41858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG4"/>
+  <dimension ref="A1:DC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -40157,105 +42194,215 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
           <t>2019-02</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>2019-03</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>2019-04</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>2019-05</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>2019-06</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>2019-07</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>2019-08</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>2019-09</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>2019-10</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>2019-11</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>2019-12</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
         <is>
           <t>2021-02</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>2021-03</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>2021-04</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>2021-05</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CX3" t="inlineStr">
         <is>
           <t>2021-06</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CY3" t="inlineStr">
         <is>
           <t>2021-07</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CZ3" t="inlineStr">
         <is>
           <t>2021-08</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="DA3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="DB3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="DC3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -40457,66 +42604,132 @@
         <v>34734.1</v>
       </c>
       <c r="BM4" s="1" t="n">
+        <v>61081.8</v>
+      </c>
+      <c r="BN4" s="1" t="n">
+        <v>29193.6</v>
+      </c>
+      <c r="BO4" s="1" t="n">
+        <v>28541.9</v>
+      </c>
+      <c r="BP4" s="1" t="n">
+        <v>30359.1</v>
+      </c>
+      <c r="BQ4" s="1" t="n">
+        <v>30841.6</v>
+      </c>
+      <c r="BR4" s="1" t="n">
+        <v>30733.7</v>
+      </c>
+      <c r="BS4" s="1" t="n">
+        <v>31542.3</v>
+      </c>
+      <c r="BT4" s="1" t="n">
+        <v>32005.4</v>
+      </c>
+      <c r="BU4" s="1" t="n">
+        <v>35534.4</v>
+      </c>
+      <c r="BV4" s="1" t="n">
+        <v>35259.7</v>
+      </c>
+      <c r="BW4" s="1" t="n">
+        <v>35893.4983358266</v>
+      </c>
+      <c r="BX4" s="1" t="n">
         <v>66064</v>
       </c>
-      <c r="BN4" s="1" t="n">
+      <c r="BY4" s="1" t="n">
         <v>31725.7</v>
       </c>
-      <c r="BO4" s="1" t="n">
+      <c r="BZ4" s="1" t="n">
         <v>30586.1</v>
       </c>
-      <c r="BP4" s="1" t="n">
+      <c r="CA4" s="1" t="n">
         <v>32955.7</v>
       </c>
-      <c r="BQ4" s="1" t="n">
+      <c r="CB4" s="1" t="n">
         <v>33878.1</v>
       </c>
-      <c r="BR4" s="1" t="n">
+      <c r="CC4" s="1" t="n">
         <v>33073.3</v>
       </c>
-      <c r="BS4" s="1" t="n">
+      <c r="CD4" s="1" t="n">
         <v>33896.3</v>
       </c>
-      <c r="BT4" s="1" t="n">
+      <c r="CE4" s="1" t="n">
         <v>34494.9</v>
       </c>
-      <c r="BU4" s="1" t="n">
+      <c r="CF4" s="1" t="n">
         <v>38104.3</v>
       </c>
-      <c r="BV4" s="1" t="n">
+      <c r="CG4" s="1" t="n">
         <v>38093.8</v>
       </c>
-      <c r="BW4" s="1" t="n">
+      <c r="CH4" s="1" t="n">
         <v>38776.7</v>
       </c>
-      <c r="BX4" s="1" t="n">
+      <c r="CI4" s="1" t="n">
+        <v>52129.8</v>
+      </c>
+      <c r="CJ4" s="1" t="n">
+        <v>26449.9</v>
+      </c>
+      <c r="CK4" s="1" t="n">
+        <v>28177.8</v>
+      </c>
+      <c r="CL4" s="1" t="n">
+        <v>31972.8</v>
+      </c>
+      <c r="CM4" s="1" t="n">
+        <v>33525.9</v>
+      </c>
+      <c r="CN4" s="1" t="n">
+        <v>32202.5</v>
+      </c>
+      <c r="CO4" s="1" t="n">
+        <v>33570.6</v>
+      </c>
+      <c r="CP4" s="1" t="n">
+        <v>35294.7</v>
+      </c>
+      <c r="CQ4" s="1" t="n">
+        <v>38576.5</v>
+      </c>
+      <c r="CR4" s="1" t="n">
+        <v>39514.2</v>
+      </c>
+      <c r="CS4" s="1" t="n">
+        <v>40566</v>
+      </c>
+      <c r="CT4" s="1" t="n">
         <v>69736.8</v>
       </c>
-      <c r="BY4" s="1" t="n">
+      <c r="CU4" s="1" t="n">
         <v>35484.1</v>
       </c>
-      <c r="BZ4" s="1" t="n">
+      <c r="CV4" s="1" t="n">
         <v>33152.6</v>
       </c>
-      <c r="CA4" s="1" t="n">
+      <c r="CW4" s="1" t="n">
         <v>35945.1</v>
       </c>
-      <c r="CB4" s="1" t="n">
+      <c r="CX4" s="1" t="n">
         <v>37585.8</v>
       </c>
-      <c r="CC4" s="1" t="n">
+      <c r="CY4" s="1" t="n">
         <v>34925.1</v>
       </c>
-      <c r="CD4" s="1" t="n">
+      <c r="CZ4" s="1" t="n">
         <v>34394.9</v>
       </c>
-      <c r="CE4" s="1" t="n">
+      <c r="DA4" s="1" t="n">
         <v>37246.5</v>
       </c>
-      <c r="CF4" s="1" t="n">
+      <c r="DB4" s="1" t="n">
         <v>41090</v>
       </c>
-      <c r="CG4" s="1" t="n">
+      <c r="DC4" s="1" t="n">
         <v>42690.7</v>
       </c>
     </row>
@@ -40531,7 +42744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AK4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -40612,75 +42825,120 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>2011-04</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2011-05</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2011-06</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2011-07</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2011-08</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2011-09</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2011-11</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2011-12</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>2012-01</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>2012-02</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>2012-03</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>2012-04</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>2012-05</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2012-06</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>2012-07</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2012-08</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2012-09</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>2012-10</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>2012-11</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>2012-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -40729,48 +42987,75 @@
         <v>115.61691436</v>
       </c>
       <c r="N4" s="1" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>122.89901327</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>120.67523767</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>119.12941106</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>118.34977882</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>117.64173953</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>116.40800023</v>
+      </c>
+      <c r="W4" s="1" t="n">
         <v>102.30910475</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="X4" s="1" t="n">
         <v>97.92451483000001</v>
       </c>
-      <c r="P4" s="1" t="n">
+      <c r="Y4" s="1" t="n">
         <v>96.50952325999999</v>
       </c>
-      <c r="Q4" s="1" t="n">
+      <c r="Z4" s="1" t="n">
         <v>94.88338365</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="AA4" s="1" t="n">
         <v>94.47879593</v>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="AB4" s="1" t="n">
         <v>95.38789233999999</v>
       </c>
-      <c r="T4" s="1" t="n">
+      <c r="AC4" s="1" t="n">
         <v>96.96033654</v>
       </c>
-      <c r="U4" s="1" t="n">
+      <c r="AD4" s="1" t="n">
         <v>98.25743283</v>
       </c>
-      <c r="V4" s="1" t="n">
+      <c r="AE4" s="1" t="n">
         <v>99.10720877999999</v>
       </c>
-      <c r="W4" s="1" t="n">
+      <c r="AF4" s="1" t="n">
         <v>99.54025846</v>
       </c>
-      <c r="X4" s="1" t="n">
+      <c r="AG4" s="1" t="n">
         <v>99.24083367</v>
       </c>
-      <c r="Y4" s="1" t="n">
+      <c r="AH4" s="1" t="n">
         <v>98.83373603</v>
       </c>
-      <c r="Z4" s="1" t="n">
+      <c r="AI4" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="AA4" s="1" t="n">
+      <c r="AJ4" s="1" t="n">
         <v>101.9</v>
       </c>
-      <c r="AB4" s="1" t="n">
+      <c r="AK4" s="1" t="n">
         <v>101.5</v>
       </c>
     </row>
